--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E09DDE-F2DB-41DC-ADEF-F8B0C2AFD7F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003CD53C-42D2-4D79-BFA7-D5CD4DB3ADA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,8 @@
 1.普通
 2.拉火车
 3.黄金列车
-4.all board</t>
+4.all board(二选一触发局)
+5.免费</t>
         </r>
       </text>
     </comment>
@@ -128,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
   <si>
     <t>id</t>
   </si>
@@ -191,9 +192,6 @@
   </si>
   <si>
     <t>enterLimitMax</t>
-  </si>
-  <si>
-    <t>1,99608;2,392</t>
   </si>
   <si>
     <t>放水池+3</t>
@@ -225,11 +223,11 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>1,99608;2,392</t>
+    <t>1,0&amp;100000-1;2,0&amp;100000-1;3,0&amp;100000-1;4,0&amp;100000-1;5,0&amp;100000-1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>1,0&amp;1-71631811^1&amp;10-2601243^10&amp;20-5109541^20&amp;30-1922382^30&amp;40-2781374^40&amp;50-820206^50&amp;60-919625^60&amp;70-1721059^70&amp;80-515213^80&amp;90-413243^90&amp;100-390874^100&amp;120-924203^120&amp;140-996544^140&amp;160-520380^160&amp;180-437443^180&amp;200-384006^200&amp;300-1893799^300&amp;500-2169163^500&amp;800-1661015^800&amp;1000-604297^1000&amp;1500-784428^1500&amp;2000-398555^2000&amp;3000-317392^3000&amp;4000-96803^4000&amp;5000-35320^5000&amp;7000-27864^7000&amp;10000-9092^10000&amp;15000-2551^15000&amp;20000-458^20000&amp;30000-131^30000&amp;40000-1^40000&amp;50000-1^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0;2,0&amp;1-66490^1&amp;10-83112^10&amp;20-132979^20&amp;30-49868^30&amp;40-99735^40&amp;50-33245^50&amp;60-116357^60&amp;70-116357^70&amp;80-116357^80&amp;90-149602^90&amp;100-99735^100&amp;120-132979^120&amp;140-132979^140&amp;160-199469^160&amp;180-265958^180&amp;200-166224^200&amp;300-897607^300&amp;500-1628990^500&amp;800-2642953^800&amp;1000-2094415^1000&amp;1500-5269282^1500&amp;2000-4920213^2000&amp;3000-10189495^3000&amp;4000-9574469^4000&amp;5000-8161570^5000&amp;7000-14660905^7000&amp;10000-14727394^10000&amp;15000-12616357^15000&amp;20000-5601729^20000&amp;30000-3673538^30000&amp;40000-847740^40000&amp;50000-299203^50000&amp;60000-83112^60000&amp;70000-83112^70000&amp;80000-16623^80000&amp;100000-33245^100000&amp;200000-16623^200000&amp;500000-1^500000&amp;1000000-0^1000000&amp;1000000000-0</t>
+    <t>1,0;2,0;3,0;4,111</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -656,7 +654,7 @@
         <v>12</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>10</v>
@@ -689,7 +687,7 @@
         <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>18</v>
@@ -735,7 +733,7 @@
         <v>31</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -747,7 +745,7 @@
         <v>999999</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
@@ -767,10 +765,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -782,7 +780,7 @@
         <v>2000</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
@@ -802,10 +800,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -817,7 +815,7 @@
         <v>1000</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
@@ -837,10 +835,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -852,7 +850,7 @@
         <v>500</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
@@ -872,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -887,7 +885,7 @@
         <v>-500</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
@@ -907,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
@@ -922,7 +920,7 @@
         <v>-1000</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
@@ -942,10 +940,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -957,7 +955,7 @@
         <v>-2000</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003CD53C-42D2-4D79-BFA7-D5CD4DB3ADA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAABF347-82B2-4F5E-BA61-EFDD0913C45B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="33">
   <si>
     <t>id</t>
   </si>
@@ -228,6 +228,10 @@
   </si>
   <si>
     <t>1,0;2,0;3,0;4,111</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,0;2,0;3,0;4,112</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -730,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>30</v>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAABF347-82B2-4F5E-BA61-EFDD0913C45B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1DCEE4A-8744-40B3-845D-340F75565B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1DCEE4A-8744-40B3-845D-340F75565B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B197B78-D7FD-4BF7-AC16-81580EDF1513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
   <si>
     <t>id</t>
   </si>
@@ -227,11 +227,7 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>1,0;2,0;3,0;4,111</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,0;2,0;3,0;4,112</t>
+    <t>1,200;2,40;3,5;4,10</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -734,7 +730,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>30</v>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B197B78-D7FD-4BF7-AC16-81580EDF1513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DF335B-7C62-4D46-BAEE-F9916CF7189B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,9 @@
 2.拉火车
 3.黄金列车
 4.all board(二选一触发局)
-5.免费</t>
+5.免费
+6.重转之拉火车
+7.重转之黄金列车</t>
         </r>
       </text>
     </comment>
@@ -223,11 +225,11 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>1,0&amp;100000-1;2,0&amp;100000-1;3,0&amp;100000-1;4,0&amp;100000-1;5,0&amp;100000-1</t>
+    <t>1,200;2,40;3,5;4,10</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>1,200;2,40;3,5;4,10</t>
+    <t>1,0&amp;100000-1;2,0&amp;100000-1;3,0&amp;100000-1;4,0&amp;100000-1;5,0&amp;100000-1;6,0&amp;100000-1;7,0&amp;100000-1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -730,10 +732,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -765,10 +767,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -800,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -835,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -870,10 +872,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -905,10 +907,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
@@ -940,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DF335B-7C62-4D46-BAEE-F9916CF7189B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE64B84-4608-4D45-B6BC-D57A3BBDA367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -225,11 +225,11 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>1,200;2,40;3,5;4,10</t>
+    <t>1,0&amp;100000-1;2,0&amp;100000-1;3,0&amp;100000-1;4,0&amp;100000-1;5,0&amp;100000-1;6,0&amp;100000-1;7,0&amp;100000-1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>1,0&amp;100000-1;2,0&amp;100000-1;3,0&amp;100000-1;4,0&amp;100000-1;5,0&amp;100000-1;6,0&amp;100000-1;7,0&amp;100000-1</t>
+    <t>1,200;2,40;3,500;4,10</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -732,10 +732,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -767,10 +767,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -872,10 +872,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -907,10 +907,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE64B84-4608-4D45-B6BC-D57A3BBDA367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7314EC46-0627-4D66-92DE-5F3DAA3B85BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -229,7 +229,7 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>1,200;2,40;3,500;4,10</t>
+    <t>1,200;2,10;3,5;4,10</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7314EC46-0627-4D66-92DE-5F3DAA3B85BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FFE8AB-5067-4613-A9F2-038F3987099F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>线注倍数只有1，填0即可；
@@ -46,7 +45,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>格式：类型1,权重1；类型2，权重2；…
@@ -66,7 +64,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">[{类型1,[{[倍数区间下限,倍数区间上限],权重值},{[倍数区间下限,倍数区间上限],权重值}]}]
@@ -83,7 +80,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>[区间上限，区间上限],左开右闭，值/10000，公式：水池超出标准线：（当前RTP-标准RTP）/标准RTP，进入对应水池
@@ -97,7 +93,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>[区间上限，区间上限],左开右闭，值/10000，公式：水池超出标准线：（当前RTP-标准RTP）/标准RTP，进入对应水池
@@ -111,7 +106,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">一个水池对应一个滚轴模式ID，对应一个RTP值
@@ -172,6 +166,9 @@
     <t>Map&lt;int{,}int&gt;{;}</t>
   </si>
   <si>
+    <t>Map&lt;int{,}list&lt;string&gt;{^}&gt;{;}</t>
+  </si>
+  <si>
     <t>gameType</t>
   </si>
   <si>
@@ -187,6 +184,9 @@
     <t>typeProp</t>
   </si>
   <si>
+    <t>sectionProp</t>
+  </si>
+  <si>
     <t>targetGameType</t>
   </si>
   <si>
@@ -196,6 +196,9 @@
     <t>enterLimitMax</t>
   </si>
   <si>
+    <t>1,200;2,10;3,5;4,10</t>
+  </si>
+  <si>
     <t>放水池+3</t>
   </si>
   <si>
@@ -217,27 +220,15 @@
     <t>吸水池-3</t>
   </si>
   <si>
-    <t>sectionProp</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map&lt;int{,}list&lt;string&gt;{^}&gt;{;}</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,0&amp;100000-1;2,0&amp;100000-1;3,0&amp;100000-1;4,0&amp;100000-1;5,0&amp;100000-1;6,0&amp;100000-1;7,0&amp;100000-1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,200;2,10;3,5;4,10</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>1,0&amp;1000000-1;2,0&amp;1000000-1;3,0&amp;1000000-1;4,0&amp;1000000-1;5,0&amp;1000000-1;6,0&amp;1000000-1;7,0&amp;1000000-1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,29 +240,38 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -295,12 +295,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -319,13 +325,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -586,7 +585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.25" customWidth="1"/>
@@ -601,7 +600,7 @@
     <col min="11" max="11" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -617,7 +616,7 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -636,7 +635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -656,7 +655,7 @@
         <v>12</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>10</v>
@@ -669,40 +668,40 @@
       </c>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -715,7 +714,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -732,10 +731,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -747,10 +746,13 @@
         <v>999999</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="L5">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -767,10 +769,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -782,10 +784,13 @@
         <v>2000</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="L6">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -802,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -817,10 +822,13 @@
         <v>1000</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="L7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -837,10 +845,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -852,10 +860,13 @@
         <v>500</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+      <c r="L8">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -872,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -887,10 +898,13 @@
         <v>-500</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="L9">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -907,10 +921,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
@@ -922,10 +936,13 @@
         <v>-1000</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+      <c r="L10">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -942,10 +959,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -957,11 +974,14 @@
         <v>-2000</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="L11">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -1,32 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FFE8AB-5067-4613-A9F2-038F3987099F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="24045" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author>chuge</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -39,7 +46,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -58,7 +65,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="G1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -68,13 +75,17 @@
           </rPr>
           <t xml:space="preserve">[{类型1,[{[倍数区间下限,倍数区间上限],权重值},{[倍数区间下限,倍数区间上限],权重值}]}]
 1.普通
-2.免费
-3.重转
+2.拉火车
+3.黄金列车
+4.all board(二选一触发局)
+5.免费
+6.重转之拉火车
+7.重转之黄金列车
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -87,7 +98,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -100,7 +111,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -125,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
   <si>
     <t>id</t>
   </si>
@@ -196,21 +207,42 @@
     <t>enterLimitMax</t>
   </si>
   <si>
-    <t>1,200;2,10;3,5;4,10</t>
+    <t>1,9657;2,63;3,137;4,47</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-69376672^1&amp;10-0^10&amp;20-2744554^20&amp;30-3992455^30&amp;40-2799486^40&amp;50-3208889^50&amp;60-1809664^60&amp;70-2310276^70&amp;80-1224063^80&amp;90-1442757^90&amp;100-1050974^100&amp;120-1650049^120&amp;140-1462449^140&amp;160-924525^160&amp;180-604258^180&amp;200-531706^200&amp;300-1889472^300&amp;500-1374350^500&amp;800-744181^800&amp;1000-317158^1000&amp;1500-308866^1500&amp;2000-109866^2000&amp;3000-82918^3000&amp;4000-29021^4000&amp;5000-7256^5000&amp;7000-4146^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;2,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-1740507^3000&amp;4000-5696203^4000&amp;5000-14240507^5000&amp;7000-30696203^7000&amp;10000-21993671^10000&amp;15000-17246836^15000&amp;20000-5379747^20000&amp;30000-3006330^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;3,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-2407003^3000&amp;4000-37636762^4000&amp;5000-48504742^5000&amp;7000-8971554^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-72940^20000&amp;30000-1531729^30000&amp;40000-875274^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;4,0&amp;1-87211741^1&amp;10-0^10&amp;20-2096437^20&amp;30-2935011^30&amp;40-838575^40&amp;50-2096437^50&amp;60-209644^60&amp;70-838575^70&amp;80-419288^80&amp;90-209644^90&amp;100-419288^100&amp;120-628931^120&amp;140-0^140&amp;160-419288^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-209644^500&amp;800-209644^800&amp;1000-0^1000&amp;1500-209644^1500&amp;2000-209644^2000&amp;3000-0^3000&amp;4000-419288^4000&amp;5000-419288^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;5,0&amp;1-43186583^1&amp;10-0^10&amp;20-288260^20&amp;30-943397^30&amp;40-288260^40&amp;50-1519917^50&amp;60-655137^60&amp;70-1415095^70&amp;80-104822^80&amp;90-1912998^90&amp;100-131028^100&amp;120-1808177^120&amp;140-1624738^140&amp;160-943397^160&amp;180-1048219^180&amp;200-628931^200&amp;300-7206499^300&amp;500-9119497^500&amp;800-6708596^800&amp;1000-2987422^1000&amp;1500-5083858^1500&amp;2000-3432915^2000&amp;3000-3616353^3000&amp;4000-2122642^4000&amp;5000-1310273^5000&amp;7000-1022013^7000&amp;10000-576520^10000&amp;15000-235850^15000&amp;20000-52411^20000&amp;30000-26206^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;6,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-4394532^3000&amp;4000-0^4000&amp;5000-1074219^5000&amp;7000-585938^7000&amp;10000-683594^10000&amp;15000-97657^15000&amp;20000-1^20000&amp;30000-1^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;7,0&amp;1-37636762^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-2407003^3000&amp;4000-0^4000&amp;5000-0^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^</t>
   </si>
   <si>
     <t>放水池+3</t>
   </si>
   <si>
+    <t>1,0&amp;1-69376672^1&amp;10-0^10&amp;20-2744554^20&amp;30-3992455^30&amp;40-2799486^40&amp;50-3208889^50&amp;60-1809664^60&amp;70-2310276^70&amp;80-1224063^80&amp;90-1442757^90&amp;100-1050974^100&amp;120-1650049^120&amp;140-1462449^140&amp;160-924525^160&amp;180-604258^180&amp;200-531706^200&amp;300-1889472^300&amp;500-1374350^500&amp;800-744181^800&amp;1000-317158^1000&amp;1500-308866^1500&amp;2000-109866^2000&amp;3000-82918^3000&amp;4000-29021^4000&amp;5000-7256^5000&amp;7000-4146^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;2,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-1740507^3000&amp;4000-5696203^4000&amp;5000-14240507^5000&amp;7000-30696203^7000&amp;10000-21993671^10000&amp;15000-17246836^15000&amp;20000-5379747^20000&amp;30000-3006330^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;3,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-2407003^3000&amp;4000-37636762^4000&amp;5000-48504742^5000&amp;7000-8971554^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-72940^20000&amp;30000-1531729^30000&amp;40000-875274^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;4,0&amp;1-87211741^1&amp;10-0^10&amp;20-2096437^20&amp;30-2935011^30&amp;40-838575^40&amp;50-2096437^50&amp;60-209644^60&amp;70-838575^70&amp;80-419288^80&amp;90-209644^90&amp;100-419288^100&amp;120-628931^120&amp;140-0^140&amp;160-419288^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-209644^500&amp;800-209644^800&amp;1000-0^1000&amp;1500-209644^1500&amp;2000-209644^2000&amp;3000-0^3000&amp;4000-419288^4000&amp;5000-419288^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;5,0&amp;1-43186583^1&amp;10-0^10&amp;20-288260^20&amp;30-943397^30&amp;40-288260^40&amp;50-1519917^50&amp;60-655137^60&amp;70-1415095^70&amp;80-104822^80&amp;90-1912998^90&amp;100-131028^100&amp;120-1808177^120&amp;140-1624738^140&amp;160-943397^160&amp;180-1048219^180&amp;200-628931^200&amp;300-7206499^300&amp;500-9119497^500&amp;800-6708596^800&amp;1000-2987422^1000&amp;1500-5083858^1500&amp;2000-3432915^2000&amp;3000-3616353^3000&amp;4000-2122642^4000&amp;5000-1310273^5000&amp;7000-1022013^7000&amp;10000-576520^10000&amp;15000-235850^15000&amp;20000-52411^20000&amp;30000-26206^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;6,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-4394532^3000&amp;4000-0^4000&amp;5000-1074219^5000&amp;7000-585938^7000&amp;10000-683594^10000&amp;15000-97657^15000&amp;20000-1^20000&amp;30000-1^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;7,0&amp;1-100000000^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-0^3000&amp;4000-0^4000&amp;5000-0^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^</t>
+  </si>
+  <si>
     <t>放水池+2</t>
   </si>
   <si>
+    <t>1,9702;2,49;3,132;4,38</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-71005113^1&amp;10-0^10&amp;20-2571529^20&amp;30-3649613^30&amp;40-2554008^40&amp;50-3031209^50&amp;60-1671752^60&amp;70-2197395^70&amp;80-1164661^80&amp;90-1463556^90&amp;100-1042011^100&amp;120-1604758^120&amp;140-1384194^140&amp;160-872980^160&amp;180-574085^180&amp;200-496785^200&amp;300-1809862^300&amp;500-1284219^500&amp;800-726625^800&amp;1000-310233^1000&amp;1500-289620^1500&amp;2000-146356^2000&amp;3000-111313^3000&amp;4000-24737^4000&amp;5000-12369^5000&amp;7000-1031^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;2,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-2805612^3000&amp;4000-7414830^4000&amp;5000-14228457^5000&amp;7000-29458918^7000&amp;10000-24649299^10000&amp;15000-16032065^15000&amp;20000-4208417^20000&amp;30000-1202405^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;3,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-9214502^1500&amp;2000-28549849^2000&amp;3000-604230^3000&amp;4000-5287010^4000&amp;5000-18277946^5000&amp;7000-16616315^7000&amp;10000-13595167^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;4,0&amp;1-84415585^1&amp;10-0^10&amp;20-3376624^20&amp;30-3896104^30&amp;40-519481^40&amp;50-1558442^50&amp;60-259741^60&amp;70-1298702^70&amp;80-519481^80&amp;90-259741^90&amp;100-259741^100&amp;120-259741^120&amp;140-259741^140&amp;160-519481^160&amp;180-0^180&amp;200-0^200&amp;300-779221^300&amp;500-779221^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-0^3000&amp;4000-0^4000&amp;5000-0^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-1^15000&amp;20000-259741^20000&amp;30000-1^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;5,0&amp;1-43246754^1&amp;10-0^10&amp;20-292208^20&amp;30-1233767^30&amp;40-194806^40&amp;50-1461039^50&amp;60-681819^60&amp;70-1298702^70&amp;80-227273^80&amp;90-1071429^90&amp;100-227273^100&amp;120-1785715^120&amp;140-1883117^140&amp;160-974026^160&amp;180-1103897^180&amp;200-779221^200&amp;300-6915585^300&amp;500-8928572^500&amp;800-7597403^800&amp;1000-3409091^1000&amp;1500-4935065^1500&amp;2000-3246754^2000&amp;3000-3214286^3000&amp;4000-1948052^4000&amp;5000-1331169^5000&amp;7000-1136364^7000&amp;10000-714286^10000&amp;15000-0^15000&amp;20000-1^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;6,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-4394532^3000&amp;4000-0^4000&amp;5000-1074219^5000&amp;7000-585938^7000&amp;10000-683594^10000&amp;15000-97657^15000&amp;20000-1^20000&amp;30000-1^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;7,0&amp;1-100000000^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-0^3000&amp;4000-0^4000&amp;5000-0^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^</t>
+  </si>
+  <si>
     <t>放水池+1</t>
   </si>
   <si>
+    <t>1,9833;2,29;3,96;4,13</t>
+  </si>
+  <si>
     <t>标准池</t>
   </si>
   <si>
+    <t>1,98339;2,278;3,999;4,128</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-77319274^1&amp;10-0^10&amp;20-2380541^20&amp;30-3125922^30&amp;40-1890400^40&amp;50-2325629^50&amp;60-1135867^60&amp;70-1688039^70&amp;80-820631^80&amp;90-1120614^90&amp;100-643692^100&amp;120-1048415^120&amp;140-1078921^140&amp;160-653861^160&amp;180-401672^180&amp;200-392520^200&amp;300-1310772^300&amp;500-1047398^500&amp;800-680300^800&amp;1000-331507^1000&amp;1500-301000^1500&amp;2000-145416^2000&amp;3000-107791^3000&amp;4000-31524^4000&amp;5000-10169^5000&amp;7000-7119^7000&amp;10000-22302159^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;2,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-719425^2000&amp;3000-1438849^3000&amp;4000-7913670^4000&amp;5000-15467626^5000&amp;7000-30935252^7000&amp;10000-22302159^10000&amp;15000-16187051^15000&amp;20000-1^20000&amp;30000-1^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;3,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-46846847^1500&amp;2000-33933934^2000&amp;3000-900901^3000&amp;4000-10110111^4000&amp;5000-8208209^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;4,0&amp;1-90625001^1&amp;10-0^10&amp;20-781251^20&amp;30-1562501^30&amp;40-2343751^40&amp;50-2343751^50&amp;60-781251^60&amp;70-0^70&amp;80-0^80&amp;90-1562501^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-0^3000&amp;4000-0^4000&amp;5000-0^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;5,0&amp;1-90625001^1&amp;10-0^10&amp;20-781251^20&amp;30-1562501^30&amp;40-2343751^40&amp;50-2343751^50&amp;60-781251^60&amp;70-1^70&amp;80-1^80&amp;90-1562501^90&amp;100-1^100&amp;120-1^120&amp;140-1562501^140&amp;160-1367188^160&amp;180-1464844^180&amp;200-781251^200&amp;300-6933594^300&amp;500-8691407^500&amp;800-8203126^800&amp;1000-2734376^1000&amp;1500-5566407^1500&amp;2000-2832032^2000&amp;3000-4394532^3000&amp;4000-1660157^4000&amp;5000-1074219^5000&amp;7000-585938^7000&amp;10000-683594^10000&amp;15000-97657^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;6,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-4394532^3000&amp;4000-0^4000&amp;5000-1074219^5000&amp;7000-585938^7000&amp;10000-683594^10000&amp;15000-97657^15000&amp;20000-1^20000&amp;30000-1^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;7,0&amp;1-100000000^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-0^3000&amp;4000-0^4000&amp;5000-0^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^</t>
+  </si>
+  <si>
     <t>吸水池-1</t>
   </si>
   <si>
@@ -218,17 +250,19 @@
   </si>
   <si>
     <t>吸水池-3</t>
-  </si>
-  <si>
-    <t>1,0&amp;1000000-1;2,0&amp;1000000-1;3,0&amp;1000000-1;4,0&amp;1000000-1;5,0&amp;1000000-1;6,0&amp;1000000-1;7,0&amp;1000000-1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,16 +277,147 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -260,29 +425,202 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -290,38 +628,318 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 73" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -579,14 +1197,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="15.25" customWidth="1"/>
     <col min="3" max="3" width="13.875" customWidth="1"/>
@@ -600,7 +1218,7 @@
     <col min="11" max="11" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" ht="16.5" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -616,7 +1234,7 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -635,7 +1253,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="2" ht="16.5" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -668,7 +1286,7 @@
       </c>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="16.5" hidden="1" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -701,7 +1319,7 @@
       </c>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:12" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="16.5" hidden="1" spans="1:11">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -714,7 +1332,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="5" ht="16.5" spans="1:12">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -733,8 +1351,8 @@
       <c r="F5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>31</v>
+      <c r="G5" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -746,13 +1364,13 @@
         <v>999999</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L5">
         <v>180</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="6" ht="16.5" spans="1:12">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -771,8 +1389,8 @@
       <c r="F6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>31</v>
+      <c r="G6" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -784,13 +1402,13 @@
         <v>2000</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L6">
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="7" ht="16.5" spans="1:12">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -807,10 +1425,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -822,13 +1440,13 @@
         <v>1000</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L7">
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="8" ht="16.5" spans="1:12">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -845,10 +1463,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="4" t="s">
         <v>31</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -860,13 +1478,13 @@
         <v>500</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L8">
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="9" ht="16.5" spans="1:12">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -883,10 +1501,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -898,13 +1516,13 @@
         <v>-500</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="L9">
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="10" ht="16.5" spans="1:12">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -921,10 +1539,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
@@ -936,13 +1554,13 @@
         <v>-1000</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="L10">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="11" ht="16.5" spans="1:12">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -959,10 +1577,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -974,15 +1592,15 @@
         <v>-2000</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L11">
         <v>50</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -1,39 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CE4890-10BF-428E-9C0A-B5BE89E33E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView xWindow="31950" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author>chuge</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -46,7 +39,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -65,7 +58,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1">
+    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -85,7 +78,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -98,7 +91,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -111,7 +104,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -255,14 +248,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,147 +264,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -425,202 +275,22 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -628,318 +298,32 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 73" xfId="49"/>
+    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1197,14 +581,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.25" customWidth="1"/>
     <col min="3" max="3" width="13.875" customWidth="1"/>
@@ -1218,7 +602,7 @@
     <col min="11" max="11" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:11">
+    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1253,7 +637,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:11">
+    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1286,7 +670,7 @@
       </c>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" ht="16.5" hidden="1" spans="1:11">
+    <row r="3" spans="1:12" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1319,7 +703,7 @@
       </c>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" ht="16.5" hidden="1" spans="1:11">
+    <row r="4" spans="1:12" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1332,7 +716,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" ht="16.5" spans="1:12">
+    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1370,7 +754,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:12">
+    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1408,7 +792,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:12">
+    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1446,7 +830,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:12">
+    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1484,7 +868,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:12">
+    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1522,7 +906,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="10" ht="16.5" spans="1:12">
+    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -1560,7 +944,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" ht="16.5" spans="1:12">
+    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1599,8 +983,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -1,45 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CE4890-10BF-428E-9C0A-B5BE89E33E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31950" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author>chuge</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>线注倍数只有1，填0即可；
-有其他线注倍数，则填写对应即可</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -48,17 +42,22 @@
             <charset val="134"/>
           </rPr>
           <t>格式：类型1,权重1；类型2，权重2；…
+在SpecialMode表中根据游戏ID对应游戏模式进行触发
+金矿大亨
 1.普通
 2.拉火车
 3.黄金列车
 4.all board(二选一触发局)
-5.免费
-6.重转之拉火车
-7.重转之黄金列车</t>
+5.保险箱
+麻将胡了
+1.常规旋转
+2.免费旋转
+埃及艳后
+1.常规旋转</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="E1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -66,19 +65,11 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">[{类型1,[{[倍数区间下限,倍数区间上限],权重值},{[倍数区间下限,倍数区间上限],权重值}]}]
-1.普通
-2.拉火车
-3.黄金列车
-4.all board(二选一触发局)
-5.免费
-6.重转之拉火车
-7.重转之黄金列车
-</t>
+          <t>[{类型1,[{[倍数区间下限,倍数区间上限],权重值},{[倍数区间下限,倍数区间上限],权重值}]}]</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -91,7 +82,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -104,7 +95,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -129,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="34">
   <si>
     <t>id</t>
   </si>
@@ -137,13 +128,7 @@
     <t>游戏ID</t>
   </si>
   <si>
-    <t>滚轴模式ID</t>
-  </si>
-  <si>
-    <t>是否额外投注</t>
-  </si>
-  <si>
-    <t>线注倍数</t>
+    <t>调控序列ID</t>
   </si>
   <si>
     <t>类型权重</t>
@@ -152,10 +137,10 @@
     <t>倍数区间及权重</t>
   </si>
   <si>
-    <t>换皮游戏ID</t>
-  </si>
-  <si>
-    <t>进入条件</t>
+    <t>进入条件下线</t>
+  </si>
+  <si>
+    <t>进入条件上限</t>
   </si>
   <si>
     <t>对应水池描述</t>
@@ -164,13 +149,10 @@
     <t>int</t>
   </si>
   <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>Map&lt;int{,}int&gt;{;}</t>
-  </si>
-  <si>
-    <t>Map&lt;int{,}list&lt;string&gt;{^}&gt;{;}</t>
+    <t>Map&lt;int{_}int&gt;{|}</t>
+  </si>
+  <si>
+    <t>Map&lt;int{,}list&lt;string&gt;{|}&gt;{;}</t>
   </si>
   <si>
     <t>gameType</t>
@@ -179,77 +161,80 @@
     <t>modelId</t>
   </si>
   <si>
-    <t>extraBet</t>
-  </si>
-  <si>
-    <t>lineTimes</t>
-  </si>
-  <si>
     <t>typeProp</t>
   </si>
   <si>
     <t>sectionProp</t>
   </si>
   <si>
-    <t>targetGameType</t>
-  </si>
-  <si>
     <t>enterLimitMin</t>
   </si>
   <si>
     <t>enterLimitMax</t>
   </si>
   <si>
-    <t>1,9657;2,63;3,137;4,47</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-69376672^1&amp;10-0^10&amp;20-2744554^20&amp;30-3992455^30&amp;40-2799486^40&amp;50-3208889^50&amp;60-1809664^60&amp;70-2310276^70&amp;80-1224063^80&amp;90-1442757^90&amp;100-1050974^100&amp;120-1650049^120&amp;140-1462449^140&amp;160-924525^160&amp;180-604258^180&amp;200-531706^200&amp;300-1889472^300&amp;500-1374350^500&amp;800-744181^800&amp;1000-317158^1000&amp;1500-308866^1500&amp;2000-109866^2000&amp;3000-82918^3000&amp;4000-29021^4000&amp;5000-7256^5000&amp;7000-4146^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;2,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-1740507^3000&amp;4000-5696203^4000&amp;5000-14240507^5000&amp;7000-30696203^7000&amp;10000-21993671^10000&amp;15000-17246836^15000&amp;20000-5379747^20000&amp;30000-3006330^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;3,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-2407003^3000&amp;4000-37636762^4000&amp;5000-48504742^5000&amp;7000-8971554^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-72940^20000&amp;30000-1531729^30000&amp;40000-875274^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;4,0&amp;1-87211741^1&amp;10-0^10&amp;20-2096437^20&amp;30-2935011^30&amp;40-838575^40&amp;50-2096437^50&amp;60-209644^60&amp;70-838575^70&amp;80-419288^80&amp;90-209644^90&amp;100-419288^100&amp;120-628931^120&amp;140-0^140&amp;160-419288^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-209644^500&amp;800-209644^800&amp;1000-0^1000&amp;1500-209644^1500&amp;2000-209644^2000&amp;3000-0^3000&amp;4000-419288^4000&amp;5000-419288^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;5,0&amp;1-43186583^1&amp;10-0^10&amp;20-288260^20&amp;30-943397^30&amp;40-288260^40&amp;50-1519917^50&amp;60-655137^60&amp;70-1415095^70&amp;80-104822^80&amp;90-1912998^90&amp;100-131028^100&amp;120-1808177^120&amp;140-1624738^140&amp;160-943397^160&amp;180-1048219^180&amp;200-628931^200&amp;300-7206499^300&amp;500-9119497^500&amp;800-6708596^800&amp;1000-2987422^1000&amp;1500-5083858^1500&amp;2000-3432915^2000&amp;3000-3616353^3000&amp;4000-2122642^4000&amp;5000-1310273^5000&amp;7000-1022013^7000&amp;10000-576520^10000&amp;15000-235850^15000&amp;20000-52411^20000&amp;30000-26206^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;6,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-4394532^3000&amp;4000-0^4000&amp;5000-1074219^5000&amp;7000-585938^7000&amp;10000-683594^10000&amp;15000-97657^15000&amp;20000-1^20000&amp;30000-1^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;7,0&amp;1-37636762^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-2407003^3000&amp;4000-0^4000&amp;5000-0^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^</t>
+    <t>1_9550|2_80|3_20|4_60|5_50</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-69376672|1&amp;10-0|10&amp;20-3444554|20&amp;30-3992455|30&amp;40-3208889|40&amp;50-2799486|50&amp;60-2310276|60&amp;70-1809664|70&amp;80-1224063|80&amp;90-1442757|90&amp;100-1050974|100&amp;120-1650049|120&amp;140-1462449|140&amp;160-1889472|160&amp;180-1374350|180&amp;200-824525|200&amp;300-604258|300&amp;500-531706|500&amp;800-444181|800&amp;1000-217158|1000&amp;1500-108866|1500&amp;2000-109866|2000&amp;3000-82918|3000&amp;4000-29021|4000&amp;5000-7256|5000&amp;7000-4146|7000&amp;10000-0|10000&amp;15000-0|15000&amp;20000-0|20000&amp;30000-0|30000&amp;40000-0|40000&amp;50000-0|50000&amp;60000-0|60000&amp;70000-0|70000&amp;80000-0|80000&amp;100000-0|100000&amp;200000-0|200000&amp;500000-0|500000&amp;1000000-0|1000000&amp;1000000000-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-30696203|3000&amp;4000-21993671|4000&amp;5000-17246836|5000&amp;7000-14240507|7000&amp;10000-5696203|10000&amp;15000-5379747|15000&amp;20000-3006330|20000&amp;30000-1740507|30000&amp;40000-0|40000&amp;50000-0|50000&amp;60000-0|60000&amp;70000-0|70000&amp;80000-0|80000&amp;100000-0|100000&amp;200000-0|200000&amp;500000-0|500000&amp;1000000-0|1000000&amp;1000000000-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-2407003|3000&amp;4000-37636762|4000&amp;5000-48504742|5000&amp;7000-8971554|7000&amp;10000-0|10000&amp;15000-0|15000&amp;20000-72940|20000&amp;30000-1531729|30000&amp;40000-875274|40000&amp;50000-0|50000&amp;60000-0|60000&amp;70000-0|70000&amp;80000-0|80000&amp;100000-0|100000&amp;200000-0|200000&amp;500000-0|500000&amp;1000000-0|1000000&amp;1000000000-0;4,0&amp;1-87211741|1&amp;10-0|10&amp;20-2096437|20&amp;30-2935011|30&amp;40-838575|40&amp;50-2096437|50&amp;60-209644|60&amp;70-838575|70&amp;80-419288|80&amp;90-209644|90&amp;100-419288|100&amp;120-628931|120&amp;140-0|140&amp;160-419288|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-209644|500&amp;800-209644|800&amp;1000-0|1000&amp;1500-209644|1500&amp;2000-209644|2000&amp;3000-0|3000&amp;4000-419288|4000&amp;5000-419288|5000&amp;7000-0|7000&amp;10000-0|10000&amp;15000-0|15000&amp;20000-0|20000&amp;30000-0|30000&amp;40000-0|40000&amp;50000-0|50000&amp;60000-0|60000&amp;70000-0|70000&amp;80000-0|80000&amp;100000-0|100000&amp;200000-0|200000&amp;500000-0|500000&amp;1000000-0|1000000&amp;1000000000-0;5,0&amp;1-43186583|1&amp;10-0|10&amp;20-288260|20&amp;30-943397|30&amp;40-288260|40&amp;50-1519917|50&amp;60-655137|60&amp;70-1415095|70&amp;80-104822|80&amp;90-1912998|90&amp;100-131028|100&amp;120-1808177|120&amp;140-1624738|140&amp;160-943397|160&amp;180-1048219|180&amp;200-628931|200&amp;300-7206499|300&amp;500-9119497|500&amp;800-6708596|800&amp;1000-2987422|1000&amp;1500-5083858|1500&amp;2000-3432915|2000&amp;3000-3616353|3000&amp;4000-2122642|4000&amp;5000-1310273|5000&amp;7000-1022013|7000&amp;10000-576520|10000&amp;15000-235850|15000&amp;20000-52411|20000&amp;30000-26206|30000&amp;40000-0|40000&amp;50000-0|50000&amp;60000-0|60000&amp;70000-0|70000&amp;80000-0|80000&amp;100000-0|100000&amp;200000-0|200000&amp;500000-0|500000&amp;1000000-0|1000000&amp;1000000000-0;6,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-4394532|3000&amp;4000-0|4000&amp;5000-1074219|5000&amp;7000-585938|7000&amp;10000-683594|10000&amp;15000-97657|15000&amp;20000-1|20000&amp;30000-1|30000&amp;40000-0|40000&amp;50000-0|50000&amp;60000-0|60000&amp;70000-0|70000&amp;80000-0|80000&amp;100000-0|100000&amp;200000-0|200000&amp;500000-0|500000&amp;1000000-0|1000000&amp;1000000000-0</t>
   </si>
   <si>
     <t>放水池+3</t>
   </si>
   <si>
-    <t>1,0&amp;1-69376672^1&amp;10-0^10&amp;20-2744554^20&amp;30-3992455^30&amp;40-2799486^40&amp;50-3208889^50&amp;60-1809664^60&amp;70-2310276^70&amp;80-1224063^80&amp;90-1442757^90&amp;100-1050974^100&amp;120-1650049^120&amp;140-1462449^140&amp;160-924525^160&amp;180-604258^180&amp;200-531706^200&amp;300-1889472^300&amp;500-1374350^500&amp;800-744181^800&amp;1000-317158^1000&amp;1500-308866^1500&amp;2000-109866^2000&amp;3000-82918^3000&amp;4000-29021^4000&amp;5000-7256^5000&amp;7000-4146^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;2,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-1740507^3000&amp;4000-5696203^4000&amp;5000-14240507^5000&amp;7000-30696203^7000&amp;10000-21993671^10000&amp;15000-17246836^15000&amp;20000-5379747^20000&amp;30000-3006330^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;3,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-2407003^3000&amp;4000-37636762^4000&amp;5000-48504742^5000&amp;7000-8971554^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-72940^20000&amp;30000-1531729^30000&amp;40000-875274^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;4,0&amp;1-87211741^1&amp;10-0^10&amp;20-2096437^20&amp;30-2935011^30&amp;40-838575^40&amp;50-2096437^50&amp;60-209644^60&amp;70-838575^70&amp;80-419288^80&amp;90-209644^90&amp;100-419288^100&amp;120-628931^120&amp;140-0^140&amp;160-419288^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-209644^500&amp;800-209644^800&amp;1000-0^1000&amp;1500-209644^1500&amp;2000-209644^2000&amp;3000-0^3000&amp;4000-419288^4000&amp;5000-419288^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;5,0&amp;1-43186583^1&amp;10-0^10&amp;20-288260^20&amp;30-943397^30&amp;40-288260^40&amp;50-1519917^50&amp;60-655137^60&amp;70-1415095^70&amp;80-104822^80&amp;90-1912998^90&amp;100-131028^100&amp;120-1808177^120&amp;140-1624738^140&amp;160-943397^160&amp;180-1048219^180&amp;200-628931^200&amp;300-7206499^300&amp;500-9119497^500&amp;800-6708596^800&amp;1000-2987422^1000&amp;1500-5083858^1500&amp;2000-3432915^2000&amp;3000-3616353^3000&amp;4000-2122642^4000&amp;5000-1310273^5000&amp;7000-1022013^7000&amp;10000-576520^10000&amp;15000-235850^15000&amp;20000-52411^20000&amp;30000-26206^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;6,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-4394532^3000&amp;4000-0^4000&amp;5000-1074219^5000&amp;7000-585938^7000&amp;10000-683594^10000&amp;15000-97657^15000&amp;20000-1^20000&amp;30000-1^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;7,0&amp;1-100000000^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-0^3000&amp;4000-0^4000&amp;5000-0^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^</t>
+    <t>1_9550|2_70|3_15|4_60|5_50</t>
   </si>
   <si>
     <t>放水池+2</t>
   </si>
   <si>
-    <t>1,9702;2,49;3,132;4,38</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-71005113^1&amp;10-0^10&amp;20-2571529^20&amp;30-3649613^30&amp;40-2554008^40&amp;50-3031209^50&amp;60-1671752^60&amp;70-2197395^70&amp;80-1164661^80&amp;90-1463556^90&amp;100-1042011^100&amp;120-1604758^120&amp;140-1384194^140&amp;160-872980^160&amp;180-574085^180&amp;200-496785^200&amp;300-1809862^300&amp;500-1284219^500&amp;800-726625^800&amp;1000-310233^1000&amp;1500-289620^1500&amp;2000-146356^2000&amp;3000-111313^3000&amp;4000-24737^4000&amp;5000-12369^5000&amp;7000-1031^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;2,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-2805612^3000&amp;4000-7414830^4000&amp;5000-14228457^5000&amp;7000-29458918^7000&amp;10000-24649299^10000&amp;15000-16032065^15000&amp;20000-4208417^20000&amp;30000-1202405^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;3,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-9214502^1500&amp;2000-28549849^2000&amp;3000-604230^3000&amp;4000-5287010^4000&amp;5000-18277946^5000&amp;7000-16616315^7000&amp;10000-13595167^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;4,0&amp;1-84415585^1&amp;10-0^10&amp;20-3376624^20&amp;30-3896104^30&amp;40-519481^40&amp;50-1558442^50&amp;60-259741^60&amp;70-1298702^70&amp;80-519481^80&amp;90-259741^90&amp;100-259741^100&amp;120-259741^120&amp;140-259741^140&amp;160-519481^160&amp;180-0^180&amp;200-0^200&amp;300-779221^300&amp;500-779221^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-0^3000&amp;4000-0^4000&amp;5000-0^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-1^15000&amp;20000-259741^20000&amp;30000-1^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;5,0&amp;1-43246754^1&amp;10-0^10&amp;20-292208^20&amp;30-1233767^30&amp;40-194806^40&amp;50-1461039^50&amp;60-681819^60&amp;70-1298702^70&amp;80-227273^80&amp;90-1071429^90&amp;100-227273^100&amp;120-1785715^120&amp;140-1883117^140&amp;160-974026^160&amp;180-1103897^180&amp;200-779221^200&amp;300-6915585^300&amp;500-8928572^500&amp;800-7597403^800&amp;1000-3409091^1000&amp;1500-4935065^1500&amp;2000-3246754^2000&amp;3000-3214286^3000&amp;4000-1948052^4000&amp;5000-1331169^5000&amp;7000-1136364^7000&amp;10000-714286^10000&amp;15000-0^15000&amp;20000-1^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;6,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-4394532^3000&amp;4000-0^4000&amp;5000-1074219^5000&amp;7000-585938^7000&amp;10000-683594^10000&amp;15000-97657^15000&amp;20000-1^20000&amp;30000-1^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;7,0&amp;1-100000000^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-0^3000&amp;4000-0^4000&amp;5000-0^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^</t>
+    <t>1_9550|2_70|3_15|4_50|5_50</t>
   </si>
   <si>
     <t>放水池+1</t>
   </si>
   <si>
-    <t>1,9833;2,29;3,96;4,13</t>
+    <t>1_9550|2_60|3_10|4_50|5_50</t>
   </si>
   <si>
     <t>标准池</t>
   </si>
   <si>
-    <t>1,98339;2,278;3,999;4,128</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-77319274^1&amp;10-0^10&amp;20-2380541^20&amp;30-3125922^30&amp;40-1890400^40&amp;50-2325629^50&amp;60-1135867^60&amp;70-1688039^70&amp;80-820631^80&amp;90-1120614^90&amp;100-643692^100&amp;120-1048415^120&amp;140-1078921^140&amp;160-653861^160&amp;180-401672^180&amp;200-392520^200&amp;300-1310772^300&amp;500-1047398^500&amp;800-680300^800&amp;1000-331507^1000&amp;1500-301000^1500&amp;2000-145416^2000&amp;3000-107791^3000&amp;4000-31524^4000&amp;5000-10169^5000&amp;7000-7119^7000&amp;10000-22302159^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;2,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-719425^2000&amp;3000-1438849^3000&amp;4000-7913670^4000&amp;5000-15467626^5000&amp;7000-30935252^7000&amp;10000-22302159^10000&amp;15000-16187051^15000&amp;20000-1^20000&amp;30000-1^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;3,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-46846847^1500&amp;2000-33933934^2000&amp;3000-900901^3000&amp;4000-10110111^4000&amp;5000-8208209^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;4,0&amp;1-90625001^1&amp;10-0^10&amp;20-781251^20&amp;30-1562501^30&amp;40-2343751^40&amp;50-2343751^50&amp;60-781251^60&amp;70-0^70&amp;80-0^80&amp;90-1562501^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-0^3000&amp;4000-0^4000&amp;5000-0^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;5,0&amp;1-90625001^1&amp;10-0^10&amp;20-781251^20&amp;30-1562501^30&amp;40-2343751^40&amp;50-2343751^50&amp;60-781251^60&amp;70-1^70&amp;80-1^80&amp;90-1562501^90&amp;100-1^100&amp;120-1^120&amp;140-1562501^140&amp;160-1367188^160&amp;180-1464844^180&amp;200-781251^200&amp;300-6933594^300&amp;500-8691407^500&amp;800-8203126^800&amp;1000-2734376^1000&amp;1500-5566407^1500&amp;2000-2832032^2000&amp;3000-4394532^3000&amp;4000-1660157^4000&amp;5000-1074219^5000&amp;7000-585938^7000&amp;10000-683594^10000&amp;15000-97657^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;6,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-4394532^3000&amp;4000-0^4000&amp;5000-1074219^5000&amp;7000-585938^7000&amp;10000-683594^10000&amp;15000-97657^15000&amp;20000-1^20000&amp;30000-1^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;7,0&amp;1-100000000^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-0^3000&amp;4000-0^4000&amp;5000-0^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^</t>
+    <t>1_9550|2_50|3_10|4_50|5_50</t>
   </si>
   <si>
     <t>吸水池-1</t>
   </si>
   <si>
+    <t>1_9550|2_40|3_10|4_50|5_50</t>
+  </si>
+  <si>
     <t>吸水池-2</t>
   </si>
   <si>
+    <t>1_9550|2_40|3_5|4_40|5_50</t>
+  </si>
+  <si>
     <t>吸水池-3</t>
+  </si>
+  <si>
+    <t>1_9550|2_450</t>
+  </si>
+  <si>
+    <t>1_10000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,10 +249,147 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -275,22 +397,214 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -298,32 +612,338 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 73" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -581,410 +1201,658 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
+    <col min="1" max="1" width="9.25"/>
     <col min="2" max="2" width="15.25" customWidth="1"/>
-    <col min="3" max="3" width="13.875" customWidth="1"/>
-    <col min="4" max="4" width="13.625" customWidth="1"/>
-    <col min="5" max="5" width="16.5" customWidth="1"/>
-    <col min="6" max="6" width="23.125" customWidth="1"/>
-    <col min="7" max="7" width="55" customWidth="1"/>
-    <col min="8" max="8" width="17.5" customWidth="1"/>
-    <col min="9" max="9" width="15.625" customWidth="1"/>
-    <col min="10" max="10" width="15.125" customWidth="1"/>
-    <col min="11" max="11" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
+    <col min="4" max="4" width="25.2666666666667" style="3" customWidth="1"/>
+    <col min="5" max="5" width="114.025" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.625" customWidth="1"/>
+    <col min="7" max="7" width="15.125" customWidth="1"/>
+    <col min="8" max="8" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="16.5" spans="1:8">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" ht="16.5" spans="1:8">
+      <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="B2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="E2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" ht="16.5" spans="1:8">
+      <c r="A3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="C3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="D3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="1"/>
-    </row>
-    <row r="3" spans="1:12" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="G3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" ht="16.5" spans="1:8">
+      <c r="A4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:8">
+      <c r="A5" s="4">
+        <v>1001</v>
+      </c>
+      <c r="B5" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="E5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="4">
+        <v>2000</v>
+      </c>
+      <c r="G5" s="4">
+        <v>999999</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="1" t="s">
+    </row>
+    <row r="6" ht="16.5" spans="1:8">
+      <c r="A6" s="4">
+        <v>1002</v>
+      </c>
+      <c r="B6" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C6" s="4">
+        <v>2</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="E6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G6" s="4">
+        <v>2000</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="1" t="s">
+    </row>
+    <row r="7" ht="16.5" spans="1:8">
+      <c r="A7" s="4">
+        <v>1003</v>
+      </c>
+      <c r="B7" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C7" s="4">
+        <v>3</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:12" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
+      <c r="E7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="4">
+        <v>500</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1000</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:8">
+      <c r="A8" s="4">
+        <v>1004</v>
+      </c>
+      <c r="B8" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C8" s="4">
+        <v>4</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="4">
+        <v>-500</v>
+      </c>
+      <c r="G8" s="4">
+        <v>500</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:8">
+      <c r="A9" s="4">
+        <v>1005</v>
+      </c>
+      <c r="B9" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C9" s="4">
+        <v>5</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="G9" s="4">
+        <v>-500</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:8">
+      <c r="A10" s="4">
+        <v>1006</v>
+      </c>
+      <c r="B10" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C10" s="4">
+        <v>6</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="G10" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:8">
+      <c r="A11" s="4">
+        <v>1007</v>
+      </c>
+      <c r="B11" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C11" s="4">
+        <v>7</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="4">
+        <v>-999999</v>
+      </c>
+      <c r="G11" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A12" s="4">
+        <v>7001</v>
+      </c>
+      <c r="B12" s="7">
+        <v>100700</v>
+      </c>
+      <c r="C12" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="D12" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="7">
+        <v>2000</v>
+      </c>
+      <c r="G12" s="7">
+        <v>999999</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A13" s="4">
+        <v>7002</v>
+      </c>
+      <c r="B13" s="7">
+        <v>100700</v>
+      </c>
+      <c r="C13" s="7">
+        <v>2</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="7">
+        <v>1000</v>
+      </c>
+      <c r="G13" s="7">
+        <v>2000</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A14" s="4">
+        <v>7003</v>
+      </c>
+      <c r="B14" s="7">
+        <v>100700</v>
+      </c>
+      <c r="C14" s="7">
+        <v>3</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="7">
+        <v>500</v>
+      </c>
+      <c r="G14" s="7">
+        <v>1000</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A15" s="4">
+        <v>7004</v>
+      </c>
+      <c r="B15" s="7">
+        <v>100700</v>
+      </c>
+      <c r="C15" s="7">
+        <v>4</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="7">
+        <v>-500</v>
+      </c>
+      <c r="G15" s="7">
+        <v>500</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A16" s="4">
+        <v>7005</v>
+      </c>
+      <c r="B16" s="7">
+        <v>100700</v>
+      </c>
+      <c r="C16" s="7">
+        <v>5</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="7">
+        <v>-1000</v>
+      </c>
+      <c r="G16" s="7">
+        <v>-500</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A17" s="4">
+        <v>7006</v>
+      </c>
+      <c r="B17" s="7">
+        <v>100700</v>
+      </c>
+      <c r="C17" s="7">
+        <v>6</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="7">
+        <v>-2000</v>
+      </c>
+      <c r="G17" s="7">
+        <v>-1000</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A18" s="4">
+        <v>7007</v>
+      </c>
+      <c r="B18" s="7">
+        <v>100700</v>
+      </c>
+      <c r="C18" s="7">
+        <v>7</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="7">
+        <v>-999999</v>
+      </c>
+      <c r="G18" s="7">
+        <v>-2000</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A19" s="4">
+        <v>14001</v>
+      </c>
+      <c r="B19" s="9">
+        <v>101400</v>
+      </c>
+      <c r="C19" s="9">
         <v>1</v>
       </c>
-      <c r="D5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="D19" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="9">
+        <v>2000</v>
+      </c>
+      <c r="G19" s="9">
+        <v>999999</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A20" s="4">
+        <v>14002</v>
+      </c>
+      <c r="B20" s="9">
+        <v>101400</v>
+      </c>
+      <c r="C20" s="9">
+        <v>2</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="9">
+        <v>1000</v>
+      </c>
+      <c r="G20" s="9">
+        <v>2000</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A21" s="4">
+        <v>14003</v>
+      </c>
+      <c r="B21" s="9">
+        <v>101400</v>
+      </c>
+      <c r="C21" s="9">
+        <v>3</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="9">
+        <v>500</v>
+      </c>
+      <c r="G21" s="9">
+        <v>1000</v>
+      </c>
+      <c r="H21" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1">
-        <v>2000</v>
-      </c>
-      <c r="J5" s="1">
-        <v>999999</v>
-      </c>
-      <c r="K5" s="1" t="s">
+    </row>
+    <row r="22" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A22" s="4">
+        <v>14004</v>
+      </c>
+      <c r="B22" s="9">
+        <v>101400</v>
+      </c>
+      <c r="C22" s="9">
+        <v>4</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="9">
+        <v>-500</v>
+      </c>
+      <c r="G22" s="9">
+        <v>500</v>
+      </c>
+      <c r="H22" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="L5">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C6" s="1">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1000</v>
-      </c>
-      <c r="J6" s="1">
-        <v>2000</v>
-      </c>
-      <c r="K6" s="1" t="s">
+    </row>
+    <row r="23" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A23" s="4">
+        <v>14005</v>
+      </c>
+      <c r="B23" s="9">
+        <v>101400</v>
+      </c>
+      <c r="C23" s="9">
+        <v>5</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="9">
+        <v>-1000</v>
+      </c>
+      <c r="G23" s="9">
+        <v>-500</v>
+      </c>
+      <c r="H23" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="L6">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C7" s="1">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="1" t="s">
+    </row>
+    <row r="24" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A24" s="4">
+        <v>14006</v>
+      </c>
+      <c r="B24" s="9">
+        <v>101400</v>
+      </c>
+      <c r="C24" s="9">
+        <v>6</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="9">
+        <v>-2000</v>
+      </c>
+      <c r="G24" s="9">
+        <v>-1000</v>
+      </c>
+      <c r="H24" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>500</v>
-      </c>
-      <c r="J7" s="1">
-        <v>1000</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C8" s="1">
-        <v>4</v>
-      </c>
-      <c r="D8" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1" t="s">
+    </row>
+    <row r="25" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A25" s="4">
+        <v>14007</v>
+      </c>
+      <c r="B25" s="9">
+        <v>101400</v>
+      </c>
+      <c r="C25" s="9">
+        <v>7</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="9">
+        <v>-999999</v>
+      </c>
+      <c r="G25" s="9">
+        <v>-2000</v>
+      </c>
+      <c r="H25" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1">
-        <v>-500</v>
-      </c>
-      <c r="J8" s="1">
-        <v>500</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C9" s="1">
-        <v>5</v>
-      </c>
-      <c r="D9" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1">
-        <v>-1000</v>
-      </c>
-      <c r="J9" s="1">
-        <v>-500</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L9">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>6</v>
-      </c>
-      <c r="B10" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C10" s="1">
-        <v>6</v>
-      </c>
-      <c r="D10" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
-        <v>-2000</v>
-      </c>
-      <c r="J10" s="1">
-        <v>-1000</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L10">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C11" s="1">
-        <v>7</v>
-      </c>
-      <c r="D11" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1">
-        <v>-999999</v>
-      </c>
-      <c r="J11" s="1">
-        <v>-2000</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L11">
-        <v>50</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -1,45 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CE4890-10BF-428E-9C0A-B5BE89E33E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31950" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author>chuge</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>线注倍数只有1，填0即可；
-有其他线注倍数，则填写对应即可</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -48,17 +42,22 @@
             <charset val="134"/>
           </rPr>
           <t>格式：类型1,权重1；类型2，权重2；…
+在SpecialMode表中根据游戏ID对应游戏模式进行触发
+金矿大亨
 1.普通
 2.拉火车
 3.黄金列车
 4.all board(二选一触发局)
-5.免费
-6.重转之拉火车
-7.重转之黄金列车</t>
+5.保险箱
+麻将胡了
+1.常规旋转
+2.免费旋转
+埃及艳后
+1.常规旋转</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="E1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -66,19 +65,11 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">[{类型1,[{[倍数区间下限,倍数区间上限],权重值},{[倍数区间下限,倍数区间上限],权重值}]}]
-1.普通
-2.拉火车
-3.黄金列车
-4.all board(二选一触发局)
-5.免费
-6.重转之拉火车
-7.重转之黄金列车
-</t>
+          <t>[{类型1,[{[倍数区间下限,倍数区间上限],权重值},{[倍数区间下限,倍数区间上限],权重值}]}]</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -91,7 +82,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -104,7 +95,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -129,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="36">
   <si>
     <t>id</t>
   </si>
@@ -137,13 +128,7 @@
     <t>游戏ID</t>
   </si>
   <si>
-    <t>滚轴模式ID</t>
-  </si>
-  <si>
-    <t>是否额外投注</t>
-  </si>
-  <si>
-    <t>线注倍数</t>
+    <t>调控序列ID</t>
   </si>
   <si>
     <t>类型权重</t>
@@ -152,10 +137,10 @@
     <t>倍数区间及权重</t>
   </si>
   <si>
-    <t>换皮游戏ID</t>
-  </si>
-  <si>
-    <t>进入条件</t>
+    <t>进入条件下线</t>
+  </si>
+  <si>
+    <t>进入条件上限</t>
   </si>
   <si>
     <t>对应水池描述</t>
@@ -164,13 +149,10 @@
     <t>int</t>
   </si>
   <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>Map&lt;int{,}int&gt;{;}</t>
-  </si>
-  <si>
-    <t>Map&lt;int{,}list&lt;string&gt;{^}&gt;{;}</t>
+    <t>Map&lt;int{_}int&gt;{|}</t>
+  </si>
+  <si>
+    <t>Map&lt;int{,}list&lt;string&gt;{|}&gt;{;}</t>
   </si>
   <si>
     <t>gameType</t>
@@ -179,77 +161,86 @@
     <t>modelId</t>
   </si>
   <si>
-    <t>extraBet</t>
-  </si>
-  <si>
-    <t>lineTimes</t>
-  </si>
-  <si>
     <t>typeProp</t>
   </si>
   <si>
     <t>sectionProp</t>
   </si>
   <si>
-    <t>targetGameType</t>
-  </si>
-  <si>
     <t>enterLimitMin</t>
   </si>
   <si>
     <t>enterLimitMax</t>
   </si>
   <si>
-    <t>1,9657;2,63;3,137;4,47</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-69376672^1&amp;10-0^10&amp;20-2744554^20&amp;30-3992455^30&amp;40-2799486^40&amp;50-3208889^50&amp;60-1809664^60&amp;70-2310276^70&amp;80-1224063^80&amp;90-1442757^90&amp;100-1050974^100&amp;120-1650049^120&amp;140-1462449^140&amp;160-924525^160&amp;180-604258^180&amp;200-531706^200&amp;300-1889472^300&amp;500-1374350^500&amp;800-744181^800&amp;1000-317158^1000&amp;1500-308866^1500&amp;2000-109866^2000&amp;3000-82918^3000&amp;4000-29021^4000&amp;5000-7256^5000&amp;7000-4146^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;2,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-1740507^3000&amp;4000-5696203^4000&amp;5000-14240507^5000&amp;7000-30696203^7000&amp;10000-21993671^10000&amp;15000-17246836^15000&amp;20000-5379747^20000&amp;30000-3006330^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;3,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-2407003^3000&amp;4000-37636762^4000&amp;5000-48504742^5000&amp;7000-8971554^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-72940^20000&amp;30000-1531729^30000&amp;40000-875274^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;4,0&amp;1-87211741^1&amp;10-0^10&amp;20-2096437^20&amp;30-2935011^30&amp;40-838575^40&amp;50-2096437^50&amp;60-209644^60&amp;70-838575^70&amp;80-419288^80&amp;90-209644^90&amp;100-419288^100&amp;120-628931^120&amp;140-0^140&amp;160-419288^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-209644^500&amp;800-209644^800&amp;1000-0^1000&amp;1500-209644^1500&amp;2000-209644^2000&amp;3000-0^3000&amp;4000-419288^4000&amp;5000-419288^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;5,0&amp;1-43186583^1&amp;10-0^10&amp;20-288260^20&amp;30-943397^30&amp;40-288260^40&amp;50-1519917^50&amp;60-655137^60&amp;70-1415095^70&amp;80-104822^80&amp;90-1912998^90&amp;100-131028^100&amp;120-1808177^120&amp;140-1624738^140&amp;160-943397^160&amp;180-1048219^180&amp;200-628931^200&amp;300-7206499^300&amp;500-9119497^500&amp;800-6708596^800&amp;1000-2987422^1000&amp;1500-5083858^1500&amp;2000-3432915^2000&amp;3000-3616353^3000&amp;4000-2122642^4000&amp;5000-1310273^5000&amp;7000-1022013^7000&amp;10000-576520^10000&amp;15000-235850^15000&amp;20000-52411^20000&amp;30000-26206^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;6,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-4394532^3000&amp;4000-0^4000&amp;5000-1074219^5000&amp;7000-585938^7000&amp;10000-683594^10000&amp;15000-97657^15000&amp;20000-1^20000&amp;30000-1^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;7,0&amp;1-37636762^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-2407003^3000&amp;4000-0^4000&amp;5000-0^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^</t>
+    <t>1_6700|2_800|3_400|4_800|5_400</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-46500|1&amp;10-8000|10&amp;20-10000|20&amp;30-9000|30&amp;40-7500|40&amp;50-6000|50&amp;60-4200|60&amp;70-3000|70&amp;80-1800|80&amp;90-1200|90&amp;100-1000|100&amp;120-800|120&amp;140-400|140&amp;160-150|160&amp;180-150|180&amp;200-100|200&amp;300-100|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-100|50&amp;60-400|60&amp;70-500|70&amp;80-500|80&amp;90-500|90&amp;100-500|100&amp;120-500|120&amp;140-1000|140&amp;160-4000|160&amp;180-5000|180&amp;200-5500|200&amp;300-30000|300&amp;500-33400|500&amp;800-12500|800&amp;1000-3500|1000&amp;1500-2000|1500&amp;2000-100|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-200|140&amp;160-200|160&amp;180-1000|180&amp;200-1000|200&amp;300-15000|300&amp;500-45000|500&amp;800-30000|800&amp;1000-5000|1000&amp;1500-2500|1500&amp;2000-100|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;4,0&amp;1-62000|1&amp;10-10000|10&amp;20-12500|20&amp;30-8100|30&amp;40-4000|40&amp;50-2000|50&amp;60-800|60&amp;70-400|70&amp;80-100|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-900|60&amp;70-4000|70&amp;80-8000|80&amp;90-10000|90&amp;100-12000|100&amp;120-24000|120&amp;140-16000|140&amp;160-11000|160&amp;180-7000|180&amp;200-4000|200&amp;300-3000|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;6,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-50|50&amp;60-100|60&amp;70-200|70&amp;80-200|80&amp;90-500|90&amp;100-500|100&amp;120-2000|120&amp;140-2700|140&amp;160-3500|160&amp;180-4000|180&amp;200-4000|200&amp;300-30000|300&amp;500-33000|500&amp;800-14000|800&amp;1000-3000|1000&amp;1500-2000|1500&amp;2000-200|2000&amp;3000-50|3000&amp;4000-0|4000&amp;5000-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-32000|300&amp;500-58000|500&amp;800-10000|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0</t>
   </si>
   <si>
     <t>放水池+3</t>
   </si>
   <si>
-    <t>1,0&amp;1-69376672^1&amp;10-0^10&amp;20-2744554^20&amp;30-3992455^30&amp;40-2799486^40&amp;50-3208889^50&amp;60-1809664^60&amp;70-2310276^70&amp;80-1224063^80&amp;90-1442757^90&amp;100-1050974^100&amp;120-1650049^120&amp;140-1462449^140&amp;160-924525^160&amp;180-604258^180&amp;200-531706^200&amp;300-1889472^300&amp;500-1374350^500&amp;800-744181^800&amp;1000-317158^1000&amp;1500-308866^1500&amp;2000-109866^2000&amp;3000-82918^3000&amp;4000-29021^4000&amp;5000-7256^5000&amp;7000-4146^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;2,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-1740507^3000&amp;4000-5696203^4000&amp;5000-14240507^5000&amp;7000-30696203^7000&amp;10000-21993671^10000&amp;15000-17246836^15000&amp;20000-5379747^20000&amp;30000-3006330^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;3,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-2407003^3000&amp;4000-37636762^4000&amp;5000-48504742^5000&amp;7000-8971554^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-72940^20000&amp;30000-1531729^30000&amp;40000-875274^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;4,0&amp;1-87211741^1&amp;10-0^10&amp;20-2096437^20&amp;30-2935011^30&amp;40-838575^40&amp;50-2096437^50&amp;60-209644^60&amp;70-838575^70&amp;80-419288^80&amp;90-209644^90&amp;100-419288^100&amp;120-628931^120&amp;140-0^140&amp;160-419288^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-209644^500&amp;800-209644^800&amp;1000-0^1000&amp;1500-209644^1500&amp;2000-209644^2000&amp;3000-0^3000&amp;4000-419288^4000&amp;5000-419288^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;5,0&amp;1-43186583^1&amp;10-0^10&amp;20-288260^20&amp;30-943397^30&amp;40-288260^40&amp;50-1519917^50&amp;60-655137^60&amp;70-1415095^70&amp;80-104822^80&amp;90-1912998^90&amp;100-131028^100&amp;120-1808177^120&amp;140-1624738^140&amp;160-943397^160&amp;180-1048219^180&amp;200-628931^200&amp;300-7206499^300&amp;500-9119497^500&amp;800-6708596^800&amp;1000-2987422^1000&amp;1500-5083858^1500&amp;2000-3432915^2000&amp;3000-3616353^3000&amp;4000-2122642^4000&amp;5000-1310273^5000&amp;7000-1022013^7000&amp;10000-576520^10000&amp;15000-235850^15000&amp;20000-52411^20000&amp;30000-26206^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;6,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-4394532^3000&amp;4000-0^4000&amp;5000-1074219^5000&amp;7000-585938^7000&amp;10000-683594^10000&amp;15000-97657^15000&amp;20000-1^20000&amp;30000-1^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;7,0&amp;1-100000000^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-0^3000&amp;4000-0^4000&amp;5000-0^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^</t>
+    <t>1_7100|2_800|3_400|4_800|5_400</t>
   </si>
   <si>
     <t>放水池+2</t>
   </si>
   <si>
-    <t>1,9702;2,49;3,132;4,38</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-71005113^1&amp;10-0^10&amp;20-2571529^20&amp;30-3649613^30&amp;40-2554008^40&amp;50-3031209^50&amp;60-1671752^60&amp;70-2197395^70&amp;80-1164661^80&amp;90-1463556^90&amp;100-1042011^100&amp;120-1604758^120&amp;140-1384194^140&amp;160-872980^160&amp;180-574085^180&amp;200-496785^200&amp;300-1809862^300&amp;500-1284219^500&amp;800-726625^800&amp;1000-310233^1000&amp;1500-289620^1500&amp;2000-146356^2000&amp;3000-111313^3000&amp;4000-24737^4000&amp;5000-12369^5000&amp;7000-1031^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;2,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-2805612^3000&amp;4000-7414830^4000&amp;5000-14228457^5000&amp;7000-29458918^7000&amp;10000-24649299^10000&amp;15000-16032065^15000&amp;20000-4208417^20000&amp;30000-1202405^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;3,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-9214502^1500&amp;2000-28549849^2000&amp;3000-604230^3000&amp;4000-5287010^4000&amp;5000-18277946^5000&amp;7000-16616315^7000&amp;10000-13595167^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;4,0&amp;1-84415585^1&amp;10-0^10&amp;20-3376624^20&amp;30-3896104^30&amp;40-519481^40&amp;50-1558442^50&amp;60-259741^60&amp;70-1298702^70&amp;80-519481^80&amp;90-259741^90&amp;100-259741^100&amp;120-259741^120&amp;140-259741^140&amp;160-519481^160&amp;180-0^180&amp;200-0^200&amp;300-779221^300&amp;500-779221^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-0^3000&amp;4000-0^4000&amp;5000-0^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-1^15000&amp;20000-259741^20000&amp;30000-1^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;5,0&amp;1-43246754^1&amp;10-0^10&amp;20-292208^20&amp;30-1233767^30&amp;40-194806^40&amp;50-1461039^50&amp;60-681819^60&amp;70-1298702^70&amp;80-227273^80&amp;90-1071429^90&amp;100-227273^100&amp;120-1785715^120&amp;140-1883117^140&amp;160-974026^160&amp;180-1103897^180&amp;200-779221^200&amp;300-6915585^300&amp;500-8928572^500&amp;800-7597403^800&amp;1000-3409091^1000&amp;1500-4935065^1500&amp;2000-3246754^2000&amp;3000-3214286^3000&amp;4000-1948052^4000&amp;5000-1331169^5000&amp;7000-1136364^7000&amp;10000-714286^10000&amp;15000-0^15000&amp;20000-1^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;6,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-4394532^3000&amp;4000-0^4000&amp;5000-1074219^5000&amp;7000-585938^7000&amp;10000-683594^10000&amp;15000-97657^15000&amp;20000-1^20000&amp;30000-1^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;7,0&amp;1-100000000^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-0^3000&amp;4000-0^4000&amp;5000-0^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^</t>
+    <t>1_7500|2_800|3_400|4_800|5_400</t>
   </si>
   <si>
     <t>放水池+1</t>
   </si>
   <si>
-    <t>1,9833;2,29;3,96;4,13</t>
+    <t>1_7900|2_800|3_400|4_800|5_400</t>
   </si>
   <si>
     <t>标准池</t>
   </si>
   <si>
-    <t>1,98339;2,278;3,999;4,128</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-77319274^1&amp;10-0^10&amp;20-2380541^20&amp;30-3125922^30&amp;40-1890400^40&amp;50-2325629^50&amp;60-1135867^60&amp;70-1688039^70&amp;80-820631^80&amp;90-1120614^90&amp;100-643692^100&amp;120-1048415^120&amp;140-1078921^140&amp;160-653861^160&amp;180-401672^180&amp;200-392520^200&amp;300-1310772^300&amp;500-1047398^500&amp;800-680300^800&amp;1000-331507^1000&amp;1500-301000^1500&amp;2000-145416^2000&amp;3000-107791^3000&amp;4000-31524^4000&amp;5000-10169^5000&amp;7000-7119^7000&amp;10000-22302159^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;2,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-719425^2000&amp;3000-1438849^3000&amp;4000-7913670^4000&amp;5000-15467626^5000&amp;7000-30935252^7000&amp;10000-22302159^10000&amp;15000-16187051^15000&amp;20000-1^20000&amp;30000-1^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;3,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-46846847^1500&amp;2000-33933934^2000&amp;3000-900901^3000&amp;4000-10110111^4000&amp;5000-8208209^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;4,0&amp;1-90625001^1&amp;10-0^10&amp;20-781251^20&amp;30-1562501^30&amp;40-2343751^40&amp;50-2343751^50&amp;60-781251^60&amp;70-0^70&amp;80-0^80&amp;90-1562501^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-0^3000&amp;4000-0^4000&amp;5000-0^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;5,0&amp;1-90625001^1&amp;10-0^10&amp;20-781251^20&amp;30-1562501^30&amp;40-2343751^40&amp;50-2343751^50&amp;60-781251^60&amp;70-1^70&amp;80-1^80&amp;90-1562501^90&amp;100-1^100&amp;120-1^120&amp;140-1562501^140&amp;160-1367188^160&amp;180-1464844^180&amp;200-781251^200&amp;300-6933594^300&amp;500-8691407^500&amp;800-8203126^800&amp;1000-2734376^1000&amp;1500-5566407^1500&amp;2000-2832032^2000&amp;3000-4394532^3000&amp;4000-1660157^4000&amp;5000-1074219^5000&amp;7000-585938^7000&amp;10000-683594^10000&amp;15000-97657^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;6,0&amp;1-0^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-4394532^3000&amp;4000-0^4000&amp;5000-1074219^5000&amp;7000-585938^7000&amp;10000-683594^10000&amp;15000-97657^15000&amp;20000-1^20000&amp;30000-1^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^;7,0&amp;1-100000000^1&amp;10-0^10&amp;20-0^20&amp;30-0^30&amp;40-0^40&amp;50-0^50&amp;60-0^60&amp;70-0^70&amp;80-0^80&amp;90-0^90&amp;100-0^100&amp;120-0^120&amp;140-0^140&amp;160-0^160&amp;180-0^180&amp;200-0^200&amp;300-0^300&amp;500-0^500&amp;800-0^800&amp;1000-0^1000&amp;1500-0^1500&amp;2000-0^2000&amp;3000-0^3000&amp;4000-0^4000&amp;5000-0^5000&amp;7000-0^7000&amp;10000-0^10000&amp;15000-0^15000&amp;20000-0^20000&amp;30000-0^30000&amp;40000-0^40000&amp;50000-0^50000&amp;60000-0^60000&amp;70000-0^70000&amp;80000-0^80000&amp;100000-0^100000&amp;200000-0^200000&amp;500000-0^500000&amp;1000000-0^1000000&amp;1000000000-0^</t>
+    <t>1_8300|2_800|3_400|4_800|5_400</t>
   </si>
   <si>
     <t>吸水池-1</t>
   </si>
   <si>
+    <t>1_8700|2_800|3_400|4_800|5_400</t>
+  </si>
+  <si>
     <t>吸水池-2</t>
   </si>
   <si>
+    <t>1_9100|2_800|3_400|4_800|5_400</t>
+  </si>
+  <si>
     <t>吸水池-3</t>
+  </si>
+  <si>
+    <t>1_9550|2_450</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-46500|1&amp;10-8000|10&amp;20-10000|20&amp;30-9000|30&amp;40-7500|40&amp;50-6000|50&amp;60-4200|60&amp;70-3000|70&amp;80-1800|80&amp;90-1200|90&amp;100-1000|100&amp;120-800|120&amp;140-400|140&amp;160-150|160&amp;180-150|180&amp;200-100|200&amp;300-100|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-100|50&amp;60-400|60&amp;70-500|70&amp;80-500|80&amp;90-500|90&amp;100-500|100&amp;120-500|120&amp;140-1000|140&amp;160-4000|160&amp;180-5000|180&amp;200-5500|200&amp;300-30000|300&amp;500-33400|500&amp;800-12500|800&amp;1000-3500|1000&amp;1500-2000|1500&amp;2000-100|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0</t>
+  </si>
+  <si>
+    <t>1_10000</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-46500|1&amp;10-8000|10&amp;20-10000|20&amp;30-9000|30&amp;40-7500|40&amp;50-6000|50&amp;60-4200|60&amp;70-3000|70&amp;80-1800|80&amp;90-1200|90&amp;100-1000|100&amp;120-800|120&amp;140-400|140&amp;160-150|160&amp;180-150|180&amp;200-100|200&amp;300-100|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,10 +255,147 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -275,22 +403,214 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -298,32 +618,338 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 73" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -581,410 +1207,658 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
+    <col min="1" max="1" width="9.25"/>
     <col min="2" max="2" width="15.25" customWidth="1"/>
-    <col min="3" max="3" width="13.875" customWidth="1"/>
-    <col min="4" max="4" width="13.625" customWidth="1"/>
-    <col min="5" max="5" width="16.5" customWidth="1"/>
-    <col min="6" max="6" width="23.125" customWidth="1"/>
-    <col min="7" max="7" width="55" customWidth="1"/>
-    <col min="8" max="8" width="17.5" customWidth="1"/>
-    <col min="9" max="9" width="15.625" customWidth="1"/>
-    <col min="10" max="10" width="15.125" customWidth="1"/>
-    <col min="11" max="11" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
+    <col min="4" max="4" width="33.75" style="3" customWidth="1"/>
+    <col min="5" max="5" width="114.025" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.625" customWidth="1"/>
+    <col min="7" max="7" width="15.125" customWidth="1"/>
+    <col min="8" max="8" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="16.5" spans="1:8">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" ht="16.5" spans="1:8">
+      <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="B2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="E2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" ht="16.5" spans="1:8">
+      <c r="A3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="C3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="D3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="1"/>
-    </row>
-    <row r="3" spans="1:12" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="G3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" ht="16.5" spans="1:8">
+      <c r="A4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:8">
+      <c r="A5" s="4">
+        <v>1001</v>
+      </c>
+      <c r="B5" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="F5" s="4">
+        <v>2000</v>
+      </c>
+      <c r="G5" s="4">
+        <v>999999</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="1" t="s">
+    </row>
+    <row r="6" ht="16.5" spans="1:8">
+      <c r="A6" s="4">
+        <v>1002</v>
+      </c>
+      <c r="B6" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C6" s="4">
+        <v>2</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="E6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G6" s="4">
+        <v>2000</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="1" t="s">
+    </row>
+    <row r="7" ht="16.5" spans="1:8">
+      <c r="A7" s="4">
+        <v>1003</v>
+      </c>
+      <c r="B7" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C7" s="4">
+        <v>3</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:12" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
+      <c r="E7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="4">
+        <v>500</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1000</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:8">
+      <c r="A8" s="4">
+        <v>1004</v>
+      </c>
+      <c r="B8" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C8" s="4">
+        <v>4</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="4">
+        <v>-500</v>
+      </c>
+      <c r="G8" s="4">
+        <v>500</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:8">
+      <c r="A9" s="4">
+        <v>1005</v>
+      </c>
+      <c r="B9" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C9" s="4">
+        <v>5</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="G9" s="4">
+        <v>-500</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:8">
+      <c r="A10" s="4">
+        <v>1006</v>
+      </c>
+      <c r="B10" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C10" s="4">
+        <v>6</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="G10" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:8">
+      <c r="A11" s="4">
+        <v>1007</v>
+      </c>
+      <c r="B11" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C11" s="4">
+        <v>7</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="4">
+        <v>-999999</v>
+      </c>
+      <c r="G11" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A12" s="4">
+        <v>7001</v>
+      </c>
+      <c r="B12" s="7">
+        <v>100700</v>
+      </c>
+      <c r="C12" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="D12" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="7">
+        <v>2000</v>
+      </c>
+      <c r="G12" s="7">
+        <v>999999</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A13" s="4">
+        <v>7002</v>
+      </c>
+      <c r="B13" s="7">
+        <v>100700</v>
+      </c>
+      <c r="C13" s="7">
+        <v>2</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="7">
+        <v>1000</v>
+      </c>
+      <c r="G13" s="7">
+        <v>2000</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A14" s="4">
+        <v>7003</v>
+      </c>
+      <c r="B14" s="7">
+        <v>100700</v>
+      </c>
+      <c r="C14" s="7">
+        <v>3</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="7">
+        <v>500</v>
+      </c>
+      <c r="G14" s="7">
+        <v>1000</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A15" s="4">
+        <v>7004</v>
+      </c>
+      <c r="B15" s="7">
+        <v>100700</v>
+      </c>
+      <c r="C15" s="7">
+        <v>4</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="7">
+        <v>-500</v>
+      </c>
+      <c r="G15" s="7">
+        <v>500</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A16" s="4">
+        <v>7005</v>
+      </c>
+      <c r="B16" s="7">
+        <v>100700</v>
+      </c>
+      <c r="C16" s="7">
+        <v>5</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="7">
+        <v>-1000</v>
+      </c>
+      <c r="G16" s="7">
+        <v>-500</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A17" s="4">
+        <v>7006</v>
+      </c>
+      <c r="B17" s="7">
+        <v>100700</v>
+      </c>
+      <c r="C17" s="7">
+        <v>6</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="7">
+        <v>-2000</v>
+      </c>
+      <c r="G17" s="7">
+        <v>-1000</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A18" s="4">
+        <v>7007</v>
+      </c>
+      <c r="B18" s="7">
+        <v>100700</v>
+      </c>
+      <c r="C18" s="7">
+        <v>7</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="7">
+        <v>-999999</v>
+      </c>
+      <c r="G18" s="7">
+        <v>-2000</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A19" s="4">
+        <v>14001</v>
+      </c>
+      <c r="B19" s="9">
+        <v>101400</v>
+      </c>
+      <c r="C19" s="9">
         <v>1</v>
       </c>
-      <c r="D5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="D19" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19" s="9">
+        <v>2000</v>
+      </c>
+      <c r="G19" s="9">
+        <v>999999</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A20" s="4">
+        <v>14002</v>
+      </c>
+      <c r="B20" s="9">
+        <v>101400</v>
+      </c>
+      <c r="C20" s="9">
+        <v>2</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20" s="9">
+        <v>1000</v>
+      </c>
+      <c r="G20" s="9">
+        <v>2000</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A21" s="4">
+        <v>14003</v>
+      </c>
+      <c r="B21" s="9">
+        <v>101400</v>
+      </c>
+      <c r="C21" s="9">
+        <v>3</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="9">
+        <v>500</v>
+      </c>
+      <c r="G21" s="9">
+        <v>1000</v>
+      </c>
+      <c r="H21" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1">
-        <v>2000</v>
-      </c>
-      <c r="J5" s="1">
-        <v>999999</v>
-      </c>
-      <c r="K5" s="1" t="s">
+    </row>
+    <row r="22" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A22" s="4">
+        <v>14004</v>
+      </c>
+      <c r="B22" s="9">
+        <v>101400</v>
+      </c>
+      <c r="C22" s="9">
+        <v>4</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="9">
+        <v>-500</v>
+      </c>
+      <c r="G22" s="9">
+        <v>500</v>
+      </c>
+      <c r="H22" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="L5">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C6" s="1">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1000</v>
-      </c>
-      <c r="J6" s="1">
-        <v>2000</v>
-      </c>
-      <c r="K6" s="1" t="s">
+    </row>
+    <row r="23" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A23" s="4">
+        <v>14005</v>
+      </c>
+      <c r="B23" s="9">
+        <v>101400</v>
+      </c>
+      <c r="C23" s="9">
+        <v>5</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" s="9">
+        <v>-1000</v>
+      </c>
+      <c r="G23" s="9">
+        <v>-500</v>
+      </c>
+      <c r="H23" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="L6">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C7" s="1">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="1" t="s">
+    </row>
+    <row r="24" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A24" s="4">
+        <v>14006</v>
+      </c>
+      <c r="B24" s="9">
+        <v>101400</v>
+      </c>
+      <c r="C24" s="9">
+        <v>6</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" s="9">
+        <v>-2000</v>
+      </c>
+      <c r="G24" s="9">
+        <v>-1000</v>
+      </c>
+      <c r="H24" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>500</v>
-      </c>
-      <c r="J7" s="1">
-        <v>1000</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C8" s="1">
-        <v>4</v>
-      </c>
-      <c r="D8" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1" t="s">
+    </row>
+    <row r="25" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A25" s="4">
+        <v>14007</v>
+      </c>
+      <c r="B25" s="9">
+        <v>101400</v>
+      </c>
+      <c r="C25" s="9">
+        <v>7</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" s="9">
+        <v>-999999</v>
+      </c>
+      <c r="G25" s="9">
+        <v>-2000</v>
+      </c>
+      <c r="H25" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1">
-        <v>-500</v>
-      </c>
-      <c r="J8" s="1">
-        <v>500</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C9" s="1">
-        <v>5</v>
-      </c>
-      <c r="D9" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1">
-        <v>-1000</v>
-      </c>
-      <c r="J9" s="1">
-        <v>-500</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L9">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>6</v>
-      </c>
-      <c r="B10" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C10" s="1">
-        <v>6</v>
-      </c>
-      <c r="D10" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
-        <v>-2000</v>
-      </c>
-      <c r="J10" s="1">
-        <v>-1000</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L10">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C11" s="1">
-        <v>7</v>
-      </c>
-      <c r="D11" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1">
-        <v>-999999</v>
-      </c>
-      <c r="J11" s="1">
-        <v>-2000</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L11">
-        <v>50</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -1,39 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5CCC319-D414-45D9-8378-D2C089D66C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author>chuge</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -57,7 +50,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="1">
+    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -69,7 +62,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -82,7 +75,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -95,7 +88,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -120,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="37">
   <si>
     <t>id</t>
   </si>
@@ -228,19 +221,17 @@
   </si>
   <si>
     <t>1,0&amp;1-46500|1&amp;10-8000|10&amp;20-10000|20&amp;30-9000|30&amp;40-7500|40&amp;50-6000|50&amp;60-4200|60&amp;70-3000|70&amp;80-1800|80&amp;90-1200|90&amp;100-1000|100&amp;120-800|120&amp;140-400|140&amp;160-150|160&amp;180-150|180&amp;200-100|200&amp;300-100|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-46500|1&amp;10-8000|10&amp;20-10000|20&amp;30-9000|30&amp;40-7500|40&amp;50-6000|50&amp;60-4200|60&amp;70-3000|70&amp;80-1800|80&amp;90-1200|90&amp;100-1000|100&amp;120-800|120&amp;140-400|140&amp;160-150|160&amp;180-150|180&amp;200-100|200&amp;300-100|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-100|50&amp;60-400|60&amp;70-500|70&amp;80-500|80&amp;90-500|90&amp;100-500|100&amp;120-500|120&amp;140-1000|140&amp;160-4000|160&amp;180-5000|180&amp;200-5500|200&amp;300-30000|300&amp;500-33400|500&amp;800-12500|800&amp;1000-3500|1000&amp;1500-2000|1500&amp;2000-100|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-200|140&amp;160-200|160&amp;180-1000|180&amp;200-1000|200&amp;300-15000|300&amp;500-45000|500&amp;800-30000|800&amp;1000-5000|1000&amp;1500-2500|1500&amp;2000-100|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;4,0&amp;1-62000|1&amp;10-10000|10&amp;20-12500|20&amp;30-8100|30&amp;40-4000|40&amp;50-2000|50&amp;60-800|60&amp;70-400|70&amp;80-100|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-900|60&amp;70-4000|70&amp;80-8000|80&amp;90-10000|90&amp;100-12000|100&amp;120-24000|120&amp;140-16000|140&amp;160-11000|160&amp;180-7000|180&amp;200-4000|200&amp;300-3000|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;6,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-50|50&amp;60-100|60&amp;70-200|70&amp;80-200|80&amp;90-500|90&amp;100-500|100&amp;120-2000|120&amp;140-2700|140&amp;160-3500|160&amp;180-4000|180&amp;200-4000|200&amp;300-30000|300&amp;500-33000|500&amp;800-14000|800&amp;1000-3000|1000&amp;1500-2000|1500&amp;2000-200|2000&amp;3000-50|3000&amp;4000-0|4000&amp;5000-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-32000|300&amp;500-58000|500&amp;800-10000|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -255,147 +246,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -403,8 +257,21 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -413,204 +280,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -618,254 +299,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -875,7 +314,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -893,63 +332,22 @@
     <xf numFmtId="3" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 73" xfId="49"/>
+    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1207,26 +605,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
     <col min="2" max="2" width="15.25" customWidth="1"/>
     <col min="3" max="3" width="10.875" customWidth="1"/>
     <col min="4" max="4" width="33.75" style="3" customWidth="1"/>
-    <col min="5" max="5" width="114.025" style="3" customWidth="1"/>
+    <col min="5" max="5" width="114" style="3" customWidth="1"/>
     <col min="6" max="6" width="15.625" customWidth="1"/>
     <col min="7" max="7" width="15.125" customWidth="1"/>
     <col min="8" max="8" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:8">
+    <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1252,7 +650,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:8">
+    <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -1276,7 +674,7 @@
       </c>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" ht="16.5" spans="1:8">
+    <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1300,7 +698,7 @@
       </c>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" ht="16.5" spans="1:8">
+    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="4"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -1310,7 +708,7 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" ht="16.5" spans="1:8">
+    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>1001</v>
       </c>
@@ -1323,8 +721,8 @@
       <c r="D5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>18</v>
+      <c r="E5" s="11" t="s">
+        <v>36</v>
       </c>
       <c r="F5" s="4">
         <v>2000</v>
@@ -1336,7 +734,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:8">
+    <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>1002</v>
       </c>
@@ -1362,7 +760,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:8">
+    <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>1003</v>
       </c>
@@ -1388,7 +786,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:8">
+    <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>1004</v>
       </c>
@@ -1414,7 +812,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:8">
+    <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>1005</v>
       </c>
@@ -1440,7 +838,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" ht="16.5" spans="1:8">
+    <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>1006</v>
       </c>
@@ -1466,7 +864,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" ht="16.5" spans="1:8">
+    <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>1007</v>
       </c>
@@ -1492,7 +890,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:8">
+    <row r="12" spans="1:8" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>7001</v>
       </c>
@@ -1518,7 +916,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:8">
+    <row r="13" spans="1:8" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>7002</v>
       </c>
@@ -1544,7 +942,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="16.5" spans="1:8">
+    <row r="14" spans="1:8" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>7003</v>
       </c>
@@ -1570,7 +968,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:8">
+    <row r="15" spans="1:8" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>7004</v>
       </c>
@@ -1596,7 +994,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:8">
+    <row r="16" spans="1:8" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>7005</v>
       </c>
@@ -1622,7 +1020,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="16.5" spans="1:8">
+    <row r="17" spans="1:8" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>7006</v>
       </c>
@@ -1648,7 +1046,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:8">
+    <row r="18" spans="1:8" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>7007</v>
       </c>
@@ -1674,7 +1072,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:8">
+    <row r="19" spans="1:8" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>14001</v>
       </c>
@@ -1700,7 +1098,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" ht="16.5" spans="1:8">
+    <row r="20" spans="1:8" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>14002</v>
       </c>
@@ -1726,7 +1124,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" ht="16.5" spans="1:8">
+    <row r="21" spans="1:8" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>14003</v>
       </c>
@@ -1752,7 +1150,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" ht="16.5" spans="1:8">
+    <row r="22" spans="1:8" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>14004</v>
       </c>
@@ -1778,7 +1176,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" ht="16.5" spans="1:8">
+    <row r="23" spans="1:8" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>14005</v>
       </c>
@@ -1804,7 +1202,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" ht="16.5" spans="1:8">
+    <row r="24" spans="1:8" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>14006</v>
       </c>
@@ -1830,7 +1228,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" ht="16.5" spans="1:8">
+    <row r="25" spans="1:8" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>14007</v>
       </c>
@@ -1857,8 +1255,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -1,32 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5CCC319-D414-45D9-8378-D2C089D66C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author>chuge</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -50,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="E1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -62,7 +69,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -75,7 +82,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -88,7 +95,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -113,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="28">
   <si>
     <t>id</t>
   </si>
@@ -166,72 +173,50 @@
     <t>enterLimitMax</t>
   </si>
   <si>
-    <t>1_6700|2_800|3_400|4_800|5_400</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-46500|1&amp;10-8000|10&amp;20-10000|20&amp;30-9000|30&amp;40-7500|40&amp;50-6000|50&amp;60-4200|60&amp;70-3000|70&amp;80-1800|80&amp;90-1200|90&amp;100-1000|100&amp;120-800|120&amp;140-400|140&amp;160-150|160&amp;180-150|180&amp;200-100|200&amp;300-100|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-100|50&amp;60-400|60&amp;70-500|70&amp;80-500|80&amp;90-500|90&amp;100-500|100&amp;120-500|120&amp;140-1000|140&amp;160-4000|160&amp;180-5000|180&amp;200-5500|200&amp;300-30000|300&amp;500-33400|500&amp;800-12500|800&amp;1000-3500|1000&amp;1500-2000|1500&amp;2000-100|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-200|140&amp;160-200|160&amp;180-1000|180&amp;200-1000|200&amp;300-15000|300&amp;500-45000|500&amp;800-30000|800&amp;1000-5000|1000&amp;1500-2500|1500&amp;2000-100|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;4,0&amp;1-62000|1&amp;10-10000|10&amp;20-12500|20&amp;30-8100|30&amp;40-4000|40&amp;50-2000|50&amp;60-800|60&amp;70-400|70&amp;80-100|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-900|60&amp;70-4000|70&amp;80-8000|80&amp;90-10000|90&amp;100-12000|100&amp;120-24000|120&amp;140-16000|140&amp;160-11000|160&amp;180-7000|180&amp;200-4000|200&amp;300-3000|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;6,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-50|50&amp;60-100|60&amp;70-200|70&amp;80-200|80&amp;90-500|90&amp;100-500|100&amp;120-2000|120&amp;140-2700|140&amp;160-3500|160&amp;180-4000|180&amp;200-4000|200&amp;300-30000|300&amp;500-33000|500&amp;800-14000|800&amp;1000-3000|1000&amp;1500-2000|1500&amp;2000-200|2000&amp;3000-50|3000&amp;4000-0|4000&amp;5000-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-32000|300&amp;500-58000|500&amp;800-10000|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0</t>
+    <t>1_6700|2_1000|3_500|4_800|5_400</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-63600|1&amp;10-8000|10&amp;20-10000|20&amp;30-4000|30&amp;40-4000|40&amp;50-2000|50&amp;60-1500|60&amp;70-1500|70&amp;80-1000|80&amp;90-800|90&amp;100-800|100&amp;120-800|120&amp;140-800|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-500|100&amp;120-500|120&amp;140-2000|140&amp;160-5000|160&amp;180-5000|180&amp;200-5500|200&amp;300-32500|300&amp;500-45000|500&amp;800-4000|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-16500|300&amp;500-45000|500&amp;800-30900|800&amp;1000-5000|1000&amp;1500-2500|1500&amp;2000-100|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;99999999-0;4,0&amp;1-58000|1&amp;10-10000|10&amp;20-12200|20&amp;30-6000|30&amp;40-6000|40&amp;50-1500|50&amp;60-1000|60&amp;70-1000|70&amp;80-800|80&amp;90-500|90&amp;100-500|100&amp;120-500|120&amp;140-500|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-20000|60&amp;70-21300|70&amp;80-20000|80&amp;90-12800|90&amp;100-8000|100&amp;120-8000|120&amp;140-4000|140&amp;160-2000|160&amp;180-1200|180&amp;200-1200|200&amp;300-1200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;99999999-0;6,0&amp;1-2000|1&amp;10-0|10&amp;20-200|20&amp;30-600|30&amp;40-600|40&amp;50-600|50&amp;60-600|60&amp;70-1000|70&amp;80-1000|80&amp;90-1000|90&amp;100-1000|100&amp;120-3500|120&amp;140-3500|140&amp;160-3500|160&amp;180-3500|180&amp;200-4000|200&amp;300-18000|300&amp;500-24000|500&amp;800-18000|800&amp;1000-5200|1000&amp;1500-5200|1500&amp;2000-2200|2000&amp;3000-600|3000&amp;4000-200|4000&amp;5000-0|5000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-8000|300&amp;500-58000|500&amp;800-34000|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;99999999-0</t>
   </si>
   <si>
     <t>放水池+3</t>
   </si>
   <si>
-    <t>1_7100|2_800|3_400|4_800|5_400</t>
-  </si>
-  <si>
     <t>放水池+2</t>
   </si>
   <si>
-    <t>1_7500|2_800|3_400|4_800|5_400</t>
-  </si>
-  <si>
     <t>放水池+1</t>
   </si>
   <si>
-    <t>1_7900|2_800|3_400|4_800|5_400</t>
-  </si>
-  <si>
     <t>标准池</t>
   </si>
   <si>
-    <t>1_8300|2_800|3_400|4_800|5_400</t>
-  </si>
-  <si>
     <t>吸水池-1</t>
   </si>
   <si>
-    <t>1_8700|2_800|3_400|4_800|5_400</t>
-  </si>
-  <si>
     <t>吸水池-2</t>
   </si>
   <si>
-    <t>1_9100|2_800|3_400|4_800|5_400</t>
-  </si>
-  <si>
     <t>吸水池-3</t>
   </si>
   <si>
     <t>1_9550|2_450</t>
   </si>
   <si>
-    <t>1,0&amp;1-46500|1&amp;10-8000|10&amp;20-10000|20&amp;30-9000|30&amp;40-7500|40&amp;50-6000|50&amp;60-4200|60&amp;70-3000|70&amp;80-1800|80&amp;90-1200|90&amp;100-1000|100&amp;120-800|120&amp;140-400|140&amp;160-150|160&amp;180-150|180&amp;200-100|200&amp;300-100|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-100|50&amp;60-400|60&amp;70-500|70&amp;80-500|80&amp;90-500|90&amp;100-500|100&amp;120-500|120&amp;140-1000|140&amp;160-4000|160&amp;180-5000|180&amp;200-5500|200&amp;300-30000|300&amp;500-33400|500&amp;800-12500|800&amp;1000-3500|1000&amp;1500-2000|1500&amp;2000-100|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0</t>
-  </si>
-  <si>
     <t>1_10000</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-46500|1&amp;10-8000|10&amp;20-10000|20&amp;30-9000|30&amp;40-7500|40&amp;50-6000|50&amp;60-4200|60&amp;70-3000|70&amp;80-1800|80&amp;90-1200|90&amp;100-1000|100&amp;120-800|120&amp;140-400|140&amp;160-150|160&amp;180-150|180&amp;200-100|200&amp;300-100|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-46500|1&amp;10-8000|10&amp;20-10000|20&amp;30-9000|30&amp;40-7500|40&amp;50-6000|50&amp;60-4200|60&amp;70-3000|70&amp;80-1800|80&amp;90-1200|90&amp;100-1000|100&amp;120-800|120&amp;140-400|140&amp;160-150|160&amp;180-150|180&amp;200-100|200&amp;300-100|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-100|50&amp;60-400|60&amp;70-500|70&amp;80-500|80&amp;90-500|90&amp;100-500|100&amp;120-500|120&amp;140-1000|140&amp;160-4000|160&amp;180-5000|180&amp;200-5500|200&amp;300-30000|300&amp;500-33400|500&amp;800-12500|800&amp;1000-3500|1000&amp;1500-2000|1500&amp;2000-100|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-200|140&amp;160-200|160&amp;180-1000|180&amp;200-1000|200&amp;300-15000|300&amp;500-45000|500&amp;800-30000|800&amp;1000-5000|1000&amp;1500-2500|1500&amp;2000-100|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;4,0&amp;1-62000|1&amp;10-10000|10&amp;20-12500|20&amp;30-8100|30&amp;40-4000|40&amp;50-2000|50&amp;60-800|60&amp;70-400|70&amp;80-100|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-900|60&amp;70-4000|70&amp;80-8000|80&amp;90-10000|90&amp;100-12000|100&amp;120-24000|120&amp;140-16000|140&amp;160-11000|160&amp;180-7000|180&amp;200-4000|200&amp;300-3000|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0;6,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-50|50&amp;60-100|60&amp;70-200|70&amp;80-200|80&amp;90-500|90&amp;100-500|100&amp;120-2000|120&amp;140-2700|140&amp;160-3500|160&amp;180-4000|180&amp;200-4000|200&amp;300-30000|300&amp;500-33000|500&amp;800-14000|800&amp;1000-3000|1000&amp;1500-2000|1500&amp;2000-200|2000&amp;3000-50|3000&amp;4000-0|4000&amp;5000-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-32000|300&amp;500-58000|500&amp;800-10000|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,10 +231,147 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -257,21 +379,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -280,18 +389,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -299,12 +594,254 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -314,7 +851,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -332,22 +869,63 @@
     <xf numFmtId="3" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 73" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -605,26 +1183,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
     <col min="2" max="2" width="15.25" customWidth="1"/>
     <col min="3" max="3" width="10.875" customWidth="1"/>
     <col min="4" max="4" width="33.75" style="3" customWidth="1"/>
-    <col min="5" max="5" width="114" style="3" customWidth="1"/>
+    <col min="5" max="5" width="114.025" style="3" customWidth="1"/>
     <col min="6" max="6" width="15.625" customWidth="1"/>
     <col min="7" max="7" width="15.125" customWidth="1"/>
     <col min="8" max="8" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" ht="16.5" spans="1:8">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -650,7 +1228,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="2" ht="16.5" spans="1:8">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -674,7 +1252,7 @@
       </c>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="3" ht="16.5" spans="1:8">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
@@ -698,7 +1276,7 @@
       </c>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="4" ht="16.5" spans="1:8">
       <c r="A4" s="4"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -708,7 +1286,7 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="5" ht="16.5" spans="1:8">
       <c r="A5" s="4">
         <v>1001</v>
       </c>
@@ -721,8 +1299,8 @@
       <c r="D5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="11" t="s">
-        <v>36</v>
+      <c r="E5" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="F5" s="4">
         <v>2000</v>
@@ -734,7 +1312,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="6" ht="16.5" spans="1:8">
       <c r="A6" s="4">
         <v>1002</v>
       </c>
@@ -745,7 +1323,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>18</v>
@@ -757,10 +1335,10 @@
         <v>2000</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:8">
       <c r="A7" s="4">
         <v>1003</v>
       </c>
@@ -771,7 +1349,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>18</v>
@@ -783,10 +1361,10 @@
         <v>1000</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:8">
       <c r="A8" s="4">
         <v>1004</v>
       </c>
@@ -797,7 +1375,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>18</v>
@@ -809,10 +1387,10 @@
         <v>500</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:8">
       <c r="A9" s="4">
         <v>1005</v>
       </c>
@@ -823,7 +1401,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>18</v>
@@ -835,10 +1413,10 @@
         <v>-500</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:8">
       <c r="A10" s="4">
         <v>1006</v>
       </c>
@@ -849,7 +1427,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>18</v>
@@ -861,10 +1439,10 @@
         <v>-1000</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:8">
       <c r="A11" s="4">
         <v>1007</v>
       </c>
@@ -875,7 +1453,7 @@
         <v>7</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>18</v>
@@ -887,10 +1465,10 @@
         <v>-2000</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A12" s="4">
         <v>7001</v>
       </c>
@@ -901,10 +1479,10 @@
         <v>1</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F12" s="7">
         <v>2000</v>
@@ -916,7 +1494,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:8" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A13" s="4">
         <v>7002</v>
       </c>
@@ -927,10 +1505,10 @@
         <v>2</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F13" s="7">
         <v>1000</v>
@@ -939,10 +1517,10 @@
         <v>2000</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A14" s="4">
         <v>7003</v>
       </c>
@@ -953,10 +1531,10 @@
         <v>3</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F14" s="7">
         <v>500</v>
@@ -965,10 +1543,10 @@
         <v>1000</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A15" s="4">
         <v>7004</v>
       </c>
@@ -979,10 +1557,10 @@
         <v>4</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F15" s="7">
         <v>-500</v>
@@ -991,10 +1569,10 @@
         <v>500</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A16" s="4">
         <v>7005</v>
       </c>
@@ -1005,10 +1583,10 @@
         <v>5</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F16" s="7">
         <v>-1000</v>
@@ -1017,10 +1595,10 @@
         <v>-500</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A17" s="4">
         <v>7006</v>
       </c>
@@ -1031,10 +1609,10 @@
         <v>6</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F17" s="7">
         <v>-2000</v>
@@ -1043,10 +1621,10 @@
         <v>-1000</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A18" s="4">
         <v>7007</v>
       </c>
@@ -1057,10 +1635,10 @@
         <v>7</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F18" s="7">
         <v>-999999</v>
@@ -1069,10 +1647,10 @@
         <v>-2000</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:8">
       <c r="A19" s="4">
         <v>14001</v>
       </c>
@@ -1083,10 +1661,10 @@
         <v>1</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F19" s="9">
         <v>2000</v>
@@ -1098,7 +1676,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:8" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="20" s="2" customFormat="1" ht="16.5" spans="1:8">
       <c r="A20" s="4">
         <v>14002</v>
       </c>
@@ -1109,10 +1687,10 @@
         <v>2</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F20" s="9">
         <v>1000</v>
@@ -1121,10 +1699,10 @@
         <v>2000</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="16.5" spans="1:8">
       <c r="A21" s="4">
         <v>14003</v>
       </c>
@@ -1135,10 +1713,10 @@
         <v>3</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F21" s="9">
         <v>500</v>
@@ -1147,10 +1725,10 @@
         <v>1000</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="16.5" spans="1:8">
       <c r="A22" s="4">
         <v>14004</v>
       </c>
@@ -1161,10 +1739,10 @@
         <v>4</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F22" s="9">
         <v>-500</v>
@@ -1173,10 +1751,10 @@
         <v>500</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" ht="16.5" spans="1:8">
       <c r="A23" s="4">
         <v>14005</v>
       </c>
@@ -1187,10 +1765,10 @@
         <v>5</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F23" s="9">
         <v>-1000</v>
@@ -1199,10 +1777,10 @@
         <v>-500</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" ht="16.5" spans="1:8">
       <c r="A24" s="4">
         <v>14006</v>
       </c>
@@ -1213,10 +1791,10 @@
         <v>6</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F24" s="9">
         <v>-2000</v>
@@ -1225,10 +1803,10 @@
         <v>-1000</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" ht="16.5" spans="1:8">
       <c r="A25" s="4">
         <v>14007</v>
       </c>
@@ -1239,10 +1817,10 @@
         <v>7</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F25" s="9">
         <v>-999999</v>
@@ -1251,12 +1829,12 @@
         <v>-2000</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="29">
   <si>
     <t>id</t>
   </si>
@@ -198,6 +198,9 @@
   </si>
   <si>
     <t>吸水池-3</t>
+  </si>
+  <si>
+    <t>1_6700|2_1000|3_500</t>
   </si>
   <si>
     <t>1_9550|2_450</t>
@@ -380,12 +383,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -716,7 +725,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -740,16 +749,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -758,93 +767,94 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -866,7 +876,13 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1189,646 +1205,1010 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
     <col min="2" max="2" width="15.25" customWidth="1"/>
     <col min="3" max="3" width="10.875" customWidth="1"/>
-    <col min="4" max="4" width="33.75" style="3" customWidth="1"/>
-    <col min="5" max="5" width="114.025" style="3" customWidth="1"/>
+    <col min="4" max="4" width="33.75" style="4" customWidth="1"/>
+    <col min="5" max="5" width="114.025" style="4" customWidth="1"/>
     <col min="6" max="6" width="15.625" customWidth="1"/>
     <col min="7" max="7" width="15.125" customWidth="1"/>
     <col min="8" max="8" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:8">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:8">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="4"/>
+      <c r="H2" s="5"/>
     </row>
     <row r="3" ht="16.5" spans="1:8">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="4"/>
+      <c r="H3" s="5"/>
     </row>
     <row r="4" ht="16.5" spans="1:8">
-      <c r="A4" s="4"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
     </row>
     <row r="5" ht="16.5" spans="1:8">
-      <c r="A5" s="4">
+      <c r="A5" s="5">
         <v>1001</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="5">
         <v>100100</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="5">
         <v>1</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="4">
+      <c r="E5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5">
         <v>2000</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="5">
         <v>999999</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
-      <c r="A6" s="4">
+      <c r="A6" s="5">
         <v>1002</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="5">
         <v>100100</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="5">
         <v>2</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="4">
+      <c r="E6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="5">
         <v>1000</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="5">
         <v>2000</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
-      <c r="A7" s="4">
+      <c r="A7" s="5">
         <v>1003</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="5">
         <v>100100</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="5">
         <v>3</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="4">
+      <c r="E7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="5">
         <v>500</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="5">
         <v>1000</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
-      <c r="A8" s="4">
+      <c r="A8" s="5">
         <v>1004</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="5">
         <v>100100</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="5">
         <v>4</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="4">
+      <c r="E8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="5">
         <v>-500</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="5">
         <v>500</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
-      <c r="A9" s="4">
+      <c r="A9" s="5">
         <v>1005</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="5">
         <v>100100</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="5">
         <v>5</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="4">
+      <c r="E9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="5">
         <v>-1000</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="5">
         <v>-500</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
-      <c r="A10" s="4">
+      <c r="A10" s="5">
         <v>1006</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="5">
         <v>100100</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="5">
         <v>6</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="4">
+      <c r="E10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="5">
         <v>-2000</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="5">
         <v>-1000</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
-      <c r="A11" s="4">
+      <c r="A11" s="5">
         <v>1007</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="5">
         <v>100100</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="5">
         <v>7</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="4">
+      <c r="E11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="5">
         <v>-999999</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="5">
         <v>-2000</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="16.5" spans="1:8">
-      <c r="A12" s="4">
+      <c r="A12" s="8">
+        <v>3001</v>
+      </c>
+      <c r="B12" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C12" s="8">
+        <v>1</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="8">
+        <v>2000</v>
+      </c>
+      <c r="G12" s="8">
+        <v>999999</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A13" s="8">
+        <v>3002</v>
+      </c>
+      <c r="B13" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C13" s="8">
+        <v>2</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="8">
+        <v>1000</v>
+      </c>
+      <c r="G13" s="8">
+        <v>2000</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A14" s="8">
+        <v>3003</v>
+      </c>
+      <c r="B14" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C14" s="8">
+        <v>3</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="8">
+        <v>500</v>
+      </c>
+      <c r="G14" s="8">
+        <v>1000</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A15" s="8">
+        <v>3004</v>
+      </c>
+      <c r="B15" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C15" s="8">
+        <v>4</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="8">
+        <v>-500</v>
+      </c>
+      <c r="G15" s="8">
+        <v>500</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A16" s="8">
+        <v>3005</v>
+      </c>
+      <c r="B16" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C16" s="8">
+        <v>5</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="8">
+        <v>-1000</v>
+      </c>
+      <c r="G16" s="8">
+        <v>-500</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A17" s="8">
+        <v>3006</v>
+      </c>
+      <c r="B17" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C17" s="8">
+        <v>6</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="8">
+        <v>-2000</v>
+      </c>
+      <c r="G17" s="8">
+        <v>-1000</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A18" s="8">
+        <v>3007</v>
+      </c>
+      <c r="B18" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C18" s="8">
+        <v>7</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="8">
+        <v>-999999</v>
+      </c>
+      <c r="G18" s="8">
+        <v>-2000</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A19" s="5">
         <v>7001</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B19" s="10">
         <v>100700</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C19" s="10">
         <v>1</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D19" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="10">
+        <v>2000</v>
+      </c>
+      <c r="G19" s="10">
+        <v>999999</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A20" s="5">
+        <v>7002</v>
+      </c>
+      <c r="B20" s="10">
+        <v>100700</v>
+      </c>
+      <c r="C20" s="10">
+        <v>2</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G20" s="10">
+        <v>2000</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A21" s="5">
+        <v>7003</v>
+      </c>
+      <c r="B21" s="10">
+        <v>100700</v>
+      </c>
+      <c r="C21" s="10">
+        <v>3</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="10">
+        <v>500</v>
+      </c>
+      <c r="G21" s="10">
+        <v>1000</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A22" s="5">
+        <v>7004</v>
+      </c>
+      <c r="B22" s="10">
+        <v>100700</v>
+      </c>
+      <c r="C22" s="10">
+        <v>4</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="10">
+        <v>-500</v>
+      </c>
+      <c r="G22" s="10">
+        <v>500</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A23" s="5">
+        <v>7005</v>
+      </c>
+      <c r="B23" s="10">
+        <v>100700</v>
+      </c>
+      <c r="C23" s="10">
+        <v>5</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="10">
+        <v>-1000</v>
+      </c>
+      <c r="G23" s="10">
+        <v>-500</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A24" s="5">
+        <v>7006</v>
+      </c>
+      <c r="B24" s="10">
+        <v>100700</v>
+      </c>
+      <c r="C24" s="10">
+        <v>6</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="10">
+        <v>-2000</v>
+      </c>
+      <c r="G24" s="10">
+        <v>-1000</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A25" s="5">
+        <v>7007</v>
+      </c>
+      <c r="B25" s="10">
+        <v>100700</v>
+      </c>
+      <c r="C25" s="10">
+        <v>7</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="10">
+        <v>-999999</v>
+      </c>
+      <c r="G25" s="10">
+        <v>-2000</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A26" s="8">
+        <v>12001</v>
+      </c>
+      <c r="B26" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C26" s="8">
+        <v>1</v>
+      </c>
+      <c r="D26" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="7">
+      <c r="E26" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="8">
         <v>2000</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G26" s="8">
         <v>999999</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H26" s="8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:8">
-      <c r="A13" s="4">
-        <v>7002</v>
-      </c>
-      <c r="B13" s="7">
-        <v>100700</v>
-      </c>
-      <c r="C13" s="7">
+    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A27" s="8">
+        <v>12002</v>
+      </c>
+      <c r="B27" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C27" s="8">
         <v>2</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D27" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="7">
+      <c r="E27" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="8">
         <v>1000</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G27" s="8">
         <v>2000</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H27" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="16.5" spans="1:8">
-      <c r="A14" s="4">
-        <v>7003</v>
-      </c>
-      <c r="B14" s="7">
-        <v>100700</v>
-      </c>
-      <c r="C14" s="7">
+    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A28" s="8">
+        <v>12003</v>
+      </c>
+      <c r="B28" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C28" s="8">
         <v>3</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D28" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="7">
+      <c r="E28" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="8">
         <v>500</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G28" s="8">
         <v>1000</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H28" s="8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:8">
-      <c r="A15" s="4">
-        <v>7004</v>
-      </c>
-      <c r="B15" s="7">
-        <v>100700</v>
-      </c>
-      <c r="C15" s="7">
+    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A29" s="8">
+        <v>12004</v>
+      </c>
+      <c r="B29" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C29" s="8">
         <v>4</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D29" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="7">
+      <c r="E29" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="8">
         <v>-500</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G29" s="8">
         <v>500</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H29" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:8">
-      <c r="A16" s="4">
-        <v>7005</v>
-      </c>
-      <c r="B16" s="7">
-        <v>100700</v>
-      </c>
-      <c r="C16" s="7">
+    <row r="30" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A30" s="8">
+        <v>12005</v>
+      </c>
+      <c r="B30" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C30" s="8">
         <v>5</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D30" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="7">
+      <c r="E30" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" s="8">
         <v>-1000</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G30" s="8">
         <v>-500</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H30" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="16.5" spans="1:8">
-      <c r="A17" s="4">
-        <v>7006</v>
-      </c>
-      <c r="B17" s="7">
-        <v>100700</v>
-      </c>
-      <c r="C17" s="7">
+    <row r="31" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A31" s="8">
+        <v>12006</v>
+      </c>
+      <c r="B31" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C31" s="8">
         <v>6</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D31" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" s="7">
+      <c r="E31" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" s="8">
         <v>-2000</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G31" s="8">
         <v>-1000</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H31" s="8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:8">
-      <c r="A18" s="4">
-        <v>7007</v>
-      </c>
-      <c r="B18" s="7">
-        <v>100700</v>
-      </c>
-      <c r="C18" s="7">
+    <row r="32" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A32" s="8">
+        <v>12007</v>
+      </c>
+      <c r="B32" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C32" s="8">
         <v>7</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D32" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="7">
+      <c r="E32" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="8">
         <v>-999999</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G32" s="8">
         <v>-2000</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H32" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:8">
-      <c r="A19" s="4">
+    <row r="33" s="3" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A33" s="5">
         <v>14001</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B33" s="12">
         <v>101400</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C33" s="12">
         <v>1</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" s="9">
+      <c r="D33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="12">
         <v>2000</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G33" s="12">
         <v>999999</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H33" s="12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" ht="16.5" spans="1:8">
-      <c r="A20" s="4">
+    <row r="34" s="3" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A34" s="5">
         <v>14002</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B34" s="12">
         <v>101400</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C34" s="12">
         <v>2</v>
       </c>
-      <c r="D20" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="9">
+      <c r="D34" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" s="12">
         <v>1000</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G34" s="12">
         <v>2000</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H34" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" ht="16.5" spans="1:8">
-      <c r="A21" s="4">
+    <row r="35" s="3" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A35" s="5">
         <v>14003</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B35" s="12">
         <v>101400</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C35" s="12">
         <v>3</v>
       </c>
-      <c r="D21" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" s="9">
+      <c r="D35" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" s="12">
         <v>500</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G35" s="12">
         <v>1000</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H35" s="12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" ht="16.5" spans="1:8">
-      <c r="A22" s="4">
+    <row r="36" s="3" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A36" s="5">
         <v>14004</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B36" s="12">
         <v>101400</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C36" s="12">
         <v>4</v>
       </c>
-      <c r="D22" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F22" s="9">
+      <c r="D36" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" s="12">
         <v>-500</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G36" s="12">
         <v>500</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H36" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" ht="16.5" spans="1:8">
-      <c r="A23" s="4">
+    <row r="37" s="3" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A37" s="5">
         <v>14005</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B37" s="12">
         <v>101400</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C37" s="12">
         <v>5</v>
       </c>
-      <c r="D23" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F23" s="9">
+      <c r="D37" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" s="12">
         <v>-1000</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G37" s="12">
         <v>-500</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="H37" s="12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" ht="16.5" spans="1:8">
-      <c r="A24" s="4">
+    <row r="38" s="3" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A38" s="5">
         <v>14006</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B38" s="12">
         <v>101400</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C38" s="12">
         <v>6</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F24" s="9">
+      <c r="D38" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" s="12">
         <v>-2000</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G38" s="12">
         <v>-1000</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H38" s="12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" ht="16.5" spans="1:8">
-      <c r="A25" s="4">
+    <row r="39" s="3" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A39" s="5">
         <v>14007</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B39" s="12">
         <v>101400</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C39" s="12">
         <v>7</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" s="9">
+      <c r="D39" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" s="12">
         <v>-999999</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G39" s="12">
         <v>-2000</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H39" s="12" t="s">
         <v>25</v>
       </c>
     </row>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -33,7 +33,7 @@
     <author>chuge</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -57,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="1">
+    <comment ref="F1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -66,19 +66,6 @@
             <charset val="134"/>
           </rPr>
           <t>[{类型1,[{[倍数区间下限,倍数区间上限],权重值},{[倍数区间下限,倍数区间上限],权重值}]}]</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>[区间上限，区间上限],左开右闭，值/10000，公式：水池超出标准线：（当前RTP-标准RTP）/标准RTP，进入对应水池
-标准差池范围:标准线±5%</t>
         </r>
       </text>
     </comment>
@@ -103,6 +90,19 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
+          <t>[区间上限，区间上限],左开右闭，值/10000，公式：水池超出标准线：（当前RTP-标准RTP）/标准RTP，进入对应水池
+标准差池范围:标准线±5%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
           <t xml:space="preserve">一个水池对应一个滚轴模式ID，对应一个RTP值
 1 放水池+3
 2 放水池+2
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="41">
   <si>
     <t>id</t>
   </si>
@@ -173,37 +173,73 @@
     <t>enterLimitMax</t>
   </si>
   <si>
-    <t>1_6700|2_1000|3_500|4_800|5_400</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-63600|1&amp;10-8000|10&amp;20-10000|20&amp;30-4000|30&amp;40-4000|40&amp;50-2000|50&amp;60-1500|60&amp;70-1500|70&amp;80-1000|80&amp;90-800|90&amp;100-800|100&amp;120-800|120&amp;140-800|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-500|100&amp;120-500|120&amp;140-2000|140&amp;160-5000|160&amp;180-5000|180&amp;200-5500|200&amp;300-32500|300&amp;500-45000|500&amp;800-4000|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-16500|300&amp;500-45000|500&amp;800-30900|800&amp;1000-5000|1000&amp;1500-2500|1500&amp;2000-100|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;99999999-0;4,0&amp;1-58000|1&amp;10-10000|10&amp;20-12200|20&amp;30-6000|30&amp;40-6000|40&amp;50-1500|50&amp;60-1000|60&amp;70-1000|70&amp;80-800|80&amp;90-500|90&amp;100-500|100&amp;120-500|120&amp;140-500|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-20000|60&amp;70-21300|70&amp;80-20000|80&amp;90-12800|90&amp;100-8000|100&amp;120-8000|120&amp;140-4000|140&amp;160-2000|160&amp;180-1200|180&amp;200-1200|200&amp;300-1200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;99999999-0;6,0&amp;1-2000|1&amp;10-0|10&amp;20-200|20&amp;30-600|30&amp;40-600|40&amp;50-600|50&amp;60-600|60&amp;70-1000|70&amp;80-1000|80&amp;90-1000|90&amp;100-1000|100&amp;120-3500|120&amp;140-3500|140&amp;160-3500|160&amp;180-3500|180&amp;200-4000|200&amp;300-18000|300&amp;500-24000|500&amp;800-18000|800&amp;1000-5200|1000&amp;1500-5200|1500&amp;2000-2200|2000&amp;3000-600|3000&amp;4000-200|4000&amp;5000-0|5000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-8000|300&amp;500-58000|500&amp;800-34000|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;99999999-0</t>
+    <t>金矿大亨</t>
+  </si>
+  <si>
+    <t>1_8600|2_450|3_250|4_300|5_400</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-60000|1&amp;10-2000|10&amp;20-3000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-3000|80&amp;90-2000|90&amp;100-2000|100&amp;120-1500|120&amp;140-1500|140&amp;160-1200|160&amp;180-1200|180&amp;200-800|200&amp;300-600|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|5000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-200|140&amp;160-500|160&amp;180-600|180&amp;200-700|200&amp;300-2000|300&amp;500-16000|500&amp;800-36000|800&amp;1000-22000|1000&amp;1500-20850|1500&amp;2000-1030|2000&amp;3000-20|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|5000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-4000|500&amp;800-23000|800&amp;1000-23000|1000&amp;1500-35000|1500&amp;2000-12000|2000&amp;3000-2900|3000&amp;4000-100|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|5000&amp;99999999-0;4,0&amp;1-58000|1&amp;10-10000|10&amp;20-12200|20&amp;30-6000|30&amp;40-5700|40&amp;50-2000|50&amp;60-1000|60&amp;70-1000|70&amp;80-800|80&amp;90-500|90&amp;100-500|100&amp;120-500|120&amp;140-500|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-200|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|5000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-1740|90&amp;100-4000|100&amp;120-15000|120&amp;140-20000|140&amp;160-20000|160&amp;180-15200|180&amp;200-12000|200&amp;300-11000|300&amp;500-1000|500&amp;800-50|800&amp;1000-10|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|5000&amp;99999999-0;6,0&amp;1-500|1&amp;10-0|10&amp;20-100|20&amp;30-100|30&amp;40-100|40&amp;50-100|50&amp;60-100|60&amp;70-200|70&amp;80-200|80&amp;90-200|90&amp;100-500|100&amp;120-500|120&amp;140-1000|140&amp;160-1000|160&amp;180-1000|180&amp;200-1000|200&amp;300-8000|300&amp;500-15000|500&amp;800-18000|800&amp;1000-18000|1000&amp;1500-10450|1500&amp;2000-10000|2000&amp;3000-5000|3000&amp;4000-3000|4000&amp;5000-2000|5000&amp;6000-1500|6000&amp;7000-1000|7000&amp;8000-500|8000&amp;9000-500|9000&amp;10000-200|10000&amp;11000-100|11000&amp;12000-50|12000&amp;15000-50|15000&amp;20000-50|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-10000|800&amp;1000-18000|1000&amp;1500-47000|1500&amp;2000-20000|2000&amp;3000-5000|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|5000&amp;99999999-0</t>
   </si>
   <si>
     <t>放水池+3</t>
   </si>
   <si>
+    <t>1_8800|2_400|3_200|4_250|5_350</t>
+  </si>
+  <si>
     <t>放水池+2</t>
   </si>
   <si>
+    <t>1_8900|2_350|3_150|4_250|5_350</t>
+  </si>
+  <si>
     <t>放水池+1</t>
   </si>
   <si>
+    <t>1_9000|2_300|3_100|4_250|5_350</t>
+  </si>
+  <si>
     <t>标准池</t>
   </si>
   <si>
+    <t>1_9100|2_250|3_50|4_250|5_350</t>
+  </si>
+  <si>
     <t>吸水池-1</t>
   </si>
   <si>
+    <t>1_9200|2_200|3_0|4_250|5_350</t>
+  </si>
+  <si>
     <t>吸水池-2</t>
   </si>
   <si>
+    <t>1_9400|2_150|3_0|4_200|5_250</t>
+  </si>
+  <si>
     <t>吸水池-3</t>
   </si>
   <si>
-    <t>1_6700|2_1000|3_500</t>
-  </si>
-  <si>
-    <t>1_9550|2_450</t>
+    <t>超级明星</t>
+  </si>
+  <si>
+    <t>1_9000|2_550|3_450</t>
+  </si>
+  <si>
+    <t>麻将胡了</t>
+  </si>
+  <si>
+    <t>1_9990|2_10</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-85000|1&amp;10-6000|10&amp;20-3400|20&amp;40-900|40&amp;60-800|60&amp;80-200|80&amp;100-200|100&amp;120-200|120&amp;140-200|140&amp;160-200|160&amp;180-200|180&amp;200-200|200&amp;220-200|220&amp;240-200|240&amp;260-200|260&amp;280-200|280&amp;300-200|300&amp;500-200|500&amp;800-200|800&amp;1000-200|1000&amp;1500-200|1500&amp;2000-200|2000&amp;4000-200|4000&amp;6000-200|6000&amp;8000-100|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;220-0|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-100|1500&amp;2000-300|2000&amp;4000-4500|4000&amp;6000-11000|6000&amp;8000-15800|8000&amp;10000-16600|10000&amp;12000-14800|12000&amp;14000-11500|14000&amp;16000-8700|16000&amp;18000-5900|18000&amp;20000-3900|20000&amp;24000-4200|24000&amp;28000-1700|28000&amp;32000-600|32000&amp;36000-200|36000&amp;40000-100|40000&amp;60000-100|60000&amp;80000-0|80000&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>财神</t>
+  </si>
+  <si>
+    <t>埃及艳后</t>
   </si>
   <si>
     <t>1_10000</t>
@@ -870,13 +906,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1205,1011 +1241,1060 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
+  <dimension ref="A1:I39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
-    <col min="2" max="2" width="15.25" customWidth="1"/>
-    <col min="3" max="3" width="10.875" customWidth="1"/>
-    <col min="4" max="4" width="33.75" style="4" customWidth="1"/>
-    <col min="5" max="5" width="114.025" style="4" customWidth="1"/>
-    <col min="6" max="6" width="15.625" customWidth="1"/>
-    <col min="7" max="7" width="15.125" customWidth="1"/>
-    <col min="8" max="8" width="12.5" customWidth="1"/>
+    <col min="2" max="3" width="15.25" customWidth="1"/>
+    <col min="4" max="4" width="10.875" customWidth="1"/>
+    <col min="5" max="5" width="33.75" style="4" customWidth="1"/>
+    <col min="6" max="6" width="114.025" style="4" customWidth="1"/>
+    <col min="7" max="7" width="15.625" customWidth="1"/>
+    <col min="8" max="8" width="15.125" customWidth="1"/>
+    <col min="9" max="9" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:8">
+    <row r="1" ht="16.5" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="6"/>
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:8">
+    <row r="2" ht="16.5" spans="1:9">
       <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F2" s="7" t="s">
         <v>10</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>8</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="3" ht="16.5" spans="1:8">
+      <c r="H2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="5"/>
+    </row>
+    <row r="3" ht="16.5" spans="1:9">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="5"/>
-    </row>
-    <row r="4" ht="16.5" spans="1:8">
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" ht="16.5" spans="1:9">
       <c r="A4" s="5"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
-      <c r="D4" s="7"/>
+      <c r="D4" s="6"/>
       <c r="E4" s="7"/>
-      <c r="F4" s="5"/>
+      <c r="F4" s="7"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
-    </row>
-    <row r="5" ht="16.5" spans="1:8">
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:9">
       <c r="A5" s="5">
         <v>1001</v>
       </c>
       <c r="B5" s="5">
         <v>100100</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="5">
         <v>1</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>17</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="5">
         <v>2000</v>
       </c>
-      <c r="G5" s="5">
+      <c r="H5" s="5">
         <v>999999</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:8">
+      <c r="I5" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:9">
       <c r="A6" s="5">
         <v>1002</v>
       </c>
       <c r="B6" s="5">
         <v>100100</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5">
         <v>2</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>17</v>
-      </c>
       <c r="E6" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="5">
+        <v>21</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="5">
         <v>1000</v>
       </c>
-      <c r="G6" s="5">
+      <c r="H6" s="5">
         <v>2000</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:8">
+      <c r="I6" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:9">
       <c r="A7" s="5">
         <v>1003</v>
       </c>
       <c r="B7" s="5">
         <v>100100</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="5"/>
+      <c r="D7" s="5">
         <v>3</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>17</v>
-      </c>
       <c r="E7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="5">
+        <v>23</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="5">
         <v>500</v>
       </c>
-      <c r="G7" s="5">
+      <c r="H7" s="5">
         <v>1000</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:8">
+      <c r="I7" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:9">
       <c r="A8" s="5">
         <v>1004</v>
       </c>
       <c r="B8" s="5">
         <v>100100</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5">
         <v>4</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>17</v>
-      </c>
       <c r="E8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="5">
+        <v>25</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="5">
         <v>-500</v>
       </c>
-      <c r="G8" s="5">
+      <c r="H8" s="5">
         <v>500</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:8">
+      <c r="I8" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:9">
       <c r="A9" s="5">
         <v>1005</v>
       </c>
       <c r="B9" s="5">
         <v>100100</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5">
         <v>5</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>17</v>
-      </c>
       <c r="E9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="5">
+        <v>27</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="5">
         <v>-1000</v>
       </c>
-      <c r="G9" s="5">
+      <c r="H9" s="5">
         <v>-500</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:8">
+      <c r="I9" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:9">
       <c r="A10" s="5">
         <v>1006</v>
       </c>
       <c r="B10" s="5">
         <v>100100</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5">
         <v>6</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>17</v>
-      </c>
       <c r="E10" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="5">
+        <v>29</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="5">
         <v>-2000</v>
       </c>
-      <c r="G10" s="5">
+      <c r="H10" s="5">
         <v>-1000</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:8">
+      <c r="I10" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:9">
       <c r="A11" s="5">
         <v>1007</v>
       </c>
       <c r="B11" s="5">
         <v>100100</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="5"/>
+      <c r="D11" s="5">
         <v>7</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>17</v>
-      </c>
       <c r="E11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="5">
+        <v>31</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="5">
         <v>-999999</v>
       </c>
-      <c r="G11" s="5">
+      <c r="H11" s="5">
         <v>-2000</v>
       </c>
-      <c r="H11" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I11" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A12" s="8">
         <v>3001</v>
       </c>
       <c r="B12" s="8">
         <v>100300</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="8">
         <v>1</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="8">
+      <c r="E12" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="8">
         <v>2000</v>
       </c>
-      <c r="G12" s="8">
+      <c r="H12" s="8">
         <v>999999</v>
       </c>
-      <c r="H12" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I12" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A13" s="8">
         <v>3002</v>
       </c>
       <c r="B13" s="8">
         <v>100300</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="8"/>
+      <c r="D13" s="8">
         <v>2</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="8">
+      <c r="E13" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="8">
         <v>1000</v>
       </c>
-      <c r="G13" s="8">
+      <c r="H13" s="8">
         <v>2000</v>
       </c>
-      <c r="H13" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I13" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A14" s="8">
         <v>3003</v>
       </c>
       <c r="B14" s="8">
         <v>100300</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="8"/>
+      <c r="D14" s="8">
         <v>3</v>
       </c>
-      <c r="D14" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="8">
+      <c r="E14" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="8">
         <v>500</v>
       </c>
-      <c r="G14" s="8">
+      <c r="H14" s="8">
         <v>1000</v>
       </c>
-      <c r="H14" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I14" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A15" s="8">
         <v>3004</v>
       </c>
       <c r="B15" s="8">
         <v>100300</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="8"/>
+      <c r="D15" s="8">
         <v>4</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="E15" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="8">
+        <v>-500</v>
+      </c>
+      <c r="H15" s="8">
+        <v>500</v>
+      </c>
+      <c r="I15" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="8">
-        <v>-500</v>
-      </c>
-      <c r="G15" s="8">
-        <v>500</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:8">
+    </row>
+    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A16" s="8">
         <v>3005</v>
       </c>
       <c r="B16" s="8">
         <v>100300</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="8"/>
+      <c r="D16" s="8">
         <v>5</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="8">
+      <c r="E16" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="8">
         <v>-1000</v>
       </c>
-      <c r="G16" s="8">
+      <c r="H16" s="8">
         <v>-500</v>
       </c>
-      <c r="H16" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I16" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A17" s="8">
         <v>3006</v>
       </c>
       <c r="B17" s="8">
         <v>100300</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="8"/>
+      <c r="D17" s="8">
         <v>6</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" s="8">
+      <c r="E17" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="8">
         <v>-2000</v>
       </c>
-      <c r="G17" s="8">
+      <c r="H17" s="8">
         <v>-1000</v>
       </c>
-      <c r="H17" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I17" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A18" s="8">
         <v>3007</v>
       </c>
       <c r="B18" s="8">
         <v>100300</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="8"/>
+      <c r="D18" s="8">
         <v>7</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="8">
+      <c r="E18" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="8">
         <v>-999999</v>
       </c>
-      <c r="G18" s="8">
+      <c r="H18" s="8">
         <v>-2000</v>
       </c>
-      <c r="H18" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I18" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:9">
       <c r="A19" s="5">
         <v>7001</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="9">
         <v>100700</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="9">
         <v>1</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" s="10">
+      <c r="E19" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" s="9">
         <v>2000</v>
       </c>
-      <c r="G19" s="10">
+      <c r="H19" s="9">
         <v>999999</v>
       </c>
-      <c r="H19" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I19" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" ht="16.5" spans="1:9">
       <c r="A20" s="5">
         <v>7002</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="9">
         <v>100700</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="9"/>
+      <c r="D20" s="9">
         <v>2</v>
       </c>
-      <c r="D20" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="10">
+      <c r="E20" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="9">
         <v>1000</v>
       </c>
-      <c r="G20" s="10">
+      <c r="H20" s="9">
         <v>2000</v>
       </c>
-      <c r="H20" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I20" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="16.5" spans="1:9">
       <c r="A21" s="5">
         <v>7003</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="9">
         <v>100700</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="9"/>
+      <c r="D21" s="9">
         <v>3</v>
       </c>
-      <c r="D21" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" s="10">
+      <c r="E21" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="9">
         <v>500</v>
       </c>
-      <c r="G21" s="10">
+      <c r="H21" s="9">
         <v>1000</v>
       </c>
-      <c r="H21" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I21" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="16.5" spans="1:9">
       <c r="A22" s="5">
         <v>7004</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="9">
         <v>100700</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="9"/>
+      <c r="D22" s="9">
         <v>4</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F22" s="10">
+      <c r="E22" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="9">
         <v>-500</v>
       </c>
-      <c r="G22" s="10">
+      <c r="H22" s="9">
         <v>500</v>
       </c>
-      <c r="H22" s="10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I22" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" ht="16.5" spans="1:9">
       <c r="A23" s="5">
         <v>7005</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="9">
         <v>100700</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="9"/>
+      <c r="D23" s="9">
         <v>5</v>
       </c>
-      <c r="D23" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F23" s="10">
+      <c r="E23" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" s="9">
         <v>-1000</v>
       </c>
-      <c r="G23" s="10">
+      <c r="H23" s="9">
         <v>-500</v>
       </c>
-      <c r="H23" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I23" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" ht="16.5" spans="1:9">
       <c r="A24" s="5">
         <v>7006</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="9">
         <v>100700</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="9"/>
+      <c r="D24" s="9">
         <v>6</v>
       </c>
-      <c r="D24" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F24" s="10">
+      <c r="E24" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G24" s="9">
         <v>-2000</v>
       </c>
-      <c r="G24" s="10">
+      <c r="H24" s="9">
         <v>-1000</v>
       </c>
-      <c r="H24" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I24" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" ht="16.5" spans="1:9">
       <c r="A25" s="5">
         <v>7007</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="9">
         <v>100700</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="9"/>
+      <c r="D25" s="9">
         <v>7</v>
       </c>
-      <c r="D25" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" s="10">
+      <c r="E25" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" s="9">
         <v>-999999</v>
       </c>
-      <c r="G25" s="10">
+      <c r="H25" s="9">
         <v>-2000</v>
       </c>
-      <c r="H25" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I25" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A26" s="8">
         <v>12001</v>
       </c>
       <c r="B26" s="8">
         <v>101200</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" s="8">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F26" s="8">
+      <c r="E26" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" s="8">
         <v>2000</v>
       </c>
-      <c r="G26" s="8">
+      <c r="H26" s="8">
         <v>999999</v>
       </c>
-      <c r="H26" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I26" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A27" s="8">
         <v>12002</v>
       </c>
       <c r="B27" s="8">
         <v>101200</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="8"/>
+      <c r="D27" s="8">
         <v>2</v>
       </c>
-      <c r="D27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F27" s="8">
+      <c r="E27" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="8">
         <v>1000</v>
       </c>
-      <c r="G27" s="8">
+      <c r="H27" s="8">
         <v>2000</v>
       </c>
-      <c r="H27" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I27" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A28" s="8">
         <v>12003</v>
       </c>
       <c r="B28" s="8">
         <v>101200</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="8"/>
+      <c r="D28" s="8">
         <v>3</v>
       </c>
-      <c r="D28" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F28" s="8">
+      <c r="E28" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G28" s="8">
         <v>500</v>
       </c>
-      <c r="G28" s="8">
+      <c r="H28" s="8">
         <v>1000</v>
       </c>
-      <c r="H28" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I28" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A29" s="8">
         <v>12004</v>
       </c>
       <c r="B29" s="8">
         <v>101200</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="8"/>
+      <c r="D29" s="8">
         <v>4</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="E29" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="8">
+        <v>-500</v>
+      </c>
+      <c r="H29" s="8">
+        <v>500</v>
+      </c>
+      <c r="I29" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E29" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F29" s="8">
-        <v>-500</v>
-      </c>
-      <c r="G29" s="8">
-        <v>500</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="16.5" spans="1:8">
+    </row>
+    <row r="30" s="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A30" s="8">
         <v>12005</v>
       </c>
       <c r="B30" s="8">
         <v>101200</v>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="8"/>
+      <c r="D30" s="8">
         <v>5</v>
       </c>
-      <c r="D30" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F30" s="8">
+      <c r="E30" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="8">
         <v>-1000</v>
       </c>
-      <c r="G30" s="8">
+      <c r="H30" s="8">
         <v>-500</v>
       </c>
-      <c r="H30" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I30" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A31" s="8">
         <v>12006</v>
       </c>
       <c r="B31" s="8">
         <v>101200</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="8"/>
+      <c r="D31" s="8">
         <v>6</v>
       </c>
-      <c r="D31" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F31" s="8">
+      <c r="E31" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="8">
         <v>-2000</v>
       </c>
-      <c r="G31" s="8">
+      <c r="H31" s="8">
         <v>-1000</v>
       </c>
-      <c r="H31" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I31" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A32" s="8">
         <v>12007</v>
       </c>
       <c r="B32" s="8">
         <v>101200</v>
       </c>
-      <c r="C32" s="8">
+      <c r="C32" s="8"/>
+      <c r="D32" s="8">
         <v>7</v>
       </c>
-      <c r="D32" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F32" s="8">
+      <c r="E32" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G32" s="8">
         <v>-999999</v>
       </c>
-      <c r="G32" s="8">
+      <c r="H32" s="8">
         <v>-2000</v>
       </c>
-      <c r="H32" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="33" s="3" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I32" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" s="3" customFormat="1" ht="16.5" spans="1:9">
       <c r="A33" s="5">
         <v>14001</v>
       </c>
       <c r="B33" s="12">
         <v>101400</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="12">
         <v>1</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F33" s="12">
+      <c r="E33" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="12">
         <v>2000</v>
       </c>
-      <c r="G33" s="12">
+      <c r="H33" s="12">
         <v>999999</v>
       </c>
-      <c r="H33" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" s="3" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I33" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" s="3" customFormat="1" ht="16.5" spans="1:9">
       <c r="A34" s="5">
         <v>14002</v>
       </c>
       <c r="B34" s="12">
         <v>101400</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="12"/>
+      <c r="D34" s="12">
         <v>2</v>
       </c>
-      <c r="D34" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F34" s="12">
+      <c r="E34" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G34" s="12">
         <v>1000</v>
       </c>
-      <c r="G34" s="12">
+      <c r="H34" s="12">
         <v>2000</v>
       </c>
-      <c r="H34" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" s="3" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I34" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" s="3" customFormat="1" ht="16.5" spans="1:9">
       <c r="A35" s="5">
         <v>14003</v>
       </c>
       <c r="B35" s="12">
         <v>101400</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="12"/>
+      <c r="D35" s="12">
         <v>3</v>
       </c>
-      <c r="D35" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F35" s="12">
+      <c r="E35" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35" s="12">
         <v>500</v>
       </c>
-      <c r="G35" s="12">
+      <c r="H35" s="12">
         <v>1000</v>
       </c>
-      <c r="H35" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" s="3" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I35" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" s="3" customFormat="1" ht="16.5" spans="1:9">
       <c r="A36" s="5">
         <v>14004</v>
       </c>
       <c r="B36" s="12">
         <v>101400</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="12"/>
+      <c r="D36" s="12">
         <v>4</v>
       </c>
-      <c r="D36" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F36" s="12">
+      <c r="E36" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36" s="12">
         <v>-500</v>
       </c>
-      <c r="G36" s="12">
+      <c r="H36" s="12">
         <v>500</v>
       </c>
-      <c r="H36" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" s="3" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I36" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" s="3" customFormat="1" ht="16.5" spans="1:9">
       <c r="A37" s="5">
         <v>14005</v>
       </c>
       <c r="B37" s="12">
         <v>101400</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="12"/>
+      <c r="D37" s="12">
         <v>5</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="E37" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G37" s="12">
+        <v>-1000</v>
+      </c>
+      <c r="H37" s="12">
+        <v>-500</v>
+      </c>
+      <c r="I37" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E37" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" s="12">
-        <v>-1000</v>
-      </c>
-      <c r="G37" s="12">
-        <v>-500</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="38" s="3" customFormat="1" ht="16.5" spans="1:8">
+    </row>
+    <row r="38" s="3" customFormat="1" ht="16.5" spans="1:9">
       <c r="A38" s="5">
         <v>14006</v>
       </c>
       <c r="B38" s="12">
         <v>101400</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="12"/>
+      <c r="D38" s="12">
         <v>6</v>
       </c>
-      <c r="D38" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F38" s="12">
+      <c r="E38" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G38" s="12">
         <v>-2000</v>
       </c>
-      <c r="G38" s="12">
+      <c r="H38" s="12">
         <v>-1000</v>
       </c>
-      <c r="H38" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="39" s="3" customFormat="1" ht="16.5" spans="1:8">
+      <c r="I38" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" s="3" customFormat="1" ht="16.5" spans="1:9">
       <c r="A39" s="5">
         <v>14007</v>
       </c>
       <c r="B39" s="12">
         <v>101400</v>
       </c>
-      <c r="C39" s="12">
+      <c r="C39" s="12"/>
+      <c r="D39" s="12">
         <v>7</v>
       </c>
-      <c r="D39" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F39" s="12">
+      <c r="E39" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G39" s="12">
         <v>-999999</v>
       </c>
-      <c r="G39" s="12">
+      <c r="H39" s="12">
         <v>-2000</v>
       </c>
-      <c r="H39" s="12" t="s">
-        <v>25</v>
+      <c r="I39" s="12" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="42">
   <si>
     <t>id</t>
   </si>
@@ -176,55 +176,58 @@
     <t>金矿大亨</t>
   </si>
   <si>
-    <t>1_8600|2_450|3_250|4_300|5_400</t>
+    <t>1_9630|2_150|3_70|4_90|5_60</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-1600|800&amp;1000-1700|1000&amp;1500-4600|1500&amp;2000-18700|2000&amp;3000-41400|3000&amp;4000-25300|4000&amp;5000-6200|5000&amp;6000-500|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-100|20&amp;30-100|30&amp;40-100|40&amp;50-100|50&amp;60-100|60&amp;70-200|70&amp;80-100|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-500|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-3100|800&amp;1000-6000|1000&amp;1500-20000|1500&amp;2000-20000|2000&amp;3000-25000|3000&amp;4000-15000|4000&amp;5000-8000|5000&amp;6000-2900|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>放水池+3</t>
+  </si>
+  <si>
+    <t>1_9650|2_140|3_65|4_85|5_60</t>
+  </si>
+  <si>
+    <t>放水池+2</t>
+  </si>
+  <si>
+    <t>1_9655|2_140|3_60|4_85|5_60</t>
+  </si>
+  <si>
+    <t>放水池+1</t>
+  </si>
+  <si>
+    <t>1_9670|2_130|3_60|4_80|5_60</t>
+  </si>
+  <si>
+    <t>标准池</t>
+  </si>
+  <si>
+    <t>1_9685|2_120|3_60|4_75|5_60</t>
+  </si>
+  <si>
+    <t>吸水池-1</t>
+  </si>
+  <si>
+    <t>1_9690|2_120|3_55|4_75|5_60</t>
+  </si>
+  <si>
+    <t>吸水池-2</t>
+  </si>
+  <si>
+    <t>1_9710|2_110|3_50|4_70|5_60</t>
+  </si>
+  <si>
+    <t>吸水池-3</t>
+  </si>
+  <si>
+    <t>超级明星</t>
+  </si>
+  <si>
+    <t>1_9000|2_550|3_450</t>
   </si>
   <si>
     <t>1,0&amp;1-60000|1&amp;10-2000|10&amp;20-3000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-3000|80&amp;90-2000|90&amp;100-2000|100&amp;120-1500|120&amp;140-1500|140&amp;160-1200|160&amp;180-1200|180&amp;200-800|200&amp;300-600|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|5000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-200|140&amp;160-500|160&amp;180-600|180&amp;200-700|200&amp;300-2000|300&amp;500-16000|500&amp;800-36000|800&amp;1000-22000|1000&amp;1500-20850|1500&amp;2000-1030|2000&amp;3000-20|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|5000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-4000|500&amp;800-23000|800&amp;1000-23000|1000&amp;1500-35000|1500&amp;2000-12000|2000&amp;3000-2900|3000&amp;4000-100|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|5000&amp;99999999-0;4,0&amp;1-58000|1&amp;10-10000|10&amp;20-12200|20&amp;30-6000|30&amp;40-5700|40&amp;50-2000|50&amp;60-1000|60&amp;70-1000|70&amp;80-800|80&amp;90-500|90&amp;100-500|100&amp;120-500|120&amp;140-500|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-200|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|5000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-1740|90&amp;100-4000|100&amp;120-15000|120&amp;140-20000|140&amp;160-20000|160&amp;180-15200|180&amp;200-12000|200&amp;300-11000|300&amp;500-1000|500&amp;800-50|800&amp;1000-10|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|5000&amp;99999999-0;6,0&amp;1-500|1&amp;10-0|10&amp;20-100|20&amp;30-100|30&amp;40-100|40&amp;50-100|50&amp;60-100|60&amp;70-200|70&amp;80-200|80&amp;90-200|90&amp;100-500|100&amp;120-500|120&amp;140-1000|140&amp;160-1000|160&amp;180-1000|180&amp;200-1000|200&amp;300-8000|300&amp;500-15000|500&amp;800-18000|800&amp;1000-18000|1000&amp;1500-10450|1500&amp;2000-10000|2000&amp;3000-5000|3000&amp;4000-3000|4000&amp;5000-2000|5000&amp;6000-1500|6000&amp;7000-1000|7000&amp;8000-500|8000&amp;9000-500|9000&amp;10000-200|10000&amp;11000-100|11000&amp;12000-50|12000&amp;15000-50|15000&amp;20000-50|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-10000|800&amp;1000-18000|1000&amp;1500-47000|1500&amp;2000-20000|2000&amp;3000-5000|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|5000&amp;99999999-0</t>
-  </si>
-  <si>
-    <t>放水池+3</t>
-  </si>
-  <si>
-    <t>1_8800|2_400|3_200|4_250|5_350</t>
-  </si>
-  <si>
-    <t>放水池+2</t>
-  </si>
-  <si>
-    <t>1_8900|2_350|3_150|4_250|5_350</t>
-  </si>
-  <si>
-    <t>放水池+1</t>
-  </si>
-  <si>
-    <t>1_9000|2_300|3_100|4_250|5_350</t>
-  </si>
-  <si>
-    <t>标准池</t>
-  </si>
-  <si>
-    <t>1_9100|2_250|3_50|4_250|5_350</t>
-  </si>
-  <si>
-    <t>吸水池-1</t>
-  </si>
-  <si>
-    <t>1_9200|2_200|3_0|4_250|5_350</t>
-  </si>
-  <si>
-    <t>吸水池-2</t>
-  </si>
-  <si>
-    <t>1_9400|2_150|3_0|4_200|5_250</t>
-  </si>
-  <si>
-    <t>吸水池-3</t>
-  </si>
-  <si>
-    <t>超级明星</t>
-  </si>
-  <si>
-    <t>1_9000|2_550|3_450</t>
   </si>
   <si>
     <t>麻将胡了</t>
@@ -255,7 +258,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,6 +269,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -419,7 +428,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -441,6 +450,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -755,55 +770,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -818,75 +830,78 @@
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -901,6 +916,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1358,7 +1376,7 @@
       <c r="E5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="8" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="5">
@@ -1385,8 +1403,9 @@
       <c r="E6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>19</v>
+      <c r="F6" s="7" t="str">
+        <f>F5</f>
+        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-1600|800&amp;1000-1700|1000&amp;1500-4600|1500&amp;2000-18700|2000&amp;3000-41400|3000&amp;4000-25300|4000&amp;5000-6200|5000&amp;6000-500|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-100|20&amp;30-100|30&amp;40-100|40&amp;50-100|50&amp;60-100|60&amp;70-200|70&amp;80-100|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-500|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-3100|800&amp;1000-6000|1000&amp;1500-20000|1500&amp;2000-20000|2000&amp;3000-25000|3000&amp;4000-15000|4000&amp;5000-8000|5000&amp;6000-2900|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G6" s="5">
         <v>1000</v>
@@ -1412,8 +1431,9 @@
       <c r="E7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>19</v>
+      <c r="F7" s="7" t="str">
+        <f>F6</f>
+        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-1600|800&amp;1000-1700|1000&amp;1500-4600|1500&amp;2000-18700|2000&amp;3000-41400|3000&amp;4000-25300|4000&amp;5000-6200|5000&amp;6000-500|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-100|20&amp;30-100|30&amp;40-100|40&amp;50-100|50&amp;60-100|60&amp;70-200|70&amp;80-100|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-500|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-3100|800&amp;1000-6000|1000&amp;1500-20000|1500&amp;2000-20000|2000&amp;3000-25000|3000&amp;4000-15000|4000&amp;5000-8000|5000&amp;6000-2900|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G7" s="5">
         <v>500</v>
@@ -1439,8 +1459,9 @@
       <c r="E8" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>19</v>
+      <c r="F8" s="7" t="str">
+        <f>F7</f>
+        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-1600|800&amp;1000-1700|1000&amp;1500-4600|1500&amp;2000-18700|2000&amp;3000-41400|3000&amp;4000-25300|4000&amp;5000-6200|5000&amp;6000-500|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-100|20&amp;30-100|30&amp;40-100|40&amp;50-100|50&amp;60-100|60&amp;70-200|70&amp;80-100|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-500|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-3100|800&amp;1000-6000|1000&amp;1500-20000|1500&amp;2000-20000|2000&amp;3000-25000|3000&amp;4000-15000|4000&amp;5000-8000|5000&amp;6000-2900|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G8" s="5">
         <v>-500</v>
@@ -1466,8 +1487,9 @@
       <c r="E9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>19</v>
+      <c r="F9" s="7" t="str">
+        <f>F8</f>
+        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-1600|800&amp;1000-1700|1000&amp;1500-4600|1500&amp;2000-18700|2000&amp;3000-41400|3000&amp;4000-25300|4000&amp;5000-6200|5000&amp;6000-500|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-100|20&amp;30-100|30&amp;40-100|40&amp;50-100|50&amp;60-100|60&amp;70-200|70&amp;80-100|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-500|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-3100|800&amp;1000-6000|1000&amp;1500-20000|1500&amp;2000-20000|2000&amp;3000-25000|3000&amp;4000-15000|4000&amp;5000-8000|5000&amp;6000-2900|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G9" s="5">
         <v>-1000</v>
@@ -1493,8 +1515,9 @@
       <c r="E10" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>19</v>
+      <c r="F10" s="7" t="str">
+        <f>F9</f>
+        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-1600|800&amp;1000-1700|1000&amp;1500-4600|1500&amp;2000-18700|2000&amp;3000-41400|3000&amp;4000-25300|4000&amp;5000-6200|5000&amp;6000-500|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-100|20&amp;30-100|30&amp;40-100|40&amp;50-100|50&amp;60-100|60&amp;70-200|70&amp;80-100|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-500|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-3100|800&amp;1000-6000|1000&amp;1500-20000|1500&amp;2000-20000|2000&amp;3000-25000|3000&amp;4000-15000|4000&amp;5000-8000|5000&amp;6000-2900|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G10" s="5">
         <v>-2000</v>
@@ -1520,8 +1543,9 @@
       <c r="E11" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>19</v>
+      <c r="F11" s="7" t="str">
+        <f>F10</f>
+        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-1600|800&amp;1000-1700|1000&amp;1500-4600|1500&amp;2000-18700|2000&amp;3000-41400|3000&amp;4000-25300|4000&amp;5000-6200|5000&amp;6000-500|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-100|20&amp;30-100|30&amp;40-100|40&amp;50-100|50&amp;60-100|60&amp;70-200|70&amp;80-100|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-500|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-3100|800&amp;1000-6000|1000&amp;1500-20000|1500&amp;2000-20000|2000&amp;3000-25000|3000&amp;4000-15000|4000&amp;5000-8000|5000&amp;6000-2900|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G11" s="5">
         <v>-999999</v>
@@ -1534,193 +1558,193 @@
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A12" s="8">
+      <c r="A12" s="9">
         <v>3001</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="9">
         <v>100300</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="9">
         <v>1</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="8">
+        <v>35</v>
+      </c>
+      <c r="G12" s="9">
         <v>2000</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="9">
         <v>999999</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A13" s="8">
+      <c r="A13" s="9">
         <v>3002</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="9">
         <v>100300</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8">
+      <c r="C13" s="9"/>
+      <c r="D13" s="9">
         <v>2</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="8">
+        <v>35</v>
+      </c>
+      <c r="G13" s="9">
         <v>1000</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="9">
         <v>2000</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A14" s="8">
+      <c r="A14" s="9">
         <v>3003</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="9">
         <v>100300</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8">
+      <c r="C14" s="9"/>
+      <c r="D14" s="9">
         <v>3</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" s="8">
+        <v>35</v>
+      </c>
+      <c r="G14" s="9">
         <v>500</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="9">
         <v>1000</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="9" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A15" s="8">
+      <c r="A15" s="9">
         <v>3004</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="9">
         <v>100300</v>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8">
+      <c r="C15" s="9"/>
+      <c r="D15" s="9">
         <v>4</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="8">
+        <v>35</v>
+      </c>
+      <c r="G15" s="9">
         <v>-500</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="9">
         <v>500</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A16" s="8">
+      <c r="A16" s="9">
         <v>3005</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="9">
         <v>100300</v>
       </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8">
+      <c r="C16" s="9"/>
+      <c r="D16" s="9">
         <v>5</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G16" s="8">
+        <v>35</v>
+      </c>
+      <c r="G16" s="9">
         <v>-1000</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="9">
         <v>-500</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="I16" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A17" s="8">
+      <c r="A17" s="9">
         <v>3006</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="9">
         <v>100300</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8">
+      <c r="C17" s="9"/>
+      <c r="D17" s="9">
         <v>6</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" s="8">
+        <v>35</v>
+      </c>
+      <c r="G17" s="9">
         <v>-2000</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="9">
         <v>-1000</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="I17" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A18" s="8">
+      <c r="A18" s="9">
         <v>3007</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="9">
         <v>100300</v>
       </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8">
+      <c r="C18" s="9"/>
+      <c r="D18" s="9">
         <v>7</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" s="8">
+        <v>35</v>
+      </c>
+      <c r="G18" s="9">
         <v>-999999</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="9">
         <v>-2000</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="I18" s="9" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1728,28 +1752,28 @@
       <c r="A19" s="5">
         <v>7001</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="10">
         <v>100700</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="9">
+      <c r="C19" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="10">
         <v>1</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" s="11" t="s">
+      <c r="E19" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G19" s="9">
+      <c r="F19" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="10">
         <v>2000</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="10">
         <v>999999</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="10" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1757,26 +1781,26 @@
       <c r="A20" s="5">
         <v>7002</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="10">
         <v>100700</v>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9">
+      <c r="C20" s="10"/>
+      <c r="D20" s="10">
         <v>2</v>
       </c>
-      <c r="E20" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20" s="11" t="s">
+      <c r="E20" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G20" s="9">
+      <c r="F20" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="10">
         <v>1000</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="10">
         <v>2000</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="10" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1784,26 +1808,26 @@
       <c r="A21" s="5">
         <v>7003</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="10">
         <v>100700</v>
       </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9">
+      <c r="C21" s="10"/>
+      <c r="D21" s="10">
         <v>3</v>
       </c>
-      <c r="E21" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" s="11" t="s">
+      <c r="E21" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G21" s="9">
+      <c r="F21" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" s="10">
         <v>500</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="10">
         <v>1000</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="I21" s="10" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1811,26 +1835,26 @@
       <c r="A22" s="5">
         <v>7004</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="10">
         <v>100700</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9">
+      <c r="C22" s="10"/>
+      <c r="D22" s="10">
         <v>4</v>
       </c>
-      <c r="E22" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="11" t="s">
+      <c r="E22" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G22" s="9">
+      <c r="F22" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" s="10">
         <v>-500</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="10">
         <v>500</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="I22" s="10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1838,26 +1862,26 @@
       <c r="A23" s="5">
         <v>7005</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="10">
         <v>100700</v>
       </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9">
+      <c r="C23" s="10"/>
+      <c r="D23" s="10">
         <v>5</v>
       </c>
-      <c r="E23" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" s="11" t="s">
+      <c r="E23" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G23" s="9">
+      <c r="F23" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" s="10">
         <v>-1000</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="10">
         <v>-500</v>
       </c>
-      <c r="I23" s="9" t="s">
+      <c r="I23" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1865,26 +1889,26 @@
       <c r="A24" s="5">
         <v>7006</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="10">
         <v>100700</v>
       </c>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9">
+      <c r="C24" s="10"/>
+      <c r="D24" s="10">
         <v>6</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F24" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G24" s="9">
+      <c r="F24" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="10">
         <v>-2000</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="10">
         <v>-1000</v>
       </c>
-      <c r="I24" s="9" t="s">
+      <c r="I24" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1892,217 +1916,217 @@
       <c r="A25" s="5">
         <v>7007</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B25" s="10">
         <v>100700</v>
       </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9">
+      <c r="C25" s="10"/>
+      <c r="D25" s="10">
         <v>7</v>
       </c>
-      <c r="E25" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F25" s="11" t="s">
+      <c r="E25" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G25" s="9">
+      <c r="F25" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G25" s="10">
         <v>-999999</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="10">
         <v>-2000</v>
       </c>
-      <c r="I25" s="9" t="s">
+      <c r="I25" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A26" s="8">
+      <c r="A26" s="9">
         <v>12001</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="9">
         <v>101200</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D26" s="8">
+      <c r="C26" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" s="9">
         <v>1</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G26" s="8">
+        <v>35</v>
+      </c>
+      <c r="G26" s="9">
         <v>2000</v>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="9">
         <v>999999</v>
       </c>
-      <c r="I26" s="8" t="s">
+      <c r="I26" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A27" s="8">
+      <c r="A27" s="9">
         <v>12002</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="9">
         <v>101200</v>
       </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8">
+      <c r="C27" s="9"/>
+      <c r="D27" s="9">
         <v>2</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" s="8">
+        <v>35</v>
+      </c>
+      <c r="G27" s="9">
         <v>1000</v>
       </c>
-      <c r="H27" s="8">
+      <c r="H27" s="9">
         <v>2000</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="I27" s="9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A28" s="8">
+      <c r="A28" s="9">
         <v>12003</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="9">
         <v>101200</v>
       </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8">
+      <c r="C28" s="9"/>
+      <c r="D28" s="9">
         <v>3</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G28" s="8">
+        <v>35</v>
+      </c>
+      <c r="G28" s="9">
         <v>500</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="9">
         <v>1000</v>
       </c>
-      <c r="I28" s="8" t="s">
+      <c r="I28" s="9" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A29" s="8">
+      <c r="A29" s="9">
         <v>12004</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="9">
         <v>101200</v>
       </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8">
+      <c r="C29" s="9"/>
+      <c r="D29" s="9">
         <v>4</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G29" s="8">
+        <v>35</v>
+      </c>
+      <c r="G29" s="9">
         <v>-500</v>
       </c>
-      <c r="H29" s="8">
+      <c r="H29" s="9">
         <v>500</v>
       </c>
-      <c r="I29" s="8" t="s">
+      <c r="I29" s="9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A30" s="8">
+      <c r="A30" s="9">
         <v>12005</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="9">
         <v>101200</v>
       </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8">
+      <c r="C30" s="9"/>
+      <c r="D30" s="9">
         <v>5</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="8">
+        <v>35</v>
+      </c>
+      <c r="G30" s="9">
         <v>-1000</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="9">
         <v>-500</v>
       </c>
-      <c r="I30" s="8" t="s">
+      <c r="I30" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A31" s="8">
+      <c r="A31" s="9">
         <v>12006</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="9">
         <v>101200</v>
       </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8">
+      <c r="C31" s="9"/>
+      <c r="D31" s="9">
         <v>6</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G31" s="8">
+        <v>35</v>
+      </c>
+      <c r="G31" s="9">
         <v>-2000</v>
       </c>
-      <c r="H31" s="8">
+      <c r="H31" s="9">
         <v>-1000</v>
       </c>
-      <c r="I31" s="8" t="s">
+      <c r="I31" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A32" s="8">
+      <c r="A32" s="9">
         <v>12007</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="9">
         <v>101200</v>
       </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8">
+      <c r="C32" s="9"/>
+      <c r="D32" s="9">
         <v>7</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G32" s="8">
+        <v>35</v>
+      </c>
+      <c r="G32" s="9">
         <v>-999999</v>
       </c>
-      <c r="H32" s="8">
+      <c r="H32" s="9">
         <v>-2000</v>
       </c>
-      <c r="I32" s="8" t="s">
+      <c r="I32" s="9" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2110,28 +2134,28 @@
       <c r="A33" s="5">
         <v>14001</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="13">
         <v>101400</v>
       </c>
-      <c r="C33" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33" s="12">
+      <c r="C33" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" s="13">
         <v>1</v>
       </c>
-      <c r="E33" s="13" t="s">
-        <v>40</v>
+      <c r="E33" s="14" t="s">
+        <v>41</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G33" s="12">
+        <v>35</v>
+      </c>
+      <c r="G33" s="13">
         <v>2000</v>
       </c>
-      <c r="H33" s="12">
+      <c r="H33" s="13">
         <v>999999</v>
       </c>
-      <c r="I33" s="12" t="s">
+      <c r="I33" s="13" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2139,26 +2163,26 @@
       <c r="A34" s="5">
         <v>14002</v>
       </c>
-      <c r="B34" s="12">
+      <c r="B34" s="13">
         <v>101400</v>
       </c>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12">
+      <c r="C34" s="13"/>
+      <c r="D34" s="13">
         <v>2</v>
       </c>
-      <c r="E34" s="13" t="s">
-        <v>40</v>
+      <c r="E34" s="14" t="s">
+        <v>41</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G34" s="12">
+        <v>35</v>
+      </c>
+      <c r="G34" s="13">
         <v>1000</v>
       </c>
-      <c r="H34" s="12">
+      <c r="H34" s="13">
         <v>2000</v>
       </c>
-      <c r="I34" s="12" t="s">
+      <c r="I34" s="13" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2166,26 +2190,26 @@
       <c r="A35" s="5">
         <v>14003</v>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="13">
         <v>101400</v>
       </c>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12">
+      <c r="C35" s="13"/>
+      <c r="D35" s="13">
         <v>3</v>
       </c>
-      <c r="E35" s="13" t="s">
-        <v>40</v>
+      <c r="E35" s="14" t="s">
+        <v>41</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G35" s="12">
+        <v>35</v>
+      </c>
+      <c r="G35" s="13">
         <v>500</v>
       </c>
-      <c r="H35" s="12">
+      <c r="H35" s="13">
         <v>1000</v>
       </c>
-      <c r="I35" s="12" t="s">
+      <c r="I35" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2193,26 +2217,26 @@
       <c r="A36" s="5">
         <v>14004</v>
       </c>
-      <c r="B36" s="12">
+      <c r="B36" s="13">
         <v>101400</v>
       </c>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12">
+      <c r="C36" s="13"/>
+      <c r="D36" s="13">
         <v>4</v>
       </c>
-      <c r="E36" s="13" t="s">
-        <v>40</v>
+      <c r="E36" s="14" t="s">
+        <v>41</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G36" s="12">
+        <v>35</v>
+      </c>
+      <c r="G36" s="13">
         <v>-500</v>
       </c>
-      <c r="H36" s="12">
+      <c r="H36" s="13">
         <v>500</v>
       </c>
-      <c r="I36" s="12" t="s">
+      <c r="I36" s="13" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2220,26 +2244,26 @@
       <c r="A37" s="5">
         <v>14005</v>
       </c>
-      <c r="B37" s="12">
+      <c r="B37" s="13">
         <v>101400</v>
       </c>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12">
+      <c r="C37" s="13"/>
+      <c r="D37" s="13">
         <v>5</v>
       </c>
-      <c r="E37" s="13" t="s">
-        <v>40</v>
+      <c r="E37" s="14" t="s">
+        <v>41</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G37" s="12">
+        <v>35</v>
+      </c>
+      <c r="G37" s="13">
         <v>-1000</v>
       </c>
-      <c r="H37" s="12">
+      <c r="H37" s="13">
         <v>-500</v>
       </c>
-      <c r="I37" s="12" t="s">
+      <c r="I37" s="13" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2247,26 +2271,26 @@
       <c r="A38" s="5">
         <v>14006</v>
       </c>
-      <c r="B38" s="12">
+      <c r="B38" s="13">
         <v>101400</v>
       </c>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12">
+      <c r="C38" s="13"/>
+      <c r="D38" s="13">
         <v>6</v>
       </c>
-      <c r="E38" s="13" t="s">
-        <v>40</v>
+      <c r="E38" s="14" t="s">
+        <v>41</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G38" s="12">
+        <v>35</v>
+      </c>
+      <c r="G38" s="13">
         <v>-2000</v>
       </c>
-      <c r="H38" s="12">
+      <c r="H38" s="13">
         <v>-1000</v>
       </c>
-      <c r="I38" s="12" t="s">
+      <c r="I38" s="13" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2274,26 +2298,26 @@
       <c r="A39" s="5">
         <v>14007</v>
       </c>
-      <c r="B39" s="12">
+      <c r="B39" s="13">
         <v>101400</v>
       </c>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12">
+      <c r="C39" s="13"/>
+      <c r="D39" s="13">
         <v>7</v>
       </c>
-      <c r="E39" s="13" t="s">
-        <v>40</v>
+      <c r="E39" s="14" t="s">
+        <v>41</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G39" s="12">
+        <v>35</v>
+      </c>
+      <c r="G39" s="13">
         <v>-999999</v>
       </c>
-      <c r="H39" s="12">
+      <c r="H39" s="13">
         <v>-2000</v>
       </c>
-      <c r="I39" s="12" t="s">
+      <c r="I39" s="13" t="s">
         <v>32</v>
       </c>
     </row>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -176,46 +176,46 @@
     <t>金矿大亨</t>
   </si>
   <si>
-    <t>1_9630|2_150|3_70|4_90|5_60</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-1600|800&amp;1000-1700|1000&amp;1500-4600|1500&amp;2000-18700|2000&amp;3000-41400|3000&amp;4000-25300|4000&amp;5000-6200|5000&amp;6000-500|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-100|20&amp;30-100|30&amp;40-100|40&amp;50-100|50&amp;60-100|60&amp;70-200|70&amp;80-100|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-500|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-3100|800&amp;1000-6000|1000&amp;1500-20000|1500&amp;2000-20000|2000&amp;3000-25000|3000&amp;4000-15000|4000&amp;5000-8000|5000&amp;6000-2900|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</t>
+    <t>1_9560|2_170|3_60|4_130|5_80</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</t>
   </si>
   <si>
     <t>放水池+3</t>
   </si>
   <si>
-    <t>1_9650|2_140|3_65|4_85|5_60</t>
+    <t>1_9580|2_160|3_60|4_120|5_80</t>
   </si>
   <si>
     <t>放水池+2</t>
   </si>
   <si>
-    <t>1_9655|2_140|3_60|4_85|5_60</t>
+    <t>1_9600|2_150|3_60|4_110|5_80</t>
   </si>
   <si>
     <t>放水池+1</t>
   </si>
   <si>
-    <t>1_9670|2_130|3_60|4_80|5_60</t>
+    <t>1_9620|2_140|3_60|4_100|5_80</t>
   </si>
   <si>
     <t>标准池</t>
   </si>
   <si>
-    <t>1_9685|2_120|3_60|4_75|5_60</t>
+    <t>1_9640|2_130|3_60|4_90|5_80</t>
   </si>
   <si>
     <t>吸水池-1</t>
   </si>
   <si>
-    <t>1_9690|2_120|3_55|4_75|5_60</t>
+    <t>1_9660|2_120|3_60|4_80|5_80</t>
   </si>
   <si>
     <t>吸水池-2</t>
   </si>
   <si>
-    <t>1_9710|2_110|3_50|4_70|5_60</t>
+    <t>1_9680|2_110|3_60|4_70|5_80</t>
   </si>
   <si>
     <t>吸水池-3</t>
@@ -1404,8 +1404,8 @@
         <v>21</v>
       </c>
       <c r="F6" s="7" t="str">
-        <f>F5</f>
-        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-1600|800&amp;1000-1700|1000&amp;1500-4600|1500&amp;2000-18700|2000&amp;3000-41400|3000&amp;4000-25300|4000&amp;5000-6200|5000&amp;6000-500|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-100|20&amp;30-100|30&amp;40-100|40&amp;50-100|50&amp;60-100|60&amp;70-200|70&amp;80-100|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-500|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-3100|800&amp;1000-6000|1000&amp;1500-20000|1500&amp;2000-20000|2000&amp;3000-25000|3000&amp;4000-15000|4000&amp;5000-8000|5000&amp;6000-2900|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
+        <f t="shared" ref="F6:F11" si="0">F5</f>
+        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G6" s="5">
         <v>1000</v>
@@ -1432,8 +1432,8 @@
         <v>23</v>
       </c>
       <c r="F7" s="7" t="str">
-        <f>F6</f>
-        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-1600|800&amp;1000-1700|1000&amp;1500-4600|1500&amp;2000-18700|2000&amp;3000-41400|3000&amp;4000-25300|4000&amp;5000-6200|5000&amp;6000-500|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-100|20&amp;30-100|30&amp;40-100|40&amp;50-100|50&amp;60-100|60&amp;70-200|70&amp;80-100|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-500|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-3100|800&amp;1000-6000|1000&amp;1500-20000|1500&amp;2000-20000|2000&amp;3000-25000|3000&amp;4000-15000|4000&amp;5000-8000|5000&amp;6000-2900|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
+        <f t="shared" si="0"/>
+        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G7" s="5">
         <v>500</v>
@@ -1460,8 +1460,8 @@
         <v>25</v>
       </c>
       <c r="F8" s="7" t="str">
-        <f>F7</f>
-        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-1600|800&amp;1000-1700|1000&amp;1500-4600|1500&amp;2000-18700|2000&amp;3000-41400|3000&amp;4000-25300|4000&amp;5000-6200|5000&amp;6000-500|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-100|20&amp;30-100|30&amp;40-100|40&amp;50-100|50&amp;60-100|60&amp;70-200|70&amp;80-100|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-500|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-3100|800&amp;1000-6000|1000&amp;1500-20000|1500&amp;2000-20000|2000&amp;3000-25000|3000&amp;4000-15000|4000&amp;5000-8000|5000&amp;6000-2900|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
+        <f t="shared" si="0"/>
+        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G8" s="5">
         <v>-500</v>
@@ -1488,8 +1488,8 @@
         <v>27</v>
       </c>
       <c r="F9" s="7" t="str">
-        <f>F8</f>
-        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-1600|800&amp;1000-1700|1000&amp;1500-4600|1500&amp;2000-18700|2000&amp;3000-41400|3000&amp;4000-25300|4000&amp;5000-6200|5000&amp;6000-500|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-100|20&amp;30-100|30&amp;40-100|40&amp;50-100|50&amp;60-100|60&amp;70-200|70&amp;80-100|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-500|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-3100|800&amp;1000-6000|1000&amp;1500-20000|1500&amp;2000-20000|2000&amp;3000-25000|3000&amp;4000-15000|4000&amp;5000-8000|5000&amp;6000-2900|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
+        <f t="shared" si="0"/>
+        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G9" s="5">
         <v>-1000</v>
@@ -1516,8 +1516,8 @@
         <v>29</v>
       </c>
       <c r="F10" s="7" t="str">
-        <f>F9</f>
-        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-1600|800&amp;1000-1700|1000&amp;1500-4600|1500&amp;2000-18700|2000&amp;3000-41400|3000&amp;4000-25300|4000&amp;5000-6200|5000&amp;6000-500|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-100|20&amp;30-100|30&amp;40-100|40&amp;50-100|50&amp;60-100|60&amp;70-200|70&amp;80-100|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-500|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-3100|800&amp;1000-6000|1000&amp;1500-20000|1500&amp;2000-20000|2000&amp;3000-25000|3000&amp;4000-15000|4000&amp;5000-8000|5000&amp;6000-2900|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
+        <f t="shared" si="0"/>
+        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G10" s="5">
         <v>-2000</v>
@@ -1544,8 +1544,8 @@
         <v>31</v>
       </c>
       <c r="F11" s="7" t="str">
-        <f>F10</f>
-        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-1600|800&amp;1000-1700|1000&amp;1500-4600|1500&amp;2000-18700|2000&amp;3000-41400|3000&amp;4000-25300|4000&amp;5000-6200|5000&amp;6000-500|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-100|20&amp;30-100|30&amp;40-100|40&amp;50-100|50&amp;60-100|60&amp;70-200|70&amp;80-100|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-500|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-3100|800&amp;1000-6000|1000&amp;1500-20000|1500&amp;2000-20000|2000&amp;3000-25000|3000&amp;4000-15000|4000&amp;5000-8000|5000&amp;6000-2900|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
+        <f t="shared" si="0"/>
+        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G11" s="5">
         <v>-999999</v>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="48">
   <si>
     <t>id</t>
   </si>
@@ -233,10 +233,28 @@
     <t>麻将胡了</t>
   </si>
   <si>
-    <t>1_9990|2_10</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-85000|1&amp;10-6000|10&amp;20-3400|20&amp;40-900|40&amp;60-800|60&amp;80-200|80&amp;100-200|100&amp;120-200|120&amp;140-200|140&amp;160-200|160&amp;180-200|180&amp;200-200|200&amp;220-200|220&amp;240-200|240&amp;260-200|260&amp;280-200|280&amp;300-200|300&amp;500-200|500&amp;800-200|800&amp;1000-200|1000&amp;1500-200|1500&amp;2000-200|2000&amp;4000-200|4000&amp;6000-200|6000&amp;8000-100|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;220-0|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-100|1500&amp;2000-300|2000&amp;4000-4500|4000&amp;6000-11000|6000&amp;8000-15800|8000&amp;10000-16600|10000&amp;12000-14800|12000&amp;14000-11500|14000&amp;16000-8700|16000&amp;18000-5900|18000&amp;20000-3900|20000&amp;24000-4200|24000&amp;28000-1700|28000&amp;32000-600|32000&amp;36000-200|36000&amp;40000-100|40000&amp;60000-100|60000&amp;80000-0|80000&amp;99999999-0</t>
+    <t>1_9840|2_160</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-42000|1&amp;10-20000|10&amp;20-20000|20&amp;40-10000|40&amp;60-3200|60&amp;80-1500|80&amp;100-1000|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-100|200&amp;220-0|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-100|280&amp;300-100|300&amp;500-4000|500&amp;800-10600|800&amp;1000-12000|1000&amp;1500-25000|1500&amp;2000-25000|2000&amp;4000-20000|4000&amp;6000-2600|6000&amp;8000-200|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>1_9870|2_130</t>
+  </si>
+  <si>
+    <t>1_9890|2_110</t>
+  </si>
+  <si>
+    <t>1_9920|2_80</t>
+  </si>
+  <si>
+    <t>1_9950|2_50</t>
+  </si>
+  <si>
+    <t>1_9970|2_30</t>
+  </si>
+  <si>
+    <t>1_10000|2_0</t>
   </si>
   <si>
     <t>财神</t>
@@ -1764,7 +1782,7 @@
       <c r="E19" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G19" s="10">
@@ -1789,10 +1807,11 @@
         <v>2</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="F20" s="12" t="str">
+        <f t="shared" ref="F20:F25" si="1">F19</f>
+        <v>1,0&amp;1-42000|1&amp;10-20000|10&amp;20-20000|20&amp;40-10000|40&amp;60-3200|60&amp;80-1500|80&amp;100-1000|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-100|200&amp;220-0|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-100|280&amp;300-100|300&amp;500-4000|500&amp;800-10600|800&amp;1000-12000|1000&amp;1500-25000|1500&amp;2000-25000|2000&amp;4000-20000|4000&amp;6000-2600|6000&amp;8000-200|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0</v>
       </c>
       <c r="G20" s="10">
         <v>1000</v>
@@ -1816,10 +1835,11 @@
         <v>3</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="F21" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>1,0&amp;1-42000|1&amp;10-20000|10&amp;20-20000|20&amp;40-10000|40&amp;60-3200|60&amp;80-1500|80&amp;100-1000|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-100|200&amp;220-0|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-100|280&amp;300-100|300&amp;500-4000|500&amp;800-10600|800&amp;1000-12000|1000&amp;1500-25000|1500&amp;2000-25000|2000&amp;4000-20000|4000&amp;6000-2600|6000&amp;8000-200|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0</v>
       </c>
       <c r="G21" s="10">
         <v>500</v>
@@ -1843,10 +1863,11 @@
         <v>4</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>38</v>
+        <v>41</v>
+      </c>
+      <c r="F22" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>1,0&amp;1-42000|1&amp;10-20000|10&amp;20-20000|20&amp;40-10000|40&amp;60-3200|60&amp;80-1500|80&amp;100-1000|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-100|200&amp;220-0|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-100|280&amp;300-100|300&amp;500-4000|500&amp;800-10600|800&amp;1000-12000|1000&amp;1500-25000|1500&amp;2000-25000|2000&amp;4000-20000|4000&amp;6000-2600|6000&amp;8000-200|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0</v>
       </c>
       <c r="G22" s="10">
         <v>-500</v>
@@ -1870,10 +1891,11 @@
         <v>5</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>38</v>
+        <v>42</v>
+      </c>
+      <c r="F23" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>1,0&amp;1-42000|1&amp;10-20000|10&amp;20-20000|20&amp;40-10000|40&amp;60-3200|60&amp;80-1500|80&amp;100-1000|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-100|200&amp;220-0|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-100|280&amp;300-100|300&amp;500-4000|500&amp;800-10600|800&amp;1000-12000|1000&amp;1500-25000|1500&amp;2000-25000|2000&amp;4000-20000|4000&amp;6000-2600|6000&amp;8000-200|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0</v>
       </c>
       <c r="G23" s="10">
         <v>-1000</v>
@@ -1897,10 +1919,11 @@
         <v>6</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>38</v>
+        <v>43</v>
+      </c>
+      <c r="F24" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>1,0&amp;1-42000|1&amp;10-20000|10&amp;20-20000|20&amp;40-10000|40&amp;60-3200|60&amp;80-1500|80&amp;100-1000|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-100|200&amp;220-0|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-100|280&amp;300-100|300&amp;500-4000|500&amp;800-10600|800&amp;1000-12000|1000&amp;1500-25000|1500&amp;2000-25000|2000&amp;4000-20000|4000&amp;6000-2600|6000&amp;8000-200|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0</v>
       </c>
       <c r="G24" s="10">
         <v>-2000</v>
@@ -1924,10 +1947,11 @@
         <v>7</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
+      </c>
+      <c r="F25" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>1,0&amp;1-42000|1&amp;10-20000|10&amp;20-20000|20&amp;40-10000|40&amp;60-3200|60&amp;80-1500|80&amp;100-1000|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-100|200&amp;220-0|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-100|280&amp;300-100|300&amp;500-4000|500&amp;800-10600|800&amp;1000-12000|1000&amp;1500-25000|1500&amp;2000-25000|2000&amp;4000-20000|4000&amp;6000-2600|6000&amp;8000-200|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0</v>
       </c>
       <c r="G25" s="10">
         <v>-999999</v>
@@ -1947,7 +1971,7 @@
         <v>101200</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D26" s="9">
         <v>1</v>
@@ -2138,13 +2162,13 @@
         <v>101400</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D33" s="13">
         <v>1</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>35</v>
@@ -2171,7 +2195,7 @@
         <v>2</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>35</v>
@@ -2198,7 +2222,7 @@
         <v>3</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>35</v>
@@ -2225,7 +2249,7 @@
         <v>4</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>35</v>
@@ -2252,7 +2276,7 @@
         <v>5</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>35</v>
@@ -2279,7 +2303,7 @@
         <v>6</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>35</v>
@@ -2306,7 +2330,7 @@
         <v>7</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>35</v>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="55">
   <si>
     <t>id</t>
   </si>
@@ -263,7 +263,28 @@
     <t>埃及艳后</t>
   </si>
   <si>
-    <t>1_10000</t>
+    <t>1_5500|2_4500|3_1</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-85200|1&amp;10-0|10&amp;20-2400|20&amp;40-5000|40&amp;60-3200|60&amp;80-1600|80&amp;100-1000|100&amp;120-500|120&amp;140-400|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-69300|1&amp;10-0|10&amp;20-4900|20&amp;30-5600|30&amp;40-4500|40&amp;50-3600|50&amp;60-2800|60&amp;70-2100|70&amp;80-1500|80&amp;90-1100|90&amp;100-1100|100&amp;120-1100|120&amp;140-900|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-97300|1&amp;10-0|10&amp;20-1100|20&amp;30-600|30&amp;40-700|40&amp;50-100|50&amp;60-100|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>1_6000|2_4000|3_1</t>
+  </si>
+  <si>
+    <t>1_6500|2_3500|3_1</t>
+  </si>
+  <si>
+    <t>1_7000|2_3000|3_1</t>
+  </si>
+  <si>
+    <t>1_7500|2_2500|3_1</t>
+  </si>
+  <si>
+    <t>1_8000|2_2000|3_1</t>
+  </si>
+  <si>
+    <t>1_8500|2_1500|3_1</t>
   </si>
 </sst>
 </file>
@@ -2170,8 +2191,8 @@
       <c r="E33" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>35</v>
+      <c r="F33" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="G33" s="13">
         <v>2000</v>
@@ -2195,10 +2216,11 @@
         <v>2</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>35</v>
+        <v>49</v>
+      </c>
+      <c r="F34" s="7" t="str">
+        <f>F33</f>
+        <v>1,0&amp;1-85200|1&amp;10-0|10&amp;20-2400|20&amp;40-5000|40&amp;60-3200|60&amp;80-1600|80&amp;100-1000|100&amp;120-500|120&amp;140-400|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-69300|1&amp;10-0|10&amp;20-4900|20&amp;30-5600|30&amp;40-4500|40&amp;50-3600|50&amp;60-2800|60&amp;70-2100|70&amp;80-1500|80&amp;90-1100|90&amp;100-1100|100&amp;120-1100|120&amp;140-900|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-97300|1&amp;10-0|10&amp;20-1100|20&amp;30-600|30&amp;40-700|40&amp;50-100|50&amp;60-100|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G34" s="13">
         <v>1000</v>
@@ -2222,10 +2244,11 @@
         <v>3</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>35</v>
+        <v>50</v>
+      </c>
+      <c r="F35" s="7" t="str">
+        <f>F34</f>
+        <v>1,0&amp;1-85200|1&amp;10-0|10&amp;20-2400|20&amp;40-5000|40&amp;60-3200|60&amp;80-1600|80&amp;100-1000|100&amp;120-500|120&amp;140-400|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-69300|1&amp;10-0|10&amp;20-4900|20&amp;30-5600|30&amp;40-4500|40&amp;50-3600|50&amp;60-2800|60&amp;70-2100|70&amp;80-1500|80&amp;90-1100|90&amp;100-1100|100&amp;120-1100|120&amp;140-900|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-97300|1&amp;10-0|10&amp;20-1100|20&amp;30-600|30&amp;40-700|40&amp;50-100|50&amp;60-100|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G35" s="13">
         <v>500</v>
@@ -2249,10 +2272,11 @@
         <v>4</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>35</v>
+        <v>51</v>
+      </c>
+      <c r="F36" s="7" t="str">
+        <f>F35</f>
+        <v>1,0&amp;1-85200|1&amp;10-0|10&amp;20-2400|20&amp;40-5000|40&amp;60-3200|60&amp;80-1600|80&amp;100-1000|100&amp;120-500|120&amp;140-400|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-69300|1&amp;10-0|10&amp;20-4900|20&amp;30-5600|30&amp;40-4500|40&amp;50-3600|50&amp;60-2800|60&amp;70-2100|70&amp;80-1500|80&amp;90-1100|90&amp;100-1100|100&amp;120-1100|120&amp;140-900|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-97300|1&amp;10-0|10&amp;20-1100|20&amp;30-600|30&amp;40-700|40&amp;50-100|50&amp;60-100|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G36" s="13">
         <v>-500</v>
@@ -2276,10 +2300,11 @@
         <v>5</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>35</v>
+        <v>52</v>
+      </c>
+      <c r="F37" s="7" t="str">
+        <f>F36</f>
+        <v>1,0&amp;1-85200|1&amp;10-0|10&amp;20-2400|20&amp;40-5000|40&amp;60-3200|60&amp;80-1600|80&amp;100-1000|100&amp;120-500|120&amp;140-400|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-69300|1&amp;10-0|10&amp;20-4900|20&amp;30-5600|30&amp;40-4500|40&amp;50-3600|50&amp;60-2800|60&amp;70-2100|70&amp;80-1500|80&amp;90-1100|90&amp;100-1100|100&amp;120-1100|120&amp;140-900|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-97300|1&amp;10-0|10&amp;20-1100|20&amp;30-600|30&amp;40-700|40&amp;50-100|50&amp;60-100|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G37" s="13">
         <v>-1000</v>
@@ -2303,10 +2328,11 @@
         <v>6</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>35</v>
+        <v>53</v>
+      </c>
+      <c r="F38" s="7" t="str">
+        <f>F37</f>
+        <v>1,0&amp;1-85200|1&amp;10-0|10&amp;20-2400|20&amp;40-5000|40&amp;60-3200|60&amp;80-1600|80&amp;100-1000|100&amp;120-500|120&amp;140-400|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-69300|1&amp;10-0|10&amp;20-4900|20&amp;30-5600|30&amp;40-4500|40&amp;50-3600|50&amp;60-2800|60&amp;70-2100|70&amp;80-1500|80&amp;90-1100|90&amp;100-1100|100&amp;120-1100|120&amp;140-900|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-97300|1&amp;10-0|10&amp;20-1100|20&amp;30-600|30&amp;40-700|40&amp;50-100|50&amp;60-100|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G38" s="13">
         <v>-2000</v>
@@ -2330,10 +2356,11 @@
         <v>7</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>35</v>
+        <v>54</v>
+      </c>
+      <c r="F39" s="7" t="str">
+        <f>F38</f>
+        <v>1,0&amp;1-85200|1&amp;10-0|10&amp;20-2400|20&amp;40-5000|40&amp;60-3200|60&amp;80-1600|80&amp;100-1000|100&amp;120-500|120&amp;140-400|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-69300|1&amp;10-0|10&amp;20-4900|20&amp;30-5600|30&amp;40-4500|40&amp;50-3600|50&amp;60-2800|60&amp;70-2100|70&amp;80-1500|80&amp;90-1100|90&amp;100-1100|100&amp;120-1100|120&amp;140-900|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-97300|1&amp;10-0|10&amp;20-1100|20&amp;30-600|30&amp;40-700|40&amp;50-100|50&amp;60-100|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G39" s="13">
         <v>-999999</v>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="63">
   <si>
     <t>id</t>
   </si>
@@ -258,6 +258,30 @@
   </si>
   <si>
     <t>财神</t>
+  </si>
+  <si>
+    <t>1_9944|2_1|3_55</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-65000|1&amp;10-14000|10&amp;20-8000|20&amp;40-5000|40&amp;60-2500|60&amp;80-1500|80&amp;100-1000|100&amp;120-1100|120&amp;140-500|140&amp;160-500|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-25|280&amp;300-25|300&amp;500-150|500&amp;800-150|800&amp;1000-25|1000&amp;1500-25|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-88700|1&amp;10-5400|10&amp;20-3500|20&amp;30-1000|30&amp;40-800|40&amp;50-300|50&amp;60-100|60&amp;70-100|70&amp;80-100|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-1100|10&amp;20-1900|20&amp;30-1900|30&amp;40-2000|40&amp;50-2000|50&amp;60-1500|60&amp;70-1700|70&amp;80-1400|80&amp;90-1400|90&amp;100-1100|100&amp;120-2300|120&amp;140-1900|140&amp;160-1600|160&amp;180-1300|180&amp;200-1000|200&amp;300-6000|300&amp;500-16000|500&amp;800-18000|800&amp;1000-9850|1000&amp;1500-8000|1500&amp;2000-6800|2000&amp;3000-5300|3000&amp;4000-2700|4000&amp;5000-1200|5000&amp;6000-700|6000&amp;7000-400|7000&amp;8000-300|8000&amp;9000-200|9000&amp;10000-100|10000&amp;11000-100|11000&amp;12000-100|12000&amp;15000-100|15000&amp;20000-50|20000&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>1_9949|2_1|3_50</t>
+  </si>
+  <si>
+    <t>1_9954|2_1|3_45</t>
+  </si>
+  <si>
+    <t>1_9964|2_1|3_35</t>
+  </si>
+  <si>
+    <t>1_9974|2_1|3_25</t>
+  </si>
+  <si>
+    <t>1_9979|2_1|3_20</t>
+  </si>
+  <si>
+    <t>1_9984|2_1|3_15</t>
   </si>
   <si>
     <t>埃及艳后</t>
@@ -1998,10 +2022,10 @@
         <v>1</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>35</v>
+        <v>46</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="G26" s="9">
         <v>2000</v>
@@ -2025,10 +2049,11 @@
         <v>2</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>35</v>
+        <v>48</v>
+      </c>
+      <c r="F27" s="7" t="str">
+        <f t="shared" ref="F27:F32" si="2">F26</f>
+        <v>1,0&amp;1-65000|1&amp;10-14000|10&amp;20-8000|20&amp;40-5000|40&amp;60-2500|60&amp;80-1500|80&amp;100-1000|100&amp;120-1100|120&amp;140-500|140&amp;160-500|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-25|280&amp;300-25|300&amp;500-150|500&amp;800-150|800&amp;1000-25|1000&amp;1500-25|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-88700|1&amp;10-5400|10&amp;20-3500|20&amp;30-1000|30&amp;40-800|40&amp;50-300|50&amp;60-100|60&amp;70-100|70&amp;80-100|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-1100|10&amp;20-1900|20&amp;30-1900|30&amp;40-2000|40&amp;50-2000|50&amp;60-1500|60&amp;70-1700|70&amp;80-1400|80&amp;90-1400|90&amp;100-1100|100&amp;120-2300|120&amp;140-1900|140&amp;160-1600|160&amp;180-1300|180&amp;200-1000|200&amp;300-6000|300&amp;500-16000|500&amp;800-18000|800&amp;1000-9850|1000&amp;1500-8000|1500&amp;2000-6800|2000&amp;3000-5300|3000&amp;4000-2700|4000&amp;5000-1200|5000&amp;6000-700|6000&amp;7000-400|7000&amp;8000-300|8000&amp;9000-200|9000&amp;10000-100|10000&amp;11000-100|11000&amp;12000-100|12000&amp;15000-100|15000&amp;20000-50|20000&amp;99999999-0</v>
       </c>
       <c r="G27" s="9">
         <v>1000</v>
@@ -2052,10 +2077,11 @@
         <v>3</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>35</v>
+        <v>49</v>
+      </c>
+      <c r="F28" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>1,0&amp;1-65000|1&amp;10-14000|10&amp;20-8000|20&amp;40-5000|40&amp;60-2500|60&amp;80-1500|80&amp;100-1000|100&amp;120-1100|120&amp;140-500|140&amp;160-500|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-25|280&amp;300-25|300&amp;500-150|500&amp;800-150|800&amp;1000-25|1000&amp;1500-25|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-88700|1&amp;10-5400|10&amp;20-3500|20&amp;30-1000|30&amp;40-800|40&amp;50-300|50&amp;60-100|60&amp;70-100|70&amp;80-100|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-1100|10&amp;20-1900|20&amp;30-1900|30&amp;40-2000|40&amp;50-2000|50&amp;60-1500|60&amp;70-1700|70&amp;80-1400|80&amp;90-1400|90&amp;100-1100|100&amp;120-2300|120&amp;140-1900|140&amp;160-1600|160&amp;180-1300|180&amp;200-1000|200&amp;300-6000|300&amp;500-16000|500&amp;800-18000|800&amp;1000-9850|1000&amp;1500-8000|1500&amp;2000-6800|2000&amp;3000-5300|3000&amp;4000-2700|4000&amp;5000-1200|5000&amp;6000-700|6000&amp;7000-400|7000&amp;8000-300|8000&amp;9000-200|9000&amp;10000-100|10000&amp;11000-100|11000&amp;12000-100|12000&amp;15000-100|15000&amp;20000-50|20000&amp;99999999-0</v>
       </c>
       <c r="G28" s="9">
         <v>500</v>
@@ -2079,10 +2105,11 @@
         <v>4</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>35</v>
+        <v>50</v>
+      </c>
+      <c r="F29" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>1,0&amp;1-65000|1&amp;10-14000|10&amp;20-8000|20&amp;40-5000|40&amp;60-2500|60&amp;80-1500|80&amp;100-1000|100&amp;120-1100|120&amp;140-500|140&amp;160-500|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-25|280&amp;300-25|300&amp;500-150|500&amp;800-150|800&amp;1000-25|1000&amp;1500-25|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-88700|1&amp;10-5400|10&amp;20-3500|20&amp;30-1000|30&amp;40-800|40&amp;50-300|50&amp;60-100|60&amp;70-100|70&amp;80-100|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-1100|10&amp;20-1900|20&amp;30-1900|30&amp;40-2000|40&amp;50-2000|50&amp;60-1500|60&amp;70-1700|70&amp;80-1400|80&amp;90-1400|90&amp;100-1100|100&amp;120-2300|120&amp;140-1900|140&amp;160-1600|160&amp;180-1300|180&amp;200-1000|200&amp;300-6000|300&amp;500-16000|500&amp;800-18000|800&amp;1000-9850|1000&amp;1500-8000|1500&amp;2000-6800|2000&amp;3000-5300|3000&amp;4000-2700|4000&amp;5000-1200|5000&amp;6000-700|6000&amp;7000-400|7000&amp;8000-300|8000&amp;9000-200|9000&amp;10000-100|10000&amp;11000-100|11000&amp;12000-100|12000&amp;15000-100|15000&amp;20000-50|20000&amp;99999999-0</v>
       </c>
       <c r="G29" s="9">
         <v>-500</v>
@@ -2106,10 +2133,11 @@
         <v>5</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>35</v>
+        <v>51</v>
+      </c>
+      <c r="F30" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>1,0&amp;1-65000|1&amp;10-14000|10&amp;20-8000|20&amp;40-5000|40&amp;60-2500|60&amp;80-1500|80&amp;100-1000|100&amp;120-1100|120&amp;140-500|140&amp;160-500|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-25|280&amp;300-25|300&amp;500-150|500&amp;800-150|800&amp;1000-25|1000&amp;1500-25|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-88700|1&amp;10-5400|10&amp;20-3500|20&amp;30-1000|30&amp;40-800|40&amp;50-300|50&amp;60-100|60&amp;70-100|70&amp;80-100|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-1100|10&amp;20-1900|20&amp;30-1900|30&amp;40-2000|40&amp;50-2000|50&amp;60-1500|60&amp;70-1700|70&amp;80-1400|80&amp;90-1400|90&amp;100-1100|100&amp;120-2300|120&amp;140-1900|140&amp;160-1600|160&amp;180-1300|180&amp;200-1000|200&amp;300-6000|300&amp;500-16000|500&amp;800-18000|800&amp;1000-9850|1000&amp;1500-8000|1500&amp;2000-6800|2000&amp;3000-5300|3000&amp;4000-2700|4000&amp;5000-1200|5000&amp;6000-700|6000&amp;7000-400|7000&amp;8000-300|8000&amp;9000-200|9000&amp;10000-100|10000&amp;11000-100|11000&amp;12000-100|12000&amp;15000-100|15000&amp;20000-50|20000&amp;99999999-0</v>
       </c>
       <c r="G30" s="9">
         <v>-1000</v>
@@ -2133,10 +2161,11 @@
         <v>6</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>35</v>
+        <v>52</v>
+      </c>
+      <c r="F31" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>1,0&amp;1-65000|1&amp;10-14000|10&amp;20-8000|20&amp;40-5000|40&amp;60-2500|60&amp;80-1500|80&amp;100-1000|100&amp;120-1100|120&amp;140-500|140&amp;160-500|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-25|280&amp;300-25|300&amp;500-150|500&amp;800-150|800&amp;1000-25|1000&amp;1500-25|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-88700|1&amp;10-5400|10&amp;20-3500|20&amp;30-1000|30&amp;40-800|40&amp;50-300|50&amp;60-100|60&amp;70-100|70&amp;80-100|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-1100|10&amp;20-1900|20&amp;30-1900|30&amp;40-2000|40&amp;50-2000|50&amp;60-1500|60&amp;70-1700|70&amp;80-1400|80&amp;90-1400|90&amp;100-1100|100&amp;120-2300|120&amp;140-1900|140&amp;160-1600|160&amp;180-1300|180&amp;200-1000|200&amp;300-6000|300&amp;500-16000|500&amp;800-18000|800&amp;1000-9850|1000&amp;1500-8000|1500&amp;2000-6800|2000&amp;3000-5300|3000&amp;4000-2700|4000&amp;5000-1200|5000&amp;6000-700|6000&amp;7000-400|7000&amp;8000-300|8000&amp;9000-200|9000&amp;10000-100|10000&amp;11000-100|11000&amp;12000-100|12000&amp;15000-100|15000&amp;20000-50|20000&amp;99999999-0</v>
       </c>
       <c r="G31" s="9">
         <v>-2000</v>
@@ -2160,10 +2189,11 @@
         <v>7</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>35</v>
+        <v>53</v>
+      </c>
+      <c r="F32" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>1,0&amp;1-65000|1&amp;10-14000|10&amp;20-8000|20&amp;40-5000|40&amp;60-2500|60&amp;80-1500|80&amp;100-1000|100&amp;120-1100|120&amp;140-500|140&amp;160-500|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-25|280&amp;300-25|300&amp;500-150|500&amp;800-150|800&amp;1000-25|1000&amp;1500-25|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-88700|1&amp;10-5400|10&amp;20-3500|20&amp;30-1000|30&amp;40-800|40&amp;50-300|50&amp;60-100|60&amp;70-100|70&amp;80-100|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-1100|10&amp;20-1900|20&amp;30-1900|30&amp;40-2000|40&amp;50-2000|50&amp;60-1500|60&amp;70-1700|70&amp;80-1400|80&amp;90-1400|90&amp;100-1100|100&amp;120-2300|120&amp;140-1900|140&amp;160-1600|160&amp;180-1300|180&amp;200-1000|200&amp;300-6000|300&amp;500-16000|500&amp;800-18000|800&amp;1000-9850|1000&amp;1500-8000|1500&amp;2000-6800|2000&amp;3000-5300|3000&amp;4000-2700|4000&amp;5000-1200|5000&amp;6000-700|6000&amp;7000-400|7000&amp;8000-300|8000&amp;9000-200|9000&amp;10000-100|10000&amp;11000-100|11000&amp;12000-100|12000&amp;15000-100|15000&amp;20000-50|20000&amp;99999999-0</v>
       </c>
       <c r="G32" s="9">
         <v>-999999</v>
@@ -2183,16 +2213,16 @@
         <v>101400</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D33" s="13">
         <v>1</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G33" s="13">
         <v>2000</v>
@@ -2216,10 +2246,10 @@
         <v>2</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F34" s="7" t="str">
-        <f>F33</f>
+        <f t="shared" ref="F34:F39" si="3">F33</f>
         <v>1,0&amp;1-85200|1&amp;10-0|10&amp;20-2400|20&amp;40-5000|40&amp;60-3200|60&amp;80-1600|80&amp;100-1000|100&amp;120-500|120&amp;140-400|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-69300|1&amp;10-0|10&amp;20-4900|20&amp;30-5600|30&amp;40-4500|40&amp;50-3600|50&amp;60-2800|60&amp;70-2100|70&amp;80-1500|80&amp;90-1100|90&amp;100-1100|100&amp;120-1100|120&amp;140-900|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-97300|1&amp;10-0|10&amp;20-1100|20&amp;30-600|30&amp;40-700|40&amp;50-100|50&amp;60-100|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G34" s="13">
@@ -2244,10 +2274,10 @@
         <v>3</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F35" s="7" t="str">
-        <f>F34</f>
+        <f t="shared" si="3"/>
         <v>1,0&amp;1-85200|1&amp;10-0|10&amp;20-2400|20&amp;40-5000|40&amp;60-3200|60&amp;80-1600|80&amp;100-1000|100&amp;120-500|120&amp;140-400|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-69300|1&amp;10-0|10&amp;20-4900|20&amp;30-5600|30&amp;40-4500|40&amp;50-3600|50&amp;60-2800|60&amp;70-2100|70&amp;80-1500|80&amp;90-1100|90&amp;100-1100|100&amp;120-1100|120&amp;140-900|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-97300|1&amp;10-0|10&amp;20-1100|20&amp;30-600|30&amp;40-700|40&amp;50-100|50&amp;60-100|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G35" s="13">
@@ -2272,10 +2302,10 @@
         <v>4</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F36" s="7" t="str">
-        <f>F35</f>
+        <f t="shared" si="3"/>
         <v>1,0&amp;1-85200|1&amp;10-0|10&amp;20-2400|20&amp;40-5000|40&amp;60-3200|60&amp;80-1600|80&amp;100-1000|100&amp;120-500|120&amp;140-400|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-69300|1&amp;10-0|10&amp;20-4900|20&amp;30-5600|30&amp;40-4500|40&amp;50-3600|50&amp;60-2800|60&amp;70-2100|70&amp;80-1500|80&amp;90-1100|90&amp;100-1100|100&amp;120-1100|120&amp;140-900|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-97300|1&amp;10-0|10&amp;20-1100|20&amp;30-600|30&amp;40-700|40&amp;50-100|50&amp;60-100|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G36" s="13">
@@ -2300,10 +2330,10 @@
         <v>5</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F37" s="7" t="str">
-        <f>F36</f>
+        <f t="shared" si="3"/>
         <v>1,0&amp;1-85200|1&amp;10-0|10&amp;20-2400|20&amp;40-5000|40&amp;60-3200|60&amp;80-1600|80&amp;100-1000|100&amp;120-500|120&amp;140-400|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-69300|1&amp;10-0|10&amp;20-4900|20&amp;30-5600|30&amp;40-4500|40&amp;50-3600|50&amp;60-2800|60&amp;70-2100|70&amp;80-1500|80&amp;90-1100|90&amp;100-1100|100&amp;120-1100|120&amp;140-900|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-97300|1&amp;10-0|10&amp;20-1100|20&amp;30-600|30&amp;40-700|40&amp;50-100|50&amp;60-100|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G37" s="13">
@@ -2328,10 +2358,10 @@
         <v>6</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F38" s="7" t="str">
-        <f>F37</f>
+        <f t="shared" si="3"/>
         <v>1,0&amp;1-85200|1&amp;10-0|10&amp;20-2400|20&amp;40-5000|40&amp;60-3200|60&amp;80-1600|80&amp;100-1000|100&amp;120-500|120&amp;140-400|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-69300|1&amp;10-0|10&amp;20-4900|20&amp;30-5600|30&amp;40-4500|40&amp;50-3600|50&amp;60-2800|60&amp;70-2100|70&amp;80-1500|80&amp;90-1100|90&amp;100-1100|100&amp;120-1100|120&amp;140-900|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-97300|1&amp;10-0|10&amp;20-1100|20&amp;30-600|30&amp;40-700|40&amp;50-100|50&amp;60-100|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G38" s="13">
@@ -2356,10 +2386,10 @@
         <v>7</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F39" s="7" t="str">
-        <f>F38</f>
+        <f t="shared" si="3"/>
         <v>1,0&amp;1-85200|1&amp;10-0|10&amp;20-2400|20&amp;40-5000|40&amp;60-3200|60&amp;80-1600|80&amp;100-1000|100&amp;120-500|120&amp;140-400|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-69300|1&amp;10-0|10&amp;20-4900|20&amp;30-5600|30&amp;40-4500|40&amp;50-3600|50&amp;60-2800|60&amp;70-2100|70&amp;80-1500|80&amp;90-1100|90&amp;100-1100|100&amp;120-1100|120&amp;140-900|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-97300|1&amp;10-0|10&amp;20-1100|20&amp;30-600|30&amp;40-700|40&amp;50-100|50&amp;60-100|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
       <c r="G39" s="13">

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="24045" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="69">
   <si>
     <t>id</t>
   </si>
@@ -224,91 +224,109 @@
     <t>超级明星</t>
   </si>
   <si>
-    <t>1_9000|2_550|3_450</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-60000|1&amp;10-2000|10&amp;20-3000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-3000|80&amp;90-2000|90&amp;100-2000|100&amp;120-1500|120&amp;140-1500|140&amp;160-1200|160&amp;180-1200|180&amp;200-800|200&amp;300-600|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|5000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-200|140&amp;160-500|160&amp;180-600|180&amp;200-700|200&amp;300-2000|300&amp;500-16000|500&amp;800-36000|800&amp;1000-22000|1000&amp;1500-20850|1500&amp;2000-1030|2000&amp;3000-20|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|5000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-4000|500&amp;800-23000|800&amp;1000-23000|1000&amp;1500-35000|1500&amp;2000-12000|2000&amp;3000-2900|3000&amp;4000-100|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|5000&amp;99999999-0;4,0&amp;1-58000|1&amp;10-10000|10&amp;20-12200|20&amp;30-6000|30&amp;40-5700|40&amp;50-2000|50&amp;60-1000|60&amp;70-1000|70&amp;80-800|80&amp;90-500|90&amp;100-500|100&amp;120-500|120&amp;140-500|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-200|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|5000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-1740|90&amp;100-4000|100&amp;120-15000|120&amp;140-20000|140&amp;160-20000|160&amp;180-15200|180&amp;200-12000|200&amp;300-11000|300&amp;500-1000|500&amp;800-50|800&amp;1000-10|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|5000&amp;99999999-0;6,0&amp;1-500|1&amp;10-0|10&amp;20-100|20&amp;30-100|30&amp;40-100|40&amp;50-100|50&amp;60-100|60&amp;70-200|70&amp;80-200|80&amp;90-200|90&amp;100-500|100&amp;120-500|120&amp;140-1000|140&amp;160-1000|160&amp;180-1000|180&amp;200-1000|200&amp;300-8000|300&amp;500-15000|500&amp;800-18000|800&amp;1000-18000|1000&amp;1500-10450|1500&amp;2000-10000|2000&amp;3000-5000|3000&amp;4000-3000|4000&amp;5000-2000|5000&amp;6000-1500|6000&amp;7000-1000|7000&amp;8000-500|8000&amp;9000-500|9000&amp;10000-200|10000&amp;11000-100|11000&amp;12000-50|12000&amp;15000-50|15000&amp;20000-50|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-10000|800&amp;1000-18000|1000&amp;1500-47000|1500&amp;2000-20000|2000&amp;3000-5000|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|5000&amp;99999999-0</t>
+    <t>1_9710|2_180|3_110</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-73800|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-2000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-12600|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-74800|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-3200|8&amp;9-1600|9&amp;10-0|10&amp;12-3900|12&amp;14-1600|14&amp;16-1200|16&amp;18-2600|18&amp;20-200|20&amp;24-1900|24&amp;28-1700|28&amp;32-400|32&amp;36-900|36&amp;40-700|40&amp;48-500|48&amp;56-700|56&amp;64-600|64&amp;72-400|72&amp;80-100|80&amp;96-900|96&amp;112-900|112&amp;128-400|128&amp;144-300|144&amp;160-200|160&amp;192-0|192&amp;224-200|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>1_9760|2_150|3_90</t>
+  </si>
+  <si>
+    <t>1_9810|2_120|3_70</t>
+  </si>
+  <si>
+    <t>1_9860|2_90|3_50</t>
+  </si>
+  <si>
+    <t>1_9910|2_60|3_30</t>
+  </si>
+  <si>
+    <t>1_9960|2_30|3_10</t>
+  </si>
+  <si>
+    <t>1_10000|2_0|3_0</t>
   </si>
   <si>
     <t>麻将胡了</t>
   </si>
   <si>
-    <t>1_9840|2_160</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-42000|1&amp;10-20000|10&amp;20-20000|20&amp;40-10000|40&amp;60-3200|60&amp;80-1500|80&amp;100-1000|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-100|200&amp;220-0|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-100|280&amp;300-100|300&amp;500-4000|500&amp;800-10600|800&amp;1000-12000|1000&amp;1500-25000|1500&amp;2000-25000|2000&amp;4000-20000|4000&amp;6000-2600|6000&amp;8000-200|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0</t>
-  </si>
-  <si>
-    <t>1_9870|2_130</t>
-  </si>
-  <si>
-    <t>1_9890|2_110</t>
-  </si>
-  <si>
-    <t>1_9920|2_80</t>
-  </si>
-  <si>
-    <t>1_9950|2_50</t>
-  </si>
-  <si>
-    <t>1_9970|2_30</t>
-  </si>
-  <si>
-    <t>1_10000|2_0</t>
+    <t>1_9990|2_85</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-65600|1&amp;20-13900|20&amp;40-9000|40&amp;60-4200|60&amp;80-2500|80&amp;100-1200|100&amp;120-800|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-400|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;240-400|240&amp;280-1000|280&amp;320-1000|320&amp;360-1000|360&amp;400-1000|400&amp;480-3000|480&amp;560-3500|560&amp;640-5000|640&amp;720-8000|720&amp;800-8000|800&amp;960-10000|960&amp;1120-10000|1120&amp;1280-10000|1280&amp;1440-8000|1440&amp;1600-8000|1600&amp;1920-8000|1920&amp;2240-5000|2240&amp;2560-4000|2560&amp;2880-2000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>1_9990|2_75</t>
+  </si>
+  <si>
+    <t>1_9990|2_65</t>
+  </si>
+  <si>
+    <t>1_9945|2_55</t>
+  </si>
+  <si>
+    <t>1_9990|2_45</t>
+  </si>
+  <si>
+    <t>1_9990|2_35</t>
+  </si>
+  <si>
+    <t>1_9990|2_25</t>
   </si>
   <si>
     <t>财神</t>
   </si>
   <si>
-    <t>1_9944|2_1|3_55</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-65000|1&amp;10-14000|10&amp;20-8000|20&amp;40-5000|40&amp;60-2500|60&amp;80-1500|80&amp;100-1000|100&amp;120-1100|120&amp;140-500|140&amp;160-500|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-25|280&amp;300-25|300&amp;500-150|500&amp;800-150|800&amp;1000-25|1000&amp;1500-25|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-88700|1&amp;10-5400|10&amp;20-3500|20&amp;30-1000|30&amp;40-800|40&amp;50-300|50&amp;60-100|60&amp;70-100|70&amp;80-100|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-1100|10&amp;20-1900|20&amp;30-1900|30&amp;40-2000|40&amp;50-2000|50&amp;60-1500|60&amp;70-1700|70&amp;80-1400|80&amp;90-1400|90&amp;100-1100|100&amp;120-2300|120&amp;140-1900|140&amp;160-1600|160&amp;180-1300|180&amp;200-1000|200&amp;300-6000|300&amp;500-16000|500&amp;800-18000|800&amp;1000-9850|1000&amp;1500-8000|1500&amp;2000-6800|2000&amp;3000-5300|3000&amp;4000-2700|4000&amp;5000-1200|5000&amp;6000-700|6000&amp;7000-400|7000&amp;8000-300|8000&amp;9000-200|9000&amp;10000-100|10000&amp;11000-100|11000&amp;12000-100|12000&amp;15000-100|15000&amp;20000-50|20000&amp;99999999-0</t>
-  </si>
-  <si>
-    <t>1_9949|2_1|3_50</t>
-  </si>
-  <si>
-    <t>1_9954|2_1|3_45</t>
-  </si>
-  <si>
-    <t>1_9964|2_1|3_35</t>
-  </si>
-  <si>
-    <t>1_9974|2_1|3_25</t>
-  </si>
-  <si>
-    <t>1_9979|2_1|3_20</t>
-  </si>
-  <si>
-    <t>1_9984|2_1|3_15</t>
+    <t>1_9849|2_1|3_150</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>1_9874|2_1|3_125</t>
+  </si>
+  <si>
+    <t>1_9890|2_0|3_110</t>
+  </si>
+  <si>
+    <t>1_9900|2_0|3_100</t>
+  </si>
+  <si>
+    <t>1_9910|2_0|3_90</t>
+  </si>
+  <si>
+    <t>1_9925|2_0|3_75</t>
+  </si>
+  <si>
+    <t>1_9950|2_0|3_50</t>
   </si>
   <si>
     <t>埃及艳后</t>
   </si>
   <si>
-    <t>1_5500|2_4500|3_1</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-85200|1&amp;10-0|10&amp;20-2400|20&amp;40-5000|40&amp;60-3200|60&amp;80-1600|80&amp;100-1000|100&amp;120-500|120&amp;140-400|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-69300|1&amp;10-0|10&amp;20-4900|20&amp;30-5600|30&amp;40-4500|40&amp;50-3600|50&amp;60-2800|60&amp;70-2100|70&amp;80-1500|80&amp;90-1100|90&amp;100-1100|100&amp;120-1100|120&amp;140-900|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-97300|1&amp;10-0|10&amp;20-1100|20&amp;30-600|30&amp;40-700|40&amp;50-100|50&amp;60-100|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</t>
-  </si>
-  <si>
-    <t>1_6000|2_4000|3_1</t>
-  </si>
-  <si>
-    <t>1_6500|2_3500|3_1</t>
-  </si>
-  <si>
-    <t>1_7000|2_3000|3_1</t>
-  </si>
-  <si>
-    <t>1_7500|2_2500|3_1</t>
-  </si>
-  <si>
-    <t>1_8000|2_2000|3_1</t>
-  </si>
-  <si>
-    <t>1_8500|2_1500|3_1</t>
+    <t>1_2999|2_7000|3_1</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-77700|1&amp;10-3700|10&amp;20-7000|20&amp;30-4100|30&amp;40-2000|40&amp;50-1700|50&amp;60-1000|60&amp;70-700|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65000|1&amp;10-3200|10&amp;20-8800|20&amp;30-6400|30&amp;40-3700|40&amp;50-3000|50&amp;60-2300|60&amp;70-1700|70&amp;80-1200|80&amp;90-900|90&amp;100-900|100&amp;120-900|120&amp;140-800|140&amp;160-400|160&amp;180-300|180&amp;200-200|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97200|1&amp;10-0|10&amp;20-1700|20&amp;30-1100|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>1_3999|2_6000|3_1</t>
+  </si>
+  <si>
+    <t>1_4999|2_5000|3_1</t>
+  </si>
+  <si>
+    <t>1_5499|2_4500|3_1</t>
+  </si>
+  <si>
+    <t>1_5999|2_4000|3_1</t>
+  </si>
+  <si>
+    <t>1_6999|2_3000|3_1</t>
+  </si>
+  <si>
+    <t>1_7999|2_2000|3_1</t>
   </si>
 </sst>
 </file>
@@ -1636,7 +1654,7 @@
       <c r="E12" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="8" t="s">
         <v>35</v>
       </c>
       <c r="G12" s="9">
@@ -1661,10 +1679,11 @@
         <v>2</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="F13" s="7" t="str">
+        <f t="shared" ref="F13:F18" si="1">F12</f>
+        <v>1,0&amp;1-73800|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-2000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-12600|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-74800|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-3200|8&amp;9-1600|9&amp;10-0|10&amp;12-3900|12&amp;14-1600|14&amp;16-1200|16&amp;18-2600|18&amp;20-200|20&amp;24-1900|24&amp;28-1700|28&amp;32-400|32&amp;36-900|36&amp;40-700|40&amp;48-500|48&amp;56-700|56&amp;64-600|64&amp;72-400|72&amp;80-100|80&amp;96-900|96&amp;112-900|112&amp;128-400|128&amp;144-300|144&amp;160-200|160&amp;192-0|192&amp;224-200|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
       <c r="G13" s="9">
         <v>1000</v>
@@ -1688,10 +1707,11 @@
         <v>3</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="F14" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>1,0&amp;1-73800|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-2000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-12600|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-74800|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-3200|8&amp;9-1600|9&amp;10-0|10&amp;12-3900|12&amp;14-1600|14&amp;16-1200|16&amp;18-2600|18&amp;20-200|20&amp;24-1900|24&amp;28-1700|28&amp;32-400|32&amp;36-900|36&amp;40-700|40&amp;48-500|48&amp;56-700|56&amp;64-600|64&amp;72-400|72&amp;80-100|80&amp;96-900|96&amp;112-900|112&amp;128-400|128&amp;144-300|144&amp;160-200|160&amp;192-0|192&amp;224-200|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
       <c r="G14" s="9">
         <v>500</v>
@@ -1715,10 +1735,11 @@
         <v>4</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="F15" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>1,0&amp;1-73800|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-2000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-12600|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-74800|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-3200|8&amp;9-1600|9&amp;10-0|10&amp;12-3900|12&amp;14-1600|14&amp;16-1200|16&amp;18-2600|18&amp;20-200|20&amp;24-1900|24&amp;28-1700|28&amp;32-400|32&amp;36-900|36&amp;40-700|40&amp;48-500|48&amp;56-700|56&amp;64-600|64&amp;72-400|72&amp;80-100|80&amp;96-900|96&amp;112-900|112&amp;128-400|128&amp;144-300|144&amp;160-200|160&amp;192-0|192&amp;224-200|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
       <c r="G15" s="9">
         <v>-500</v>
@@ -1742,10 +1763,11 @@
         <v>5</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="F16" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>1,0&amp;1-73800|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-2000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-12600|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-74800|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-3200|8&amp;9-1600|9&amp;10-0|10&amp;12-3900|12&amp;14-1600|14&amp;16-1200|16&amp;18-2600|18&amp;20-200|20&amp;24-1900|24&amp;28-1700|28&amp;32-400|32&amp;36-900|36&amp;40-700|40&amp;48-500|48&amp;56-700|56&amp;64-600|64&amp;72-400|72&amp;80-100|80&amp;96-900|96&amp;112-900|112&amp;128-400|128&amp;144-300|144&amp;160-200|160&amp;192-0|192&amp;224-200|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
       <c r="G16" s="9">
         <v>-1000</v>
@@ -1769,10 +1791,11 @@
         <v>6</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>35</v>
+        <v>40</v>
+      </c>
+      <c r="F17" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>1,0&amp;1-73800|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-2000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-12600|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-74800|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-3200|8&amp;9-1600|9&amp;10-0|10&amp;12-3900|12&amp;14-1600|14&amp;16-1200|16&amp;18-2600|18&amp;20-200|20&amp;24-1900|24&amp;28-1700|28&amp;32-400|32&amp;36-900|36&amp;40-700|40&amp;48-500|48&amp;56-700|56&amp;64-600|64&amp;72-400|72&amp;80-100|80&amp;96-900|96&amp;112-900|112&amp;128-400|128&amp;144-300|144&amp;160-200|160&amp;192-0|192&amp;224-200|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
       <c r="G17" s="9">
         <v>-2000</v>
@@ -1796,10 +1819,11 @@
         <v>7</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>35</v>
+        <v>41</v>
+      </c>
+      <c r="F18" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>1,0&amp;1-73800|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-2000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-12600|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-74800|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-3200|8&amp;9-1600|9&amp;10-0|10&amp;12-3900|12&amp;14-1600|14&amp;16-1200|16&amp;18-2600|18&amp;20-200|20&amp;24-1900|24&amp;28-1700|28&amp;32-400|32&amp;36-900|36&amp;40-700|40&amp;48-500|48&amp;56-700|56&amp;64-600|64&amp;72-400|72&amp;80-100|80&amp;96-900|96&amp;112-900|112&amp;128-400|128&amp;144-300|144&amp;160-200|160&amp;192-0|192&amp;224-200|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
       <c r="G18" s="9">
         <v>-999999</v>
@@ -1819,16 +1843,16 @@
         <v>100700</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D19" s="10">
         <v>1</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G19" s="10">
         <v>2000</v>
@@ -1852,11 +1876,11 @@
         <v>2</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F20" s="12" t="str">
-        <f t="shared" ref="F20:F25" si="1">F19</f>
-        <v>1,0&amp;1-42000|1&amp;10-20000|10&amp;20-20000|20&amp;40-10000|40&amp;60-3200|60&amp;80-1500|80&amp;100-1000|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-100|200&amp;220-0|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-100|280&amp;300-100|300&amp;500-4000|500&amp;800-10600|800&amp;1000-12000|1000&amp;1500-25000|1500&amp;2000-25000|2000&amp;4000-20000|4000&amp;6000-2600|6000&amp;8000-200|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0</v>
+        <f t="shared" ref="F20:F25" si="2">F19</f>
+        <v>1,0&amp;1-65600|1&amp;20-13900|20&amp;40-9000|40&amp;60-4200|60&amp;80-2500|80&amp;100-1200|100&amp;120-800|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-400|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;240-400|240&amp;280-1000|280&amp;320-1000|320&amp;360-1000|360&amp;400-1000|400&amp;480-3000|480&amp;560-3500|560&amp;640-5000|640&amp;720-8000|720&amp;800-8000|800&amp;960-10000|960&amp;1120-10000|1120&amp;1280-10000|1280&amp;1440-8000|1440&amp;1600-8000|1600&amp;1920-8000|1920&amp;2240-5000|2240&amp;2560-4000|2560&amp;2880-2000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G20" s="10">
         <v>1000</v>
@@ -1880,11 +1904,11 @@
         <v>3</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F21" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>1,0&amp;1-42000|1&amp;10-20000|10&amp;20-20000|20&amp;40-10000|40&amp;60-3200|60&amp;80-1500|80&amp;100-1000|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-100|200&amp;220-0|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-100|280&amp;300-100|300&amp;500-4000|500&amp;800-10600|800&amp;1000-12000|1000&amp;1500-25000|1500&amp;2000-25000|2000&amp;4000-20000|4000&amp;6000-2600|6000&amp;8000-200|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0</v>
+        <f t="shared" si="2"/>
+        <v>1,0&amp;1-65600|1&amp;20-13900|20&amp;40-9000|40&amp;60-4200|60&amp;80-2500|80&amp;100-1200|100&amp;120-800|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-400|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;240-400|240&amp;280-1000|280&amp;320-1000|320&amp;360-1000|360&amp;400-1000|400&amp;480-3000|480&amp;560-3500|560&amp;640-5000|640&amp;720-8000|720&amp;800-8000|800&amp;960-10000|960&amp;1120-10000|1120&amp;1280-10000|1280&amp;1440-8000|1440&amp;1600-8000|1600&amp;1920-8000|1920&amp;2240-5000|2240&amp;2560-4000|2560&amp;2880-2000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G21" s="10">
         <v>500</v>
@@ -1908,11 +1932,11 @@
         <v>4</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F22" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>1,0&amp;1-42000|1&amp;10-20000|10&amp;20-20000|20&amp;40-10000|40&amp;60-3200|60&amp;80-1500|80&amp;100-1000|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-100|200&amp;220-0|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-100|280&amp;300-100|300&amp;500-4000|500&amp;800-10600|800&amp;1000-12000|1000&amp;1500-25000|1500&amp;2000-25000|2000&amp;4000-20000|4000&amp;6000-2600|6000&amp;8000-200|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0</v>
+        <f t="shared" si="2"/>
+        <v>1,0&amp;1-65600|1&amp;20-13900|20&amp;40-9000|40&amp;60-4200|60&amp;80-2500|80&amp;100-1200|100&amp;120-800|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-400|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;240-400|240&amp;280-1000|280&amp;320-1000|320&amp;360-1000|360&amp;400-1000|400&amp;480-3000|480&amp;560-3500|560&amp;640-5000|640&amp;720-8000|720&amp;800-8000|800&amp;960-10000|960&amp;1120-10000|1120&amp;1280-10000|1280&amp;1440-8000|1440&amp;1600-8000|1600&amp;1920-8000|1920&amp;2240-5000|2240&amp;2560-4000|2560&amp;2880-2000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G22" s="10">
         <v>-500</v>
@@ -1936,11 +1960,11 @@
         <v>5</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F23" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>1,0&amp;1-42000|1&amp;10-20000|10&amp;20-20000|20&amp;40-10000|40&amp;60-3200|60&amp;80-1500|80&amp;100-1000|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-100|200&amp;220-0|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-100|280&amp;300-100|300&amp;500-4000|500&amp;800-10600|800&amp;1000-12000|1000&amp;1500-25000|1500&amp;2000-25000|2000&amp;4000-20000|4000&amp;6000-2600|6000&amp;8000-200|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0</v>
+        <f t="shared" si="2"/>
+        <v>1,0&amp;1-65600|1&amp;20-13900|20&amp;40-9000|40&amp;60-4200|60&amp;80-2500|80&amp;100-1200|100&amp;120-800|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-400|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;240-400|240&amp;280-1000|280&amp;320-1000|320&amp;360-1000|360&amp;400-1000|400&amp;480-3000|480&amp;560-3500|560&amp;640-5000|640&amp;720-8000|720&amp;800-8000|800&amp;960-10000|960&amp;1120-10000|1120&amp;1280-10000|1280&amp;1440-8000|1440&amp;1600-8000|1600&amp;1920-8000|1920&amp;2240-5000|2240&amp;2560-4000|2560&amp;2880-2000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G23" s="10">
         <v>-1000</v>
@@ -1964,11 +1988,11 @@
         <v>6</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F24" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>1,0&amp;1-42000|1&amp;10-20000|10&amp;20-20000|20&amp;40-10000|40&amp;60-3200|60&amp;80-1500|80&amp;100-1000|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-100|200&amp;220-0|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-100|280&amp;300-100|300&amp;500-4000|500&amp;800-10600|800&amp;1000-12000|1000&amp;1500-25000|1500&amp;2000-25000|2000&amp;4000-20000|4000&amp;6000-2600|6000&amp;8000-200|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0</v>
+        <f t="shared" si="2"/>
+        <v>1,0&amp;1-65600|1&amp;20-13900|20&amp;40-9000|40&amp;60-4200|60&amp;80-2500|80&amp;100-1200|100&amp;120-800|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-400|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;240-400|240&amp;280-1000|280&amp;320-1000|320&amp;360-1000|360&amp;400-1000|400&amp;480-3000|480&amp;560-3500|560&amp;640-5000|640&amp;720-8000|720&amp;800-8000|800&amp;960-10000|960&amp;1120-10000|1120&amp;1280-10000|1280&amp;1440-8000|1440&amp;1600-8000|1600&amp;1920-8000|1920&amp;2240-5000|2240&amp;2560-4000|2560&amp;2880-2000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G24" s="10">
         <v>-2000</v>
@@ -1992,11 +2016,11 @@
         <v>7</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F25" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>1,0&amp;1-42000|1&amp;10-20000|10&amp;20-20000|20&amp;40-10000|40&amp;60-3200|60&amp;80-1500|80&amp;100-1000|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-100|200&amp;220-0|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-100|280&amp;300-100|300&amp;500-4000|500&amp;800-10600|800&amp;1000-12000|1000&amp;1500-25000|1500&amp;2000-25000|2000&amp;4000-20000|4000&amp;6000-2600|6000&amp;8000-200|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0</v>
+        <f t="shared" si="2"/>
+        <v>1,0&amp;1-65600|1&amp;20-13900|20&amp;40-9000|40&amp;60-4200|60&amp;80-2500|80&amp;100-1200|100&amp;120-800|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-400|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;240-400|240&amp;280-1000|280&amp;320-1000|320&amp;360-1000|360&amp;400-1000|400&amp;480-3000|480&amp;560-3500|560&amp;640-5000|640&amp;720-8000|720&amp;800-8000|800&amp;960-10000|960&amp;1120-10000|1120&amp;1280-10000|1280&amp;1440-8000|1440&amp;1600-8000|1600&amp;1920-8000|1920&amp;2240-5000|2240&amp;2560-4000|2560&amp;2880-2000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G25" s="10">
         <v>-999999</v>
@@ -2016,16 +2040,16 @@
         <v>101200</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D26" s="9">
         <v>1</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G26" s="9">
         <v>2000</v>
@@ -2049,11 +2073,11 @@
         <v>2</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F27" s="7" t="str">
-        <f t="shared" ref="F27:F32" si="2">F26</f>
-        <v>1,0&amp;1-65000|1&amp;10-14000|10&amp;20-8000|20&amp;40-5000|40&amp;60-2500|60&amp;80-1500|80&amp;100-1000|100&amp;120-1100|120&amp;140-500|140&amp;160-500|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-25|280&amp;300-25|300&amp;500-150|500&amp;800-150|800&amp;1000-25|1000&amp;1500-25|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-88700|1&amp;10-5400|10&amp;20-3500|20&amp;30-1000|30&amp;40-800|40&amp;50-300|50&amp;60-100|60&amp;70-100|70&amp;80-100|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-1100|10&amp;20-1900|20&amp;30-1900|30&amp;40-2000|40&amp;50-2000|50&amp;60-1500|60&amp;70-1700|70&amp;80-1400|80&amp;90-1400|90&amp;100-1100|100&amp;120-2300|120&amp;140-1900|140&amp;160-1600|160&amp;180-1300|180&amp;200-1000|200&amp;300-6000|300&amp;500-16000|500&amp;800-18000|800&amp;1000-9850|1000&amp;1500-8000|1500&amp;2000-6800|2000&amp;3000-5300|3000&amp;4000-2700|4000&amp;5000-1200|5000&amp;6000-700|6000&amp;7000-400|7000&amp;8000-300|8000&amp;9000-200|9000&amp;10000-100|10000&amp;11000-100|11000&amp;12000-100|12000&amp;15000-100|15000&amp;20000-50|20000&amp;99999999-0</v>
+        <f t="shared" ref="F27:F32" si="3">F26</f>
+        <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="G27" s="9">
         <v>1000</v>
@@ -2077,11 +2101,11 @@
         <v>3</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F28" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>1,0&amp;1-65000|1&amp;10-14000|10&amp;20-8000|20&amp;40-5000|40&amp;60-2500|60&amp;80-1500|80&amp;100-1000|100&amp;120-1100|120&amp;140-500|140&amp;160-500|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-25|280&amp;300-25|300&amp;500-150|500&amp;800-150|800&amp;1000-25|1000&amp;1500-25|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-88700|1&amp;10-5400|10&amp;20-3500|20&amp;30-1000|30&amp;40-800|40&amp;50-300|50&amp;60-100|60&amp;70-100|70&amp;80-100|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-1100|10&amp;20-1900|20&amp;30-1900|30&amp;40-2000|40&amp;50-2000|50&amp;60-1500|60&amp;70-1700|70&amp;80-1400|80&amp;90-1400|90&amp;100-1100|100&amp;120-2300|120&amp;140-1900|140&amp;160-1600|160&amp;180-1300|180&amp;200-1000|200&amp;300-6000|300&amp;500-16000|500&amp;800-18000|800&amp;1000-9850|1000&amp;1500-8000|1500&amp;2000-6800|2000&amp;3000-5300|3000&amp;4000-2700|4000&amp;5000-1200|5000&amp;6000-700|6000&amp;7000-400|7000&amp;8000-300|8000&amp;9000-200|9000&amp;10000-100|10000&amp;11000-100|11000&amp;12000-100|12000&amp;15000-100|15000&amp;20000-50|20000&amp;99999999-0</v>
+        <f t="shared" si="3"/>
+        <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="G28" s="9">
         <v>500</v>
@@ -2105,11 +2129,11 @@
         <v>4</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F29" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>1,0&amp;1-65000|1&amp;10-14000|10&amp;20-8000|20&amp;40-5000|40&amp;60-2500|60&amp;80-1500|80&amp;100-1000|100&amp;120-1100|120&amp;140-500|140&amp;160-500|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-25|280&amp;300-25|300&amp;500-150|500&amp;800-150|800&amp;1000-25|1000&amp;1500-25|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-88700|1&amp;10-5400|10&amp;20-3500|20&amp;30-1000|30&amp;40-800|40&amp;50-300|50&amp;60-100|60&amp;70-100|70&amp;80-100|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-1100|10&amp;20-1900|20&amp;30-1900|30&amp;40-2000|40&amp;50-2000|50&amp;60-1500|60&amp;70-1700|70&amp;80-1400|80&amp;90-1400|90&amp;100-1100|100&amp;120-2300|120&amp;140-1900|140&amp;160-1600|160&amp;180-1300|180&amp;200-1000|200&amp;300-6000|300&amp;500-16000|500&amp;800-18000|800&amp;1000-9850|1000&amp;1500-8000|1500&amp;2000-6800|2000&amp;3000-5300|3000&amp;4000-2700|4000&amp;5000-1200|5000&amp;6000-700|6000&amp;7000-400|7000&amp;8000-300|8000&amp;9000-200|9000&amp;10000-100|10000&amp;11000-100|11000&amp;12000-100|12000&amp;15000-100|15000&amp;20000-50|20000&amp;99999999-0</v>
+        <f t="shared" si="3"/>
+        <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="G29" s="9">
         <v>-500</v>
@@ -2133,11 +2157,11 @@
         <v>5</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F30" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>1,0&amp;1-65000|1&amp;10-14000|10&amp;20-8000|20&amp;40-5000|40&amp;60-2500|60&amp;80-1500|80&amp;100-1000|100&amp;120-1100|120&amp;140-500|140&amp;160-500|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-25|280&amp;300-25|300&amp;500-150|500&amp;800-150|800&amp;1000-25|1000&amp;1500-25|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-88700|1&amp;10-5400|10&amp;20-3500|20&amp;30-1000|30&amp;40-800|40&amp;50-300|50&amp;60-100|60&amp;70-100|70&amp;80-100|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-1100|10&amp;20-1900|20&amp;30-1900|30&amp;40-2000|40&amp;50-2000|50&amp;60-1500|60&amp;70-1700|70&amp;80-1400|80&amp;90-1400|90&amp;100-1100|100&amp;120-2300|120&amp;140-1900|140&amp;160-1600|160&amp;180-1300|180&amp;200-1000|200&amp;300-6000|300&amp;500-16000|500&amp;800-18000|800&amp;1000-9850|1000&amp;1500-8000|1500&amp;2000-6800|2000&amp;3000-5300|3000&amp;4000-2700|4000&amp;5000-1200|5000&amp;6000-700|6000&amp;7000-400|7000&amp;8000-300|8000&amp;9000-200|9000&amp;10000-100|10000&amp;11000-100|11000&amp;12000-100|12000&amp;15000-100|15000&amp;20000-50|20000&amp;99999999-0</v>
+        <f t="shared" si="3"/>
+        <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="G30" s="9">
         <v>-1000</v>
@@ -2161,11 +2185,11 @@
         <v>6</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F31" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>1,0&amp;1-65000|1&amp;10-14000|10&amp;20-8000|20&amp;40-5000|40&amp;60-2500|60&amp;80-1500|80&amp;100-1000|100&amp;120-1100|120&amp;140-500|140&amp;160-500|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-25|280&amp;300-25|300&amp;500-150|500&amp;800-150|800&amp;1000-25|1000&amp;1500-25|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-88700|1&amp;10-5400|10&amp;20-3500|20&amp;30-1000|30&amp;40-800|40&amp;50-300|50&amp;60-100|60&amp;70-100|70&amp;80-100|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-1100|10&amp;20-1900|20&amp;30-1900|30&amp;40-2000|40&amp;50-2000|50&amp;60-1500|60&amp;70-1700|70&amp;80-1400|80&amp;90-1400|90&amp;100-1100|100&amp;120-2300|120&amp;140-1900|140&amp;160-1600|160&amp;180-1300|180&amp;200-1000|200&amp;300-6000|300&amp;500-16000|500&amp;800-18000|800&amp;1000-9850|1000&amp;1500-8000|1500&amp;2000-6800|2000&amp;3000-5300|3000&amp;4000-2700|4000&amp;5000-1200|5000&amp;6000-700|6000&amp;7000-400|7000&amp;8000-300|8000&amp;9000-200|9000&amp;10000-100|10000&amp;11000-100|11000&amp;12000-100|12000&amp;15000-100|15000&amp;20000-50|20000&amp;99999999-0</v>
+        <f t="shared" si="3"/>
+        <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="G31" s="9">
         <v>-2000</v>
@@ -2189,11 +2213,11 @@
         <v>7</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F32" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>1,0&amp;1-65000|1&amp;10-14000|10&amp;20-8000|20&amp;40-5000|40&amp;60-2500|60&amp;80-1500|80&amp;100-1000|100&amp;120-1100|120&amp;140-500|140&amp;160-500|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-100|240&amp;260-100|260&amp;280-25|280&amp;300-25|300&amp;500-150|500&amp;800-150|800&amp;1000-25|1000&amp;1500-25|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-88700|1&amp;10-5400|10&amp;20-3500|20&amp;30-1000|30&amp;40-800|40&amp;50-300|50&amp;60-100|60&amp;70-100|70&amp;80-100|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-1100|10&amp;20-1900|20&amp;30-1900|30&amp;40-2000|40&amp;50-2000|50&amp;60-1500|60&amp;70-1700|70&amp;80-1400|80&amp;90-1400|90&amp;100-1100|100&amp;120-2300|120&amp;140-1900|140&amp;160-1600|160&amp;180-1300|180&amp;200-1000|200&amp;300-6000|300&amp;500-16000|500&amp;800-18000|800&amp;1000-9850|1000&amp;1500-8000|1500&amp;2000-6800|2000&amp;3000-5300|3000&amp;4000-2700|4000&amp;5000-1200|5000&amp;6000-700|6000&amp;7000-400|7000&amp;8000-300|8000&amp;9000-200|9000&amp;10000-100|10000&amp;11000-100|11000&amp;12000-100|12000&amp;15000-100|15000&amp;20000-50|20000&amp;99999999-0</v>
+        <f t="shared" si="3"/>
+        <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="G32" s="9">
         <v>-999999</v>
@@ -2213,16 +2237,16 @@
         <v>101400</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D33" s="13">
         <v>1</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G33" s="13">
         <v>2000</v>
@@ -2246,11 +2270,11 @@
         <v>2</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F34" s="7" t="str">
-        <f t="shared" ref="F34:F39" si="3">F33</f>
-        <v>1,0&amp;1-85200|1&amp;10-0|10&amp;20-2400|20&amp;40-5000|40&amp;60-3200|60&amp;80-1600|80&amp;100-1000|100&amp;120-500|120&amp;140-400|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-69300|1&amp;10-0|10&amp;20-4900|20&amp;30-5600|30&amp;40-4500|40&amp;50-3600|50&amp;60-2800|60&amp;70-2100|70&amp;80-1500|80&amp;90-1100|90&amp;100-1100|100&amp;120-1100|120&amp;140-900|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-97300|1&amp;10-0|10&amp;20-1100|20&amp;30-600|30&amp;40-700|40&amp;50-100|50&amp;60-100|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
+        <f t="shared" ref="F34:F39" si="4">F33</f>
+        <v>1,0&amp;1-77700|1&amp;10-3700|10&amp;20-7000|20&amp;30-4100|30&amp;40-2000|40&amp;50-1700|50&amp;60-1000|60&amp;70-700|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65000|1&amp;10-3200|10&amp;20-8800|20&amp;30-6400|30&amp;40-3700|40&amp;50-3000|50&amp;60-2300|60&amp;70-1700|70&amp;80-1200|80&amp;90-900|90&amp;100-900|100&amp;120-900|120&amp;140-800|140&amp;160-400|160&amp;180-300|180&amp;200-200|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97200|1&amp;10-0|10&amp;20-1700|20&amp;30-1100|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G34" s="13">
         <v>1000</v>
@@ -2274,11 +2298,11 @@
         <v>3</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F35" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>1,0&amp;1-85200|1&amp;10-0|10&amp;20-2400|20&amp;40-5000|40&amp;60-3200|60&amp;80-1600|80&amp;100-1000|100&amp;120-500|120&amp;140-400|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-69300|1&amp;10-0|10&amp;20-4900|20&amp;30-5600|30&amp;40-4500|40&amp;50-3600|50&amp;60-2800|60&amp;70-2100|70&amp;80-1500|80&amp;90-1100|90&amp;100-1100|100&amp;120-1100|120&amp;140-900|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-97300|1&amp;10-0|10&amp;20-1100|20&amp;30-600|30&amp;40-700|40&amp;50-100|50&amp;60-100|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
+        <f t="shared" si="4"/>
+        <v>1,0&amp;1-77700|1&amp;10-3700|10&amp;20-7000|20&amp;30-4100|30&amp;40-2000|40&amp;50-1700|50&amp;60-1000|60&amp;70-700|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65000|1&amp;10-3200|10&amp;20-8800|20&amp;30-6400|30&amp;40-3700|40&amp;50-3000|50&amp;60-2300|60&amp;70-1700|70&amp;80-1200|80&amp;90-900|90&amp;100-900|100&amp;120-900|120&amp;140-800|140&amp;160-400|160&amp;180-300|180&amp;200-200|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97200|1&amp;10-0|10&amp;20-1700|20&amp;30-1100|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G35" s="13">
         <v>500</v>
@@ -2302,11 +2326,11 @@
         <v>4</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F36" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>1,0&amp;1-85200|1&amp;10-0|10&amp;20-2400|20&amp;40-5000|40&amp;60-3200|60&amp;80-1600|80&amp;100-1000|100&amp;120-500|120&amp;140-400|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-69300|1&amp;10-0|10&amp;20-4900|20&amp;30-5600|30&amp;40-4500|40&amp;50-3600|50&amp;60-2800|60&amp;70-2100|70&amp;80-1500|80&amp;90-1100|90&amp;100-1100|100&amp;120-1100|120&amp;140-900|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-97300|1&amp;10-0|10&amp;20-1100|20&amp;30-600|30&amp;40-700|40&amp;50-100|50&amp;60-100|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
+        <f t="shared" si="4"/>
+        <v>1,0&amp;1-77700|1&amp;10-3700|10&amp;20-7000|20&amp;30-4100|30&amp;40-2000|40&amp;50-1700|50&amp;60-1000|60&amp;70-700|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65000|1&amp;10-3200|10&amp;20-8800|20&amp;30-6400|30&amp;40-3700|40&amp;50-3000|50&amp;60-2300|60&amp;70-1700|70&amp;80-1200|80&amp;90-900|90&amp;100-900|100&amp;120-900|120&amp;140-800|140&amp;160-400|160&amp;180-300|180&amp;200-200|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97200|1&amp;10-0|10&amp;20-1700|20&amp;30-1100|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G36" s="13">
         <v>-500</v>
@@ -2330,11 +2354,11 @@
         <v>5</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F37" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>1,0&amp;1-85200|1&amp;10-0|10&amp;20-2400|20&amp;40-5000|40&amp;60-3200|60&amp;80-1600|80&amp;100-1000|100&amp;120-500|120&amp;140-400|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-69300|1&amp;10-0|10&amp;20-4900|20&amp;30-5600|30&amp;40-4500|40&amp;50-3600|50&amp;60-2800|60&amp;70-2100|70&amp;80-1500|80&amp;90-1100|90&amp;100-1100|100&amp;120-1100|120&amp;140-900|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-97300|1&amp;10-0|10&amp;20-1100|20&amp;30-600|30&amp;40-700|40&amp;50-100|50&amp;60-100|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
+        <f t="shared" si="4"/>
+        <v>1,0&amp;1-77700|1&amp;10-3700|10&amp;20-7000|20&amp;30-4100|30&amp;40-2000|40&amp;50-1700|50&amp;60-1000|60&amp;70-700|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65000|1&amp;10-3200|10&amp;20-8800|20&amp;30-6400|30&amp;40-3700|40&amp;50-3000|50&amp;60-2300|60&amp;70-1700|70&amp;80-1200|80&amp;90-900|90&amp;100-900|100&amp;120-900|120&amp;140-800|140&amp;160-400|160&amp;180-300|180&amp;200-200|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97200|1&amp;10-0|10&amp;20-1700|20&amp;30-1100|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G37" s="13">
         <v>-1000</v>
@@ -2358,11 +2382,11 @@
         <v>6</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F38" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>1,0&amp;1-85200|1&amp;10-0|10&amp;20-2400|20&amp;40-5000|40&amp;60-3200|60&amp;80-1600|80&amp;100-1000|100&amp;120-500|120&amp;140-400|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-69300|1&amp;10-0|10&amp;20-4900|20&amp;30-5600|30&amp;40-4500|40&amp;50-3600|50&amp;60-2800|60&amp;70-2100|70&amp;80-1500|80&amp;90-1100|90&amp;100-1100|100&amp;120-1100|120&amp;140-900|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-97300|1&amp;10-0|10&amp;20-1100|20&amp;30-600|30&amp;40-700|40&amp;50-100|50&amp;60-100|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
+        <f t="shared" si="4"/>
+        <v>1,0&amp;1-77700|1&amp;10-3700|10&amp;20-7000|20&amp;30-4100|30&amp;40-2000|40&amp;50-1700|50&amp;60-1000|60&amp;70-700|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65000|1&amp;10-3200|10&amp;20-8800|20&amp;30-6400|30&amp;40-3700|40&amp;50-3000|50&amp;60-2300|60&amp;70-1700|70&amp;80-1200|80&amp;90-900|90&amp;100-900|100&amp;120-900|120&amp;140-800|140&amp;160-400|160&amp;180-300|180&amp;200-200|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97200|1&amp;10-0|10&amp;20-1700|20&amp;30-1100|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G38" s="13">
         <v>-2000</v>
@@ -2386,11 +2410,11 @@
         <v>7</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F39" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>1,0&amp;1-85200|1&amp;10-0|10&amp;20-2400|20&amp;40-5000|40&amp;60-3200|60&amp;80-1600|80&amp;100-1000|100&amp;120-500|120&amp;140-400|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;220-100|220&amp;240-0|240&amp;260-0|260&amp;280-0|280&amp;300-0|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;4000-0|4000&amp;6000-0|6000&amp;8000-0|8000&amp;10000-0|10000&amp;12000-0|12000&amp;14000-0|14000&amp;16000-0|16000&amp;18000-0|18000&amp;20000-0|20000&amp;24000-0|24000&amp;28000-0|28000&amp;32000-0|32000&amp;36000-0|36000&amp;40000-0|40000&amp;60000-0|60000&amp;80000-0|80000&amp;99999999-0;2,0&amp;1-69300|1&amp;10-0|10&amp;20-4900|20&amp;30-5600|30&amp;40-4500|40&amp;50-3600|50&amp;60-2800|60&amp;70-2100|70&amp;80-1500|80&amp;90-1100|90&amp;100-1100|100&amp;120-1100|120&amp;140-900|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;300-500|300&amp;500-100|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-97300|1&amp;10-0|10&amp;20-1100|20&amp;30-600|30&amp;40-700|40&amp;50-100|50&amp;60-100|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
+        <f t="shared" si="4"/>
+        <v>1,0&amp;1-77700|1&amp;10-3700|10&amp;20-7000|20&amp;30-4100|30&amp;40-2000|40&amp;50-1700|50&amp;60-1000|60&amp;70-700|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65000|1&amp;10-3200|10&amp;20-8800|20&amp;30-6400|30&amp;40-3700|40&amp;50-3000|50&amp;60-2300|60&amp;70-1700|70&amp;80-1200|80&amp;90-900|90&amp;100-900|100&amp;120-900|120&amp;140-800|140&amp;160-400|160&amp;180-300|180&amp;200-200|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97200|1&amp;10-0|10&amp;20-1700|20&amp;30-1100|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G39" s="13">
         <v>-999999</v>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -308,7 +308,7 @@
     <t>1_2999|2_7000|3_1</t>
   </si>
   <si>
-    <t>1,0&amp;1-77700|1&amp;10-3700|10&amp;20-7000|20&amp;30-4100|30&amp;40-2000|40&amp;50-1700|50&amp;60-1000|60&amp;70-700|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65000|1&amp;10-3200|10&amp;20-8800|20&amp;30-6400|30&amp;40-3700|40&amp;50-3000|50&amp;60-2300|60&amp;70-1700|70&amp;80-1200|80&amp;90-900|90&amp;100-900|100&amp;120-900|120&amp;140-800|140&amp;160-400|160&amp;180-300|180&amp;200-200|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97200|1&amp;10-0|10&amp;20-1700|20&amp;30-1100|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</t>
+    <t>1,0&amp;1-78500|1&amp;10-3200|10&amp;20-7200|20&amp;30-3400|30&amp;40-2300|40&amp;50-1600|50&amp;60-900|60&amp;70-600|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65500|1&amp;10-3000|10&amp;20-10400|20&amp;30-5700|30&amp;40-4000|40&amp;50-2800|50&amp;60-1800|60&amp;70-1200|70&amp;80-1000|80&amp;90-800|90&amp;100-800|100&amp;120-700|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-100|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97100|1&amp;10-0|10&amp;20-1000|20&amp;30-600|30&amp;40-600|40&amp;50-200|50&amp;60-100|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</t>
   </si>
   <si>
     <t>1_3999|2_6000|3_1</t>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="F34" s="7" t="str">
         <f t="shared" ref="F34:F39" si="4">F33</f>
-        <v>1,0&amp;1-77700|1&amp;10-3700|10&amp;20-7000|20&amp;30-4100|30&amp;40-2000|40&amp;50-1700|50&amp;60-1000|60&amp;70-700|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65000|1&amp;10-3200|10&amp;20-8800|20&amp;30-6400|30&amp;40-3700|40&amp;50-3000|50&amp;60-2300|60&amp;70-1700|70&amp;80-1200|80&amp;90-900|90&amp;100-900|100&amp;120-900|120&amp;140-800|140&amp;160-400|160&amp;180-300|180&amp;200-200|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97200|1&amp;10-0|10&amp;20-1700|20&amp;30-1100|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
+        <v>1,0&amp;1-78500|1&amp;10-3200|10&amp;20-7200|20&amp;30-3400|30&amp;40-2300|40&amp;50-1600|50&amp;60-900|60&amp;70-600|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65500|1&amp;10-3000|10&amp;20-10400|20&amp;30-5700|30&amp;40-4000|40&amp;50-2800|50&amp;60-1800|60&amp;70-1200|70&amp;80-1000|80&amp;90-800|90&amp;100-800|100&amp;120-700|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-100|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97100|1&amp;10-0|10&amp;20-1000|20&amp;30-600|30&amp;40-600|40&amp;50-200|50&amp;60-100|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G34" s="13">
         <v>1000</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="F35" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-77700|1&amp;10-3700|10&amp;20-7000|20&amp;30-4100|30&amp;40-2000|40&amp;50-1700|50&amp;60-1000|60&amp;70-700|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65000|1&amp;10-3200|10&amp;20-8800|20&amp;30-6400|30&amp;40-3700|40&amp;50-3000|50&amp;60-2300|60&amp;70-1700|70&amp;80-1200|80&amp;90-900|90&amp;100-900|100&amp;120-900|120&amp;140-800|140&amp;160-400|160&amp;180-300|180&amp;200-200|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97200|1&amp;10-0|10&amp;20-1700|20&amp;30-1100|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
+        <v>1,0&amp;1-78500|1&amp;10-3200|10&amp;20-7200|20&amp;30-3400|30&amp;40-2300|40&amp;50-1600|50&amp;60-900|60&amp;70-600|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65500|1&amp;10-3000|10&amp;20-10400|20&amp;30-5700|30&amp;40-4000|40&amp;50-2800|50&amp;60-1800|60&amp;70-1200|70&amp;80-1000|80&amp;90-800|90&amp;100-800|100&amp;120-700|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-100|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97100|1&amp;10-0|10&amp;20-1000|20&amp;30-600|30&amp;40-600|40&amp;50-200|50&amp;60-100|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G35" s="13">
         <v>500</v>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="F36" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-77700|1&amp;10-3700|10&amp;20-7000|20&amp;30-4100|30&amp;40-2000|40&amp;50-1700|50&amp;60-1000|60&amp;70-700|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65000|1&amp;10-3200|10&amp;20-8800|20&amp;30-6400|30&amp;40-3700|40&amp;50-3000|50&amp;60-2300|60&amp;70-1700|70&amp;80-1200|80&amp;90-900|90&amp;100-900|100&amp;120-900|120&amp;140-800|140&amp;160-400|160&amp;180-300|180&amp;200-200|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97200|1&amp;10-0|10&amp;20-1700|20&amp;30-1100|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
+        <v>1,0&amp;1-78500|1&amp;10-3200|10&amp;20-7200|20&amp;30-3400|30&amp;40-2300|40&amp;50-1600|50&amp;60-900|60&amp;70-600|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65500|1&amp;10-3000|10&amp;20-10400|20&amp;30-5700|30&amp;40-4000|40&amp;50-2800|50&amp;60-1800|60&amp;70-1200|70&amp;80-1000|80&amp;90-800|90&amp;100-800|100&amp;120-700|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-100|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97100|1&amp;10-0|10&amp;20-1000|20&amp;30-600|30&amp;40-600|40&amp;50-200|50&amp;60-100|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G36" s="13">
         <v>-500</v>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F37" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-77700|1&amp;10-3700|10&amp;20-7000|20&amp;30-4100|30&amp;40-2000|40&amp;50-1700|50&amp;60-1000|60&amp;70-700|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65000|1&amp;10-3200|10&amp;20-8800|20&amp;30-6400|30&amp;40-3700|40&amp;50-3000|50&amp;60-2300|60&amp;70-1700|70&amp;80-1200|80&amp;90-900|90&amp;100-900|100&amp;120-900|120&amp;140-800|140&amp;160-400|160&amp;180-300|180&amp;200-200|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97200|1&amp;10-0|10&amp;20-1700|20&amp;30-1100|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
+        <v>1,0&amp;1-78500|1&amp;10-3200|10&amp;20-7200|20&amp;30-3400|30&amp;40-2300|40&amp;50-1600|50&amp;60-900|60&amp;70-600|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65500|1&amp;10-3000|10&amp;20-10400|20&amp;30-5700|30&amp;40-4000|40&amp;50-2800|50&amp;60-1800|60&amp;70-1200|70&amp;80-1000|80&amp;90-800|90&amp;100-800|100&amp;120-700|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-100|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97100|1&amp;10-0|10&amp;20-1000|20&amp;30-600|30&amp;40-600|40&amp;50-200|50&amp;60-100|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G37" s="13">
         <v>-1000</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="F38" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-77700|1&amp;10-3700|10&amp;20-7000|20&amp;30-4100|30&amp;40-2000|40&amp;50-1700|50&amp;60-1000|60&amp;70-700|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65000|1&amp;10-3200|10&amp;20-8800|20&amp;30-6400|30&amp;40-3700|40&amp;50-3000|50&amp;60-2300|60&amp;70-1700|70&amp;80-1200|80&amp;90-900|90&amp;100-900|100&amp;120-900|120&amp;140-800|140&amp;160-400|160&amp;180-300|180&amp;200-200|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97200|1&amp;10-0|10&amp;20-1700|20&amp;30-1100|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
+        <v>1,0&amp;1-78500|1&amp;10-3200|10&amp;20-7200|20&amp;30-3400|30&amp;40-2300|40&amp;50-1600|50&amp;60-900|60&amp;70-600|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65500|1&amp;10-3000|10&amp;20-10400|20&amp;30-5700|30&amp;40-4000|40&amp;50-2800|50&amp;60-1800|60&amp;70-1200|70&amp;80-1000|80&amp;90-800|90&amp;100-800|100&amp;120-700|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-100|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97100|1&amp;10-0|10&amp;20-1000|20&amp;30-600|30&amp;40-600|40&amp;50-200|50&amp;60-100|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G38" s="13">
         <v>-2000</v>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="F39" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-77700|1&amp;10-3700|10&amp;20-7000|20&amp;30-4100|30&amp;40-2000|40&amp;50-1700|50&amp;60-1000|60&amp;70-700|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65000|1&amp;10-3200|10&amp;20-8800|20&amp;30-6400|30&amp;40-3700|40&amp;50-3000|50&amp;60-2300|60&amp;70-1700|70&amp;80-1200|80&amp;90-900|90&amp;100-900|100&amp;120-900|120&amp;140-800|140&amp;160-400|160&amp;180-300|180&amp;200-200|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97200|1&amp;10-0|10&amp;20-1700|20&amp;30-1100|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
+        <v>1,0&amp;1-78500|1&amp;10-3200|10&amp;20-7200|20&amp;30-3400|30&amp;40-2300|40&amp;50-1600|50&amp;60-900|60&amp;70-600|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65500|1&amp;10-3000|10&amp;20-10400|20&amp;30-5700|30&amp;40-4000|40&amp;50-2800|50&amp;60-1800|60&amp;70-1200|70&amp;80-1000|80&amp;90-800|90&amp;100-800|100&amp;120-700|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-100|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97100|1&amp;10-0|10&amp;20-1000|20&amp;30-600|30&amp;40-600|40&amp;50-200|50&amp;60-100|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G39" s="13">
         <v>-999999</v>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -305,28 +305,28 @@
     <t>埃及艳后</t>
   </si>
   <si>
-    <t>1_2999|2_7000|3_1</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-78500|1&amp;10-3200|10&amp;20-7200|20&amp;30-3400|30&amp;40-2300|40&amp;50-1600|50&amp;60-900|60&amp;70-600|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65500|1&amp;10-3000|10&amp;20-10400|20&amp;30-5700|30&amp;40-4000|40&amp;50-2800|50&amp;60-1800|60&amp;70-1200|70&amp;80-1000|80&amp;90-800|90&amp;100-800|100&amp;120-700|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-100|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97100|1&amp;10-0|10&amp;20-1000|20&amp;30-600|30&amp;40-600|40&amp;50-200|50&amp;60-100|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</t>
+    <t>1_2499|2_7500|3_1</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-73400|1&amp;10-1500|10&amp;20-7200|20&amp;30-6600|30&amp;40-3400|40&amp;50-2500|50&amp;60-1500|60&amp;70-1500|70&amp;80-500|80&amp;90-400|90&amp;100-400|100&amp;120-300|120&amp;140-400|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-63600|1&amp;10-1700|10&amp;20-9100|20&amp;30-9400|30&amp;40-4400|40&amp;50-3600|50&amp;60-2100|60&amp;70-1900|70&amp;80-1200|80&amp;90-700|90&amp;100-500|100&amp;120-500|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</t>
   </si>
   <si>
     <t>1_3999|2_6000|3_1</t>
   </si>
   <si>
-    <t>1_4999|2_5000|3_1</t>
-  </si>
-  <si>
     <t>1_5499|2_4500|3_1</t>
   </si>
   <si>
-    <t>1_5999|2_4000|3_1</t>
-  </si>
-  <si>
     <t>1_6999|2_3000|3_1</t>
   </si>
   <si>
     <t>1_7999|2_2000|3_1</t>
+  </si>
+  <si>
+    <t>1_8999|2_1000|3_1</t>
+  </si>
+  <si>
+    <t>1_9999|2_0|3_1</t>
   </si>
 </sst>
 </file>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="F34" s="7" t="str">
         <f t="shared" ref="F34:F39" si="4">F33</f>
-        <v>1,0&amp;1-78500|1&amp;10-3200|10&amp;20-7200|20&amp;30-3400|30&amp;40-2300|40&amp;50-1600|50&amp;60-900|60&amp;70-600|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65500|1&amp;10-3000|10&amp;20-10400|20&amp;30-5700|30&amp;40-4000|40&amp;50-2800|50&amp;60-1800|60&amp;70-1200|70&amp;80-1000|80&amp;90-800|90&amp;100-800|100&amp;120-700|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-100|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97100|1&amp;10-0|10&amp;20-1000|20&amp;30-600|30&amp;40-600|40&amp;50-200|50&amp;60-100|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
+        <v>1,0&amp;1-73400|1&amp;10-1500|10&amp;20-7200|20&amp;30-6600|30&amp;40-3400|40&amp;50-2500|50&amp;60-1500|60&amp;70-1500|70&amp;80-500|80&amp;90-400|90&amp;100-400|100&amp;120-300|120&amp;140-400|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-63600|1&amp;10-1700|10&amp;20-9100|20&amp;30-9400|30&amp;40-4400|40&amp;50-3600|50&amp;60-2100|60&amp;70-1900|70&amp;80-1200|80&amp;90-700|90&amp;100-500|100&amp;120-500|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G34" s="13">
         <v>1000</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="F35" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-78500|1&amp;10-3200|10&amp;20-7200|20&amp;30-3400|30&amp;40-2300|40&amp;50-1600|50&amp;60-900|60&amp;70-600|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65500|1&amp;10-3000|10&amp;20-10400|20&amp;30-5700|30&amp;40-4000|40&amp;50-2800|50&amp;60-1800|60&amp;70-1200|70&amp;80-1000|80&amp;90-800|90&amp;100-800|100&amp;120-700|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-100|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97100|1&amp;10-0|10&amp;20-1000|20&amp;30-600|30&amp;40-600|40&amp;50-200|50&amp;60-100|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
+        <v>1,0&amp;1-73400|1&amp;10-1500|10&amp;20-7200|20&amp;30-6600|30&amp;40-3400|40&amp;50-2500|50&amp;60-1500|60&amp;70-1500|70&amp;80-500|80&amp;90-400|90&amp;100-400|100&amp;120-300|120&amp;140-400|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-63600|1&amp;10-1700|10&amp;20-9100|20&amp;30-9400|30&amp;40-4400|40&amp;50-3600|50&amp;60-2100|60&amp;70-1900|70&amp;80-1200|80&amp;90-700|90&amp;100-500|100&amp;120-500|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G35" s="13">
         <v>500</v>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="F36" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-78500|1&amp;10-3200|10&amp;20-7200|20&amp;30-3400|30&amp;40-2300|40&amp;50-1600|50&amp;60-900|60&amp;70-600|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65500|1&amp;10-3000|10&amp;20-10400|20&amp;30-5700|30&amp;40-4000|40&amp;50-2800|50&amp;60-1800|60&amp;70-1200|70&amp;80-1000|80&amp;90-800|90&amp;100-800|100&amp;120-700|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-100|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97100|1&amp;10-0|10&amp;20-1000|20&amp;30-600|30&amp;40-600|40&amp;50-200|50&amp;60-100|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
+        <v>1,0&amp;1-73400|1&amp;10-1500|10&amp;20-7200|20&amp;30-6600|30&amp;40-3400|40&amp;50-2500|50&amp;60-1500|60&amp;70-1500|70&amp;80-500|80&amp;90-400|90&amp;100-400|100&amp;120-300|120&amp;140-400|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-63600|1&amp;10-1700|10&amp;20-9100|20&amp;30-9400|30&amp;40-4400|40&amp;50-3600|50&amp;60-2100|60&amp;70-1900|70&amp;80-1200|80&amp;90-700|90&amp;100-500|100&amp;120-500|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G36" s="13">
         <v>-500</v>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F37" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-78500|1&amp;10-3200|10&amp;20-7200|20&amp;30-3400|30&amp;40-2300|40&amp;50-1600|50&amp;60-900|60&amp;70-600|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65500|1&amp;10-3000|10&amp;20-10400|20&amp;30-5700|30&amp;40-4000|40&amp;50-2800|50&amp;60-1800|60&amp;70-1200|70&amp;80-1000|80&amp;90-800|90&amp;100-800|100&amp;120-700|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-100|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97100|1&amp;10-0|10&amp;20-1000|20&amp;30-600|30&amp;40-600|40&amp;50-200|50&amp;60-100|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
+        <v>1,0&amp;1-73400|1&amp;10-1500|10&amp;20-7200|20&amp;30-6600|30&amp;40-3400|40&amp;50-2500|50&amp;60-1500|60&amp;70-1500|70&amp;80-500|80&amp;90-400|90&amp;100-400|100&amp;120-300|120&amp;140-400|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-63600|1&amp;10-1700|10&amp;20-9100|20&amp;30-9400|30&amp;40-4400|40&amp;50-3600|50&amp;60-2100|60&amp;70-1900|70&amp;80-1200|80&amp;90-700|90&amp;100-500|100&amp;120-500|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G37" s="13">
         <v>-1000</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="F38" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-78500|1&amp;10-3200|10&amp;20-7200|20&amp;30-3400|30&amp;40-2300|40&amp;50-1600|50&amp;60-900|60&amp;70-600|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65500|1&amp;10-3000|10&amp;20-10400|20&amp;30-5700|30&amp;40-4000|40&amp;50-2800|50&amp;60-1800|60&amp;70-1200|70&amp;80-1000|80&amp;90-800|90&amp;100-800|100&amp;120-700|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-100|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97100|1&amp;10-0|10&amp;20-1000|20&amp;30-600|30&amp;40-600|40&amp;50-200|50&amp;60-100|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
+        <v>1,0&amp;1-73400|1&amp;10-1500|10&amp;20-7200|20&amp;30-6600|30&amp;40-3400|40&amp;50-2500|50&amp;60-1500|60&amp;70-1500|70&amp;80-500|80&amp;90-400|90&amp;100-400|100&amp;120-300|120&amp;140-400|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-63600|1&amp;10-1700|10&amp;20-9100|20&amp;30-9400|30&amp;40-4400|40&amp;50-3600|50&amp;60-2100|60&amp;70-1900|70&amp;80-1200|80&amp;90-700|90&amp;100-500|100&amp;120-500|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G38" s="13">
         <v>-2000</v>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="F39" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-78500|1&amp;10-3200|10&amp;20-7200|20&amp;30-3400|30&amp;40-2300|40&amp;50-1600|50&amp;60-900|60&amp;70-600|70&amp;80-500|80&amp;90-400|90&amp;100-300|100&amp;120-300|120&amp;140-300|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-65500|1&amp;10-3000|10&amp;20-10400|20&amp;30-5700|30&amp;40-4000|40&amp;50-2800|50&amp;60-1800|60&amp;70-1200|70&amp;80-1000|80&amp;90-800|90&amp;100-800|100&amp;120-700|120&amp;140-600|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-100|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-97100|1&amp;10-0|10&amp;20-1000|20&amp;30-600|30&amp;40-600|40&amp;50-200|50&amp;60-100|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
+        <v>1,0&amp;1-73400|1&amp;10-1500|10&amp;20-7200|20&amp;30-6600|30&amp;40-3400|40&amp;50-2500|50&amp;60-1500|60&amp;70-1500|70&amp;80-500|80&amp;90-400|90&amp;100-400|100&amp;120-300|120&amp;140-400|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-63600|1&amp;10-1700|10&amp;20-9100|20&amp;30-9400|30&amp;40-4400|40&amp;50-3600|50&amp;60-2100|60&amp;70-1900|70&amp;80-1200|80&amp;90-700|90&amp;100-500|100&amp;120-500|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G39" s="13">
         <v>-999999</v>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -305,16 +305,19 @@
     <t>埃及艳后</t>
   </si>
   <si>
-    <t>1_2499|2_7500|3_1</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-73400|1&amp;10-1500|10&amp;20-7200|20&amp;30-6600|30&amp;40-3400|40&amp;50-2500|50&amp;60-1500|60&amp;70-1500|70&amp;80-500|80&amp;90-400|90&amp;100-400|100&amp;120-300|120&amp;140-400|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-63600|1&amp;10-1700|10&amp;20-9100|20&amp;30-9400|30&amp;40-4400|40&amp;50-3600|50&amp;60-2100|60&amp;70-1900|70&amp;80-1200|80&amp;90-700|90&amp;100-500|100&amp;120-500|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</t>
+    <t>1_2999|2_7000|3_1</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</t>
   </si>
   <si>
     <t>1_3999|2_6000|3_1</t>
   </si>
   <si>
-    <t>1_5499|2_4500|3_1</t>
+    <t>1_4999|2_5000|3_1</t>
+  </si>
+  <si>
+    <t>1_5999|2_4000|3_1</t>
   </si>
   <si>
     <t>1_6999|2_3000|3_1</t>
@@ -324,9 +327,6 @@
   </si>
   <si>
     <t>1_8999|2_1000|3_1</t>
-  </si>
-  <si>
-    <t>1_9999|2_0|3_1</t>
   </si>
 </sst>
 </file>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="F34" s="7" t="str">
         <f t="shared" ref="F34:F39" si="4">F33</f>
-        <v>1,0&amp;1-73400|1&amp;10-1500|10&amp;20-7200|20&amp;30-6600|30&amp;40-3400|40&amp;50-2500|50&amp;60-1500|60&amp;70-1500|70&amp;80-500|80&amp;90-400|90&amp;100-400|100&amp;120-300|120&amp;140-400|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-63600|1&amp;10-1700|10&amp;20-9100|20&amp;30-9400|30&amp;40-4400|40&amp;50-3600|50&amp;60-2100|60&amp;70-1900|70&amp;80-1200|80&amp;90-700|90&amp;100-500|100&amp;120-500|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
+        <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G34" s="13">
         <v>1000</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="F35" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-73400|1&amp;10-1500|10&amp;20-7200|20&amp;30-6600|30&amp;40-3400|40&amp;50-2500|50&amp;60-1500|60&amp;70-1500|70&amp;80-500|80&amp;90-400|90&amp;100-400|100&amp;120-300|120&amp;140-400|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-63600|1&amp;10-1700|10&amp;20-9100|20&amp;30-9400|30&amp;40-4400|40&amp;50-3600|50&amp;60-2100|60&amp;70-1900|70&amp;80-1200|80&amp;90-700|90&amp;100-500|100&amp;120-500|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
+        <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G35" s="13">
         <v>500</v>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="F36" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-73400|1&amp;10-1500|10&amp;20-7200|20&amp;30-6600|30&amp;40-3400|40&amp;50-2500|50&amp;60-1500|60&amp;70-1500|70&amp;80-500|80&amp;90-400|90&amp;100-400|100&amp;120-300|120&amp;140-400|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-63600|1&amp;10-1700|10&amp;20-9100|20&amp;30-9400|30&amp;40-4400|40&amp;50-3600|50&amp;60-2100|60&amp;70-1900|70&amp;80-1200|80&amp;90-700|90&amp;100-500|100&amp;120-500|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
+        <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G36" s="13">
         <v>-500</v>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F37" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-73400|1&amp;10-1500|10&amp;20-7200|20&amp;30-6600|30&amp;40-3400|40&amp;50-2500|50&amp;60-1500|60&amp;70-1500|70&amp;80-500|80&amp;90-400|90&amp;100-400|100&amp;120-300|120&amp;140-400|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-63600|1&amp;10-1700|10&amp;20-9100|20&amp;30-9400|30&amp;40-4400|40&amp;50-3600|50&amp;60-2100|60&amp;70-1900|70&amp;80-1200|80&amp;90-700|90&amp;100-500|100&amp;120-500|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
+        <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G37" s="13">
         <v>-1000</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="F38" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-73400|1&amp;10-1500|10&amp;20-7200|20&amp;30-6600|30&amp;40-3400|40&amp;50-2500|50&amp;60-1500|60&amp;70-1500|70&amp;80-500|80&amp;90-400|90&amp;100-400|100&amp;120-300|120&amp;140-400|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-63600|1&amp;10-1700|10&amp;20-9100|20&amp;30-9400|30&amp;40-4400|40&amp;50-3600|50&amp;60-2100|60&amp;70-1900|70&amp;80-1200|80&amp;90-700|90&amp;100-500|100&amp;120-500|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
+        <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G38" s="13">
         <v>-2000</v>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="F39" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-73400|1&amp;10-1500|10&amp;20-7200|20&amp;30-6600|30&amp;40-3400|40&amp;50-2500|50&amp;60-1500|60&amp;70-1500|70&amp;80-500|80&amp;90-400|90&amp;100-400|100&amp;120-300|120&amp;140-400|140&amp;160-100|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-63600|1&amp;10-1700|10&amp;20-9100|20&amp;30-9400|30&amp;40-4400|40&amp;50-3600|50&amp;60-2100|60&amp;70-1900|70&amp;80-1200|80&amp;90-700|90&amp;100-500|100&amp;120-500|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
+        <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="G39" s="13">
         <v>-999999</v>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -251,28 +251,28 @@
     <t>麻将胡了</t>
   </si>
   <si>
-    <t>1_9990|2_85</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-65600|1&amp;20-13900|20&amp;40-9000|40&amp;60-4200|60&amp;80-2500|80&amp;100-1200|100&amp;120-800|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-400|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;240-400|240&amp;280-1000|280&amp;320-1000|320&amp;360-1000|360&amp;400-1000|400&amp;480-3000|480&amp;560-3500|560&amp;640-5000|640&amp;720-8000|720&amp;800-8000|800&amp;960-10000|960&amp;1120-10000|1120&amp;1280-10000|1280&amp;1440-8000|1440&amp;1600-8000|1600&amp;1920-8000|1920&amp;2240-5000|2240&amp;2560-4000|2560&amp;2880-2000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
-  </si>
-  <si>
     <t>1_9990|2_75</t>
   </si>
   <si>
+    <t>1,0&amp;1-69000|1&amp;20-12000|20&amp;40-6500|40&amp;60-3000|60&amp;80-2400|80&amp;100-2500|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-600|180&amp;200-600|200&amp;240-600|240&amp;280-500|280&amp;320-400|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-500|180&amp;200-400|200&amp;240-1000|240&amp;280-1100|280&amp;320-1200|320&amp;360-1200|360&amp;400-1300|400&amp;480-2600|480&amp;560-2700|560&amp;640-2700|640&amp;720-2600|720&amp;800-2800|800&amp;960-5100|960&amp;1120-4800|1120&amp;1280-4600|1280&amp;1440-4300|1440&amp;1600-4500|1600&amp;1920-7200|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
+  </si>
+  <si>
     <t>1_9990|2_65</t>
   </si>
   <si>
-    <t>1_9945|2_55</t>
-  </si>
-  <si>
-    <t>1_9990|2_45</t>
+    <t>1_9990|2_55</t>
+  </si>
+  <si>
+    <t>1_9955|2_45</t>
   </si>
   <si>
     <t>1_9990|2_35</t>
   </si>
   <si>
     <t>1_9990|2_25</t>
+  </si>
+  <si>
+    <t>1_9990|2_15</t>
   </si>
   <si>
     <t>财神</t>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="F20" s="12" t="str">
         <f t="shared" ref="F20:F25" si="2">F19</f>
-        <v>1,0&amp;1-65600|1&amp;20-13900|20&amp;40-9000|40&amp;60-4200|60&amp;80-2500|80&amp;100-1200|100&amp;120-800|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-400|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;240-400|240&amp;280-1000|280&amp;320-1000|320&amp;360-1000|360&amp;400-1000|400&amp;480-3000|480&amp;560-3500|560&amp;640-5000|640&amp;720-8000|720&amp;800-8000|800&amp;960-10000|960&amp;1120-10000|1120&amp;1280-10000|1280&amp;1440-8000|1440&amp;1600-8000|1600&amp;1920-8000|1920&amp;2240-5000|2240&amp;2560-4000|2560&amp;2880-2000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-69000|1&amp;20-12000|20&amp;40-6500|40&amp;60-3000|60&amp;80-2400|80&amp;100-2500|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-600|180&amp;200-600|200&amp;240-600|240&amp;280-500|280&amp;320-400|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-500|180&amp;200-400|200&amp;240-1000|240&amp;280-1100|280&amp;320-1200|320&amp;360-1200|360&amp;400-1300|400&amp;480-2600|480&amp;560-2700|560&amp;640-2700|640&amp;720-2600|720&amp;800-2800|800&amp;960-5100|960&amp;1120-4800|1120&amp;1280-4600|1280&amp;1440-4300|1440&amp;1600-4500|1600&amp;1920-7200|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G20" s="10">
         <v>1000</v>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="F21" s="12" t="str">
         <f t="shared" si="2"/>
-        <v>1,0&amp;1-65600|1&amp;20-13900|20&amp;40-9000|40&amp;60-4200|60&amp;80-2500|80&amp;100-1200|100&amp;120-800|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-400|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;240-400|240&amp;280-1000|280&amp;320-1000|320&amp;360-1000|360&amp;400-1000|400&amp;480-3000|480&amp;560-3500|560&amp;640-5000|640&amp;720-8000|720&amp;800-8000|800&amp;960-10000|960&amp;1120-10000|1120&amp;1280-10000|1280&amp;1440-8000|1440&amp;1600-8000|1600&amp;1920-8000|1920&amp;2240-5000|2240&amp;2560-4000|2560&amp;2880-2000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-69000|1&amp;20-12000|20&amp;40-6500|40&amp;60-3000|60&amp;80-2400|80&amp;100-2500|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-600|180&amp;200-600|200&amp;240-600|240&amp;280-500|280&amp;320-400|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-500|180&amp;200-400|200&amp;240-1000|240&amp;280-1100|280&amp;320-1200|320&amp;360-1200|360&amp;400-1300|400&amp;480-2600|480&amp;560-2700|560&amp;640-2700|640&amp;720-2600|720&amp;800-2800|800&amp;960-5100|960&amp;1120-4800|1120&amp;1280-4600|1280&amp;1440-4300|1440&amp;1600-4500|1600&amp;1920-7200|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G21" s="10">
         <v>500</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="F22" s="12" t="str">
         <f t="shared" si="2"/>
-        <v>1,0&amp;1-65600|1&amp;20-13900|20&amp;40-9000|40&amp;60-4200|60&amp;80-2500|80&amp;100-1200|100&amp;120-800|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-400|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;240-400|240&amp;280-1000|280&amp;320-1000|320&amp;360-1000|360&amp;400-1000|400&amp;480-3000|480&amp;560-3500|560&amp;640-5000|640&amp;720-8000|720&amp;800-8000|800&amp;960-10000|960&amp;1120-10000|1120&amp;1280-10000|1280&amp;1440-8000|1440&amp;1600-8000|1600&amp;1920-8000|1920&amp;2240-5000|2240&amp;2560-4000|2560&amp;2880-2000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-69000|1&amp;20-12000|20&amp;40-6500|40&amp;60-3000|60&amp;80-2400|80&amp;100-2500|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-600|180&amp;200-600|200&amp;240-600|240&amp;280-500|280&amp;320-400|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-500|180&amp;200-400|200&amp;240-1000|240&amp;280-1100|280&amp;320-1200|320&amp;360-1200|360&amp;400-1300|400&amp;480-2600|480&amp;560-2700|560&amp;640-2700|640&amp;720-2600|720&amp;800-2800|800&amp;960-5100|960&amp;1120-4800|1120&amp;1280-4600|1280&amp;1440-4300|1440&amp;1600-4500|1600&amp;1920-7200|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G22" s="10">
         <v>-500</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="F23" s="12" t="str">
         <f t="shared" si="2"/>
-        <v>1,0&amp;1-65600|1&amp;20-13900|20&amp;40-9000|40&amp;60-4200|60&amp;80-2500|80&amp;100-1200|100&amp;120-800|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-400|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;240-400|240&amp;280-1000|280&amp;320-1000|320&amp;360-1000|360&amp;400-1000|400&amp;480-3000|480&amp;560-3500|560&amp;640-5000|640&amp;720-8000|720&amp;800-8000|800&amp;960-10000|960&amp;1120-10000|1120&amp;1280-10000|1280&amp;1440-8000|1440&amp;1600-8000|1600&amp;1920-8000|1920&amp;2240-5000|2240&amp;2560-4000|2560&amp;2880-2000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-69000|1&amp;20-12000|20&amp;40-6500|40&amp;60-3000|60&amp;80-2400|80&amp;100-2500|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-600|180&amp;200-600|200&amp;240-600|240&amp;280-500|280&amp;320-400|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-500|180&amp;200-400|200&amp;240-1000|240&amp;280-1100|280&amp;320-1200|320&amp;360-1200|360&amp;400-1300|400&amp;480-2600|480&amp;560-2700|560&amp;640-2700|640&amp;720-2600|720&amp;800-2800|800&amp;960-5100|960&amp;1120-4800|1120&amp;1280-4600|1280&amp;1440-4300|1440&amp;1600-4500|1600&amp;1920-7200|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G23" s="10">
         <v>-1000</v>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F24" s="12" t="str">
         <f t="shared" si="2"/>
-        <v>1,0&amp;1-65600|1&amp;20-13900|20&amp;40-9000|40&amp;60-4200|60&amp;80-2500|80&amp;100-1200|100&amp;120-800|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-400|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;240-400|240&amp;280-1000|280&amp;320-1000|320&amp;360-1000|360&amp;400-1000|400&amp;480-3000|480&amp;560-3500|560&amp;640-5000|640&amp;720-8000|720&amp;800-8000|800&amp;960-10000|960&amp;1120-10000|1120&amp;1280-10000|1280&amp;1440-8000|1440&amp;1600-8000|1600&amp;1920-8000|1920&amp;2240-5000|2240&amp;2560-4000|2560&amp;2880-2000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-69000|1&amp;20-12000|20&amp;40-6500|40&amp;60-3000|60&amp;80-2400|80&amp;100-2500|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-600|180&amp;200-600|200&amp;240-600|240&amp;280-500|280&amp;320-400|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-500|180&amp;200-400|200&amp;240-1000|240&amp;280-1100|280&amp;320-1200|320&amp;360-1200|360&amp;400-1300|400&amp;480-2600|480&amp;560-2700|560&amp;640-2700|640&amp;720-2600|720&amp;800-2800|800&amp;960-5100|960&amp;1120-4800|1120&amp;1280-4600|1280&amp;1440-4300|1440&amp;1600-4500|1600&amp;1920-7200|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G24" s="10">
         <v>-2000</v>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="F25" s="12" t="str">
         <f t="shared" si="2"/>
-        <v>1,0&amp;1-65600|1&amp;20-13900|20&amp;40-9000|40&amp;60-4200|60&amp;80-2500|80&amp;100-1200|100&amp;120-800|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-400|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-100|200&amp;240-400|240&amp;280-1000|280&amp;320-1000|320&amp;360-1000|360&amp;400-1000|400&amp;480-3000|480&amp;560-3500|560&amp;640-5000|640&amp;720-8000|720&amp;800-8000|800&amp;960-10000|960&amp;1120-10000|1120&amp;1280-10000|1280&amp;1440-8000|1440&amp;1600-8000|1600&amp;1920-8000|1920&amp;2240-5000|2240&amp;2560-4000|2560&amp;2880-2000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-69000|1&amp;20-12000|20&amp;40-6500|40&amp;60-3000|60&amp;80-2400|80&amp;100-2500|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-600|180&amp;200-600|200&amp;240-600|240&amp;280-500|280&amp;320-400|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-500|180&amp;200-400|200&amp;240-1000|240&amp;280-1100|280&amp;320-1200|320&amp;360-1200|360&amp;400-1300|400&amp;480-2600|480&amp;560-2700|560&amp;640-2700|640&amp;720-2600|720&amp;800-2800|800&amp;960-5100|960&amp;1120-4800|1120&amp;1280-4600|1280&amp;1440-4300|1440&amp;1600-4500|1600&amp;1920-7200|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G25" s="10">
         <v>-999999</v>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -227,7 +227,7 @@
     <t>1_9710|2_180|3_110</t>
   </si>
   <si>
-    <t>1,0&amp;1-73800|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-2000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-12600|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-74800|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-3200|8&amp;9-1600|9&amp;10-0|10&amp;12-3900|12&amp;14-1600|14&amp;16-1200|16&amp;18-2600|18&amp;20-200|20&amp;24-1900|24&amp;28-1700|28&amp;32-400|32&amp;36-900|36&amp;40-700|40&amp;48-500|48&amp;56-700|56&amp;64-600|64&amp;72-400|72&amp;80-100|80&amp;96-900|96&amp;112-900|112&amp;128-400|128&amp;144-300|144&amp;160-200|160&amp;192-0|192&amp;224-200|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</t>
+    <t>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</t>
   </si>
   <si>
     <t>1_9760|2_150|3_90</t>
@@ -251,28 +251,28 @@
     <t>麻将胡了</t>
   </si>
   <si>
-    <t>1_9990|2_75</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-69000|1&amp;20-12000|20&amp;40-6500|40&amp;60-3000|60&amp;80-2400|80&amp;100-2500|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-600|180&amp;200-600|200&amp;240-600|240&amp;280-500|280&amp;320-400|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-500|180&amp;200-400|200&amp;240-1000|240&amp;280-1100|280&amp;320-1200|320&amp;360-1200|360&amp;400-1300|400&amp;480-2600|480&amp;560-2700|560&amp;640-2700|640&amp;720-2600|720&amp;800-2800|800&amp;960-5100|960&amp;1120-4800|1120&amp;1280-4600|1280&amp;1440-4300|1440&amp;1600-4500|1600&amp;1920-7200|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
-  </si>
-  <si>
-    <t>1_9990|2_65</t>
-  </si>
-  <si>
-    <t>1_9990|2_55</t>
-  </si>
-  <si>
-    <t>1_9955|2_45</t>
-  </si>
-  <si>
-    <t>1_9990|2_35</t>
-  </si>
-  <si>
-    <t>1_9990|2_25</t>
-  </si>
-  <si>
-    <t>1_9990|2_15</t>
+    <t>1_9990|2_260</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>1_9990|2_240</t>
+  </si>
+  <si>
+    <t>1_9990|2_220</t>
+  </si>
+  <si>
+    <t>1_9800|2_200</t>
+  </si>
+  <si>
+    <t>1_9990|2_180</t>
+  </si>
+  <si>
+    <t>1_9990|2_160</t>
+  </si>
+  <si>
+    <t>1_9990|2_140</t>
   </si>
   <si>
     <t>财神</t>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="F13" s="7" t="str">
         <f t="shared" ref="F13:F18" si="1">F12</f>
-        <v>1,0&amp;1-73800|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-2000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-12600|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-74800|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-3200|8&amp;9-1600|9&amp;10-0|10&amp;12-3900|12&amp;14-1600|14&amp;16-1200|16&amp;18-2600|18&amp;20-200|20&amp;24-1900|24&amp;28-1700|28&amp;32-400|32&amp;36-900|36&amp;40-700|40&amp;48-500|48&amp;56-700|56&amp;64-600|64&amp;72-400|72&amp;80-100|80&amp;96-900|96&amp;112-900|112&amp;128-400|128&amp;144-300|144&amp;160-200|160&amp;192-0|192&amp;224-200|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
+        <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
       <c r="G13" s="9">
         <v>1000</v>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="F14" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>1,0&amp;1-73800|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-2000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-12600|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-74800|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-3200|8&amp;9-1600|9&amp;10-0|10&amp;12-3900|12&amp;14-1600|14&amp;16-1200|16&amp;18-2600|18&amp;20-200|20&amp;24-1900|24&amp;28-1700|28&amp;32-400|32&amp;36-900|36&amp;40-700|40&amp;48-500|48&amp;56-700|56&amp;64-600|64&amp;72-400|72&amp;80-100|80&amp;96-900|96&amp;112-900|112&amp;128-400|128&amp;144-300|144&amp;160-200|160&amp;192-0|192&amp;224-200|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
+        <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
       <c r="G14" s="9">
         <v>500</v>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="F15" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>1,0&amp;1-73800|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-2000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-12600|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-74800|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-3200|8&amp;9-1600|9&amp;10-0|10&amp;12-3900|12&amp;14-1600|14&amp;16-1200|16&amp;18-2600|18&amp;20-200|20&amp;24-1900|24&amp;28-1700|28&amp;32-400|32&amp;36-900|36&amp;40-700|40&amp;48-500|48&amp;56-700|56&amp;64-600|64&amp;72-400|72&amp;80-100|80&amp;96-900|96&amp;112-900|112&amp;128-400|128&amp;144-300|144&amp;160-200|160&amp;192-0|192&amp;224-200|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
+        <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
       <c r="G15" s="9">
         <v>-500</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F16" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>1,0&amp;1-73800|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-2000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-12600|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-74800|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-3200|8&amp;9-1600|9&amp;10-0|10&amp;12-3900|12&amp;14-1600|14&amp;16-1200|16&amp;18-2600|18&amp;20-200|20&amp;24-1900|24&amp;28-1700|28&amp;32-400|32&amp;36-900|36&amp;40-700|40&amp;48-500|48&amp;56-700|56&amp;64-600|64&amp;72-400|72&amp;80-100|80&amp;96-900|96&amp;112-900|112&amp;128-400|128&amp;144-300|144&amp;160-200|160&amp;192-0|192&amp;224-200|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
+        <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
       <c r="G16" s="9">
         <v>-1000</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="F17" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>1,0&amp;1-73800|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-2000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-12600|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-74800|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-3200|8&amp;9-1600|9&amp;10-0|10&amp;12-3900|12&amp;14-1600|14&amp;16-1200|16&amp;18-2600|18&amp;20-200|20&amp;24-1900|24&amp;28-1700|28&amp;32-400|32&amp;36-900|36&amp;40-700|40&amp;48-500|48&amp;56-700|56&amp;64-600|64&amp;72-400|72&amp;80-100|80&amp;96-900|96&amp;112-900|112&amp;128-400|128&amp;144-300|144&amp;160-200|160&amp;192-0|192&amp;224-200|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
+        <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
       <c r="G17" s="9">
         <v>-2000</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="F18" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>1,0&amp;1-73800|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-2000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-12600|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-74800|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-3200|8&amp;9-1600|9&amp;10-0|10&amp;12-3900|12&amp;14-1600|14&amp;16-1200|16&amp;18-2600|18&amp;20-200|20&amp;24-1900|24&amp;28-1700|28&amp;32-400|32&amp;36-900|36&amp;40-700|40&amp;48-500|48&amp;56-700|56&amp;64-600|64&amp;72-400|72&amp;80-100|80&amp;96-900|96&amp;112-900|112&amp;128-400|128&amp;144-300|144&amp;160-200|160&amp;192-0|192&amp;224-200|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
+        <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
       <c r="G18" s="9">
         <v>-999999</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="F20" s="12" t="str">
         <f t="shared" ref="F20:F25" si="2">F19</f>
-        <v>1,0&amp;1-69000|1&amp;20-12000|20&amp;40-6500|40&amp;60-3000|60&amp;80-2400|80&amp;100-2500|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-600|180&amp;200-600|200&amp;240-600|240&amp;280-500|280&amp;320-400|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-500|180&amp;200-400|200&amp;240-1000|240&amp;280-1100|280&amp;320-1200|320&amp;360-1200|360&amp;400-1300|400&amp;480-2600|480&amp;560-2700|560&amp;640-2700|640&amp;720-2600|720&amp;800-2800|800&amp;960-5100|960&amp;1120-4800|1120&amp;1280-4600|1280&amp;1440-4300|1440&amp;1600-4500|1600&amp;1920-7200|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G20" s="10">
         <v>1000</v>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="F21" s="12" t="str">
         <f t="shared" si="2"/>
-        <v>1,0&amp;1-69000|1&amp;20-12000|20&amp;40-6500|40&amp;60-3000|60&amp;80-2400|80&amp;100-2500|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-600|180&amp;200-600|200&amp;240-600|240&amp;280-500|280&amp;320-400|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-500|180&amp;200-400|200&amp;240-1000|240&amp;280-1100|280&amp;320-1200|320&amp;360-1200|360&amp;400-1300|400&amp;480-2600|480&amp;560-2700|560&amp;640-2700|640&amp;720-2600|720&amp;800-2800|800&amp;960-5100|960&amp;1120-4800|1120&amp;1280-4600|1280&amp;1440-4300|1440&amp;1600-4500|1600&amp;1920-7200|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G21" s="10">
         <v>500</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="F22" s="12" t="str">
         <f t="shared" si="2"/>
-        <v>1,0&amp;1-69000|1&amp;20-12000|20&amp;40-6500|40&amp;60-3000|60&amp;80-2400|80&amp;100-2500|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-600|180&amp;200-600|200&amp;240-600|240&amp;280-500|280&amp;320-400|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-500|180&amp;200-400|200&amp;240-1000|240&amp;280-1100|280&amp;320-1200|320&amp;360-1200|360&amp;400-1300|400&amp;480-2600|480&amp;560-2700|560&amp;640-2700|640&amp;720-2600|720&amp;800-2800|800&amp;960-5100|960&amp;1120-4800|1120&amp;1280-4600|1280&amp;1440-4300|1440&amp;1600-4500|1600&amp;1920-7200|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G22" s="10">
         <v>-500</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="F23" s="12" t="str">
         <f t="shared" si="2"/>
-        <v>1,0&amp;1-69000|1&amp;20-12000|20&amp;40-6500|40&amp;60-3000|60&amp;80-2400|80&amp;100-2500|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-600|180&amp;200-600|200&amp;240-600|240&amp;280-500|280&amp;320-400|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-500|180&amp;200-400|200&amp;240-1000|240&amp;280-1100|280&amp;320-1200|320&amp;360-1200|360&amp;400-1300|400&amp;480-2600|480&amp;560-2700|560&amp;640-2700|640&amp;720-2600|720&amp;800-2800|800&amp;960-5100|960&amp;1120-4800|1120&amp;1280-4600|1280&amp;1440-4300|1440&amp;1600-4500|1600&amp;1920-7200|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G23" s="10">
         <v>-1000</v>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F24" s="12" t="str">
         <f t="shared" si="2"/>
-        <v>1,0&amp;1-69000|1&amp;20-12000|20&amp;40-6500|40&amp;60-3000|60&amp;80-2400|80&amp;100-2500|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-600|180&amp;200-600|200&amp;240-600|240&amp;280-500|280&amp;320-400|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-500|180&amp;200-400|200&amp;240-1000|240&amp;280-1100|280&amp;320-1200|320&amp;360-1200|360&amp;400-1300|400&amp;480-2600|480&amp;560-2700|560&amp;640-2700|640&amp;720-2600|720&amp;800-2800|800&amp;960-5100|960&amp;1120-4800|1120&amp;1280-4600|1280&amp;1440-4300|1440&amp;1600-4500|1600&amp;1920-7200|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G24" s="10">
         <v>-2000</v>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="F25" s="12" t="str">
         <f t="shared" si="2"/>
-        <v>1,0&amp;1-69000|1&amp;20-12000|20&amp;40-6500|40&amp;60-3000|60&amp;80-2400|80&amp;100-2500|100&amp;120-800|120&amp;140-600|140&amp;160-500|160&amp;180-600|180&amp;200-600|200&amp;240-600|240&amp;280-500|280&amp;320-400|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-500|180&amp;200-400|200&amp;240-1000|240&amp;280-1100|280&amp;320-1200|320&amp;360-1200|360&amp;400-1300|400&amp;480-2600|480&amp;560-2700|560&amp;640-2700|640&amp;720-2600|720&amp;800-2800|800&amp;960-5100|960&amp;1120-4800|1120&amp;1280-4600|1280&amp;1440-4300|1440&amp;1600-4500|1600&amp;1920-7200|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G25" s="10">
         <v>-999999</v>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -251,28 +251,28 @@
     <t>麻将胡了</t>
   </si>
   <si>
-    <t>1_9990|2_260</t>
+    <t>1_9740|2_260</t>
   </si>
   <si>
     <t>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
   </si>
   <si>
-    <t>1_9990|2_240</t>
-  </si>
-  <si>
-    <t>1_9990|2_220</t>
+    <t>1_9760|2_240</t>
+  </si>
+  <si>
+    <t>1_9780|2_220</t>
   </si>
   <si>
     <t>1_9800|2_200</t>
   </si>
   <si>
-    <t>1_9990|2_180</t>
-  </si>
-  <si>
-    <t>1_9990|2_160</t>
-  </si>
-  <si>
-    <t>1_9990|2_140</t>
+    <t>1_9820|2_180</t>
+  </si>
+  <si>
+    <t>1_9840|2_160</t>
+  </si>
+  <si>
+    <t>1_9860|2_140</t>
   </si>
   <si>
     <t>财神</t>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="69">
   <si>
     <t>id</t>
   </si>
@@ -1340,7 +1340,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
@@ -2426,6 +2426,203 @@
         <v>32</v>
       </c>
     </row>
+    <row r="40" ht="16.5" spans="1:9">
+      <c r="A40" s="5">
+        <v>24001</v>
+      </c>
+      <c r="B40" s="5">
+        <v>102400</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="5">
+        <v>1</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G40" s="5">
+        <v>2000</v>
+      </c>
+      <c r="H40" s="5">
+        <v>999999</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" spans="1:9">
+      <c r="A41" s="5">
+        <v>24002</v>
+      </c>
+      <c r="B41" s="5">
+        <v>102400</v>
+      </c>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5">
+        <v>2</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F41" s="7" t="str">
+        <f t="shared" ref="F41:F46" si="5">F40</f>
+        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
+      </c>
+      <c r="G41" s="5">
+        <v>1000</v>
+      </c>
+      <c r="H41" s="5">
+        <v>2000</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" spans="1:9">
+      <c r="A42" s="5">
+        <v>24003</v>
+      </c>
+      <c r="B42" s="5">
+        <v>102400</v>
+      </c>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5">
+        <v>3</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
+      </c>
+      <c r="G42" s="5">
+        <v>500</v>
+      </c>
+      <c r="H42" s="5">
+        <v>1000</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" spans="1:9">
+      <c r="A43" s="5">
+        <v>24004</v>
+      </c>
+      <c r="B43" s="5">
+        <v>102400</v>
+      </c>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5">
+        <v>4</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
+      </c>
+      <c r="G43" s="5">
+        <v>-500</v>
+      </c>
+      <c r="H43" s="5">
+        <v>500</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="1:9">
+      <c r="A44" s="5">
+        <v>24005</v>
+      </c>
+      <c r="B44" s="5">
+        <v>102400</v>
+      </c>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5">
+        <v>5</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F44" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
+      </c>
+      <c r="G44" s="5">
+        <v>-1000</v>
+      </c>
+      <c r="H44" s="5">
+        <v>-500</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" spans="1:9">
+      <c r="A45" s="5">
+        <v>24006</v>
+      </c>
+      <c r="B45" s="5">
+        <v>102400</v>
+      </c>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5">
+        <v>6</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F45" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
+      </c>
+      <c r="G45" s="5">
+        <v>-2000</v>
+      </c>
+      <c r="H45" s="5">
+        <v>-1000</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="1:9">
+      <c r="A46" s="5">
+        <v>24007</v>
+      </c>
+      <c r="B46" s="5">
+        <v>102400</v>
+      </c>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5">
+        <v>7</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F46" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
+      </c>
+      <c r="G46" s="5">
+        <v>-999999</v>
+      </c>
+      <c r="H46" s="5">
+        <v>-2000</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="78">
   <si>
     <t>id</t>
   </si>
@@ -327,6 +327,33 @@
   </si>
   <si>
     <t>1_8999|2_1000|3_1</t>
+  </si>
+  <si>
+    <t>圣诞狂欢夜</t>
+  </si>
+  <si>
+    <t>1_9600|2_260|3_140</t>
+  </si>
+  <si>
+    <t>1_9640|2_240|3_120</t>
+  </si>
+  <si>
+    <t>1_9680|2_220|3_100</t>
+  </si>
+  <si>
+    <t>1_9720|2_200|3_80</t>
+  </si>
+  <si>
+    <t>1_9760|2_180|3_60</t>
+  </si>
+  <si>
+    <t>1_9800|2_160|3_40</t>
+  </si>
+  <si>
+    <t>1_9840|2_140|3_20</t>
+  </si>
+  <si>
+    <t>雷神</t>
   </si>
 </sst>
 </file>
@@ -982,11 +1009,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1019,6 +1047,18 @@
     </xf>
     <xf numFmtId="3" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1340,1286 +1380,1686 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
     <col min="2" max="3" width="15.25" customWidth="1"/>
     <col min="4" max="4" width="10.875" customWidth="1"/>
-    <col min="5" max="5" width="33.75" style="4" customWidth="1"/>
-    <col min="6" max="6" width="114.025" style="4" customWidth="1"/>
+    <col min="5" max="5" width="33.75" style="5" customWidth="1"/>
+    <col min="6" max="6" width="114.025" style="5" customWidth="1"/>
     <col min="7" max="7" width="15.625" customWidth="1"/>
     <col min="8" max="8" width="15.125" customWidth="1"/>
     <col min="9" max="9" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:9">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="7"/>
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6" t="s">
+      <c r="C2" s="7"/>
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="5"/>
+      <c r="I2" s="6"/>
     </row>
     <row r="3" ht="16.5" spans="1:9">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="5"/>
+      <c r="I3" s="6"/>
     </row>
     <row r="4" ht="16.5" spans="1:9">
-      <c r="A4" s="5"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
     </row>
     <row r="5" ht="16.5" spans="1:9">
-      <c r="A5" s="5">
+      <c r="A5" s="6">
         <v>1001</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="6">
         <v>100100</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="6">
         <v>1</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="6">
         <v>2000</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="6">
         <v>999999</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:9">
-      <c r="A6" s="5">
+      <c r="A6" s="6">
         <v>1002</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="6">
         <v>100100</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5">
+      <c r="C6" s="6"/>
+      <c r="D6" s="6">
         <v>2</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="7" t="str">
+      <c r="F6" s="8" t="str">
         <f t="shared" ref="F6:F11" si="0">F5</f>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="6">
         <v>1000</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="6">
         <v>2000</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
-      <c r="A7" s="5">
+      <c r="A7" s="6">
         <v>1003</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="6">
         <v>100100</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5">
+      <c r="C7" s="6"/>
+      <c r="D7" s="6">
         <v>3</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="7" t="str">
+      <c r="F7" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="6">
         <v>500</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="6">
         <v>1000</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
-      <c r="A8" s="5">
+      <c r="A8" s="6">
         <v>1004</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="6">
         <v>100100</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5">
+      <c r="C8" s="6"/>
+      <c r="D8" s="6">
         <v>4</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="7" t="str">
+      <c r="F8" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="6">
         <v>-500</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="6">
         <v>500</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:9">
-      <c r="A9" s="5">
+      <c r="A9" s="6">
         <v>1005</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="6">
         <v>100100</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6">
         <v>5</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="7" t="str">
+      <c r="F9" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="6">
         <v>-1000</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="6">
         <v>-500</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:9">
-      <c r="A10" s="5">
+      <c r="A10" s="6">
         <v>1006</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="6">
         <v>100100</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5">
+      <c r="C10" s="6"/>
+      <c r="D10" s="6">
         <v>6</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="7" t="str">
+      <c r="F10" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="6">
         <v>-2000</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="6">
         <v>-1000</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:9">
-      <c r="A11" s="5">
+      <c r="A11" s="6">
         <v>1007</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="6">
         <v>100100</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5">
+      <c r="C11" s="6"/>
+      <c r="D11" s="6">
         <v>7</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="7" t="str">
+      <c r="F11" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="6">
         <v>-999999</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="6">
         <v>-2000</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A12" s="9">
+      <c r="A12" s="10">
         <v>3001</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="10">
         <v>100300</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="10">
         <v>1</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="10">
         <v>2000</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="10">
         <v>999999</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A13" s="9">
+      <c r="A13" s="10">
         <v>3002</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="10">
         <v>100300</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9">
+      <c r="C13" s="10"/>
+      <c r="D13" s="10">
         <v>2</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="7" t="str">
+      <c r="F13" s="8" t="str">
         <f t="shared" ref="F13:F18" si="1">F12</f>
         <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="10">
         <v>1000</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="10">
         <v>2000</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A14" s="9">
+      <c r="A14" s="10">
         <v>3003</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="10">
         <v>100300</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9">
+      <c r="C14" s="10"/>
+      <c r="D14" s="10">
         <v>3</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="7" t="str">
+      <c r="F14" s="8" t="str">
         <f t="shared" si="1"/>
         <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="10">
         <v>500</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="10">
         <v>1000</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A15" s="9">
+      <c r="A15" s="10">
         <v>3004</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="10">
         <v>100300</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9">
+      <c r="C15" s="10"/>
+      <c r="D15" s="10">
         <v>4</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="7" t="str">
+      <c r="F15" s="8" t="str">
         <f t="shared" si="1"/>
         <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="10">
         <v>-500</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="10">
         <v>500</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="10" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A16" s="9">
+      <c r="A16" s="10">
         <v>3005</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="10">
         <v>100300</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9">
+      <c r="C16" s="10"/>
+      <c r="D16" s="10">
         <v>5</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="7" t="str">
+      <c r="F16" s="8" t="str">
         <f t="shared" si="1"/>
         <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="10">
         <v>-1000</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="10">
         <v>-500</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="I16" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A17" s="9">
+      <c r="A17" s="10">
         <v>3006</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="10">
         <v>100300</v>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9">
+      <c r="C17" s="10"/>
+      <c r="D17" s="10">
         <v>6</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="7" t="str">
+      <c r="F17" s="8" t="str">
         <f t="shared" si="1"/>
         <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="10">
         <v>-2000</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="10">
         <v>-1000</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A18" s="9">
+      <c r="A18" s="10">
         <v>3007</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="10">
         <v>100300</v>
       </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9">
+      <c r="C18" s="10"/>
+      <c r="D18" s="10">
         <v>7</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="7" t="str">
+      <c r="F18" s="8" t="str">
         <f t="shared" si="1"/>
         <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="10">
         <v>-999999</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="10">
         <v>-2000</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A19" s="5">
+      <c r="A19" s="6">
         <v>7001</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="11">
         <v>100700</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="11">
         <v>1</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="11">
         <v>2000</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="11">
         <v>999999</v>
       </c>
-      <c r="I19" s="10" t="s">
+      <c r="I19" s="11" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A20" s="5">
+      <c r="A20" s="6">
         <v>7002</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="11">
         <v>100700</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10">
+      <c r="C20" s="11"/>
+      <c r="D20" s="11">
         <v>2</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F20" s="12" t="str">
+      <c r="F20" s="13" t="str">
         <f t="shared" ref="F20:F25" si="2">F19</f>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="11">
         <v>1000</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="11">
         <v>2000</v>
       </c>
-      <c r="I20" s="10" t="s">
+      <c r="I20" s="11" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A21" s="5">
+      <c r="A21" s="6">
         <v>7003</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="11">
         <v>100700</v>
       </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10">
+      <c r="C21" s="11"/>
+      <c r="D21" s="11">
         <v>3</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F21" s="12" t="str">
+      <c r="F21" s="13" t="str">
         <f t="shared" si="2"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="11">
         <v>500</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="11">
         <v>1000</v>
       </c>
-      <c r="I21" s="10" t="s">
+      <c r="I21" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A22" s="5">
+      <c r="A22" s="6">
         <v>7004</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="11">
         <v>100700</v>
       </c>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10">
+      <c r="C22" s="11"/>
+      <c r="D22" s="11">
         <v>4</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="12" t="str">
+      <c r="F22" s="13" t="str">
         <f t="shared" si="2"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="11">
         <v>-500</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="11">
         <v>500</v>
       </c>
-      <c r="I22" s="10" t="s">
+      <c r="I22" s="11" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A23" s="5">
+      <c r="A23" s="6">
         <v>7005</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="11">
         <v>100700</v>
       </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10">
+      <c r="C23" s="11"/>
+      <c r="D23" s="11">
         <v>5</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="12" t="str">
+      <c r="F23" s="13" t="str">
         <f t="shared" si="2"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="11">
         <v>-1000</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="11">
         <v>-500</v>
       </c>
-      <c r="I23" s="10" t="s">
+      <c r="I23" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A24" s="5">
+      <c r="A24" s="6">
         <v>7006</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="11">
         <v>100700</v>
       </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10">
+      <c r="C24" s="11"/>
+      <c r="D24" s="11">
         <v>6</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="F24" s="12" t="str">
+      <c r="F24" s="13" t="str">
         <f t="shared" si="2"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="11">
         <v>-2000</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="11">
         <v>-1000</v>
       </c>
-      <c r="I24" s="10" t="s">
+      <c r="I24" s="11" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A25" s="5">
+      <c r="A25" s="6">
         <v>7007</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="11">
         <v>100700</v>
       </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10">
+      <c r="C25" s="11"/>
+      <c r="D25" s="11">
         <v>7</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="F25" s="12" t="str">
+      <c r="F25" s="13" t="str">
         <f t="shared" si="2"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="11">
         <v>-999999</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="11">
         <v>-2000</v>
       </c>
-      <c r="I25" s="10" t="s">
+      <c r="I25" s="11" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A26" s="9">
+      <c r="A26" s="10">
         <v>12001</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="10">
         <v>101200</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="10">
         <v>1</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="10">
         <v>2000</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="10">
         <v>999999</v>
       </c>
-      <c r="I26" s="9" t="s">
+      <c r="I26" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A27" s="9">
+      <c r="A27" s="10">
         <v>12002</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="10">
         <v>101200</v>
       </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9">
+      <c r="C27" s="10"/>
+      <c r="D27" s="10">
         <v>2</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F27" s="7" t="str">
+      <c r="F27" s="8" t="str">
         <f t="shared" ref="F27:F32" si="3">F26</f>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="10">
         <v>1000</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="10">
         <v>2000</v>
       </c>
-      <c r="I27" s="9" t="s">
+      <c r="I27" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A28" s="9">
+      <c r="A28" s="10">
         <v>12003</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="10">
         <v>101200</v>
       </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9">
+      <c r="C28" s="10"/>
+      <c r="D28" s="10">
         <v>3</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F28" s="7" t="str">
+      <c r="F28" s="8" t="str">
         <f t="shared" si="3"/>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="10">
         <v>500</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="10">
         <v>1000</v>
       </c>
-      <c r="I28" s="9" t="s">
+      <c r="I28" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A29" s="9">
+      <c r="A29" s="10">
         <v>12004</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="10">
         <v>101200</v>
       </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9">
+      <c r="C29" s="10"/>
+      <c r="D29" s="10">
         <v>4</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F29" s="7" t="str">
+      <c r="F29" s="8" t="str">
         <f t="shared" si="3"/>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="10">
         <v>-500</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="10">
         <v>500</v>
       </c>
-      <c r="I29" s="9" t="s">
+      <c r="I29" s="10" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A30" s="9">
+      <c r="A30" s="10">
         <v>12005</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="10">
         <v>101200</v>
       </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9">
+      <c r="C30" s="10"/>
+      <c r="D30" s="10">
         <v>5</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="F30" s="7" t="str">
+      <c r="F30" s="8" t="str">
         <f t="shared" si="3"/>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="10">
         <v>-1000</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="10">
         <v>-500</v>
       </c>
-      <c r="I30" s="9" t="s">
+      <c r="I30" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A31" s="9">
+      <c r="A31" s="10">
         <v>12006</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="10">
         <v>101200</v>
       </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9">
+      <c r="C31" s="10"/>
+      <c r="D31" s="10">
         <v>6</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F31" s="7" t="str">
+      <c r="F31" s="8" t="str">
         <f t="shared" si="3"/>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="10">
         <v>-2000</v>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="10">
         <v>-1000</v>
       </c>
-      <c r="I31" s="9" t="s">
+      <c r="I31" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A32" s="9">
+      <c r="A32" s="10">
         <v>12007</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="10">
         <v>101200</v>
       </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9">
+      <c r="C32" s="10"/>
+      <c r="D32" s="10">
         <v>7</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="F32" s="7" t="str">
+      <c r="F32" s="8" t="str">
         <f t="shared" si="3"/>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="10">
         <v>-999999</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H32" s="10">
         <v>-2000</v>
       </c>
-      <c r="I32" s="9" t="s">
+      <c r="I32" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="33" s="3" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A33" s="5">
+      <c r="A33" s="6">
         <v>14001</v>
       </c>
-      <c r="B33" s="13">
+      <c r="B33" s="14">
         <v>101400</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="13">
+      <c r="D33" s="14">
         <v>1</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F33" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="G33" s="13">
+      <c r="G33" s="14">
         <v>2000</v>
       </c>
-      <c r="H33" s="13">
+      <c r="H33" s="14">
         <v>999999</v>
       </c>
-      <c r="I33" s="13" t="s">
+      <c r="I33" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="34" s="3" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A34" s="5">
+      <c r="A34" s="6">
         <v>14002</v>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="14">
         <v>101400</v>
       </c>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13">
+      <c r="C34" s="14"/>
+      <c r="D34" s="14">
         <v>2</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="E34" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="F34" s="7" t="str">
+      <c r="F34" s="8" t="str">
         <f t="shared" ref="F34:F39" si="4">F33</f>
         <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
-      <c r="G34" s="13">
+      <c r="G34" s="14">
         <v>1000</v>
       </c>
-      <c r="H34" s="13">
+      <c r="H34" s="14">
         <v>2000</v>
       </c>
-      <c r="I34" s="13" t="s">
+      <c r="I34" s="14" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A35" s="5">
+      <c r="A35" s="6">
         <v>14003</v>
       </c>
-      <c r="B35" s="13">
+      <c r="B35" s="14">
         <v>101400</v>
       </c>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13">
+      <c r="C35" s="14"/>
+      <c r="D35" s="14">
         <v>3</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="F35" s="7" t="str">
+      <c r="F35" s="8" t="str">
         <f t="shared" si="4"/>
         <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
-      <c r="G35" s="13">
+      <c r="G35" s="14">
         <v>500</v>
       </c>
-      <c r="H35" s="13">
+      <c r="H35" s="14">
         <v>1000</v>
       </c>
-      <c r="I35" s="13" t="s">
+      <c r="I35" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="36" s="3" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A36" s="5">
+      <c r="A36" s="6">
         <v>14004</v>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="14">
         <v>101400</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13">
+      <c r="C36" s="14"/>
+      <c r="D36" s="14">
         <v>4</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E36" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="F36" s="7" t="str">
+      <c r="F36" s="8" t="str">
         <f t="shared" si="4"/>
         <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
-      <c r="G36" s="13">
+      <c r="G36" s="14">
         <v>-500</v>
       </c>
-      <c r="H36" s="13">
+      <c r="H36" s="14">
         <v>500</v>
       </c>
-      <c r="I36" s="13" t="s">
+      <c r="I36" s="14" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="37" s="3" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A37" s="5">
+      <c r="A37" s="6">
         <v>14005</v>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="14">
         <v>101400</v>
       </c>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13">
+      <c r="C37" s="14"/>
+      <c r="D37" s="14">
         <v>5</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="F37" s="7" t="str">
+      <c r="F37" s="8" t="str">
         <f t="shared" si="4"/>
         <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
-      <c r="G37" s="13">
+      <c r="G37" s="14">
         <v>-1000</v>
       </c>
-      <c r="H37" s="13">
+      <c r="H37" s="14">
         <v>-500</v>
       </c>
-      <c r="I37" s="13" t="s">
+      <c r="I37" s="14" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A38" s="5">
+      <c r="A38" s="6">
         <v>14006</v>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="14">
         <v>101400</v>
       </c>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13">
+      <c r="C38" s="14"/>
+      <c r="D38" s="14">
         <v>6</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="F38" s="7" t="str">
+      <c r="F38" s="8" t="str">
         <f t="shared" si="4"/>
         <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
-      <c r="G38" s="13">
+      <c r="G38" s="14">
         <v>-2000</v>
       </c>
-      <c r="H38" s="13">
+      <c r="H38" s="14">
         <v>-1000</v>
       </c>
-      <c r="I38" s="13" t="s">
+      <c r="I38" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A39" s="5">
+      <c r="A39" s="6">
         <v>14007</v>
       </c>
-      <c r="B39" s="13">
+      <c r="B39" s="14">
         <v>101400</v>
       </c>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13">
+      <c r="C39" s="14"/>
+      <c r="D39" s="14">
         <v>7</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="F39" s="7" t="str">
+      <c r="F39" s="8" t="str">
         <f t="shared" si="4"/>
         <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
-      <c r="G39" s="13">
+      <c r="G39" s="14">
         <v>-999999</v>
       </c>
-      <c r="H39" s="13">
+      <c r="H39" s="14">
         <v>-2000</v>
       </c>
-      <c r="I39" s="13" t="s">
+      <c r="I39" s="14" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:9">
-      <c r="A40" s="5">
+      <c r="A40" s="6">
         <v>24001</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="6">
         <v>102400</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="6">
         <v>1</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E40" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="F40" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="G40" s="5">
+      <c r="G40" s="6">
         <v>2000</v>
       </c>
-      <c r="H40" s="5">
+      <c r="H40" s="6">
         <v>999999</v>
       </c>
-      <c r="I40" s="5" t="s">
+      <c r="I40" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:9">
-      <c r="A41" s="5">
+      <c r="A41" s="6">
         <v>24002</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41" s="6">
         <v>102400</v>
       </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5">
+      <c r="C41" s="6"/>
+      <c r="D41" s="6">
         <v>2</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F41" s="7" t="str">
+      <c r="F41" s="8" t="str">
         <f t="shared" ref="F41:F46" si="5">F40</f>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G41" s="5">
+      <c r="G41" s="6">
         <v>1000</v>
       </c>
-      <c r="H41" s="5">
+      <c r="H41" s="6">
         <v>2000</v>
       </c>
-      <c r="I41" s="5" t="s">
+      <c r="I41" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:9">
-      <c r="A42" s="5">
+      <c r="A42" s="6">
         <v>24003</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="6">
         <v>102400</v>
       </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5">
+      <c r="C42" s="6"/>
+      <c r="D42" s="6">
         <v>3</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F42" s="7" t="str">
+      <c r="F42" s="8" t="str">
         <f t="shared" si="5"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G42" s="5">
+      <c r="G42" s="6">
         <v>500</v>
       </c>
-      <c r="H42" s="5">
+      <c r="H42" s="6">
         <v>1000</v>
       </c>
-      <c r="I42" s="5" t="s">
+      <c r="I42" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:9">
-      <c r="A43" s="5">
+      <c r="A43" s="6">
         <v>24004</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="6">
         <v>102400</v>
       </c>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5">
+      <c r="C43" s="6"/>
+      <c r="D43" s="6">
         <v>4</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="E43" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F43" s="7" t="str">
+      <c r="F43" s="8" t="str">
         <f t="shared" si="5"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G43" s="5">
+      <c r="G43" s="6">
         <v>-500</v>
       </c>
-      <c r="H43" s="5">
+      <c r="H43" s="6">
         <v>500</v>
       </c>
-      <c r="I43" s="5" t="s">
+      <c r="I43" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:9">
-      <c r="A44" s="5">
+      <c r="A44" s="6">
         <v>24005</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="6">
         <v>102400</v>
       </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5">
+      <c r="C44" s="6"/>
+      <c r="D44" s="6">
         <v>5</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E44" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F44" s="7" t="str">
+      <c r="F44" s="8" t="str">
         <f t="shared" si="5"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G44" s="5">
+      <c r="G44" s="6">
         <v>-1000</v>
       </c>
-      <c r="H44" s="5">
+      <c r="H44" s="6">
         <v>-500</v>
       </c>
-      <c r="I44" s="5" t="s">
+      <c r="I44" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:9">
-      <c r="A45" s="5">
+      <c r="A45" s="6">
         <v>24006</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45" s="6">
         <v>102400</v>
       </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5">
+      <c r="C45" s="6"/>
+      <c r="D45" s="6">
         <v>6</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="E45" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F45" s="7" t="str">
+      <c r="F45" s="8" t="str">
         <f t="shared" si="5"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G45" s="5">
+      <c r="G45" s="6">
         <v>-2000</v>
       </c>
-      <c r="H45" s="5">
+      <c r="H45" s="6">
         <v>-1000</v>
       </c>
-      <c r="I45" s="5" t="s">
+      <c r="I45" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:9">
-      <c r="A46" s="5">
+      <c r="A46" s="6">
         <v>24007</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46" s="6">
         <v>102400</v>
       </c>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5">
+      <c r="C46" s="6"/>
+      <c r="D46" s="6">
         <v>7</v>
       </c>
-      <c r="E46" s="7" t="s">
+      <c r="E46" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F46" s="7" t="str">
+      <c r="F46" s="8" t="str">
         <f t="shared" si="5"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G46" s="5">
+      <c r="G46" s="6">
         <v>-999999</v>
       </c>
-      <c r="H46" s="5">
+      <c r="H46" s="6">
         <v>-2000</v>
       </c>
-      <c r="I46" s="5" t="s">
+      <c r="I46" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A47" s="6">
+        <v>17001</v>
+      </c>
+      <c r="B47" s="11">
+        <v>101700</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D47" s="11">
+        <v>1</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G47" s="11">
+        <v>2000</v>
+      </c>
+      <c r="H47" s="11">
+        <v>999999</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A48" s="6">
+        <v>17002</v>
+      </c>
+      <c r="B48" s="11">
+        <v>101700</v>
+      </c>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11">
+        <v>2</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F48" s="13" t="str">
+        <f t="shared" ref="F48:F53" si="6">F47</f>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G48" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H48" s="11">
+        <v>2000</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A49" s="6">
+        <v>17003</v>
+      </c>
+      <c r="B49" s="11">
+        <v>101700</v>
+      </c>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11">
+        <v>3</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F49" s="13" t="str">
+        <f t="shared" si="6"/>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G49" s="11">
+        <v>500</v>
+      </c>
+      <c r="H49" s="11">
+        <v>1000</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A50" s="6">
+        <v>17004</v>
+      </c>
+      <c r="B50" s="11">
+        <v>101700</v>
+      </c>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11">
+        <v>4</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F50" s="13" t="str">
+        <f t="shared" si="6"/>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G50" s="11">
+        <v>-500</v>
+      </c>
+      <c r="H50" s="11">
+        <v>500</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A51" s="6">
+        <v>17005</v>
+      </c>
+      <c r="B51" s="11">
+        <v>101700</v>
+      </c>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11">
+        <v>5</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F51" s="13" t="str">
+        <f t="shared" si="6"/>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G51" s="11">
+        <v>-1000</v>
+      </c>
+      <c r="H51" s="11">
+        <v>-500</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="52" s="2" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A52" s="6">
+        <v>17006</v>
+      </c>
+      <c r="B52" s="11">
+        <v>101700</v>
+      </c>
+      <c r="C52" s="11"/>
+      <c r="D52" s="11">
+        <v>6</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F52" s="13" t="str">
+        <f t="shared" si="6"/>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G52" s="11">
+        <v>-2000</v>
+      </c>
+      <c r="H52" s="11">
+        <v>-1000</v>
+      </c>
+      <c r="I52" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" s="2" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A53" s="6">
+        <v>17007</v>
+      </c>
+      <c r="B53" s="11">
+        <v>101700</v>
+      </c>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11">
+        <v>7</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F53" s="13" t="str">
+        <f t="shared" si="6"/>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G53" s="11">
+        <v>-999999</v>
+      </c>
+      <c r="H53" s="11">
+        <v>-2000</v>
+      </c>
+      <c r="I53" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="54" s="4" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A54" s="16">
+        <v>22001</v>
+      </c>
+      <c r="B54" s="17">
+        <v>102200</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D54" s="17">
+        <v>1</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G54" s="6">
+        <v>2000</v>
+      </c>
+      <c r="H54" s="6">
+        <v>999999</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" s="4" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A55" s="16">
+        <v>22002</v>
+      </c>
+      <c r="B55" s="17">
+        <v>102200</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D55" s="17">
+        <v>2</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G55" s="6">
+        <v>1000</v>
+      </c>
+      <c r="H55" s="6">
+        <v>2000</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" s="4" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A56" s="16">
+        <v>22003</v>
+      </c>
+      <c r="B56" s="17">
+        <v>102200</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D56" s="17">
+        <v>3</v>
+      </c>
+      <c r="E56" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G56" s="6">
+        <v>500</v>
+      </c>
+      <c r="H56" s="6">
+        <v>1000</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" s="4" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A57" s="16">
+        <v>22004</v>
+      </c>
+      <c r="B57" s="17">
+        <v>102200</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D57" s="17">
+        <v>4</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G57" s="6">
+        <v>-500</v>
+      </c>
+      <c r="H57" s="6">
+        <v>500</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" s="4" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A58" s="16">
+        <v>22005</v>
+      </c>
+      <c r="B58" s="17">
+        <v>102200</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D58" s="17">
+        <v>5</v>
+      </c>
+      <c r="E58" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G58" s="6">
+        <v>-1000</v>
+      </c>
+      <c r="H58" s="6">
+        <v>-500</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="59" s="4" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A59" s="16">
+        <v>22006</v>
+      </c>
+      <c r="B59" s="17">
+        <v>102200</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D59" s="17">
+        <v>6</v>
+      </c>
+      <c r="E59" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G59" s="6">
+        <v>-2000</v>
+      </c>
+      <c r="H59" s="6">
+        <v>-1000</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" s="4" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A60" s="16">
+        <v>22007</v>
+      </c>
+      <c r="B60" s="17">
+        <v>102200</v>
+      </c>
+      <c r="C60" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D60" s="17">
+        <v>7</v>
+      </c>
+      <c r="E60" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G60" s="6">
+        <v>-999999</v>
+      </c>
+      <c r="H60" s="6">
+        <v>-2000</v>
+      </c>
+      <c r="I60" s="6" t="s">
         <v>32</v>
       </c>
     </row>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="79">
   <si>
     <t>id</t>
   </si>
@@ -354,6 +354,9 @@
   </si>
   <si>
     <t>雷神</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</t>
   </si>
 </sst>
 </file>
@@ -1009,7 +1012,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1053,12 +1056,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -2867,17 +2864,17 @@
       <c r="B54" s="17">
         <v>102200</v>
       </c>
-      <c r="C54" s="18" t="s">
+      <c r="C54" s="17" t="s">
         <v>77</v>
       </c>
       <c r="D54" s="17">
         <v>1</v>
       </c>
-      <c r="E54" s="19" t="s">
+      <c r="E54" s="16" t="s">
         <v>70</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="G54" s="6">
         <v>2000</v>
@@ -2896,17 +2893,18 @@
       <c r="B55" s="17">
         <v>102200</v>
       </c>
-      <c r="C55" s="18" t="s">
+      <c r="C55" s="17" t="s">
         <v>77</v>
       </c>
       <c r="D55" s="17">
         <v>2</v>
       </c>
-      <c r="E55" s="19" t="s">
+      <c r="E55" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="F55" s="8" t="s">
-        <v>62</v>
+      <c r="F55" s="8" t="str">
+        <f>F54</f>
+        <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="G55" s="6">
         <v>1000</v>
@@ -2925,17 +2923,18 @@
       <c r="B56" s="17">
         <v>102200</v>
       </c>
-      <c r="C56" s="18" t="s">
+      <c r="C56" s="17" t="s">
         <v>77</v>
       </c>
       <c r="D56" s="17">
         <v>3</v>
       </c>
-      <c r="E56" s="19" t="s">
+      <c r="E56" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="F56" s="8" t="s">
-        <v>62</v>
+      <c r="F56" s="8" t="str">
+        <f>F55</f>
+        <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="G56" s="6">
         <v>500</v>
@@ -2954,17 +2953,18 @@
       <c r="B57" s="17">
         <v>102200</v>
       </c>
-      <c r="C57" s="18" t="s">
+      <c r="C57" s="17" t="s">
         <v>77</v>
       </c>
       <c r="D57" s="17">
         <v>4</v>
       </c>
-      <c r="E57" s="19" t="s">
+      <c r="E57" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="F57" s="8" t="s">
-        <v>62</v>
+      <c r="F57" s="8" t="str">
+        <f>F56</f>
+        <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="G57" s="6">
         <v>-500</v>
@@ -2983,17 +2983,18 @@
       <c r="B58" s="17">
         <v>102200</v>
       </c>
-      <c r="C58" s="18" t="s">
+      <c r="C58" s="17" t="s">
         <v>77</v>
       </c>
       <c r="D58" s="17">
         <v>5</v>
       </c>
-      <c r="E58" s="19" t="s">
+      <c r="E58" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="8" t="s">
-        <v>62</v>
+      <c r="F58" s="8" t="str">
+        <f>F57</f>
+        <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="G58" s="6">
         <v>-1000</v>
@@ -3012,17 +3013,18 @@
       <c r="B59" s="17">
         <v>102200</v>
       </c>
-      <c r="C59" s="18" t="s">
+      <c r="C59" s="17" t="s">
         <v>77</v>
       </c>
       <c r="D59" s="17">
         <v>6</v>
       </c>
-      <c r="E59" s="19" t="s">
+      <c r="E59" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="F59" s="8" t="s">
-        <v>62</v>
+      <c r="F59" s="8" t="str">
+        <f>F58</f>
+        <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="G59" s="6">
         <v>-2000</v>
@@ -3041,17 +3043,18 @@
       <c r="B60" s="17">
         <v>102200</v>
       </c>
-      <c r="C60" s="18" t="s">
+      <c r="C60" s="17" t="s">
         <v>77</v>
       </c>
       <c r="D60" s="17">
         <v>7</v>
       </c>
-      <c r="E60" s="19" t="s">
+      <c r="E60" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="F60" s="8" t="s">
-        <v>62</v>
+      <c r="F60" s="8" t="str">
+        <f>F59</f>
+        <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="G60" s="6">
         <v>-999999</v>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="89">
   <si>
     <t>id</t>
   </si>
@@ -335,6 +335,9 @@
     <t>1_9600|2_260|3_140</t>
   </si>
   <si>
+    <t>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
+  </si>
+  <si>
     <t>1_9640|2_240|3_120</t>
   </si>
   <si>
@@ -357,6 +360,33 @@
   </si>
   <si>
     <t>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>杰克船长</t>
+  </si>
+  <si>
+    <t>1_9740|2_130|3_65|4_65</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>1_9760|2_120|3_60|4_60</t>
+  </si>
+  <si>
+    <t>1_9780|2_110|3_55|4_55</t>
+  </si>
+  <si>
+    <t>1_9800|2_100|3_50|4_50</t>
+  </si>
+  <si>
+    <t>1_9820|2_90|3_45|4_45</t>
+  </si>
+  <si>
+    <t>1_9840|2_80|3_40|4_40</t>
+  </si>
+  <si>
+    <t>1_9860|2_70|3_35|4_35</t>
   </si>
 </sst>
 </file>
@@ -1052,10 +1082,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1377,7 +1407,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
@@ -2677,7 +2707,7 @@
         <v>70</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="G47" s="11">
         <v>2000</v>
@@ -2701,11 +2731,11 @@
         <v>2</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F48" s="13" t="str">
         <f t="shared" ref="F48:F53" si="6">F47</f>
-        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G48" s="11">
         <v>1000</v>
@@ -2729,11 +2759,11 @@
         <v>3</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F49" s="13" t="str">
         <f t="shared" si="6"/>
-        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G49" s="11">
         <v>500</v>
@@ -2757,11 +2787,11 @@
         <v>4</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F50" s="13" t="str">
         <f t="shared" si="6"/>
-        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G50" s="11">
         <v>-500</v>
@@ -2785,11 +2815,11 @@
         <v>5</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F51" s="13" t="str">
         <f t="shared" si="6"/>
-        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G51" s="11">
         <v>-1000</v>
@@ -2813,11 +2843,11 @@
         <v>6</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F52" s="13" t="str">
         <f t="shared" si="6"/>
-        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G52" s="11">
         <v>-2000</v>
@@ -2841,11 +2871,11 @@
         <v>7</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F53" s="13" t="str">
         <f t="shared" si="6"/>
-        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G53" s="11">
         <v>-999999</v>
@@ -2861,20 +2891,20 @@
       <c r="A54" s="16">
         <v>22001</v>
       </c>
-      <c r="B54" s="17">
+      <c r="B54" s="16">
         <v>102200</v>
       </c>
-      <c r="C54" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D54" s="17">
+      <c r="C54" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D54" s="16">
         <v>1</v>
       </c>
-      <c r="E54" s="16" t="s">
+      <c r="E54" s="17" t="s">
         <v>70</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G54" s="6">
         <v>2000</v>
@@ -2890,20 +2920,20 @@
       <c r="A55" s="16">
         <v>22002</v>
       </c>
-      <c r="B55" s="17">
+      <c r="B55" s="16">
         <v>102200</v>
       </c>
-      <c r="C55" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D55" s="17">
+      <c r="C55" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D55" s="16">
         <v>2</v>
       </c>
-      <c r="E55" s="16" t="s">
-        <v>71</v>
+      <c r="E55" s="17" t="s">
+        <v>72</v>
       </c>
       <c r="F55" s="8" t="str">
-        <f>F54</f>
+        <f t="shared" ref="F55:F60" si="7">F54</f>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="G55" s="6">
@@ -2920,20 +2950,20 @@
       <c r="A56" s="16">
         <v>22003</v>
       </c>
-      <c r="B56" s="17">
+      <c r="B56" s="16">
         <v>102200</v>
       </c>
-      <c r="C56" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D56" s="17">
+      <c r="C56" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D56" s="16">
         <v>3</v>
       </c>
-      <c r="E56" s="16" t="s">
-        <v>72</v>
+      <c r="E56" s="17" t="s">
+        <v>73</v>
       </c>
       <c r="F56" s="8" t="str">
-        <f>F55</f>
+        <f t="shared" si="7"/>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="G56" s="6">
@@ -2950,20 +2980,20 @@
       <c r="A57" s="16">
         <v>22004</v>
       </c>
-      <c r="B57" s="17">
+      <c r="B57" s="16">
         <v>102200</v>
       </c>
-      <c r="C57" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D57" s="17">
+      <c r="C57" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D57" s="16">
         <v>4</v>
       </c>
-      <c r="E57" s="16" t="s">
-        <v>73</v>
+      <c r="E57" s="17" t="s">
+        <v>74</v>
       </c>
       <c r="F57" s="8" t="str">
-        <f>F56</f>
+        <f t="shared" si="7"/>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="G57" s="6">
@@ -2980,20 +3010,20 @@
       <c r="A58" s="16">
         <v>22005</v>
       </c>
-      <c r="B58" s="17">
+      <c r="B58" s="16">
         <v>102200</v>
       </c>
-      <c r="C58" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D58" s="17">
+      <c r="C58" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D58" s="16">
         <v>5</v>
       </c>
-      <c r="E58" s="16" t="s">
-        <v>74</v>
+      <c r="E58" s="17" t="s">
+        <v>75</v>
       </c>
       <c r="F58" s="8" t="str">
-        <f>F57</f>
+        <f t="shared" si="7"/>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="G58" s="6">
@@ -3010,20 +3040,20 @@
       <c r="A59" s="16">
         <v>22006</v>
       </c>
-      <c r="B59" s="17">
+      <c r="B59" s="16">
         <v>102200</v>
       </c>
-      <c r="C59" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D59" s="17">
+      <c r="C59" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D59" s="16">
         <v>6</v>
       </c>
-      <c r="E59" s="16" t="s">
-        <v>75</v>
+      <c r="E59" s="17" t="s">
+        <v>76</v>
       </c>
       <c r="F59" s="8" t="str">
-        <f>F58</f>
+        <f t="shared" si="7"/>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="G59" s="6">
@@ -3040,20 +3070,20 @@
       <c r="A60" s="16">
         <v>22007</v>
       </c>
-      <c r="B60" s="17">
+      <c r="B60" s="16">
         <v>102200</v>
       </c>
-      <c r="C60" s="17" t="s">
+      <c r="C60" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D60" s="16">
+        <v>7</v>
+      </c>
+      <c r="E60" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="D60" s="17">
-        <v>7</v>
-      </c>
-      <c r="E60" s="16" t="s">
-        <v>76</v>
-      </c>
       <c r="F60" s="8" t="str">
-        <f>F59</f>
+        <f t="shared" si="7"/>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="G60" s="6">
@@ -3063,6 +3093,215 @@
         <v>-2000</v>
       </c>
       <c r="I60" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="61" s="4" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A61" s="16">
+        <v>21001</v>
+      </c>
+      <c r="B61" s="16">
+        <v>102100</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D61" s="16">
+        <v>1</v>
+      </c>
+      <c r="E61" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G61" s="6">
+        <v>2000</v>
+      </c>
+      <c r="H61" s="6">
+        <v>999999</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" s="4" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A62" s="16">
+        <v>21002</v>
+      </c>
+      <c r="B62" s="16">
+        <v>102100</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D62" s="16">
+        <v>2</v>
+      </c>
+      <c r="E62" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="F62" s="8" t="str">
+        <f>F61</f>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G62" s="6">
+        <v>1000</v>
+      </c>
+      <c r="H62" s="6">
+        <v>2000</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63" s="4" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A63" s="16">
+        <v>21003</v>
+      </c>
+      <c r="B63" s="16">
+        <v>102100</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D63" s="16">
+        <v>3</v>
+      </c>
+      <c r="E63" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F63" s="8" t="str">
+        <f>F62</f>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G63" s="6">
+        <v>500</v>
+      </c>
+      <c r="H63" s="6">
+        <v>1000</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" s="4" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A64" s="16">
+        <v>21004</v>
+      </c>
+      <c r="B64" s="16">
+        <v>102100</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D64" s="16">
+        <v>4</v>
+      </c>
+      <c r="E64" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="F64" s="8" t="str">
+        <f>F63</f>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G64" s="6">
+        <v>-500</v>
+      </c>
+      <c r="H64" s="6">
+        <v>500</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="65" s="4" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A65" s="16">
+        <v>21005</v>
+      </c>
+      <c r="B65" s="16">
+        <v>102100</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D65" s="16">
+        <v>5</v>
+      </c>
+      <c r="E65" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="F65" s="8" t="str">
+        <f>F64</f>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G65" s="6">
+        <v>-1000</v>
+      </c>
+      <c r="H65" s="6">
+        <v>-500</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="66" s="4" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A66" s="16">
+        <v>21006</v>
+      </c>
+      <c r="B66" s="16">
+        <v>102100</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D66" s="16">
+        <v>6</v>
+      </c>
+      <c r="E66" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="F66" s="8" t="str">
+        <f>F65</f>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G66" s="6">
+        <v>-2000</v>
+      </c>
+      <c r="H66" s="6">
+        <v>-1000</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" s="4" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A67" s="16">
+        <v>21007</v>
+      </c>
+      <c r="B67" s="16">
+        <v>102100</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D67" s="16">
+        <v>7</v>
+      </c>
+      <c r="E67" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="F67" s="8" t="str">
+        <f>F66</f>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G67" s="6">
+        <v>-999999</v>
+      </c>
+      <c r="H67" s="6">
+        <v>-2000</v>
+      </c>
+      <c r="I67" s="6" t="s">
         <v>32</v>
       </c>
     </row>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="96">
   <si>
     <t>id</t>
   </si>
@@ -332,10 +332,37 @@
     <t>圣诞狂欢夜</t>
   </si>
   <si>
+    <t>1_9730|2_260|3_10</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>1_9750|2_240|3_10</t>
+  </si>
+  <si>
+    <t>1_9770|2_220|3_10</t>
+  </si>
+  <si>
+    <t>1_9790|2_200|3_10</t>
+  </si>
+  <si>
+    <t>1_9810|2_180|3_10</t>
+  </si>
+  <si>
+    <t>1_9830|2_160|3_10</t>
+  </si>
+  <si>
+    <t>1_9850|2_140|3_10</t>
+  </si>
+  <si>
+    <t>雷神</t>
+  </si>
+  <si>
     <t>1_9600|2_260|3_140</t>
   </si>
   <si>
-    <t>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
+    <t>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</t>
   </si>
   <si>
     <t>1_9640|2_240|3_120</t>
@@ -354,12 +381,6 @@
   </si>
   <si>
     <t>1_9840|2_140|3_20</t>
-  </si>
-  <si>
-    <t>雷神</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</t>
   </si>
   <si>
     <t>杰克船长</t>
@@ -2735,7 +2756,7 @@
       </c>
       <c r="F48" s="13" t="str">
         <f t="shared" ref="F48:F53" si="6">F47</f>
-        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G48" s="11">
         <v>1000</v>
@@ -2763,7 +2784,7 @@
       </c>
       <c r="F49" s="13" t="str">
         <f t="shared" si="6"/>
-        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G49" s="11">
         <v>500</v>
@@ -2791,7 +2812,7 @@
       </c>
       <c r="F50" s="13" t="str">
         <f t="shared" si="6"/>
-        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G50" s="11">
         <v>-500</v>
@@ -2819,7 +2840,7 @@
       </c>
       <c r="F51" s="13" t="str">
         <f t="shared" si="6"/>
-        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G51" s="11">
         <v>-1000</v>
@@ -2847,7 +2868,7 @@
       </c>
       <c r="F52" s="13" t="str">
         <f t="shared" si="6"/>
-        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G52" s="11">
         <v>-2000</v>
@@ -2875,7 +2896,7 @@
       </c>
       <c r="F53" s="13" t="str">
         <f t="shared" si="6"/>
-        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G53" s="11">
         <v>-999999</v>
@@ -2901,10 +2922,10 @@
         <v>1</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G54" s="6">
         <v>2000</v>
@@ -2930,7 +2951,7 @@
         <v>2</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="F55" s="8" t="str">
         <f t="shared" ref="F55:F60" si="7">F54</f>
@@ -2960,7 +2981,7 @@
         <v>3</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F56" s="8" t="str">
         <f t="shared" si="7"/>
@@ -2990,7 +3011,7 @@
         <v>4</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F57" s="8" t="str">
         <f t="shared" si="7"/>
@@ -3020,7 +3041,7 @@
         <v>5</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F58" s="8" t="str">
         <f t="shared" si="7"/>
@@ -3050,7 +3071,7 @@
         <v>6</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F59" s="8" t="str">
         <f t="shared" si="7"/>
@@ -3080,7 +3101,7 @@
         <v>7</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F60" s="8" t="str">
         <f t="shared" si="7"/>
@@ -3104,16 +3125,16 @@
         <v>102100</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D61" s="16">
         <v>1</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G61" s="6">
         <v>2000</v>
@@ -3133,16 +3154,16 @@
         <v>102100</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D62" s="16">
         <v>2</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F62" s="8" t="str">
-        <f>F61</f>
+        <f t="shared" ref="F62:F67" si="8">F61</f>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G62" s="6">
@@ -3163,16 +3184,16 @@
         <v>102100</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D63" s="16">
         <v>3</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F63" s="8" t="str">
-        <f>F62</f>
+        <f t="shared" si="8"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G63" s="6">
@@ -3193,16 +3214,16 @@
         <v>102100</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D64" s="16">
         <v>4</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F64" s="8" t="str">
-        <f>F63</f>
+        <f t="shared" si="8"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G64" s="6">
@@ -3223,16 +3244,16 @@
         <v>102100</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D65" s="16">
         <v>5</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F65" s="8" t="str">
-        <f>F64</f>
+        <f t="shared" si="8"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G65" s="6">
@@ -3253,16 +3274,16 @@
         <v>102100</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D66" s="16">
         <v>6</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="F66" s="8" t="str">
-        <f>F65</f>
+        <f t="shared" si="8"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G66" s="6">
@@ -3283,16 +3304,16 @@
         <v>102100</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D67" s="16">
         <v>7</v>
       </c>
       <c r="E67" s="17" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F67" s="8" t="str">
-        <f>F66</f>
+        <f t="shared" si="8"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G67" s="6">

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="89">
   <si>
     <t>id</t>
   </si>
@@ -359,28 +359,7 @@
     <t>雷神</t>
   </si>
   <si>
-    <t>1_9600|2_260|3_140</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</t>
-  </si>
-  <si>
-    <t>1_9640|2_240|3_120</t>
-  </si>
-  <si>
-    <t>1_9680|2_220|3_100</t>
-  </si>
-  <si>
-    <t>1_9720|2_200|3_80</t>
-  </si>
-  <si>
-    <t>1_9760|2_180|3_60</t>
-  </si>
-  <si>
-    <t>1_9800|2_160|3_40</t>
-  </si>
-  <si>
-    <t>1_9840|2_140|3_20</t>
+    <t>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
   </si>
   <si>
     <t>杰克船长</t>
@@ -2922,10 +2901,10 @@
         <v>1</v>
       </c>
       <c r="E54" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F54" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="G54" s="6">
         <v>2000</v>
@@ -2951,11 +2930,11 @@
         <v>2</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="F55" s="8" t="str">
         <f t="shared" ref="F55:F60" si="7">F54</f>
-        <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G55" s="6">
         <v>1000</v>
@@ -2981,11 +2960,11 @@
         <v>3</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F56" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G56" s="6">
         <v>500</v>
@@ -3011,11 +2990,11 @@
         <v>4</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F57" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G57" s="6">
         <v>-500</v>
@@ -3041,11 +3020,11 @@
         <v>5</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F58" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G58" s="6">
         <v>-1000</v>
@@ -3071,11 +3050,11 @@
         <v>6</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F59" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G59" s="6">
         <v>-2000</v>
@@ -3101,11 +3080,11 @@
         <v>7</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="F60" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G60" s="6">
         <v>-999999</v>
@@ -3125,16 +3104,16 @@
         <v>102100</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D61" s="16">
         <v>1</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="G61" s="6">
         <v>2000</v>
@@ -3154,13 +3133,13 @@
         <v>102100</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D62" s="16">
         <v>2</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F62" s="8" t="str">
         <f t="shared" ref="F62:F67" si="8">F61</f>
@@ -3184,13 +3163,13 @@
         <v>102100</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D63" s="16">
         <v>3</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F63" s="8" t="str">
         <f t="shared" si="8"/>
@@ -3214,13 +3193,13 @@
         <v>102100</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D64" s="16">
         <v>4</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F64" s="8" t="str">
         <f t="shared" si="8"/>
@@ -3244,13 +3223,13 @@
         <v>102100</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D65" s="16">
         <v>5</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F65" s="8" t="str">
         <f t="shared" si="8"/>
@@ -3274,13 +3253,13 @@
         <v>102100</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D66" s="16">
         <v>6</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F66" s="8" t="str">
         <f t="shared" si="8"/>
@@ -3304,13 +3283,13 @@
         <v>102100</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D67" s="16">
         <v>7</v>
       </c>
       <c r="E67" s="17" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F67" s="8" t="str">
         <f t="shared" si="8"/>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="89">
   <si>
     <t>id</t>
   </si>
@@ -359,7 +359,7 @@
     <t>雷神</t>
   </si>
   <si>
-    <t>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
+    <t>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
   </si>
   <si>
     <t>杰克船长</t>
@@ -2932,9 +2932,8 @@
       <c r="E55" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="F55" s="8" t="str">
-        <f t="shared" ref="F55:F60" si="7">F54</f>
-        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      <c r="F55" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="G55" s="6">
         <v>1000</v>
@@ -2962,9 +2961,8 @@
       <c r="E56" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="F56" s="8" t="str">
-        <f t="shared" si="7"/>
-        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      <c r="F56" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="G56" s="6">
         <v>500</v>
@@ -2992,9 +2990,8 @@
       <c r="E57" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="8" t="str">
-        <f t="shared" si="7"/>
-        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      <c r="F57" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="G57" s="6">
         <v>-500</v>
@@ -3022,9 +3019,8 @@
       <c r="E58" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="F58" s="8" t="str">
-        <f t="shared" si="7"/>
-        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      <c r="F58" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="G58" s="6">
         <v>-1000</v>
@@ -3052,9 +3048,8 @@
       <c r="E59" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="F59" s="8" t="str">
-        <f t="shared" si="7"/>
-        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      <c r="F59" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="G59" s="6">
         <v>-2000</v>
@@ -3082,9 +3077,8 @@
       <c r="E60" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="F60" s="8" t="str">
-        <f t="shared" si="7"/>
-        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      <c r="F60" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="G60" s="6">
         <v>-999999</v>
@@ -3142,7 +3136,7 @@
         <v>83</v>
       </c>
       <c r="F62" s="8" t="str">
-        <f t="shared" ref="F62:F67" si="8">F61</f>
+        <f t="shared" ref="F62:F67" si="7">F61</f>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G62" s="6">
@@ -3172,7 +3166,7 @@
         <v>84</v>
       </c>
       <c r="F63" s="8" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G63" s="6">
@@ -3202,7 +3196,7 @@
         <v>85</v>
       </c>
       <c r="F64" s="8" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G64" s="6">
@@ -3232,7 +3226,7 @@
         <v>86</v>
       </c>
       <c r="F65" s="8" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G65" s="6">
@@ -3262,7 +3256,7 @@
         <v>87</v>
       </c>
       <c r="F66" s="8" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G66" s="6">
@@ -3292,7 +3286,7 @@
         <v>88</v>
       </c>
       <c r="F67" s="8" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G67" s="6">

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="89">
   <si>
     <t>id</t>
   </si>
@@ -2932,8 +2932,9 @@
       <c r="E55" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="F55" s="8" t="s">
-        <v>79</v>
+      <c r="F55" s="8" t="str">
+        <f t="shared" ref="F55:F60" si="7">F54</f>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G55" s="6">
         <v>1000</v>
@@ -2961,8 +2962,9 @@
       <c r="E56" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="F56" s="8" t="s">
-        <v>79</v>
+      <c r="F56" s="8" t="str">
+        <f t="shared" si="7"/>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G56" s="6">
         <v>500</v>
@@ -2990,8 +2992,9 @@
       <c r="E57" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="8" t="s">
-        <v>79</v>
+      <c r="F57" s="8" t="str">
+        <f t="shared" si="7"/>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G57" s="6">
         <v>-500</v>
@@ -3019,8 +3022,9 @@
       <c r="E58" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="F58" s="8" t="s">
-        <v>79</v>
+      <c r="F58" s="8" t="str">
+        <f t="shared" si="7"/>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G58" s="6">
         <v>-1000</v>
@@ -3048,8 +3052,9 @@
       <c r="E59" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="F59" s="8" t="s">
-        <v>79</v>
+      <c r="F59" s="8" t="str">
+        <f t="shared" si="7"/>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G59" s="6">
         <v>-2000</v>
@@ -3077,8 +3082,9 @@
       <c r="E60" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="F60" s="8" t="s">
-        <v>79</v>
+      <c r="F60" s="8" t="str">
+        <f t="shared" si="7"/>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G60" s="6">
         <v>-999999</v>
@@ -3136,7 +3142,7 @@
         <v>83</v>
       </c>
       <c r="F62" s="8" t="str">
-        <f t="shared" ref="F62:F67" si="7">F61</f>
+        <f t="shared" ref="F62:F67" si="8">F61</f>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G62" s="6">
@@ -3166,7 +3172,7 @@
         <v>84</v>
       </c>
       <c r="F63" s="8" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G63" s="6">
@@ -3196,7 +3202,7 @@
         <v>85</v>
       </c>
       <c r="F64" s="8" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G64" s="6">
@@ -3226,7 +3232,7 @@
         <v>86</v>
       </c>
       <c r="F65" s="8" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G65" s="6">
@@ -3256,7 +3262,7 @@
         <v>87</v>
       </c>
       <c r="F66" s="8" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G66" s="6">
@@ -3286,7 +3292,7 @@
         <v>88</v>
       </c>
       <c r="F67" s="8" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G67" s="6">

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
   <si>
     <t>id</t>
   </si>
@@ -387,6 +387,15 @@
   </si>
   <si>
     <t>1_9860|2_70|3_35|4_35</t>
+  </si>
+  <si>
+    <t>篮球巨星</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>寒冰王座</t>
   </si>
 </sst>
 </file>
@@ -569,7 +578,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -591,6 +600,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -917,7 +944,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -941,16 +968,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -959,95 +986,98 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1060,7 +1090,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1081,11 +1111,47 @@
     <xf numFmtId="3" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1407,1901 +1473,2319 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
     <col min="2" max="3" width="15.25" customWidth="1"/>
     <col min="4" max="4" width="10.875" customWidth="1"/>
-    <col min="5" max="5" width="33.75" style="5" customWidth="1"/>
-    <col min="6" max="6" width="114.025" style="5" customWidth="1"/>
+    <col min="5" max="5" width="33.75" style="8" customWidth="1"/>
+    <col min="6" max="6" width="114.025" style="8" customWidth="1"/>
     <col min="7" max="7" width="15.625" customWidth="1"/>
     <col min="8" max="8" width="15.125" customWidth="1"/>
     <col min="9" max="9" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:9">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7" t="s">
+      <c r="C1" s="10"/>
+      <c r="D1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:9">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7" t="s">
+      <c r="C2" s="10"/>
+      <c r="D2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="6"/>
+      <c r="I2" s="9"/>
     </row>
     <row r="3" ht="16.5" spans="1:9">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="10"/>
+      <c r="D3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="6"/>
+      <c r="I3" s="9"/>
     </row>
     <row r="4" ht="16.5" spans="1:9">
-      <c r="A4" s="6"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
     </row>
     <row r="5" ht="16.5" spans="1:9">
-      <c r="A5" s="6">
+      <c r="A5" s="9">
         <v>1001</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="9">
         <v>100100</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="9">
         <v>1</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="9">
         <v>2000</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="9">
         <v>999999</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:9">
-      <c r="A6" s="6">
+      <c r="A6" s="9">
         <v>1002</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="9">
         <v>100100</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6">
+      <c r="C6" s="9"/>
+      <c r="D6" s="9">
         <v>2</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="8" t="str">
+      <c r="F6" s="11" t="str">
         <f t="shared" ref="F6:F11" si="0">F5</f>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="9">
         <v>1000</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="9">
         <v>2000</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
-      <c r="A7" s="6">
+      <c r="A7" s="9">
         <v>1003</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="9">
         <v>100100</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6">
+      <c r="C7" s="9"/>
+      <c r="D7" s="9">
         <v>3</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="8" t="str">
+      <c r="F7" s="11" t="str">
         <f t="shared" si="0"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="9">
         <v>500</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="9">
         <v>1000</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="9" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
-      <c r="A8" s="6">
+      <c r="A8" s="9">
         <v>1004</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="9">
         <v>100100</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6">
+      <c r="C8" s="9"/>
+      <c r="D8" s="9">
         <v>4</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="8" t="str">
+      <c r="F8" s="11" t="str">
         <f t="shared" si="0"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="9">
         <v>-500</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="9">
         <v>500</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:9">
-      <c r="A9" s="6">
+      <c r="A9" s="9">
         <v>1005</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="9">
         <v>100100</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6">
+      <c r="C9" s="9"/>
+      <c r="D9" s="9">
         <v>5</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="8" t="str">
+      <c r="F9" s="11" t="str">
         <f t="shared" si="0"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="9">
         <v>-1000</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="9">
         <v>-500</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:9">
-      <c r="A10" s="6">
+      <c r="A10" s="9">
         <v>1006</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="9">
         <v>100100</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6">
+      <c r="C10" s="9"/>
+      <c r="D10" s="9">
         <v>6</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="8" t="str">
+      <c r="F10" s="11" t="str">
         <f t="shared" si="0"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="9">
         <v>-2000</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="9">
         <v>-1000</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:9">
-      <c r="A11" s="6">
+      <c r="A11" s="9">
         <v>1007</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="9">
         <v>100100</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6">
+      <c r="C11" s="9"/>
+      <c r="D11" s="9">
         <v>7</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="8" t="str">
+      <c r="F11" s="11" t="str">
         <f t="shared" si="0"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="9">
         <v>-999999</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="9">
         <v>-2000</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A12" s="10">
+      <c r="A12" s="13">
         <v>3001</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="13">
         <v>100300</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="13">
         <v>1</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="13">
         <v>2000</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="13">
         <v>999999</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="13" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A13" s="10">
+      <c r="A13" s="13">
         <v>3002</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="13">
         <v>100300</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10">
+      <c r="C13" s="13"/>
+      <c r="D13" s="13">
         <v>2</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="8" t="str">
+      <c r="F13" s="11" t="str">
         <f t="shared" ref="F13:F18" si="1">F12</f>
         <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="13">
         <v>1000</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="13">
         <v>2000</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A14" s="10">
+      <c r="A14" s="13">
         <v>3003</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="13">
         <v>100300</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10">
+      <c r="C14" s="13"/>
+      <c r="D14" s="13">
         <v>3</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="8" t="str">
+      <c r="F14" s="11" t="str">
         <f t="shared" si="1"/>
         <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="13">
         <v>500</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="13">
         <v>1000</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="13" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A15" s="10">
+      <c r="A15" s="13">
         <v>3004</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="13">
         <v>100300</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10">
+      <c r="C15" s="13"/>
+      <c r="D15" s="13">
         <v>4</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="8" t="str">
+      <c r="F15" s="11" t="str">
         <f t="shared" si="1"/>
         <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="13">
         <v>-500</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="13">
         <v>500</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="I15" s="13" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A16" s="10">
+      <c r="A16" s="13">
         <v>3005</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="13">
         <v>100300</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10">
+      <c r="C16" s="13"/>
+      <c r="D16" s="13">
         <v>5</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="8" t="str">
+      <c r="F16" s="11" t="str">
         <f t="shared" si="1"/>
         <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="13">
         <v>-1000</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="13">
         <v>-500</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="I16" s="13" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A17" s="10">
+      <c r="A17" s="13">
         <v>3006</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="13">
         <v>100300</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10">
+      <c r="C17" s="13"/>
+      <c r="D17" s="13">
         <v>6</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="8" t="str">
+      <c r="F17" s="11" t="str">
         <f t="shared" si="1"/>
         <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="13">
         <v>-2000</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="13">
         <v>-1000</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="I17" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A18" s="10">
+      <c r="A18" s="13">
         <v>3007</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="13">
         <v>100300</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10">
+      <c r="C18" s="13"/>
+      <c r="D18" s="13">
         <v>7</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="8" t="str">
+      <c r="F18" s="11" t="str">
         <f t="shared" si="1"/>
         <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="13">
         <v>-999999</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="13">
         <v>-2000</v>
       </c>
-      <c r="I18" s="10" t="s">
+      <c r="I18" s="13" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A19" s="6">
+      <c r="A19" s="9">
         <v>7001</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="14">
         <v>100700</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="14">
         <v>1</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="14">
         <v>2000</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="14">
         <v>999999</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A20" s="6">
+      <c r="A20" s="9">
         <v>7002</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="14">
         <v>100700</v>
       </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11">
+      <c r="C20" s="14"/>
+      <c r="D20" s="14">
         <v>2</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="F20" s="13" t="str">
+      <c r="F20" s="16" t="str">
         <f t="shared" ref="F20:F25" si="2">F19</f>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="14">
         <v>1000</v>
       </c>
-      <c r="H20" s="11">
+      <c r="H20" s="14">
         <v>2000</v>
       </c>
-      <c r="I20" s="11" t="s">
+      <c r="I20" s="14" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A21" s="6">
+      <c r="A21" s="9">
         <v>7003</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="14">
         <v>100700</v>
       </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11">
+      <c r="C21" s="14"/>
+      <c r="D21" s="14">
         <v>3</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="F21" s="13" t="str">
+      <c r="F21" s="16" t="str">
         <f t="shared" si="2"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="14">
         <v>500</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="14">
         <v>1000</v>
       </c>
-      <c r="I21" s="11" t="s">
+      <c r="I21" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A22" s="6">
+      <c r="A22" s="9">
         <v>7004</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="14">
         <v>100700</v>
       </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11">
+      <c r="C22" s="14"/>
+      <c r="D22" s="14">
         <v>4</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="13" t="str">
+      <c r="F22" s="16" t="str">
         <f t="shared" si="2"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="14">
         <v>-500</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="14">
         <v>500</v>
       </c>
-      <c r="I22" s="11" t="s">
+      <c r="I22" s="14" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A23" s="6">
+      <c r="A23" s="9">
         <v>7005</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="14">
         <v>100700</v>
       </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11">
+      <c r="C23" s="14"/>
+      <c r="D23" s="14">
         <v>5</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="13" t="str">
+      <c r="F23" s="16" t="str">
         <f t="shared" si="2"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="14">
         <v>-1000</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="14">
         <v>-500</v>
       </c>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="14" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A24" s="6">
+      <c r="A24" s="9">
         <v>7006</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="14">
         <v>100700</v>
       </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11">
+      <c r="C24" s="14"/>
+      <c r="D24" s="14">
         <v>6</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="F24" s="13" t="str">
+      <c r="F24" s="16" t="str">
         <f t="shared" si="2"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="14">
         <v>-2000</v>
       </c>
-      <c r="H24" s="11">
+      <c r="H24" s="14">
         <v>-1000</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="I24" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A25" s="6">
+      <c r="A25" s="9">
         <v>7007</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="14">
         <v>100700</v>
       </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11">
+      <c r="C25" s="14"/>
+      <c r="D25" s="14">
         <v>7</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="F25" s="13" t="str">
+      <c r="F25" s="16" t="str">
         <f t="shared" si="2"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="14">
         <v>-999999</v>
       </c>
-      <c r="H25" s="11">
+      <c r="H25" s="14">
         <v>-2000</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="I25" s="14" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A26" s="10">
+      <c r="A26" s="13">
         <v>12001</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="13">
         <v>101200</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="13">
         <v>1</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="13">
         <v>2000</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="13">
         <v>999999</v>
       </c>
-      <c r="I26" s="10" t="s">
+      <c r="I26" s="13" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A27" s="10">
+      <c r="A27" s="13">
         <v>12002</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="13">
         <v>101200</v>
       </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10">
+      <c r="C27" s="13"/>
+      <c r="D27" s="13">
         <v>2</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="F27" s="8" t="str">
+      <c r="F27" s="11" t="str">
         <f t="shared" ref="F27:F32" si="3">F26</f>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="13">
         <v>1000</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="13">
         <v>2000</v>
       </c>
-      <c r="I27" s="10" t="s">
+      <c r="I27" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A28" s="10">
+      <c r="A28" s="13">
         <v>12003</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="13">
         <v>101200</v>
       </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10">
+      <c r="C28" s="13"/>
+      <c r="D28" s="13">
         <v>3</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="F28" s="8" t="str">
+      <c r="F28" s="11" t="str">
         <f t="shared" si="3"/>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="13">
         <v>500</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="13">
         <v>1000</v>
       </c>
-      <c r="I28" s="10" t="s">
+      <c r="I28" s="13" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A29" s="10">
+      <c r="A29" s="13">
         <v>12004</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="13">
         <v>101200</v>
       </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10">
+      <c r="C29" s="13"/>
+      <c r="D29" s="13">
         <v>4</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F29" s="8" t="str">
+      <c r="F29" s="11" t="str">
         <f t="shared" si="3"/>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="13">
         <v>-500</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="13">
         <v>500</v>
       </c>
-      <c r="I29" s="10" t="s">
+      <c r="I29" s="13" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A30" s="10">
+      <c r="A30" s="13">
         <v>12005</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="13">
         <v>101200</v>
       </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10">
+      <c r="C30" s="13"/>
+      <c r="D30" s="13">
         <v>5</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="F30" s="8" t="str">
+      <c r="F30" s="11" t="str">
         <f t="shared" si="3"/>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="13">
         <v>-1000</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="13">
         <v>-500</v>
       </c>
-      <c r="I30" s="10" t="s">
+      <c r="I30" s="13" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A31" s="10">
+      <c r="A31" s="13">
         <v>12006</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="13">
         <v>101200</v>
       </c>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10">
+      <c r="C31" s="13"/>
+      <c r="D31" s="13">
         <v>6</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="F31" s="8" t="str">
+      <c r="F31" s="11" t="str">
         <f t="shared" si="3"/>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="13">
         <v>-2000</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="13">
         <v>-1000</v>
       </c>
-      <c r="I31" s="10" t="s">
+      <c r="I31" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A32" s="10">
+      <c r="A32" s="13">
         <v>12007</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="13">
         <v>101200</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10">
+      <c r="C32" s="13"/>
+      <c r="D32" s="13">
         <v>7</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E32" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="F32" s="8" t="str">
+      <c r="F32" s="11" t="str">
         <f t="shared" si="3"/>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="13">
         <v>-999999</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="13">
         <v>-2000</v>
       </c>
-      <c r="I32" s="10" t="s">
+      <c r="I32" s="13" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="33" s="3" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A33" s="6">
+      <c r="A33" s="9">
         <v>14001</v>
       </c>
-      <c r="B33" s="14">
+      <c r="B33" s="17">
         <v>101400</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="17">
         <v>1</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="E33" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F33" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="G33" s="14">
+      <c r="G33" s="17">
         <v>2000</v>
       </c>
-      <c r="H33" s="14">
+      <c r="H33" s="17">
         <v>999999</v>
       </c>
-      <c r="I33" s="14" t="s">
+      <c r="I33" s="17" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="34" s="3" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A34" s="6">
+      <c r="A34" s="9">
         <v>14002</v>
       </c>
-      <c r="B34" s="14">
+      <c r="B34" s="17">
         <v>101400</v>
       </c>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14">
+      <c r="C34" s="17"/>
+      <c r="D34" s="17">
         <v>2</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="F34" s="8" t="str">
+      <c r="F34" s="11" t="str">
         <f t="shared" ref="F34:F39" si="4">F33</f>
         <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
-      <c r="G34" s="14">
+      <c r="G34" s="17">
         <v>1000</v>
       </c>
-      <c r="H34" s="14">
+      <c r="H34" s="17">
         <v>2000</v>
       </c>
-      <c r="I34" s="14" t="s">
+      <c r="I34" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A35" s="6">
+      <c r="A35" s="9">
         <v>14003</v>
       </c>
-      <c r="B35" s="14">
+      <c r="B35" s="17">
         <v>101400</v>
       </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14">
+      <c r="C35" s="17"/>
+      <c r="D35" s="17">
         <v>3</v>
       </c>
-      <c r="E35" s="15" t="s">
+      <c r="E35" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="F35" s="8" t="str">
+      <c r="F35" s="11" t="str">
         <f t="shared" si="4"/>
         <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
-      <c r="G35" s="14">
+      <c r="G35" s="17">
         <v>500</v>
       </c>
-      <c r="H35" s="14">
+      <c r="H35" s="17">
         <v>1000</v>
       </c>
-      <c r="I35" s="14" t="s">
+      <c r="I35" s="17" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="36" s="3" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A36" s="6">
+      <c r="A36" s="9">
         <v>14004</v>
       </c>
-      <c r="B36" s="14">
+      <c r="B36" s="17">
         <v>101400</v>
       </c>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14">
+      <c r="C36" s="17"/>
+      <c r="D36" s="17">
         <v>4</v>
       </c>
-      <c r="E36" s="15" t="s">
+      <c r="E36" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="F36" s="8" t="str">
+      <c r="F36" s="11" t="str">
         <f t="shared" si="4"/>
         <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
-      <c r="G36" s="14">
+      <c r="G36" s="17">
         <v>-500</v>
       </c>
-      <c r="H36" s="14">
+      <c r="H36" s="17">
         <v>500</v>
       </c>
-      <c r="I36" s="14" t="s">
+      <c r="I36" s="17" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="37" s="3" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A37" s="6">
+      <c r="A37" s="9">
         <v>14005</v>
       </c>
-      <c r="B37" s="14">
+      <c r="B37" s="17">
         <v>101400</v>
       </c>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14">
+      <c r="C37" s="17"/>
+      <c r="D37" s="17">
         <v>5</v>
       </c>
-      <c r="E37" s="15" t="s">
+      <c r="E37" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="F37" s="8" t="str">
+      <c r="F37" s="11" t="str">
         <f t="shared" si="4"/>
         <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
-      <c r="G37" s="14">
+      <c r="G37" s="17">
         <v>-1000</v>
       </c>
-      <c r="H37" s="14">
+      <c r="H37" s="17">
         <v>-500</v>
       </c>
-      <c r="I37" s="14" t="s">
+      <c r="I37" s="17" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A38" s="6">
+      <c r="A38" s="9">
         <v>14006</v>
       </c>
-      <c r="B38" s="14">
+      <c r="B38" s="17">
         <v>101400</v>
       </c>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14">
+      <c r="C38" s="17"/>
+      <c r="D38" s="17">
         <v>6</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="E38" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="F38" s="8" t="str">
+      <c r="F38" s="11" t="str">
         <f t="shared" si="4"/>
         <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
-      <c r="G38" s="14">
+      <c r="G38" s="17">
         <v>-2000</v>
       </c>
-      <c r="H38" s="14">
+      <c r="H38" s="17">
         <v>-1000</v>
       </c>
-      <c r="I38" s="14" t="s">
+      <c r="I38" s="17" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A39" s="6">
+      <c r="A39" s="9">
         <v>14007</v>
       </c>
-      <c r="B39" s="14">
+      <c r="B39" s="17">
         <v>101400</v>
       </c>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14">
+      <c r="C39" s="17"/>
+      <c r="D39" s="17">
         <v>7</v>
       </c>
-      <c r="E39" s="15" t="s">
+      <c r="E39" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="F39" s="8" t="str">
+      <c r="F39" s="11" t="str">
         <f t="shared" si="4"/>
         <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
-      <c r="G39" s="14">
+      <c r="G39" s="17">
         <v>-999999</v>
       </c>
-      <c r="H39" s="14">
+      <c r="H39" s="17">
         <v>-2000</v>
       </c>
-      <c r="I39" s="14" t="s">
+      <c r="I39" s="17" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:9">
-      <c r="A40" s="6">
+      <c r="A40" s="9">
         <v>24001</v>
       </c>
-      <c r="B40" s="6">
+      <c r="B40" s="9">
         <v>102400</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40" s="9">
         <v>1</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F40" s="9" t="s">
+      <c r="F40" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G40" s="6">
+      <c r="G40" s="9">
         <v>2000</v>
       </c>
-      <c r="H40" s="6">
+      <c r="H40" s="9">
         <v>999999</v>
       </c>
-      <c r="I40" s="6" t="s">
+      <c r="I40" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:9">
-      <c r="A41" s="6">
+      <c r="A41" s="9">
         <v>24002</v>
       </c>
-      <c r="B41" s="6">
+      <c r="B41" s="9">
         <v>102400</v>
       </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6">
+      <c r="C41" s="9"/>
+      <c r="D41" s="9">
         <v>2</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E41" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F41" s="8" t="str">
+      <c r="F41" s="11" t="str">
         <f t="shared" ref="F41:F46" si="5">F40</f>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G41" s="6">
+      <c r="G41" s="9">
         <v>1000</v>
       </c>
-      <c r="H41" s="6">
+      <c r="H41" s="9">
         <v>2000</v>
       </c>
-      <c r="I41" s="6" t="s">
+      <c r="I41" s="9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:9">
-      <c r="A42" s="6">
+      <c r="A42" s="9">
         <v>24003</v>
       </c>
-      <c r="B42" s="6">
+      <c r="B42" s="9">
         <v>102400</v>
       </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6">
+      <c r="C42" s="9"/>
+      <c r="D42" s="9">
         <v>3</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F42" s="8" t="str">
+      <c r="F42" s="11" t="str">
         <f t="shared" si="5"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G42" s="6">
+      <c r="G42" s="9">
         <v>500</v>
       </c>
-      <c r="H42" s="6">
+      <c r="H42" s="9">
         <v>1000</v>
       </c>
-      <c r="I42" s="6" t="s">
+      <c r="I42" s="9" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:9">
-      <c r="A43" s="6">
+      <c r="A43" s="9">
         <v>24004</v>
       </c>
-      <c r="B43" s="6">
+      <c r="B43" s="9">
         <v>102400</v>
       </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6">
+      <c r="C43" s="9"/>
+      <c r="D43" s="9">
         <v>4</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E43" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F43" s="8" t="str">
+      <c r="F43" s="11" t="str">
         <f t="shared" si="5"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G43" s="6">
+      <c r="G43" s="9">
         <v>-500</v>
       </c>
-      <c r="H43" s="6">
+      <c r="H43" s="9">
         <v>500</v>
       </c>
-      <c r="I43" s="6" t="s">
+      <c r="I43" s="9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:9">
-      <c r="A44" s="6">
+      <c r="A44" s="9">
         <v>24005</v>
       </c>
-      <c r="B44" s="6">
+      <c r="B44" s="9">
         <v>102400</v>
       </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6">
+      <c r="C44" s="9"/>
+      <c r="D44" s="9">
         <v>5</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="F44" s="8" t="str">
+      <c r="F44" s="11" t="str">
         <f t="shared" si="5"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G44" s="6">
+      <c r="G44" s="9">
         <v>-1000</v>
       </c>
-      <c r="H44" s="6">
+      <c r="H44" s="9">
         <v>-500</v>
       </c>
-      <c r="I44" s="6" t="s">
+      <c r="I44" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:9">
-      <c r="A45" s="6">
+      <c r="A45" s="9">
         <v>24006</v>
       </c>
-      <c r="B45" s="6">
+      <c r="B45" s="9">
         <v>102400</v>
       </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6">
+      <c r="C45" s="9"/>
+      <c r="D45" s="9">
         <v>6</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E45" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="F45" s="8" t="str">
+      <c r="F45" s="11" t="str">
         <f t="shared" si="5"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G45" s="6">
+      <c r="G45" s="9">
         <v>-2000</v>
       </c>
-      <c r="H45" s="6">
+      <c r="H45" s="9">
         <v>-1000</v>
       </c>
-      <c r="I45" s="6" t="s">
+      <c r="I45" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:9">
-      <c r="A46" s="6">
+      <c r="A46" s="9">
         <v>24007</v>
       </c>
-      <c r="B46" s="6">
+      <c r="B46" s="9">
         <v>102400</v>
       </c>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6">
+      <c r="C46" s="9"/>
+      <c r="D46" s="9">
         <v>7</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F46" s="8" t="str">
+      <c r="F46" s="11" t="str">
         <f t="shared" si="5"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G46" s="6">
+      <c r="G46" s="9">
         <v>-999999</v>
       </c>
-      <c r="H46" s="6">
+      <c r="H46" s="9">
         <v>-2000</v>
       </c>
-      <c r="I46" s="6" t="s">
+      <c r="I46" s="9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A47" s="6">
+      <c r="A47" s="9">
         <v>17001</v>
       </c>
-      <c r="B47" s="11">
+      <c r="B47" s="14">
         <v>101700</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="14">
         <v>1</v>
       </c>
-      <c r="E47" s="12" t="s">
+      <c r="E47" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="F47" s="9" t="s">
+      <c r="F47" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="G47" s="11">
+      <c r="G47" s="14">
         <v>2000</v>
       </c>
-      <c r="H47" s="11">
+      <c r="H47" s="14">
         <v>999999</v>
       </c>
-      <c r="I47" s="11" t="s">
+      <c r="I47" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A48" s="6">
+      <c r="A48" s="9">
         <v>17002</v>
       </c>
-      <c r="B48" s="11">
+      <c r="B48" s="14">
         <v>101700</v>
       </c>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11">
+      <c r="C48" s="14"/>
+      <c r="D48" s="14">
         <v>2</v>
       </c>
-      <c r="E48" s="12" t="s">
+      <c r="E48" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="F48" s="13" t="str">
+      <c r="F48" s="16" t="str">
         <f t="shared" ref="F48:F53" si="6">F47</f>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G48" s="11">
+      <c r="G48" s="14">
         <v>1000</v>
       </c>
-      <c r="H48" s="11">
+      <c r="H48" s="14">
         <v>2000</v>
       </c>
-      <c r="I48" s="11" t="s">
+      <c r="I48" s="14" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A49" s="6">
+      <c r="A49" s="9">
         <v>17003</v>
       </c>
-      <c r="B49" s="11">
+      <c r="B49" s="14">
         <v>101700</v>
       </c>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11">
+      <c r="C49" s="14"/>
+      <c r="D49" s="14">
         <v>3</v>
       </c>
-      <c r="E49" s="12" t="s">
+      <c r="E49" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="F49" s="13" t="str">
+      <c r="F49" s="16" t="str">
         <f t="shared" si="6"/>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G49" s="11">
+      <c r="G49" s="14">
         <v>500</v>
       </c>
-      <c r="H49" s="11">
+      <c r="H49" s="14">
         <v>1000</v>
       </c>
-      <c r="I49" s="11" t="s">
+      <c r="I49" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A50" s="6">
+      <c r="A50" s="9">
         <v>17004</v>
       </c>
-      <c r="B50" s="11">
+      <c r="B50" s="14">
         <v>101700</v>
       </c>
-      <c r="C50" s="11"/>
-      <c r="D50" s="11">
+      <c r="C50" s="14"/>
+      <c r="D50" s="14">
         <v>4</v>
       </c>
-      <c r="E50" s="12" t="s">
+      <c r="E50" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="13" t="str">
+      <c r="F50" s="16" t="str">
         <f t="shared" si="6"/>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G50" s="11">
+      <c r="G50" s="14">
         <v>-500</v>
       </c>
-      <c r="H50" s="11">
+      <c r="H50" s="14">
         <v>500</v>
       </c>
-      <c r="I50" s="11" t="s">
+      <c r="I50" s="14" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="51" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A51" s="6">
+      <c r="A51" s="9">
         <v>17005</v>
       </c>
-      <c r="B51" s="11">
+      <c r="B51" s="14">
         <v>101700</v>
       </c>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11">
+      <c r="C51" s="14"/>
+      <c r="D51" s="14">
         <v>5</v>
       </c>
-      <c r="E51" s="12" t="s">
+      <c r="E51" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="F51" s="13" t="str">
+      <c r="F51" s="16" t="str">
         <f t="shared" si="6"/>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G51" s="11">
+      <c r="G51" s="14">
         <v>-1000</v>
       </c>
-      <c r="H51" s="11">
+      <c r="H51" s="14">
         <v>-500</v>
       </c>
-      <c r="I51" s="11" t="s">
+      <c r="I51" s="14" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="52" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A52" s="6">
+      <c r="A52" s="9">
         <v>17006</v>
       </c>
-      <c r="B52" s="11">
+      <c r="B52" s="14">
         <v>101700</v>
       </c>
-      <c r="C52" s="11"/>
-      <c r="D52" s="11">
+      <c r="C52" s="14"/>
+      <c r="D52" s="14">
         <v>6</v>
       </c>
-      <c r="E52" s="12" t="s">
+      <c r="E52" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="F52" s="13" t="str">
+      <c r="F52" s="16" t="str">
         <f t="shared" si="6"/>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G52" s="11">
+      <c r="G52" s="14">
         <v>-2000</v>
       </c>
-      <c r="H52" s="11">
+      <c r="H52" s="14">
         <v>-1000</v>
       </c>
-      <c r="I52" s="11" t="s">
+      <c r="I52" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="53" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A53" s="6">
+      <c r="A53" s="9">
         <v>17007</v>
       </c>
-      <c r="B53" s="11">
+      <c r="B53" s="14">
         <v>101700</v>
       </c>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11">
+      <c r="C53" s="14"/>
+      <c r="D53" s="14">
         <v>7</v>
       </c>
-      <c r="E53" s="12" t="s">
+      <c r="E53" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="F53" s="13" t="str">
+      <c r="F53" s="16" t="str">
         <f t="shared" si="6"/>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G53" s="11">
+      <c r="G53" s="14">
         <v>-999999</v>
       </c>
-      <c r="H53" s="11">
+      <c r="H53" s="14">
         <v>-2000</v>
       </c>
-      <c r="I53" s="11" t="s">
+      <c r="I53" s="14" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="54" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A54" s="16">
+      <c r="A54" s="19">
         <v>22001</v>
       </c>
-      <c r="B54" s="16">
+      <c r="B54" s="19">
         <v>102200</v>
       </c>
-      <c r="C54" s="16" t="s">
+      <c r="C54" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="D54" s="16">
+      <c r="D54" s="19">
         <v>1</v>
       </c>
-      <c r="E54" s="17" t="s">
+      <c r="E54" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="F54" s="8" t="s">
+      <c r="F54" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="G54" s="6">
+      <c r="G54" s="22">
         <v>2000</v>
       </c>
-      <c r="H54" s="6">
+      <c r="H54" s="22">
         <v>999999</v>
       </c>
-      <c r="I54" s="6" t="s">
+      <c r="I54" s="22" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="55" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A55" s="16">
+      <c r="A55" s="19">
         <v>22002</v>
       </c>
-      <c r="B55" s="16">
+      <c r="B55" s="19">
         <v>102200</v>
       </c>
-      <c r="C55" s="16" t="s">
+      <c r="C55" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="D55" s="16">
+      <c r="D55" s="19">
         <v>2</v>
       </c>
-      <c r="E55" s="17" t="s">
+      <c r="E55" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="F55" s="8" t="str">
+      <c r="F55" s="21" t="str">
         <f t="shared" ref="F55:F60" si="7">F54</f>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G55" s="6">
+      <c r="G55" s="22">
         <v>1000</v>
       </c>
-      <c r="H55" s="6">
+      <c r="H55" s="22">
         <v>2000</v>
       </c>
-      <c r="I55" s="6" t="s">
+      <c r="I55" s="22" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="56" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A56" s="16">
+      <c r="A56" s="19">
         <v>22003</v>
       </c>
-      <c r="B56" s="16">
+      <c r="B56" s="19">
         <v>102200</v>
       </c>
-      <c r="C56" s="16" t="s">
+      <c r="C56" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="D56" s="16">
+      <c r="D56" s="19">
         <v>3</v>
       </c>
-      <c r="E56" s="17" t="s">
+      <c r="E56" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="F56" s="8" t="str">
+      <c r="F56" s="21" t="str">
         <f t="shared" si="7"/>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G56" s="6">
+      <c r="G56" s="22">
         <v>500</v>
       </c>
-      <c r="H56" s="6">
+      <c r="H56" s="22">
         <v>1000</v>
       </c>
-      <c r="I56" s="6" t="s">
+      <c r="I56" s="22" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="57" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A57" s="16">
+      <c r="A57" s="19">
         <v>22004</v>
       </c>
-      <c r="B57" s="16">
+      <c r="B57" s="19">
         <v>102200</v>
       </c>
-      <c r="C57" s="16" t="s">
+      <c r="C57" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="D57" s="16">
+      <c r="D57" s="19">
         <v>4</v>
       </c>
-      <c r="E57" s="17" t="s">
+      <c r="E57" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="8" t="str">
+      <c r="F57" s="21" t="str">
         <f t="shared" si="7"/>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G57" s="6">
+      <c r="G57" s="22">
         <v>-500</v>
       </c>
-      <c r="H57" s="6">
+      <c r="H57" s="22">
         <v>500</v>
       </c>
-      <c r="I57" s="6" t="s">
+      <c r="I57" s="22" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="58" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A58" s="16">
+      <c r="A58" s="19">
         <v>22005</v>
       </c>
-      <c r="B58" s="16">
+      <c r="B58" s="19">
         <v>102200</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="C58" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="D58" s="16">
+      <c r="D58" s="19">
         <v>5</v>
       </c>
-      <c r="E58" s="17" t="s">
+      <c r="E58" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="F58" s="8" t="str">
+      <c r="F58" s="21" t="str">
         <f t="shared" si="7"/>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G58" s="6">
+      <c r="G58" s="22">
         <v>-1000</v>
       </c>
-      <c r="H58" s="6">
+      <c r="H58" s="22">
         <v>-500</v>
       </c>
-      <c r="I58" s="6" t="s">
+      <c r="I58" s="22" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="59" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A59" s="16">
+      <c r="A59" s="19">
         <v>22006</v>
       </c>
-      <c r="B59" s="16">
+      <c r="B59" s="19">
         <v>102200</v>
       </c>
-      <c r="C59" s="16" t="s">
+      <c r="C59" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="D59" s="16">
+      <c r="D59" s="19">
         <v>6</v>
       </c>
-      <c r="E59" s="17" t="s">
+      <c r="E59" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="F59" s="8" t="str">
+      <c r="F59" s="21" t="str">
         <f t="shared" si="7"/>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G59" s="6">
+      <c r="G59" s="22">
         <v>-2000</v>
       </c>
-      <c r="H59" s="6">
+      <c r="H59" s="22">
         <v>-1000</v>
       </c>
-      <c r="I59" s="6" t="s">
+      <c r="I59" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="60" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A60" s="16">
+      <c r="A60" s="19">
         <v>22007</v>
       </c>
-      <c r="B60" s="16">
+      <c r="B60" s="19">
         <v>102200</v>
       </c>
-      <c r="C60" s="16" t="s">
+      <c r="C60" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="D60" s="16">
+      <c r="D60" s="19">
         <v>7</v>
       </c>
-      <c r="E60" s="17" t="s">
+      <c r="E60" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="F60" s="8" t="str">
+      <c r="F60" s="21" t="str">
         <f t="shared" si="7"/>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G60" s="6">
+      <c r="G60" s="22">
         <v>-999999</v>
       </c>
-      <c r="H60" s="6">
+      <c r="H60" s="22">
         <v>-2000</v>
       </c>
-      <c r="I60" s="6" t="s">
+      <c r="I60" s="22" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="61" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A61" s="16">
+    <row r="61" s="5" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A61" s="23">
         <v>21001</v>
       </c>
-      <c r="B61" s="16">
+      <c r="B61" s="23">
         <v>102100</v>
       </c>
-      <c r="C61" s="16" t="s">
+      <c r="C61" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D61" s="16">
+      <c r="D61" s="23">
         <v>1</v>
       </c>
-      <c r="E61" s="17" t="s">
+      <c r="E61" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="F61" s="8" t="s">
+      <c r="F61" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G61" s="6">
+      <c r="G61" s="14">
         <v>2000</v>
       </c>
-      <c r="H61" s="6">
+      <c r="H61" s="14">
         <v>999999</v>
       </c>
-      <c r="I61" s="6" t="s">
+      <c r="I61" s="14" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="62" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A62" s="16">
+    <row r="62" s="5" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A62" s="23">
         <v>21002</v>
       </c>
-      <c r="B62" s="16">
+      <c r="B62" s="23">
         <v>102100</v>
       </c>
-      <c r="C62" s="16" t="s">
+      <c r="C62" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D62" s="16">
+      <c r="D62" s="23">
         <v>2</v>
       </c>
-      <c r="E62" s="17" t="s">
+      <c r="E62" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="F62" s="8" t="str">
+      <c r="F62" s="15" t="str">
         <f t="shared" ref="F62:F67" si="8">F61</f>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G62" s="6">
+      <c r="G62" s="14">
         <v>1000</v>
       </c>
-      <c r="H62" s="6">
+      <c r="H62" s="14">
         <v>2000</v>
       </c>
-      <c r="I62" s="6" t="s">
+      <c r="I62" s="14" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="63" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A63" s="16">
+    <row r="63" s="5" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A63" s="23">
         <v>21003</v>
       </c>
-      <c r="B63" s="16">
+      <c r="B63" s="23">
         <v>102100</v>
       </c>
-      <c r="C63" s="16" t="s">
+      <c r="C63" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D63" s="16">
+      <c r="D63" s="23">
         <v>3</v>
       </c>
-      <c r="E63" s="17" t="s">
+      <c r="E63" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="F63" s="8" t="str">
+      <c r="F63" s="15" t="str">
         <f t="shared" si="8"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G63" s="6">
+      <c r="G63" s="14">
         <v>500</v>
       </c>
-      <c r="H63" s="6">
+      <c r="H63" s="14">
         <v>1000</v>
       </c>
-      <c r="I63" s="6" t="s">
+      <c r="I63" s="14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="64" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A64" s="16">
+    <row r="64" s="5" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A64" s="23">
         <v>21004</v>
       </c>
-      <c r="B64" s="16">
+      <c r="B64" s="23">
         <v>102100</v>
       </c>
-      <c r="C64" s="16" t="s">
+      <c r="C64" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D64" s="16">
+      <c r="D64" s="23">
         <v>4</v>
       </c>
-      <c r="E64" s="17" t="s">
+      <c r="E64" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="F64" s="8" t="str">
+      <c r="F64" s="15" t="str">
         <f t="shared" si="8"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G64" s="6">
+      <c r="G64" s="14">
         <v>-500</v>
       </c>
-      <c r="H64" s="6">
+      <c r="H64" s="14">
         <v>500</v>
       </c>
-      <c r="I64" s="6" t="s">
+      <c r="I64" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="65" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A65" s="16">
+    <row r="65" s="5" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A65" s="23">
         <v>21005</v>
       </c>
-      <c r="B65" s="16">
+      <c r="B65" s="23">
         <v>102100</v>
       </c>
-      <c r="C65" s="16" t="s">
+      <c r="C65" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D65" s="16">
+      <c r="D65" s="23">
         <v>5</v>
       </c>
-      <c r="E65" s="17" t="s">
+      <c r="E65" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F65" s="8" t="str">
+      <c r="F65" s="15" t="str">
         <f t="shared" si="8"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G65" s="6">
+      <c r="G65" s="14">
         <v>-1000</v>
       </c>
-      <c r="H65" s="6">
+      <c r="H65" s="14">
         <v>-500</v>
       </c>
-      <c r="I65" s="6" t="s">
+      <c r="I65" s="14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="66" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A66" s="16">
+    <row r="66" s="5" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A66" s="23">
         <v>21006</v>
       </c>
-      <c r="B66" s="16">
+      <c r="B66" s="23">
         <v>102100</v>
       </c>
-      <c r="C66" s="16" t="s">
+      <c r="C66" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D66" s="16">
+      <c r="D66" s="23">
         <v>6</v>
       </c>
-      <c r="E66" s="17" t="s">
+      <c r="E66" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="F66" s="8" t="str">
+      <c r="F66" s="15" t="str">
         <f t="shared" si="8"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G66" s="6">
+      <c r="G66" s="14">
         <v>-2000</v>
       </c>
-      <c r="H66" s="6">
+      <c r="H66" s="14">
         <v>-1000</v>
       </c>
-      <c r="I66" s="6" t="s">
+      <c r="I66" s="14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="67" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A67" s="16">
+    <row r="67" s="5" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A67" s="23">
         <v>21007</v>
       </c>
-      <c r="B67" s="16">
+      <c r="B67" s="23">
         <v>102100</v>
       </c>
-      <c r="C67" s="16" t="s">
+      <c r="C67" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D67" s="16">
+      <c r="D67" s="23">
         <v>7</v>
       </c>
-      <c r="E67" s="17" t="s">
+      <c r="E67" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="F67" s="8" t="str">
+      <c r="F67" s="15" t="str">
         <f t="shared" si="8"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G67" s="6">
+      <c r="G67" s="14">
         <v>-999999</v>
       </c>
-      <c r="H67" s="6">
+      <c r="H67" s="14">
         <v>-2000</v>
       </c>
-      <c r="I67" s="6" t="s">
+      <c r="I67" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="68" s="6" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A68" s="25">
+        <v>18001</v>
+      </c>
+      <c r="B68" s="25">
+        <v>101800</v>
+      </c>
+      <c r="C68" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D68" s="25">
+        <v>1</v>
+      </c>
+      <c r="E68" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="F68" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="G68" s="28">
+        <v>2000</v>
+      </c>
+      <c r="H68" s="28">
+        <v>999999</v>
+      </c>
+      <c r="I68" s="28" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" s="6" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A69" s="25">
+        <v>18002</v>
+      </c>
+      <c r="B69" s="25">
+        <v>101800</v>
+      </c>
+      <c r="C69" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D69" s="25">
+        <v>2</v>
+      </c>
+      <c r="E69" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="F69" s="27" t="str">
+        <f>F68</f>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G69" s="28">
+        <v>1000</v>
+      </c>
+      <c r="H69" s="28">
+        <v>2000</v>
+      </c>
+      <c r="I69" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="70" s="6" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A70" s="25">
+        <v>18003</v>
+      </c>
+      <c r="B70" s="25">
+        <v>101800</v>
+      </c>
+      <c r="C70" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D70" s="25">
+        <v>3</v>
+      </c>
+      <c r="E70" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="F70" s="27" t="str">
+        <f>F69</f>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G70" s="28">
+        <v>500</v>
+      </c>
+      <c r="H70" s="28">
+        <v>1000</v>
+      </c>
+      <c r="I70" s="28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71" s="6" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A71" s="25">
+        <v>18004</v>
+      </c>
+      <c r="B71" s="25">
+        <v>101800</v>
+      </c>
+      <c r="C71" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D71" s="25">
+        <v>4</v>
+      </c>
+      <c r="E71" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="F71" s="27" t="str">
+        <f>F70</f>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G71" s="28">
+        <v>-500</v>
+      </c>
+      <c r="H71" s="28">
+        <v>500</v>
+      </c>
+      <c r="I71" s="28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="72" s="6" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A72" s="25">
+        <v>18005</v>
+      </c>
+      <c r="B72" s="25">
+        <v>101800</v>
+      </c>
+      <c r="C72" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D72" s="25">
+        <v>5</v>
+      </c>
+      <c r="E72" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="F72" s="27" t="str">
+        <f>F71</f>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G72" s="28">
+        <v>-1000</v>
+      </c>
+      <c r="H72" s="28">
+        <v>-500</v>
+      </c>
+      <c r="I72" s="28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="73" s="6" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A73" s="25">
+        <v>18006</v>
+      </c>
+      <c r="B73" s="25">
+        <v>101800</v>
+      </c>
+      <c r="C73" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D73" s="25">
+        <v>6</v>
+      </c>
+      <c r="E73" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="F73" s="27" t="str">
+        <f>F72</f>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G73" s="28">
+        <v>-2000</v>
+      </c>
+      <c r="H73" s="28">
+        <v>-1000</v>
+      </c>
+      <c r="I73" s="28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74" s="6" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A74" s="25">
+        <v>18007</v>
+      </c>
+      <c r="B74" s="25">
+        <v>101800</v>
+      </c>
+      <c r="C74" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D74" s="25">
+        <v>7</v>
+      </c>
+      <c r="E74" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="F74" s="27" t="str">
+        <f>F73</f>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G74" s="28">
+        <v>-999999</v>
+      </c>
+      <c r="H74" s="28">
+        <v>-2000</v>
+      </c>
+      <c r="I74" s="28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="75" s="7" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A75" s="29">
+        <v>25001</v>
+      </c>
+      <c r="B75" s="29">
+        <v>102500</v>
+      </c>
+      <c r="C75" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="D75" s="29">
+        <v>1</v>
+      </c>
+      <c r="E75" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="F75" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="G75" s="32">
+        <v>2000</v>
+      </c>
+      <c r="H75" s="32">
+        <v>999999</v>
+      </c>
+      <c r="I75" s="32" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76" s="7" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A76" s="29">
+        <v>25002</v>
+      </c>
+      <c r="B76" s="29">
+        <v>102500</v>
+      </c>
+      <c r="C76" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="D76" s="29">
+        <v>2</v>
+      </c>
+      <c r="E76" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="F76" s="31" t="str">
+        <f>F75</f>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G76" s="32">
+        <v>1000</v>
+      </c>
+      <c r="H76" s="32">
+        <v>2000</v>
+      </c>
+      <c r="I76" s="32" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" s="7" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A77" s="29">
+        <v>25003</v>
+      </c>
+      <c r="B77" s="29">
+        <v>102500</v>
+      </c>
+      <c r="C77" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="D77" s="29">
+        <v>3</v>
+      </c>
+      <c r="E77" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="F77" s="31" t="str">
+        <f>F76</f>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G77" s="32">
+        <v>500</v>
+      </c>
+      <c r="H77" s="32">
+        <v>1000</v>
+      </c>
+      <c r="I77" s="32" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78" s="7" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A78" s="29">
+        <v>25004</v>
+      </c>
+      <c r="B78" s="29">
+        <v>102500</v>
+      </c>
+      <c r="C78" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="D78" s="29">
+        <v>4</v>
+      </c>
+      <c r="E78" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="F78" s="31" t="str">
+        <f>F77</f>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G78" s="32">
+        <v>-500</v>
+      </c>
+      <c r="H78" s="32">
+        <v>500</v>
+      </c>
+      <c r="I78" s="32" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="79" s="7" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A79" s="29">
+        <v>25005</v>
+      </c>
+      <c r="B79" s="29">
+        <v>102500</v>
+      </c>
+      <c r="C79" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="D79" s="29">
+        <v>5</v>
+      </c>
+      <c r="E79" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="F79" s="31" t="str">
+        <f>F78</f>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G79" s="32">
+        <v>-1000</v>
+      </c>
+      <c r="H79" s="32">
+        <v>-500</v>
+      </c>
+      <c r="I79" s="32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="80" s="7" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A80" s="29">
+        <v>25006</v>
+      </c>
+      <c r="B80" s="29">
+        <v>102500</v>
+      </c>
+      <c r="C80" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="D80" s="29">
+        <v>6</v>
+      </c>
+      <c r="E80" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="F80" s="31" t="str">
+        <f>F79</f>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G80" s="32">
+        <v>-2000</v>
+      </c>
+      <c r="H80" s="32">
+        <v>-1000</v>
+      </c>
+      <c r="I80" s="32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="81" s="7" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A81" s="29">
+        <v>25007</v>
+      </c>
+      <c r="B81" s="29">
+        <v>102500</v>
+      </c>
+      <c r="C81" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="D81" s="29">
+        <v>7</v>
+      </c>
+      <c r="E81" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="F81" s="31" t="str">
+        <f>F80</f>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G81" s="32">
+        <v>-999999</v>
+      </c>
+      <c r="H81" s="32">
+        <v>-2000</v>
+      </c>
+      <c r="I81" s="32" t="s">
         <v>32</v>
       </c>
     </row>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="93">
   <si>
     <t>id</t>
   </si>
@@ -396,6 +396,9 @@
   </si>
   <si>
     <t>寒冰王座</t>
+  </si>
+  <si>
+    <t>蒸汽时代</t>
   </si>
 </sst>
 </file>
@@ -1473,7 +1476,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
@@ -3417,7 +3420,7 @@
         <v>72</v>
       </c>
       <c r="F69" s="27" t="str">
-        <f>F68</f>
+        <f t="shared" ref="F69:F74" si="9">F68</f>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G69" s="28">
@@ -3447,7 +3450,7 @@
         <v>73</v>
       </c>
       <c r="F70" s="27" t="str">
-        <f>F69</f>
+        <f t="shared" si="9"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G70" s="28">
@@ -3477,7 +3480,7 @@
         <v>74</v>
       </c>
       <c r="F71" s="27" t="str">
-        <f>F70</f>
+        <f t="shared" si="9"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G71" s="28">
@@ -3507,7 +3510,7 @@
         <v>75</v>
       </c>
       <c r="F72" s="27" t="str">
-        <f>F71</f>
+        <f t="shared" si="9"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G72" s="28">
@@ -3537,7 +3540,7 @@
         <v>76</v>
       </c>
       <c r="F73" s="27" t="str">
-        <f>F72</f>
+        <f t="shared" si="9"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G73" s="28">
@@ -3567,7 +3570,7 @@
         <v>77</v>
       </c>
       <c r="F74" s="27" t="str">
-        <f>F73</f>
+        <f t="shared" si="9"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G74" s="28">
@@ -3626,7 +3629,7 @@
         <v>72</v>
       </c>
       <c r="F76" s="31" t="str">
-        <f>F75</f>
+        <f t="shared" ref="F76:F81" si="10">F75</f>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G76" s="32">
@@ -3656,7 +3659,7 @@
         <v>73</v>
       </c>
       <c r="F77" s="31" t="str">
-        <f>F76</f>
+        <f t="shared" si="10"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G77" s="32">
@@ -3686,7 +3689,7 @@
         <v>74</v>
       </c>
       <c r="F78" s="31" t="str">
-        <f>F77</f>
+        <f t="shared" si="10"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G78" s="32">
@@ -3716,7 +3719,7 @@
         <v>75</v>
       </c>
       <c r="F79" s="31" t="str">
-        <f>F78</f>
+        <f t="shared" si="10"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G79" s="32">
@@ -3746,7 +3749,7 @@
         <v>76</v>
       </c>
       <c r="F80" s="31" t="str">
-        <f>F79</f>
+        <f t="shared" si="10"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G80" s="32">
@@ -3776,7 +3779,7 @@
         <v>77</v>
       </c>
       <c r="F81" s="31" t="str">
-        <f>F80</f>
+        <f t="shared" si="10"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G81" s="32">
@@ -3786,6 +3789,215 @@
         <v>-2000</v>
       </c>
       <c r="I81" s="32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="82" s="7" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A82" s="29">
+        <v>23001</v>
+      </c>
+      <c r="B82" s="29">
+        <v>102300</v>
+      </c>
+      <c r="C82" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D82" s="29">
+        <v>1</v>
+      </c>
+      <c r="E82" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="F82" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="G82" s="32">
+        <v>2000</v>
+      </c>
+      <c r="H82" s="32">
+        <v>999999</v>
+      </c>
+      <c r="I82" s="32" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83" s="7" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A83" s="29">
+        <v>23002</v>
+      </c>
+      <c r="B83" s="29">
+        <v>102300</v>
+      </c>
+      <c r="C83" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D83" s="29">
+        <v>2</v>
+      </c>
+      <c r="E83" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="F83" s="31" t="str">
+        <f t="shared" ref="F83:F88" si="11">F82</f>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G83" s="32">
+        <v>1000</v>
+      </c>
+      <c r="H83" s="32">
+        <v>2000</v>
+      </c>
+      <c r="I83" s="32" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="84" s="7" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A84" s="29">
+        <v>23003</v>
+      </c>
+      <c r="B84" s="29">
+        <v>102300</v>
+      </c>
+      <c r="C84" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D84" s="29">
+        <v>3</v>
+      </c>
+      <c r="E84" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="F84" s="31" t="str">
+        <f t="shared" si="11"/>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G84" s="32">
+        <v>500</v>
+      </c>
+      <c r="H84" s="32">
+        <v>1000</v>
+      </c>
+      <c r="I84" s="32" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="85" s="7" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A85" s="29">
+        <v>23004</v>
+      </c>
+      <c r="B85" s="29">
+        <v>102300</v>
+      </c>
+      <c r="C85" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D85" s="29">
+        <v>4</v>
+      </c>
+      <c r="E85" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="F85" s="31" t="str">
+        <f t="shared" si="11"/>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G85" s="32">
+        <v>-500</v>
+      </c>
+      <c r="H85" s="32">
+        <v>500</v>
+      </c>
+      <c r="I85" s="32" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="86" s="7" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A86" s="29">
+        <v>23005</v>
+      </c>
+      <c r="B86" s="29">
+        <v>102300</v>
+      </c>
+      <c r="C86" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D86" s="29">
+        <v>5</v>
+      </c>
+      <c r="E86" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="F86" s="31" t="str">
+        <f t="shared" si="11"/>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G86" s="32">
+        <v>-1000</v>
+      </c>
+      <c r="H86" s="32">
+        <v>-500</v>
+      </c>
+      <c r="I86" s="32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="87" s="7" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A87" s="29">
+        <v>23006</v>
+      </c>
+      <c r="B87" s="29">
+        <v>102300</v>
+      </c>
+      <c r="C87" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D87" s="29">
+        <v>6</v>
+      </c>
+      <c r="E87" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="F87" s="31" t="str">
+        <f t="shared" si="11"/>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G87" s="32">
+        <v>-2000</v>
+      </c>
+      <c r="H87" s="32">
+        <v>-1000</v>
+      </c>
+      <c r="I87" s="32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="88" s="7" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A88" s="29">
+        <v>23007</v>
+      </c>
+      <c r="B88" s="29">
+        <v>102300</v>
+      </c>
+      <c r="C88" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D88" s="29">
+        <v>7</v>
+      </c>
+      <c r="E88" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="F88" s="31" t="str">
+        <f t="shared" si="11"/>
+        <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G88" s="32">
+        <v>-999999</v>
+      </c>
+      <c r="H88" s="32">
+        <v>-2000</v>
+      </c>
+      <c r="I88" s="32" t="s">
         <v>32</v>
       </c>
     </row>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="96">
   <si>
     <t>id</t>
   </si>
@@ -399,6 +399,15 @@
   </si>
   <si>
     <t>蒸汽时代</t>
+  </si>
+  <si>
+    <t>神马飞扬</t>
+  </si>
+  <si>
+    <t>1_9880|2_10|3_10|4_10|5_10|6_10|7_10|8_10|9_10|10_10|11_10|12_10|13_10</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;6,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;7,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;8,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;9,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;10,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;11,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;12,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;13,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
   </si>
 </sst>
 </file>
@@ -581,7 +590,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -621,6 +630,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -947,7 +962,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -971,16 +986,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -989,90 +1004,90 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1081,6 +1096,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1093,7 +1109,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1154,6 +1170,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1476,2528 +1504,2737 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
     <col min="2" max="3" width="15.25" customWidth="1"/>
     <col min="4" max="4" width="10.875" customWidth="1"/>
-    <col min="5" max="5" width="33.75" style="8" customWidth="1"/>
-    <col min="6" max="6" width="114.025" style="8" customWidth="1"/>
+    <col min="5" max="5" width="33.75" style="9" customWidth="1"/>
+    <col min="6" max="6" width="114.025" style="9" customWidth="1"/>
     <col min="7" max="7" width="15.625" customWidth="1"/>
     <col min="8" max="8" width="15.125" customWidth="1"/>
     <col min="9" max="9" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:9">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10" t="s">
+      <c r="C1" s="11"/>
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="9"/>
+      <c r="I2" s="10"/>
     </row>
     <row r="3" ht="16.5" spans="1:9">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10" t="s">
+      <c r="C3" s="11"/>
+      <c r="D3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="9"/>
+      <c r="I3" s="10"/>
     </row>
     <row r="4" ht="16.5" spans="1:9">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
     </row>
     <row r="5" ht="16.5" spans="1:9">
-      <c r="A5" s="9">
+      <c r="A5" s="10">
         <v>1001</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="10">
         <v>100100</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="10">
         <v>1</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="10">
         <v>2000</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="10">
         <v>999999</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:9">
-      <c r="A6" s="9">
+      <c r="A6" s="10">
         <v>1002</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="10">
         <v>100100</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9">
+      <c r="C6" s="10"/>
+      <c r="D6" s="10">
         <v>2</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="11" t="str">
+      <c r="F6" s="12" t="str">
         <f t="shared" ref="F6:F11" si="0">F5</f>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="10">
         <v>1000</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="10">
         <v>2000</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
-      <c r="A7" s="9">
+      <c r="A7" s="10">
         <v>1003</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="10">
         <v>100100</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9">
+      <c r="C7" s="10"/>
+      <c r="D7" s="10">
         <v>3</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="11" t="str">
+      <c r="F7" s="12" t="str">
         <f t="shared" si="0"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="10">
         <v>500</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="10">
         <v>1000</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
-      <c r="A8" s="9">
+      <c r="A8" s="10">
         <v>1004</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="10">
         <v>100100</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9">
+      <c r="C8" s="10"/>
+      <c r="D8" s="10">
         <v>4</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="11" t="str">
+      <c r="F8" s="12" t="str">
         <f t="shared" si="0"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="10">
         <v>-500</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="10">
         <v>500</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="10" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:9">
-      <c r="A9" s="9">
+      <c r="A9" s="10">
         <v>1005</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="10">
         <v>100100</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9">
+      <c r="C9" s="10"/>
+      <c r="D9" s="10">
         <v>5</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="11" t="str">
+      <c r="F9" s="12" t="str">
         <f t="shared" si="0"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="10">
         <v>-1000</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="10">
         <v>-500</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:9">
-      <c r="A10" s="9">
+      <c r="A10" s="10">
         <v>1006</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="10">
         <v>100100</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9">
+      <c r="C10" s="10"/>
+      <c r="D10" s="10">
         <v>6</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="11" t="str">
+      <c r="F10" s="12" t="str">
         <f t="shared" si="0"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="10">
         <v>-2000</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="10">
         <v>-1000</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:9">
-      <c r="A11" s="9">
+      <c r="A11" s="10">
         <v>1007</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="10">
         <v>100100</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9">
+      <c r="C11" s="10"/>
+      <c r="D11" s="10">
         <v>7</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="11" t="str">
+      <c r="F11" s="12" t="str">
         <f t="shared" si="0"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="10">
         <v>-999999</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="10">
         <v>-2000</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A12" s="13">
+      <c r="A12" s="14">
         <v>3001</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="14">
         <v>100300</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="14">
         <v>1</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="14">
         <v>2000</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="14">
         <v>999999</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A13" s="13">
+      <c r="A13" s="14">
         <v>3002</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="14">
         <v>100300</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13">
+      <c r="C13" s="14"/>
+      <c r="D13" s="14">
         <v>2</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="11" t="str">
+      <c r="F13" s="12" t="str">
         <f t="shared" ref="F13:F18" si="1">F12</f>
         <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="14">
         <v>1000</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="14">
         <v>2000</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="I13" s="14" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A14" s="13">
+      <c r="A14" s="14">
         <v>3003</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="14">
         <v>100300</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13">
+      <c r="C14" s="14"/>
+      <c r="D14" s="14">
         <v>3</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="11" t="str">
+      <c r="F14" s="12" t="str">
         <f t="shared" si="1"/>
         <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="14">
         <v>500</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="14">
         <v>1000</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="I14" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A15" s="13">
+      <c r="A15" s="14">
         <v>3004</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="14">
         <v>100300</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13">
+      <c r="C15" s="14"/>
+      <c r="D15" s="14">
         <v>4</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="11" t="str">
+      <c r="F15" s="12" t="str">
         <f t="shared" si="1"/>
         <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="14">
         <v>-500</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="14">
         <v>500</v>
       </c>
-      <c r="I15" s="13" t="s">
+      <c r="I15" s="14" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A16" s="13">
+      <c r="A16" s="14">
         <v>3005</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="14">
         <v>100300</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13">
+      <c r="C16" s="14"/>
+      <c r="D16" s="14">
         <v>5</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="11" t="str">
+      <c r="F16" s="12" t="str">
         <f t="shared" si="1"/>
         <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="14">
         <v>-1000</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="14">
         <v>-500</v>
       </c>
-      <c r="I16" s="13" t="s">
+      <c r="I16" s="14" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A17" s="13">
+      <c r="A17" s="14">
         <v>3006</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="14">
         <v>100300</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13">
+      <c r="C17" s="14"/>
+      <c r="D17" s="14">
         <v>6</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="11" t="str">
+      <c r="F17" s="12" t="str">
         <f t="shared" si="1"/>
         <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="14">
         <v>-2000</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="14">
         <v>-1000</v>
       </c>
-      <c r="I17" s="13" t="s">
+      <c r="I17" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A18" s="13">
+      <c r="A18" s="14">
         <v>3007</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="14">
         <v>100300</v>
       </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13">
+      <c r="C18" s="14"/>
+      <c r="D18" s="14">
         <v>7</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="11" t="str">
+      <c r="F18" s="12" t="str">
         <f t="shared" si="1"/>
         <v>1,0&amp;1-82000|1&amp;2-100|2&amp;3-100|3&amp;4-0|4&amp;5-0|5&amp;6-100|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-2000|12&amp;14-0|14&amp;16-100|16&amp;18-0|18&amp;20-0|20&amp;24-1800|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-100|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;2,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-0|8&amp;9-0|9&amp;10-0|10&amp;12-60100|12&amp;14-0|14&amp;16-0|16&amp;18-0|18&amp;20-0|20&amp;24-25000|24&amp;28-0|28&amp;32-0|32&amp;36-0|36&amp;40-0|40&amp;48-0|48&amp;56-2400|56&amp;64-0|64&amp;72-0|72&amp;80-0|80&amp;96-0|96&amp;112-0|112&amp;128-0|128&amp;144-0|144&amp;160-0|160&amp;192-0|192&amp;224-0|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0;3,0&amp;1-0|1&amp;2-0|2&amp;3-0|3&amp;4-0|4&amp;5-0|5&amp;6-0|6&amp;7-0|7&amp;8-12300|8&amp;9-6200|9&amp;10-0|10&amp;12-15650|12&amp;14-6050|14&amp;16-5250|16&amp;18-10200|18&amp;20-800|20&amp;24-7800|24&amp;28-6700|28&amp;32-1350|32&amp;36-3850|36&amp;40-2950|40&amp;48-1750|48&amp;56-3000|56&amp;64-2400|64&amp;72-1900|72&amp;80-500|80&amp;96-3450|96&amp;112-3400|112&amp;128-1600|128&amp;144-1200|144&amp;160-950|160&amp;192-100|192&amp;224-650|224&amp;256-0|256&amp;288-0|288&amp;320-0|320&amp;370-0|370&amp;420-0|420&amp;470-0|470&amp;99999999-0</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="14">
         <v>-999999</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="14">
         <v>-2000</v>
       </c>
-      <c r="I18" s="13" t="s">
+      <c r="I18" s="14" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A19" s="9">
+      <c r="A19" s="10">
         <v>7001</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="15">
         <v>100700</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="15">
         <v>1</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="15">
         <v>2000</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="15">
         <v>999999</v>
       </c>
-      <c r="I19" s="14" t="s">
+      <c r="I19" s="15" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A20" s="9">
+      <c r="A20" s="10">
         <v>7002</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="15">
         <v>100700</v>
       </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14">
+      <c r="C20" s="15"/>
+      <c r="D20" s="15">
         <v>2</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="F20" s="16" t="str">
+      <c r="F20" s="17" t="str">
         <f t="shared" ref="F20:F25" si="2">F19</f>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="15">
         <v>1000</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="15">
         <v>2000</v>
       </c>
-      <c r="I20" s="14" t="s">
+      <c r="I20" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A21" s="9">
+      <c r="A21" s="10">
         <v>7003</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="15">
         <v>100700</v>
       </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14">
+      <c r="C21" s="15"/>
+      <c r="D21" s="15">
         <v>3</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="F21" s="16" t="str">
+      <c r="F21" s="17" t="str">
         <f t="shared" si="2"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="15">
         <v>500</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="15">
         <v>1000</v>
       </c>
-      <c r="I21" s="14" t="s">
+      <c r="I21" s="15" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A22" s="9">
+      <c r="A22" s="10">
         <v>7004</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="15">
         <v>100700</v>
       </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14">
+      <c r="C22" s="15"/>
+      <c r="D22" s="15">
         <v>4</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="16" t="str">
+      <c r="F22" s="17" t="str">
         <f t="shared" si="2"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="15">
         <v>-500</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="15">
         <v>500</v>
       </c>
-      <c r="I22" s="14" t="s">
+      <c r="I22" s="15" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A23" s="9">
+      <c r="A23" s="10">
         <v>7005</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="15">
         <v>100700</v>
       </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14">
+      <c r="C23" s="15"/>
+      <c r="D23" s="15">
         <v>5</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="16" t="str">
+      <c r="F23" s="17" t="str">
         <f t="shared" si="2"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G23" s="14">
+      <c r="G23" s="15">
         <v>-1000</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="15">
         <v>-500</v>
       </c>
-      <c r="I23" s="14" t="s">
+      <c r="I23" s="15" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A24" s="9">
+      <c r="A24" s="10">
         <v>7006</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="15">
         <v>100700</v>
       </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14">
+      <c r="C24" s="15"/>
+      <c r="D24" s="15">
         <v>6</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="F24" s="16" t="str">
+      <c r="F24" s="17" t="str">
         <f t="shared" si="2"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="15">
         <v>-2000</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="15">
         <v>-1000</v>
       </c>
-      <c r="I24" s="14" t="s">
+      <c r="I24" s="15" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A25" s="9">
+      <c r="A25" s="10">
         <v>7007</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="15">
         <v>100700</v>
       </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14">
+      <c r="C25" s="15"/>
+      <c r="D25" s="15">
         <v>7</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F25" s="16" t="str">
+      <c r="F25" s="17" t="str">
         <f t="shared" si="2"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G25" s="14">
+      <c r="G25" s="15">
         <v>-999999</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="15">
         <v>-2000</v>
       </c>
-      <c r="I25" s="14" t="s">
+      <c r="I25" s="15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A26" s="13">
+      <c r="A26" s="14">
         <v>12001</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="14">
         <v>101200</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="14">
         <v>1</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F26" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="14">
         <v>2000</v>
       </c>
-      <c r="H26" s="13">
+      <c r="H26" s="14">
         <v>999999</v>
       </c>
-      <c r="I26" s="13" t="s">
+      <c r="I26" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A27" s="13">
+      <c r="A27" s="14">
         <v>12002</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="14">
         <v>101200</v>
       </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13">
+      <c r="C27" s="14"/>
+      <c r="D27" s="14">
         <v>2</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="F27" s="11" t="str">
+      <c r="F27" s="12" t="str">
         <f t="shared" ref="F27:F32" si="3">F26</f>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
-      <c r="G27" s="13">
+      <c r="G27" s="14">
         <v>1000</v>
       </c>
-      <c r="H27" s="13">
+      <c r="H27" s="14">
         <v>2000</v>
       </c>
-      <c r="I27" s="13" t="s">
+      <c r="I27" s="14" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A28" s="13">
+      <c r="A28" s="14">
         <v>12003</v>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="14">
         <v>101200</v>
       </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13">
+      <c r="C28" s="14"/>
+      <c r="D28" s="14">
         <v>3</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F28" s="11" t="str">
+      <c r="F28" s="12" t="str">
         <f t="shared" si="3"/>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
-      <c r="G28" s="13">
+      <c r="G28" s="14">
         <v>500</v>
       </c>
-      <c r="H28" s="13">
+      <c r="H28" s="14">
         <v>1000</v>
       </c>
-      <c r="I28" s="13" t="s">
+      <c r="I28" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A29" s="13">
+      <c r="A29" s="14">
         <v>12004</v>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="14">
         <v>101200</v>
       </c>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13">
+      <c r="C29" s="14"/>
+      <c r="D29" s="14">
         <v>4</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="F29" s="11" t="str">
+      <c r="F29" s="12" t="str">
         <f t="shared" si="3"/>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
-      <c r="G29" s="13">
+      <c r="G29" s="14">
         <v>-500</v>
       </c>
-      <c r="H29" s="13">
+      <c r="H29" s="14">
         <v>500</v>
       </c>
-      <c r="I29" s="13" t="s">
+      <c r="I29" s="14" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A30" s="13">
+      <c r="A30" s="14">
         <v>12005</v>
       </c>
-      <c r="B30" s="13">
+      <c r="B30" s="14">
         <v>101200</v>
       </c>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13">
+      <c r="C30" s="14"/>
+      <c r="D30" s="14">
         <v>5</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F30" s="11" t="str">
+      <c r="F30" s="12" t="str">
         <f t="shared" si="3"/>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
-      <c r="G30" s="13">
+      <c r="G30" s="14">
         <v>-1000</v>
       </c>
-      <c r="H30" s="13">
+      <c r="H30" s="14">
         <v>-500</v>
       </c>
-      <c r="I30" s="13" t="s">
+      <c r="I30" s="14" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A31" s="13">
+      <c r="A31" s="14">
         <v>12006</v>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="14">
         <v>101200</v>
       </c>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13">
+      <c r="C31" s="14"/>
+      <c r="D31" s="14">
         <v>6</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F31" s="11" t="str">
+      <c r="F31" s="12" t="str">
         <f t="shared" si="3"/>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
-      <c r="G31" s="13">
+      <c r="G31" s="14">
         <v>-2000</v>
       </c>
-      <c r="H31" s="13">
+      <c r="H31" s="14">
         <v>-1000</v>
       </c>
-      <c r="I31" s="13" t="s">
+      <c r="I31" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A32" s="13">
+      <c r="A32" s="14">
         <v>12007</v>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="14">
         <v>101200</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13">
+      <c r="C32" s="14"/>
+      <c r="D32" s="14">
         <v>7</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="F32" s="11" t="str">
+      <c r="F32" s="12" t="str">
         <f t="shared" si="3"/>
         <v>1,0&amp;1-72100|1&amp;15-12800|10&amp;30-7200|20&amp;45-3600|45&amp;60-1500|60&amp;75-900|75&amp;90-500|90&amp;105-300|105&amp;120-200|120&amp;135-100|135&amp;150-100|150&amp;180-200|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-0|300&amp;360-100|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-100|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-88800|1&amp;15-7000|10&amp;30-2600|20&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-0|1&amp;15-3000|10&amp;30-3000|20&amp;45-3000|45&amp;60-3000|60&amp;75-3000|75&amp;90-3000|90&amp;105-3000|105&amp;120-2000|120&amp;135-2000|135&amp;150-2000|150&amp;180-2000|180&amp;210-2000|210&amp;240-2000|240&amp;270-2000|270&amp;300-2000|300&amp;360-3000|360&amp;420-4000|420&amp;480-5000|480&amp;540-5000|540&amp;600-5000|600&amp;720-6000|720&amp;840-5000|840&amp;960-3800|960&amp;1080-3800|1080&amp;1200-2900|1200&amp;1440-4100|1440&amp;1680-4200|1680&amp;1920-2800|1920&amp;2160-2000|2160&amp;2400-1400|2400&amp;2880-2100|2880&amp;3360-1600|3360&amp;3840-1100|3840&amp;4320-200|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
-      <c r="G32" s="13">
+      <c r="G32" s="14">
         <v>-999999</v>
       </c>
-      <c r="H32" s="13">
+      <c r="H32" s="14">
         <v>-2000</v>
       </c>
-      <c r="I32" s="13" t="s">
+      <c r="I32" s="14" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="33" s="3" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A33" s="9">
+      <c r="A33" s="10">
         <v>14001</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B33" s="18">
         <v>101400</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="17">
+      <c r="D33" s="18">
         <v>1</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="E33" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F33" s="12" t="s">
+      <c r="F33" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="G33" s="17">
+      <c r="G33" s="18">
         <v>2000</v>
       </c>
-      <c r="H33" s="17">
+      <c r="H33" s="18">
         <v>999999</v>
       </c>
-      <c r="I33" s="17" t="s">
+      <c r="I33" s="18" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="34" s="3" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A34" s="9">
+      <c r="A34" s="10">
         <v>14002</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="18">
         <v>101400</v>
       </c>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17">
+      <c r="C34" s="18"/>
+      <c r="D34" s="18">
         <v>2</v>
       </c>
-      <c r="E34" s="18" t="s">
+      <c r="E34" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="F34" s="11" t="str">
+      <c r="F34" s="12" t="str">
         <f t="shared" ref="F34:F39" si="4">F33</f>
         <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
-      <c r="G34" s="17">
+      <c r="G34" s="18">
         <v>1000</v>
       </c>
-      <c r="H34" s="17">
+      <c r="H34" s="18">
         <v>2000</v>
       </c>
-      <c r="I34" s="17" t="s">
+      <c r="I34" s="18" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A35" s="9">
+      <c r="A35" s="10">
         <v>14003</v>
       </c>
-      <c r="B35" s="17">
+      <c r="B35" s="18">
         <v>101400</v>
       </c>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17">
+      <c r="C35" s="18"/>
+      <c r="D35" s="18">
         <v>3</v>
       </c>
-      <c r="E35" s="18" t="s">
+      <c r="E35" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="F35" s="11" t="str">
+      <c r="F35" s="12" t="str">
         <f t="shared" si="4"/>
         <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
-      <c r="G35" s="17">
+      <c r="G35" s="18">
         <v>500</v>
       </c>
-      <c r="H35" s="17">
+      <c r="H35" s="18">
         <v>1000</v>
       </c>
-      <c r="I35" s="17" t="s">
+      <c r="I35" s="18" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="36" s="3" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A36" s="9">
+      <c r="A36" s="10">
         <v>14004</v>
       </c>
-      <c r="B36" s="17">
+      <c r="B36" s="18">
         <v>101400</v>
       </c>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17">
+      <c r="C36" s="18"/>
+      <c r="D36" s="18">
         <v>4</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="F36" s="11" t="str">
+      <c r="F36" s="12" t="str">
         <f t="shared" si="4"/>
         <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
-      <c r="G36" s="17">
+      <c r="G36" s="18">
         <v>-500</v>
       </c>
-      <c r="H36" s="17">
+      <c r="H36" s="18">
         <v>500</v>
       </c>
-      <c r="I36" s="17" t="s">
+      <c r="I36" s="18" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="37" s="3" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A37" s="9">
+      <c r="A37" s="10">
         <v>14005</v>
       </c>
-      <c r="B37" s="17">
+      <c r="B37" s="18">
         <v>101400</v>
       </c>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17">
+      <c r="C37" s="18"/>
+      <c r="D37" s="18">
         <v>5</v>
       </c>
-      <c r="E37" s="18" t="s">
+      <c r="E37" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="F37" s="11" t="str">
+      <c r="F37" s="12" t="str">
         <f t="shared" si="4"/>
         <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
-      <c r="G37" s="17">
+      <c r="G37" s="18">
         <v>-1000</v>
       </c>
-      <c r="H37" s="17">
+      <c r="H37" s="18">
         <v>-500</v>
       </c>
-      <c r="I37" s="17" t="s">
+      <c r="I37" s="18" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A38" s="9">
+      <c r="A38" s="10">
         <v>14006</v>
       </c>
-      <c r="B38" s="17">
+      <c r="B38" s="18">
         <v>101400</v>
       </c>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17">
+      <c r="C38" s="18"/>
+      <c r="D38" s="18">
         <v>6</v>
       </c>
-      <c r="E38" s="18" t="s">
+      <c r="E38" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="F38" s="11" t="str">
+      <c r="F38" s="12" t="str">
         <f t="shared" si="4"/>
         <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
-      <c r="G38" s="17">
+      <c r="G38" s="18">
         <v>-2000</v>
       </c>
-      <c r="H38" s="17">
+      <c r="H38" s="18">
         <v>-1000</v>
       </c>
-      <c r="I38" s="17" t="s">
+      <c r="I38" s="18" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A39" s="9">
+      <c r="A39" s="10">
         <v>14007</v>
       </c>
-      <c r="B39" s="17">
+      <c r="B39" s="18">
         <v>101400</v>
       </c>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17">
+      <c r="C39" s="18"/>
+      <c r="D39" s="18">
         <v>7</v>
       </c>
-      <c r="E39" s="18" t="s">
+      <c r="E39" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="F39" s="11" t="str">
+      <c r="F39" s="12" t="str">
         <f t="shared" si="4"/>
         <v>1,0&amp;1-77100|1&amp;10-1400|10&amp;20-6900|20&amp;30-5800|30&amp;40-2900|40&amp;50-2000|50&amp;60-1100|60&amp;70-1100|70&amp;80-400|80&amp;90-300|90&amp;100-300|100&amp;120-200|120&amp;140-200|140&amp;160-100|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-58200|1&amp;10-1900|10&amp;20-10500|20&amp;30-10200|30&amp;40-5400|40&amp;50-4200|50&amp;60-2400|60&amp;70-2500|70&amp;80-1500|80&amp;90-700|90&amp;100-700|100&amp;120-600|120&amp;140-600|140&amp;160-200|160&amp;180-100|180&amp;200-100|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-100000|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
-      <c r="G39" s="17">
+      <c r="G39" s="18">
         <v>-999999</v>
       </c>
-      <c r="H39" s="17">
+      <c r="H39" s="18">
         <v>-2000</v>
       </c>
-      <c r="I39" s="17" t="s">
+      <c r="I39" s="18" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:9">
-      <c r="A40" s="9">
+      <c r="A40" s="10">
         <v>24001</v>
       </c>
-      <c r="B40" s="9">
+      <c r="B40" s="10">
         <v>102400</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="10">
         <v>1</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E40" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F40" s="12" t="s">
+      <c r="F40" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G40" s="10">
         <v>2000</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H40" s="10">
         <v>999999</v>
       </c>
-      <c r="I40" s="9" t="s">
+      <c r="I40" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:9">
-      <c r="A41" s="9">
+      <c r="A41" s="10">
         <v>24002</v>
       </c>
-      <c r="B41" s="9">
+      <c r="B41" s="10">
         <v>102400</v>
       </c>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9">
+      <c r="C41" s="10"/>
+      <c r="D41" s="10">
         <v>2</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E41" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F41" s="11" t="str">
+      <c r="F41" s="12" t="str">
         <f t="shared" ref="F41:F46" si="5">F40</f>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G41" s="10">
         <v>1000</v>
       </c>
-      <c r="H41" s="9">
+      <c r="H41" s="10">
         <v>2000</v>
       </c>
-      <c r="I41" s="9" t="s">
+      <c r="I41" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:9">
-      <c r="A42" s="9">
+      <c r="A42" s="10">
         <v>24003</v>
       </c>
-      <c r="B42" s="9">
+      <c r="B42" s="10">
         <v>102400</v>
       </c>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9">
+      <c r="C42" s="10"/>
+      <c r="D42" s="10">
         <v>3</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E42" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F42" s="11" t="str">
+      <c r="F42" s="12" t="str">
         <f t="shared" si="5"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G42" s="9">
+      <c r="G42" s="10">
         <v>500</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="10">
         <v>1000</v>
       </c>
-      <c r="I42" s="9" t="s">
+      <c r="I42" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:9">
-      <c r="A43" s="9">
+      <c r="A43" s="10">
         <v>24004</v>
       </c>
-      <c r="B43" s="9">
+      <c r="B43" s="10">
         <v>102400</v>
       </c>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9">
+      <c r="C43" s="10"/>
+      <c r="D43" s="10">
         <v>4</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E43" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F43" s="11" t="str">
+      <c r="F43" s="12" t="str">
         <f t="shared" si="5"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G43" s="10">
         <v>-500</v>
       </c>
-      <c r="H43" s="9">
+      <c r="H43" s="10">
         <v>500</v>
       </c>
-      <c r="I43" s="9" t="s">
+      <c r="I43" s="10" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:9">
-      <c r="A44" s="9">
+      <c r="A44" s="10">
         <v>24005</v>
       </c>
-      <c r="B44" s="9">
+      <c r="B44" s="10">
         <v>102400</v>
       </c>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9">
+      <c r="C44" s="10"/>
+      <c r="D44" s="10">
         <v>5</v>
       </c>
-      <c r="E44" s="11" t="s">
+      <c r="E44" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="F44" s="11" t="str">
+      <c r="F44" s="12" t="str">
         <f t="shared" si="5"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G44" s="10">
         <v>-1000</v>
       </c>
-      <c r="H44" s="9">
+      <c r="H44" s="10">
         <v>-500</v>
       </c>
-      <c r="I44" s="9" t="s">
+      <c r="I44" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:9">
-      <c r="A45" s="9">
+      <c r="A45" s="10">
         <v>24006</v>
       </c>
-      <c r="B45" s="9">
+      <c r="B45" s="10">
         <v>102400</v>
       </c>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9">
+      <c r="C45" s="10"/>
+      <c r="D45" s="10">
         <v>6</v>
       </c>
-      <c r="E45" s="11" t="s">
+      <c r="E45" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F45" s="11" t="str">
+      <c r="F45" s="12" t="str">
         <f t="shared" si="5"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G45" s="9">
+      <c r="G45" s="10">
         <v>-2000</v>
       </c>
-      <c r="H45" s="9">
+      <c r="H45" s="10">
         <v>-1000</v>
       </c>
-      <c r="I45" s="9" t="s">
+      <c r="I45" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:9">
-      <c r="A46" s="9">
+      <c r="A46" s="10">
         <v>24007</v>
       </c>
-      <c r="B46" s="9">
+      <c r="B46" s="10">
         <v>102400</v>
       </c>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9">
+      <c r="C46" s="10"/>
+      <c r="D46" s="10">
         <v>7</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E46" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F46" s="11" t="str">
+      <c r="F46" s="12" t="str">
         <f t="shared" si="5"/>
         <v>1,0&amp;1-68000|1&amp;10-0|10&amp;20-5000|20&amp;30-5000|30&amp;40-5000|40&amp;50-4000|50&amp;60-3000|60&amp;70-3000|70&amp;80-1000|80&amp;90-800|90&amp;100-700|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-500|180&amp;200-500|200&amp;300-500|300&amp;500-500|500&amp;800-400|800&amp;1000-200|1000&amp;1500-100|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1100|1000&amp;1500-18400|1500&amp;2000-21700|2000&amp;3000-44200|3000&amp;4000-10600|4000&amp;5000-600|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-0|500&amp;800-0|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-3400|2000&amp;3000-48900|3000&amp;4000-34900|4000&amp;5000-10800|5000&amp;6000-1900|6000&amp;7000-100|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;4,0&amp;1-80600|1&amp;10-3100|10&amp;20-4300|20&amp;30-2600|30&amp;40-2500|40&amp;50-1600|50&amp;60-800|60&amp;70-1000|70&amp;80-700|80&amp;90-300|90&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-300|160&amp;180-200|180&amp;200-200|200&amp;300-200|300&amp;500-200|500&amp;800-100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;5,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-20800|300&amp;500-74000|500&amp;800-5100|800&amp;1000-0|1000&amp;1500-0|1500&amp;2000-0|2000&amp;3000-0|3000&amp;4000-0|4000&amp;5000-0|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0;6,0&amp;1-200|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-100|90&amp;100-200|100&amp;120-300|120&amp;140-400|140&amp;160-400|160&amp;180-400|180&amp;200-1300|200&amp;300-3000|300&amp;500-6000|500&amp;800-8000|800&amp;1000-8000|1000&amp;1500-12900|1500&amp;2000-12500|2000&amp;3000-15100|3000&amp;4000-12000|4000&amp;5000-8000|5000&amp;6000-4000|6000&amp;7000-2500|7000&amp;8000-1500|8000&amp;9000-900|9000&amp;10000-600|10000&amp;11000-500|11000&amp;12000-500|12000&amp;15000-400|15000&amp;20000-300|20000&amp;99999999-0;7,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;300-0|300&amp;500-200|500&amp;800-3000|800&amp;1000-1000|1000&amp;1500-13700|1500&amp;2000-18200|2000&amp;3000-46500|3000&amp;4000-15900|4000&amp;5000-1400|5000&amp;6000-0|6000&amp;7000-0|7000&amp;8000-0|8000&amp;9000-0|9000&amp;10000-0|10000&amp;11000-0|11000&amp;12000-0|12000&amp;15000-0|15000&amp;20000-0|20000&amp;99999999-0</v>
       </c>
-      <c r="G46" s="9">
+      <c r="G46" s="10">
         <v>-999999</v>
       </c>
-      <c r="H46" s="9">
+      <c r="H46" s="10">
         <v>-2000</v>
       </c>
-      <c r="I46" s="9" t="s">
+      <c r="I46" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A47" s="9">
+      <c r="A47" s="10">
         <v>17001</v>
       </c>
-      <c r="B47" s="14">
+      <c r="B47" s="15">
         <v>101700</v>
       </c>
-      <c r="C47" s="14" t="s">
+      <c r="C47" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="D47" s="14">
+      <c r="D47" s="15">
         <v>1</v>
       </c>
-      <c r="E47" s="15" t="s">
+      <c r="E47" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="F47" s="12" t="s">
+      <c r="F47" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="G47" s="14">
+      <c r="G47" s="15">
         <v>2000</v>
       </c>
-      <c r="H47" s="14">
+      <c r="H47" s="15">
         <v>999999</v>
       </c>
-      <c r="I47" s="14" t="s">
+      <c r="I47" s="15" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A48" s="9">
+      <c r="A48" s="10">
         <v>17002</v>
       </c>
-      <c r="B48" s="14">
+      <c r="B48" s="15">
         <v>101700</v>
       </c>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14">
+      <c r="C48" s="15"/>
+      <c r="D48" s="15">
         <v>2</v>
       </c>
-      <c r="E48" s="15" t="s">
+      <c r="E48" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="F48" s="16" t="str">
+      <c r="F48" s="17" t="str">
         <f t="shared" ref="F48:F53" si="6">F47</f>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G48" s="14">
+      <c r="G48" s="15">
         <v>1000</v>
       </c>
-      <c r="H48" s="14">
+      <c r="H48" s="15">
         <v>2000</v>
       </c>
-      <c r="I48" s="14" t="s">
+      <c r="I48" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A49" s="9">
+      <c r="A49" s="10">
         <v>17003</v>
       </c>
-      <c r="B49" s="14">
+      <c r="B49" s="15">
         <v>101700</v>
       </c>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14">
+      <c r="C49" s="15"/>
+      <c r="D49" s="15">
         <v>3</v>
       </c>
-      <c r="E49" s="15" t="s">
+      <c r="E49" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="F49" s="16" t="str">
+      <c r="F49" s="17" t="str">
         <f t="shared" si="6"/>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G49" s="14">
+      <c r="G49" s="15">
         <v>500</v>
       </c>
-      <c r="H49" s="14">
+      <c r="H49" s="15">
         <v>1000</v>
       </c>
-      <c r="I49" s="14" t="s">
+      <c r="I49" s="15" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A50" s="9">
+      <c r="A50" s="10">
         <v>17004</v>
       </c>
-      <c r="B50" s="14">
+      <c r="B50" s="15">
         <v>101700</v>
       </c>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14">
+      <c r="C50" s="15"/>
+      <c r="D50" s="15">
         <v>4</v>
       </c>
-      <c r="E50" s="15" t="s">
+      <c r="E50" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="16" t="str">
+      <c r="F50" s="17" t="str">
         <f t="shared" si="6"/>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G50" s="14">
+      <c r="G50" s="15">
         <v>-500</v>
       </c>
-      <c r="H50" s="14">
+      <c r="H50" s="15">
         <v>500</v>
       </c>
-      <c r="I50" s="14" t="s">
+      <c r="I50" s="15" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="51" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A51" s="9">
+      <c r="A51" s="10">
         <v>17005</v>
       </c>
-      <c r="B51" s="14">
+      <c r="B51" s="15">
         <v>101700</v>
       </c>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14">
+      <c r="C51" s="15"/>
+      <c r="D51" s="15">
         <v>5</v>
       </c>
-      <c r="E51" s="15" t="s">
+      <c r="E51" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="F51" s="16" t="str">
+      <c r="F51" s="17" t="str">
         <f t="shared" si="6"/>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G51" s="14">
+      <c r="G51" s="15">
         <v>-1000</v>
       </c>
-      <c r="H51" s="14">
+      <c r="H51" s="15">
         <v>-500</v>
       </c>
-      <c r="I51" s="14" t="s">
+      <c r="I51" s="15" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="52" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A52" s="9">
+      <c r="A52" s="10">
         <v>17006</v>
       </c>
-      <c r="B52" s="14">
+      <c r="B52" s="15">
         <v>101700</v>
       </c>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14">
+      <c r="C52" s="15"/>
+      <c r="D52" s="15">
         <v>6</v>
       </c>
-      <c r="E52" s="15" t="s">
+      <c r="E52" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="F52" s="16" t="str">
+      <c r="F52" s="17" t="str">
         <f t="shared" si="6"/>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G52" s="14">
+      <c r="G52" s="15">
         <v>-2000</v>
       </c>
-      <c r="H52" s="14">
+      <c r="H52" s="15">
         <v>-1000</v>
       </c>
-      <c r="I52" s="14" t="s">
+      <c r="I52" s="15" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="53" s="2" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A53" s="9">
+      <c r="A53" s="10">
         <v>17007</v>
       </c>
-      <c r="B53" s="14">
+      <c r="B53" s="15">
         <v>101700</v>
       </c>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14">
+      <c r="C53" s="15"/>
+      <c r="D53" s="15">
         <v>7</v>
       </c>
-      <c r="E53" s="15" t="s">
+      <c r="E53" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="F53" s="16" t="str">
+      <c r="F53" s="17" t="str">
         <f t="shared" si="6"/>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G53" s="14">
+      <c r="G53" s="15">
         <v>-999999</v>
       </c>
-      <c r="H53" s="14">
+      <c r="H53" s="15">
         <v>-2000</v>
       </c>
-      <c r="I53" s="14" t="s">
+      <c r="I53" s="15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="54" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A54" s="19">
+      <c r="A54" s="20">
         <v>22001</v>
       </c>
-      <c r="B54" s="19">
+      <c r="B54" s="20">
         <v>102200</v>
       </c>
-      <c r="C54" s="19" t="s">
+      <c r="C54" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="20">
         <v>1</v>
       </c>
-      <c r="E54" s="20" t="s">
+      <c r="E54" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="F54" s="21" t="s">
+      <c r="F54" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="G54" s="22">
+      <c r="G54" s="23">
         <v>2000</v>
       </c>
-      <c r="H54" s="22">
+      <c r="H54" s="23">
         <v>999999</v>
       </c>
-      <c r="I54" s="22" t="s">
+      <c r="I54" s="23" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="55" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A55" s="19">
+      <c r="A55" s="20">
         <v>22002</v>
       </c>
-      <c r="B55" s="19">
+      <c r="B55" s="20">
         <v>102200</v>
       </c>
-      <c r="C55" s="19" t="s">
+      <c r="C55" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="20">
         <v>2</v>
       </c>
-      <c r="E55" s="20" t="s">
+      <c r="E55" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="F55" s="21" t="str">
+      <c r="F55" s="22" t="str">
         <f t="shared" ref="F55:F60" si="7">F54</f>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G55" s="22">
+      <c r="G55" s="23">
         <v>1000</v>
       </c>
-      <c r="H55" s="22">
+      <c r="H55" s="23">
         <v>2000</v>
       </c>
-      <c r="I55" s="22" t="s">
+      <c r="I55" s="23" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="56" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A56" s="19">
+      <c r="A56" s="20">
         <v>22003</v>
       </c>
-      <c r="B56" s="19">
+      <c r="B56" s="20">
         <v>102200</v>
       </c>
-      <c r="C56" s="19" t="s">
+      <c r="C56" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="20">
         <v>3</v>
       </c>
-      <c r="E56" s="20" t="s">
+      <c r="E56" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="F56" s="21" t="str">
+      <c r="F56" s="22" t="str">
         <f t="shared" si="7"/>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G56" s="22">
+      <c r="G56" s="23">
         <v>500</v>
       </c>
-      <c r="H56" s="22">
+      <c r="H56" s="23">
         <v>1000</v>
       </c>
-      <c r="I56" s="22" t="s">
+      <c r="I56" s="23" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="57" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A57" s="19">
+      <c r="A57" s="20">
         <v>22004</v>
       </c>
-      <c r="B57" s="19">
+      <c r="B57" s="20">
         <v>102200</v>
       </c>
-      <c r="C57" s="19" t="s">
+      <c r="C57" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="20">
         <v>4</v>
       </c>
-      <c r="E57" s="20" t="s">
+      <c r="E57" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="21" t="str">
+      <c r="F57" s="22" t="str">
         <f t="shared" si="7"/>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G57" s="22">
+      <c r="G57" s="23">
         <v>-500</v>
       </c>
-      <c r="H57" s="22">
+      <c r="H57" s="23">
         <v>500</v>
       </c>
-      <c r="I57" s="22" t="s">
+      <c r="I57" s="23" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="58" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A58" s="19">
+      <c r="A58" s="20">
         <v>22005</v>
       </c>
-      <c r="B58" s="19">
+      <c r="B58" s="20">
         <v>102200</v>
       </c>
-      <c r="C58" s="19" t="s">
+      <c r="C58" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="20">
         <v>5</v>
       </c>
-      <c r="E58" s="20" t="s">
+      <c r="E58" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="F58" s="21" t="str">
+      <c r="F58" s="22" t="str">
         <f t="shared" si="7"/>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G58" s="22">
+      <c r="G58" s="23">
         <v>-1000</v>
       </c>
-      <c r="H58" s="22">
+      <c r="H58" s="23">
         <v>-500</v>
       </c>
-      <c r="I58" s="22" t="s">
+      <c r="I58" s="23" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="59" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A59" s="19">
+      <c r="A59" s="20">
         <v>22006</v>
       </c>
-      <c r="B59" s="19">
+      <c r="B59" s="20">
         <v>102200</v>
       </c>
-      <c r="C59" s="19" t="s">
+      <c r="C59" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="20">
         <v>6</v>
       </c>
-      <c r="E59" s="20" t="s">
+      <c r="E59" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="F59" s="21" t="str">
+      <c r="F59" s="22" t="str">
         <f t="shared" si="7"/>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G59" s="22">
+      <c r="G59" s="23">
         <v>-2000</v>
       </c>
-      <c r="H59" s="22">
+      <c r="H59" s="23">
         <v>-1000</v>
       </c>
-      <c r="I59" s="22" t="s">
+      <c r="I59" s="23" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="60" s="4" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A60" s="19">
+      <c r="A60" s="20">
         <v>22007</v>
       </c>
-      <c r="B60" s="19">
+      <c r="B60" s="20">
         <v>102200</v>
       </c>
-      <c r="C60" s="19" t="s">
+      <c r="C60" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="20">
         <v>7</v>
       </c>
-      <c r="E60" s="20" t="s">
+      <c r="E60" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="F60" s="21" t="str">
+      <c r="F60" s="22" t="str">
         <f t="shared" si="7"/>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G60" s="22">
+      <c r="G60" s="23">
         <v>-999999</v>
       </c>
-      <c r="H60" s="22">
+      <c r="H60" s="23">
         <v>-2000</v>
       </c>
-      <c r="I60" s="22" t="s">
+      <c r="I60" s="23" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="61" s="5" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A61" s="23">
+      <c r="A61" s="24">
         <v>21001</v>
       </c>
-      <c r="B61" s="23">
+      <c r="B61" s="24">
         <v>102100</v>
       </c>
-      <c r="C61" s="23" t="s">
+      <c r="C61" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="D61" s="23">
+      <c r="D61" s="24">
         <v>1</v>
       </c>
-      <c r="E61" s="24" t="s">
+      <c r="E61" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="F61" s="15" t="s">
+      <c r="F61" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="G61" s="14">
+      <c r="G61" s="15">
         <v>2000</v>
       </c>
-      <c r="H61" s="14">
+      <c r="H61" s="15">
         <v>999999</v>
       </c>
-      <c r="I61" s="14" t="s">
+      <c r="I61" s="15" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="62" s="5" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A62" s="23">
+      <c r="A62" s="24">
         <v>21002</v>
       </c>
-      <c r="B62" s="23">
+      <c r="B62" s="24">
         <v>102100</v>
       </c>
-      <c r="C62" s="23" t="s">
+      <c r="C62" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="D62" s="23">
+      <c r="D62" s="24">
         <v>2</v>
       </c>
-      <c r="E62" s="24" t="s">
+      <c r="E62" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="F62" s="15" t="str">
+      <c r="F62" s="16" t="str">
         <f t="shared" ref="F62:F67" si="8">F61</f>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G62" s="14">
+      <c r="G62" s="15">
         <v>1000</v>
       </c>
-      <c r="H62" s="14">
+      <c r="H62" s="15">
         <v>2000</v>
       </c>
-      <c r="I62" s="14" t="s">
+      <c r="I62" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="63" s="5" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A63" s="23">
+      <c r="A63" s="24">
         <v>21003</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B63" s="24">
         <v>102100</v>
       </c>
-      <c r="C63" s="23" t="s">
+      <c r="C63" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="D63" s="23">
+      <c r="D63" s="24">
         <v>3</v>
       </c>
-      <c r="E63" s="24" t="s">
+      <c r="E63" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="F63" s="15" t="str">
+      <c r="F63" s="16" t="str">
         <f t="shared" si="8"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G63" s="14">
+      <c r="G63" s="15">
         <v>500</v>
       </c>
-      <c r="H63" s="14">
+      <c r="H63" s="15">
         <v>1000</v>
       </c>
-      <c r="I63" s="14" t="s">
+      <c r="I63" s="15" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="64" s="5" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A64" s="23">
+      <c r="A64" s="24">
         <v>21004</v>
       </c>
-      <c r="B64" s="23">
+      <c r="B64" s="24">
         <v>102100</v>
       </c>
-      <c r="C64" s="23" t="s">
+      <c r="C64" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="D64" s="23">
+      <c r="D64" s="24">
         <v>4</v>
       </c>
-      <c r="E64" s="24" t="s">
+      <c r="E64" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="F64" s="15" t="str">
+      <c r="F64" s="16" t="str">
         <f t="shared" si="8"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G64" s="14">
+      <c r="G64" s="15">
         <v>-500</v>
       </c>
-      <c r="H64" s="14">
+      <c r="H64" s="15">
         <v>500</v>
       </c>
-      <c r="I64" s="14" t="s">
+      <c r="I64" s="15" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="65" s="5" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A65" s="23">
+      <c r="A65" s="24">
         <v>21005</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B65" s="24">
         <v>102100</v>
       </c>
-      <c r="C65" s="23" t="s">
+      <c r="C65" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="D65" s="23">
+      <c r="D65" s="24">
         <v>5</v>
       </c>
-      <c r="E65" s="24" t="s">
+      <c r="E65" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="F65" s="15" t="str">
+      <c r="F65" s="16" t="str">
         <f t="shared" si="8"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G65" s="14">
+      <c r="G65" s="15">
         <v>-1000</v>
       </c>
-      <c r="H65" s="14">
+      <c r="H65" s="15">
         <v>-500</v>
       </c>
-      <c r="I65" s="14" t="s">
+      <c r="I65" s="15" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="66" s="5" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A66" s="23">
+      <c r="A66" s="24">
         <v>21006</v>
       </c>
-      <c r="B66" s="23">
+      <c r="B66" s="24">
         <v>102100</v>
       </c>
-      <c r="C66" s="23" t="s">
+      <c r="C66" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="D66" s="23">
+      <c r="D66" s="24">
         <v>6</v>
       </c>
-      <c r="E66" s="24" t="s">
+      <c r="E66" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="F66" s="15" t="str">
+      <c r="F66" s="16" t="str">
         <f t="shared" si="8"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G66" s="14">
+      <c r="G66" s="15">
         <v>-2000</v>
       </c>
-      <c r="H66" s="14">
+      <c r="H66" s="15">
         <v>-1000</v>
       </c>
-      <c r="I66" s="14" t="s">
+      <c r="I66" s="15" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="67" s="5" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A67" s="23">
+      <c r="A67" s="24">
         <v>21007</v>
       </c>
-      <c r="B67" s="23">
+      <c r="B67" s="24">
         <v>102100</v>
       </c>
-      <c r="C67" s="23" t="s">
+      <c r="C67" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="D67" s="23">
+      <c r="D67" s="24">
         <v>7</v>
       </c>
-      <c r="E67" s="24" t="s">
+      <c r="E67" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="F67" s="15" t="str">
+      <c r="F67" s="16" t="str">
         <f t="shared" si="8"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G67" s="14">
+      <c r="G67" s="15">
         <v>-999999</v>
       </c>
-      <c r="H67" s="14">
+      <c r="H67" s="15">
         <v>-2000</v>
       </c>
-      <c r="I67" s="14" t="s">
+      <c r="I67" s="15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="68" s="6" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A68" s="25">
+      <c r="A68" s="26">
         <v>18001</v>
       </c>
-      <c r="B68" s="25">
+      <c r="B68" s="26">
         <v>101800</v>
       </c>
-      <c r="C68" s="25" t="s">
+      <c r="C68" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="D68" s="25">
+      <c r="D68" s="26">
         <v>1</v>
       </c>
-      <c r="E68" s="26" t="s">
+      <c r="E68" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="F68" s="27" t="s">
+      <c r="F68" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="G68" s="28">
+      <c r="G68" s="29">
         <v>2000</v>
       </c>
-      <c r="H68" s="28">
+      <c r="H68" s="29">
         <v>999999</v>
       </c>
-      <c r="I68" s="28" t="s">
+      <c r="I68" s="29" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="69" s="6" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A69" s="25">
+      <c r="A69" s="26">
         <v>18002</v>
       </c>
-      <c r="B69" s="25">
+      <c r="B69" s="26">
         <v>101800</v>
       </c>
-      <c r="C69" s="25" t="s">
+      <c r="C69" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="D69" s="25">
+      <c r="D69" s="26">
         <v>2</v>
       </c>
-      <c r="E69" s="26" t="s">
+      <c r="E69" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="F69" s="27" t="str">
+      <c r="F69" s="28" t="str">
         <f t="shared" ref="F69:F74" si="9">F68</f>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G69" s="28">
+      <c r="G69" s="29">
         <v>1000</v>
       </c>
-      <c r="H69" s="28">
+      <c r="H69" s="29">
         <v>2000</v>
       </c>
-      <c r="I69" s="28" t="s">
+      <c r="I69" s="29" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="70" s="6" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A70" s="25">
+      <c r="A70" s="26">
         <v>18003</v>
       </c>
-      <c r="B70" s="25">
+      <c r="B70" s="26">
         <v>101800</v>
       </c>
-      <c r="C70" s="25" t="s">
+      <c r="C70" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="D70" s="25">
+      <c r="D70" s="26">
         <v>3</v>
       </c>
-      <c r="E70" s="26" t="s">
+      <c r="E70" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="F70" s="27" t="str">
+      <c r="F70" s="28" t="str">
         <f t="shared" si="9"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G70" s="28">
+      <c r="G70" s="29">
         <v>500</v>
       </c>
-      <c r="H70" s="28">
+      <c r="H70" s="29">
         <v>1000</v>
       </c>
-      <c r="I70" s="28" t="s">
+      <c r="I70" s="29" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="71" s="6" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A71" s="25">
+      <c r="A71" s="26">
         <v>18004</v>
       </c>
-      <c r="B71" s="25">
+      <c r="B71" s="26">
         <v>101800</v>
       </c>
-      <c r="C71" s="25" t="s">
+      <c r="C71" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="D71" s="25">
+      <c r="D71" s="26">
         <v>4</v>
       </c>
-      <c r="E71" s="26" t="s">
+      <c r="E71" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="27" t="str">
+      <c r="F71" s="28" t="str">
         <f t="shared" si="9"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G71" s="28">
+      <c r="G71" s="29">
         <v>-500</v>
       </c>
-      <c r="H71" s="28">
+      <c r="H71" s="29">
         <v>500</v>
       </c>
-      <c r="I71" s="28" t="s">
+      <c r="I71" s="29" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="72" s="6" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A72" s="25">
+      <c r="A72" s="26">
         <v>18005</v>
       </c>
-      <c r="B72" s="25">
+      <c r="B72" s="26">
         <v>101800</v>
       </c>
-      <c r="C72" s="25" t="s">
+      <c r="C72" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="D72" s="25">
+      <c r="D72" s="26">
         <v>5</v>
       </c>
-      <c r="E72" s="26" t="s">
+      <c r="E72" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="F72" s="27" t="str">
+      <c r="F72" s="28" t="str">
         <f t="shared" si="9"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G72" s="28">
+      <c r="G72" s="29">
         <v>-1000</v>
       </c>
-      <c r="H72" s="28">
+      <c r="H72" s="29">
         <v>-500</v>
       </c>
-      <c r="I72" s="28" t="s">
+      <c r="I72" s="29" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="73" s="6" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A73" s="25">
+      <c r="A73" s="26">
         <v>18006</v>
       </c>
-      <c r="B73" s="25">
+      <c r="B73" s="26">
         <v>101800</v>
       </c>
-      <c r="C73" s="25" t="s">
+      <c r="C73" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="D73" s="25">
+      <c r="D73" s="26">
         <v>6</v>
       </c>
-      <c r="E73" s="26" t="s">
+      <c r="E73" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="F73" s="27" t="str">
+      <c r="F73" s="28" t="str">
         <f t="shared" si="9"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G73" s="28">
+      <c r="G73" s="29">
         <v>-2000</v>
       </c>
-      <c r="H73" s="28">
+      <c r="H73" s="29">
         <v>-1000</v>
       </c>
-      <c r="I73" s="28" t="s">
+      <c r="I73" s="29" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="74" s="6" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A74" s="25">
+      <c r="A74" s="26">
         <v>18007</v>
       </c>
-      <c r="B74" s="25">
+      <c r="B74" s="26">
         <v>101800</v>
       </c>
-      <c r="C74" s="25" t="s">
+      <c r="C74" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="D74" s="25">
+      <c r="D74" s="26">
         <v>7</v>
       </c>
-      <c r="E74" s="26" t="s">
+      <c r="E74" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="F74" s="27" t="str">
+      <c r="F74" s="28" t="str">
         <f t="shared" si="9"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G74" s="28">
+      <c r="G74" s="29">
         <v>-999999</v>
       </c>
-      <c r="H74" s="28">
+      <c r="H74" s="29">
         <v>-2000</v>
       </c>
-      <c r="I74" s="28" t="s">
+      <c r="I74" s="29" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="75" s="7" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A75" s="29">
+      <c r="A75" s="30">
         <v>25001</v>
       </c>
-      <c r="B75" s="29">
+      <c r="B75" s="30">
         <v>102500</v>
       </c>
-      <c r="C75" s="29" t="s">
+      <c r="C75" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="D75" s="29">
+      <c r="D75" s="30">
         <v>1</v>
       </c>
-      <c r="E75" s="30" t="s">
+      <c r="E75" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="F75" s="31" t="s">
+      <c r="F75" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="G75" s="32">
+      <c r="G75" s="33">
         <v>2000</v>
       </c>
-      <c r="H75" s="32">
+      <c r="H75" s="33">
         <v>999999</v>
       </c>
-      <c r="I75" s="32" t="s">
+      <c r="I75" s="33" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="76" s="7" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A76" s="29">
+      <c r="A76" s="30">
         <v>25002</v>
       </c>
-      <c r="B76" s="29">
+      <c r="B76" s="30">
         <v>102500</v>
       </c>
-      <c r="C76" s="29" t="s">
+      <c r="C76" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="D76" s="29">
+      <c r="D76" s="30">
         <v>2</v>
       </c>
-      <c r="E76" s="30" t="s">
+      <c r="E76" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="F76" s="31" t="str">
+      <c r="F76" s="32" t="str">
         <f t="shared" ref="F76:F81" si="10">F75</f>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G76" s="32">
+      <c r="G76" s="33">
         <v>1000</v>
       </c>
-      <c r="H76" s="32">
+      <c r="H76" s="33">
         <v>2000</v>
       </c>
-      <c r="I76" s="32" t="s">
+      <c r="I76" s="33" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="77" s="7" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A77" s="29">
+      <c r="A77" s="30">
         <v>25003</v>
       </c>
-      <c r="B77" s="29">
+      <c r="B77" s="30">
         <v>102500</v>
       </c>
-      <c r="C77" s="29" t="s">
+      <c r="C77" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="D77" s="29">
+      <c r="D77" s="30">
         <v>3</v>
       </c>
-      <c r="E77" s="30" t="s">
+      <c r="E77" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="F77" s="31" t="str">
+      <c r="F77" s="32" t="str">
         <f t="shared" si="10"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G77" s="32">
+      <c r="G77" s="33">
         <v>500</v>
       </c>
-      <c r="H77" s="32">
+      <c r="H77" s="33">
         <v>1000</v>
       </c>
-      <c r="I77" s="32" t="s">
+      <c r="I77" s="33" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="78" s="7" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A78" s="29">
+      <c r="A78" s="30">
         <v>25004</v>
       </c>
-      <c r="B78" s="29">
+      <c r="B78" s="30">
         <v>102500</v>
       </c>
-      <c r="C78" s="29" t="s">
+      <c r="C78" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="D78" s="29">
+      <c r="D78" s="30">
         <v>4</v>
       </c>
-      <c r="E78" s="30" t="s">
+      <c r="E78" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="F78" s="31" t="str">
+      <c r="F78" s="32" t="str">
         <f t="shared" si="10"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G78" s="32">
+      <c r="G78" s="33">
         <v>-500</v>
       </c>
-      <c r="H78" s="32">
+      <c r="H78" s="33">
         <v>500</v>
       </c>
-      <c r="I78" s="32" t="s">
+      <c r="I78" s="33" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="79" s="7" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A79" s="29">
+      <c r="A79" s="30">
         <v>25005</v>
       </c>
-      <c r="B79" s="29">
+      <c r="B79" s="30">
         <v>102500</v>
       </c>
-      <c r="C79" s="29" t="s">
+      <c r="C79" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="D79" s="29">
+      <c r="D79" s="30">
         <v>5</v>
       </c>
-      <c r="E79" s="30" t="s">
+      <c r="E79" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="F79" s="31" t="str">
+      <c r="F79" s="32" t="str">
         <f t="shared" si="10"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G79" s="32">
+      <c r="G79" s="33">
         <v>-1000</v>
       </c>
-      <c r="H79" s="32">
+      <c r="H79" s="33">
         <v>-500</v>
       </c>
-      <c r="I79" s="32" t="s">
+      <c r="I79" s="33" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="80" s="7" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A80" s="29">
+      <c r="A80" s="30">
         <v>25006</v>
       </c>
-      <c r="B80" s="29">
+      <c r="B80" s="30">
         <v>102500</v>
       </c>
-      <c r="C80" s="29" t="s">
+      <c r="C80" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="D80" s="29">
+      <c r="D80" s="30">
         <v>6</v>
       </c>
-      <c r="E80" s="30" t="s">
+      <c r="E80" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="F80" s="31" t="str">
+      <c r="F80" s="32" t="str">
         <f t="shared" si="10"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G80" s="32">
+      <c r="G80" s="33">
         <v>-2000</v>
       </c>
-      <c r="H80" s="32">
+      <c r="H80" s="33">
         <v>-1000</v>
       </c>
-      <c r="I80" s="32" t="s">
+      <c r="I80" s="33" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="81" s="7" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A81" s="29">
+      <c r="A81" s="30">
         <v>25007</v>
       </c>
-      <c r="B81" s="29">
+      <c r="B81" s="30">
         <v>102500</v>
       </c>
-      <c r="C81" s="29" t="s">
+      <c r="C81" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="D81" s="29">
+      <c r="D81" s="30">
         <v>7</v>
       </c>
-      <c r="E81" s="30" t="s">
+      <c r="E81" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="F81" s="31" t="str">
+      <c r="F81" s="32" t="str">
         <f t="shared" si="10"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G81" s="32">
+      <c r="G81" s="33">
         <v>-999999</v>
       </c>
-      <c r="H81" s="32">
+      <c r="H81" s="33">
         <v>-2000</v>
       </c>
-      <c r="I81" s="32" t="s">
+      <c r="I81" s="33" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="82" s="7" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A82" s="29">
+      <c r="A82" s="30">
         <v>23001</v>
       </c>
-      <c r="B82" s="29">
+      <c r="B82" s="30">
         <v>102300</v>
       </c>
-      <c r="C82" s="29" t="s">
+      <c r="C82" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D82" s="29">
+      <c r="D82" s="30">
         <v>1</v>
       </c>
-      <c r="E82" s="30" t="s">
+      <c r="E82" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="F82" s="31" t="s">
+      <c r="F82" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="G82" s="32">
+      <c r="G82" s="33">
         <v>2000</v>
       </c>
-      <c r="H82" s="32">
+      <c r="H82" s="33">
         <v>999999</v>
       </c>
-      <c r="I82" s="32" t="s">
+      <c r="I82" s="33" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="83" s="7" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A83" s="29">
+      <c r="A83" s="30">
         <v>23002</v>
       </c>
-      <c r="B83" s="29">
+      <c r="B83" s="30">
         <v>102300</v>
       </c>
-      <c r="C83" s="29" t="s">
+      <c r="C83" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D83" s="29">
+      <c r="D83" s="30">
         <v>2</v>
       </c>
-      <c r="E83" s="30" t="s">
+      <c r="E83" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="F83" s="31" t="str">
+      <c r="F83" s="32" t="str">
         <f t="shared" ref="F83:F88" si="11">F82</f>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G83" s="32">
+      <c r="G83" s="33">
         <v>1000</v>
       </c>
-      <c r="H83" s="32">
+      <c r="H83" s="33">
         <v>2000</v>
       </c>
-      <c r="I83" s="32" t="s">
+      <c r="I83" s="33" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="84" s="7" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A84" s="29">
+      <c r="A84" s="30">
         <v>23003</v>
       </c>
-      <c r="B84" s="29">
+      <c r="B84" s="30">
         <v>102300</v>
       </c>
-      <c r="C84" s="29" t="s">
+      <c r="C84" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D84" s="29">
+      <c r="D84" s="30">
         <v>3</v>
       </c>
-      <c r="E84" s="30" t="s">
+      <c r="E84" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="F84" s="31" t="str">
+      <c r="F84" s="32" t="str">
         <f t="shared" si="11"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G84" s="32">
+      <c r="G84" s="33">
         <v>500</v>
       </c>
-      <c r="H84" s="32">
+      <c r="H84" s="33">
         <v>1000</v>
       </c>
-      <c r="I84" s="32" t="s">
+      <c r="I84" s="33" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="85" s="7" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A85" s="29">
+      <c r="A85" s="30">
         <v>23004</v>
       </c>
-      <c r="B85" s="29">
+      <c r="B85" s="30">
         <v>102300</v>
       </c>
-      <c r="C85" s="29" t="s">
+      <c r="C85" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D85" s="29">
+      <c r="D85" s="30">
         <v>4</v>
       </c>
-      <c r="E85" s="30" t="s">
+      <c r="E85" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="F85" s="31" t="str">
+      <c r="F85" s="32" t="str">
         <f t="shared" si="11"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G85" s="32">
+      <c r="G85" s="33">
         <v>-500</v>
       </c>
-      <c r="H85" s="32">
+      <c r="H85" s="33">
         <v>500</v>
       </c>
-      <c r="I85" s="32" t="s">
+      <c r="I85" s="33" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="86" s="7" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A86" s="29">
+      <c r="A86" s="30">
         <v>23005</v>
       </c>
-      <c r="B86" s="29">
+      <c r="B86" s="30">
         <v>102300</v>
       </c>
-      <c r="C86" s="29" t="s">
+      <c r="C86" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D86" s="29">
+      <c r="D86" s="30">
         <v>5</v>
       </c>
-      <c r="E86" s="30" t="s">
+      <c r="E86" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="F86" s="31" t="str">
+      <c r="F86" s="32" t="str">
         <f t="shared" si="11"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G86" s="32">
+      <c r="G86" s="33">
         <v>-1000</v>
       </c>
-      <c r="H86" s="32">
+      <c r="H86" s="33">
         <v>-500</v>
       </c>
-      <c r="I86" s="32" t="s">
+      <c r="I86" s="33" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="87" s="7" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A87" s="29">
+      <c r="A87" s="30">
         <v>23006</v>
       </c>
-      <c r="B87" s="29">
+      <c r="B87" s="30">
         <v>102300</v>
       </c>
-      <c r="C87" s="29" t="s">
+      <c r="C87" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D87" s="29">
+      <c r="D87" s="30">
         <v>6</v>
       </c>
-      <c r="E87" s="30" t="s">
+      <c r="E87" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="F87" s="31" t="str">
+      <c r="F87" s="32" t="str">
         <f t="shared" si="11"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G87" s="32">
+      <c r="G87" s="33">
         <v>-2000</v>
       </c>
-      <c r="H87" s="32">
+      <c r="H87" s="33">
         <v>-1000</v>
       </c>
-      <c r="I87" s="32" t="s">
+      <c r="I87" s="33" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="88" s="7" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A88" s="29">
+      <c r="A88" s="30">
         <v>23007</v>
       </c>
-      <c r="B88" s="29">
+      <c r="B88" s="30">
         <v>102300</v>
       </c>
-      <c r="C88" s="29" t="s">
+      <c r="C88" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D88" s="29">
+      <c r="D88" s="30">
         <v>7</v>
       </c>
-      <c r="E88" s="30" t="s">
+      <c r="E88" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="F88" s="31" t="str">
+      <c r="F88" s="32" t="str">
         <f t="shared" si="11"/>
         <v>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
-      <c r="G88" s="32">
+      <c r="G88" s="33">
         <v>-999999</v>
       </c>
-      <c r="H88" s="32">
+      <c r="H88" s="33">
         <v>-2000</v>
       </c>
-      <c r="I88" s="32" t="s">
+      <c r="I88" s="33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="89" s="8" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A89" s="34">
+        <v>34001</v>
+      </c>
+      <c r="B89" s="34">
+        <v>103400</v>
+      </c>
+      <c r="C89" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D89" s="34">
+        <v>1</v>
+      </c>
+      <c r="E89" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F89" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="G89" s="37">
+        <v>2000</v>
+      </c>
+      <c r="H89" s="37">
+        <v>999999</v>
+      </c>
+      <c r="I89" s="37" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90" s="8" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A90" s="34">
+        <v>34002</v>
+      </c>
+      <c r="B90" s="34">
+        <v>103400</v>
+      </c>
+      <c r="C90" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D90" s="34">
+        <v>2</v>
+      </c>
+      <c r="E90" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F90" s="36" t="str">
+        <f>F89</f>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;6,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;7,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;8,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;9,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;10,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;11,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;12,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;13,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G90" s="37">
+        <v>1000</v>
+      </c>
+      <c r="H90" s="37">
+        <v>2000</v>
+      </c>
+      <c r="I90" s="37" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="91" s="8" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A91" s="34">
+        <v>34003</v>
+      </c>
+      <c r="B91" s="34">
+        <v>103400</v>
+      </c>
+      <c r="C91" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D91" s="34">
+        <v>3</v>
+      </c>
+      <c r="E91" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F91" s="36" t="str">
+        <f>F90</f>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;6,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;7,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;8,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;9,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;10,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;11,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;12,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;13,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G91" s="37">
+        <v>500</v>
+      </c>
+      <c r="H91" s="37">
+        <v>1000</v>
+      </c>
+      <c r="I91" s="37" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="92" s="8" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A92" s="34">
+        <v>34004</v>
+      </c>
+      <c r="B92" s="34">
+        <v>103400</v>
+      </c>
+      <c r="C92" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D92" s="34">
+        <v>4</v>
+      </c>
+      <c r="E92" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F92" s="36" t="str">
+        <f>F91</f>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;6,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;7,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;8,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;9,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;10,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;11,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;12,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;13,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G92" s="37">
+        <v>-500</v>
+      </c>
+      <c r="H92" s="37">
+        <v>500</v>
+      </c>
+      <c r="I92" s="37" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93" s="8" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A93" s="34">
+        <v>34005</v>
+      </c>
+      <c r="B93" s="34">
+        <v>103400</v>
+      </c>
+      <c r="C93" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D93" s="34">
+        <v>5</v>
+      </c>
+      <c r="E93" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F93" s="36" t="str">
+        <f>F92</f>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;6,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;7,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;8,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;9,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;10,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;11,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;12,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;13,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G93" s="37">
+        <v>-1000</v>
+      </c>
+      <c r="H93" s="37">
+        <v>-500</v>
+      </c>
+      <c r="I93" s="37" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="94" s="8" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A94" s="34">
+        <v>34006</v>
+      </c>
+      <c r="B94" s="34">
+        <v>103400</v>
+      </c>
+      <c r="C94" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D94" s="34">
+        <v>6</v>
+      </c>
+      <c r="E94" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F94" s="36" t="str">
+        <f>F93</f>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;6,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;7,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;8,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;9,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;10,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;11,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;12,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;13,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G94" s="37">
+        <v>-2000</v>
+      </c>
+      <c r="H94" s="37">
+        <v>-1000</v>
+      </c>
+      <c r="I94" s="37" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="95" s="8" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A95" s="34">
+        <v>34007</v>
+      </c>
+      <c r="B95" s="34">
+        <v>103400</v>
+      </c>
+      <c r="C95" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D95" s="34">
+        <v>7</v>
+      </c>
+      <c r="E95" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F95" s="36" t="str">
+        <f>F94</f>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;6,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;7,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;8,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;9,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;10,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;11,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;12,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;13,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+      </c>
+      <c r="G95" s="37">
+        <v>-999999</v>
+      </c>
+      <c r="H95" s="37">
+        <v>-2000</v>
+      </c>
+      <c r="I95" s="37" t="s">
         <v>32</v>
       </c>
     </row>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -335,7 +335,7 @@
     <t>1_9730|2_260|3_10</t>
   </si>
   <si>
-    <t>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
+    <t>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-5100|640&amp;720-3000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
   </si>
   <si>
     <t>1_9750|2_240|3_10</t>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="F48" s="17" t="str">
         <f t="shared" ref="F48:F53" si="6">F47</f>
-        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-5100|640&amp;720-3000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G48" s="15">
         <v>1000</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="F49" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-5100|640&amp;720-3000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G49" s="15">
         <v>500</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="F50" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-5100|640&amp;720-3000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G50" s="15">
         <v>-500</v>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="F51" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-5100|640&amp;720-3000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G51" s="15">
         <v>-1000</v>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="F52" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-5100|640&amp;720-3000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G52" s="15">
         <v>-2000</v>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="F53" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-2000|640&amp;720-2000|720&amp;800-2000|800&amp;960-100|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-100|2240&amp;2560-100|2560&amp;2880-100|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-200|400&amp;480-100|480&amp;560-300|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-100|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-2000|60&amp;80-2700|80&amp;100-3100|100&amp;120-3400|120&amp;140-3800|140&amp;160-3600|160&amp;180-3800|180&amp;200-3800|200&amp;240-7300|240&amp;280-6800|280&amp;320-6200|320&amp;360-5600|360&amp;400-5100|400&amp;480-8200|480&amp;560-6400|560&amp;640-5100|640&amp;720-3000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-62100|1&amp;20-14500|20&amp;40-7700|40&amp;60-4100|60&amp;80-2700|80&amp;100-2300|100&amp;120-700|120&amp;140-1500|140&amp;160-400|160&amp;180-800|180&amp;200-500|200&amp;240-300|240&amp;280-900|280&amp;320-200|320&amp;360-300|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G53" s="15">
         <v>-999999</v>
@@ -4075,7 +4075,7 @@
         <v>94</v>
       </c>
       <c r="F90" s="36" t="str">
-        <f>F89</f>
+        <f t="shared" ref="F90:F95" si="12">F89</f>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-2200|140&amp;160-1000|160&amp;180-2500|180&amp;200-1400|200&amp;240-3200|240&amp;280-3500|280&amp;320-3000|320&amp;360-3300|360&amp;400-2700|400&amp;480-5500|480&amp;560-5000|560&amp;640-4600|640&amp;720-4000|720&amp;800-3600|800&amp;960-6100|960&amp;1120-4800|1120&amp;1280-3800|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-3700|1920&amp;2240-1500|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;6,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;7,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;8,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;9,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;10,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;11,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;12,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;13,0&amp;1-2100|1&amp;20-300|20&amp;40-500|40&amp;60-700|60&amp;80-300|80&amp;100-800|100&amp;120-500|120&amp;140-700|140&amp;160-300|160&amp;180-1000|180&amp;200-400|200&amp;240-1000|240&amp;280-1300|280&amp;320-900|320&amp;360-1300|360&amp;400-1000|400&amp;480-2200|480&amp;560-2400|560&amp;640-2200|640&amp;720-2100|720&amp;800-2100|800&amp;960-4000|960&amp;1120-3900|1120&amp;1280-3700|1280&amp;1440-1500|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="G90" s="37">
@@ -4105,7 +4105,7 @@
         <v>94</v>
       </c>
       <c r="F91" s="36" t="str">
-        <f>F90</f>
+        <f t="shared" si="12"/>
         <v>1,0&amp;1-64100|1&amp;20-13300|20&amp;40-6600|40&amp;60-3500|60&amp;80-2500|80&amp;100-2100|100&amp;120-600|120&amp;140-1400|140&amp;160-500|160&amp;180-800|180&amp;200-500|200&amp;240-400|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-7100|20&amp;40-4000|40&amp;60-1600|60&amp;80-800|80&amp;100-400|100&amp;120-300|120&amp;140-200|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-100|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-100|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-83600|1&amp;20-7700|20&amp;40-4400|40&amp;60-1800|60&amp;80-1000|80&amp;100-400|100&amp;120-400|120&amp;140-200|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-200|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-4300|1&amp;20-900|20&amp;40-1600|40&amp;60-2400|60&amp;80-1100|80&amp;100-2200|100&amp;120-1700|120&amp;140-